--- a/Broga_Weekly_Tracking.xlsx
+++ b/Broga_Weekly_Tracking.xlsx
@@ -7,10 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Oct 2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Latest Snapshot Comparison" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Oct 2026" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Oct 2026'!$1:$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Latest Snapshot Comparison'!$A$4:$N$27</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Latest Snapshot Comparison'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Oct 2026'!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,8 +21,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="7">
+  <numFmts count="5">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="dd mmm yyyy"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="+0.0;-0.0;0.0"/>
+    <numFmt numFmtId="168" formatCode="+0;-0;0"/>
+  </numFmts>
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,8 +69,13 @@
       <color rgb="008B5E34"/>
       <sz val="9"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="008B5E34"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -90,11 +104,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCE8D5"/>
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F8F4"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -184,11 +203,64 @@
       <top/>
       <bottom/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D7DCCF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D7DCCF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D7DCCF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D7DCCF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D7DCCF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D7DCCF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D7DCCF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D7DCCF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00526747"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -265,19 +337,55 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -645,6 +753,1278 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:N27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="52" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BROGA COMPETITOR SALES ANALYSIS | LATEST SNAPSHOT COMPARISON</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>Latest valid observation vs the previous valid observation for each project/layout. This is not the Monday–Sunday weekly comparison.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Unit Group / Layout</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Latest Observation</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Previous Observation</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Days Between Observations</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Latest Signed Units</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Previous Signed Units</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Change in Signed Units</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Latest Total Units</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Previous Total Units</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>Latest Signed %</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>Previous Signed %</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>Change (percentage points)</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>Data Quality / Interpretation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>Amani Gallery Homes</t>
+        </is>
+      </c>
+      <c r="B5" s="30" t="inlineStr">
+        <is>
+          <t>Terrace houses</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D5" s="31" t="n">
+        <v>46313</v>
+      </c>
+      <c r="E5" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="32" t="n">
+        <v>74</v>
+      </c>
+      <c r="G5" s="32" t="n">
+        <v>74</v>
+      </c>
+      <c r="H5" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="32" t="n">
+        <v>81</v>
+      </c>
+      <c r="J5" s="32" t="n">
+        <v>81</v>
+      </c>
+      <c r="K5" s="34" t="n">
+        <v>0.9135802469135802</v>
+      </c>
+      <c r="L5" s="34" t="n">
+        <v>0.9135802469135802</v>
+      </c>
+      <c r="M5" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="36" t="inlineStr">
+        <is>
+          <t>Balau Homes 2A</t>
+        </is>
+      </c>
+      <c r="B6" s="36" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="C6" s="37" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D6" s="37" t="n">
+        <v>46313</v>
+      </c>
+      <c r="E6" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="38" t="n">
+        <v>69</v>
+      </c>
+      <c r="G6" s="38" t="n">
+        <v>69</v>
+      </c>
+      <c r="H6" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="38" t="n">
+        <v>113</v>
+      </c>
+      <c r="J6" s="38" t="n">
+        <v>113</v>
+      </c>
+      <c r="K6" s="40" t="n">
+        <v>0.6106194690265486</v>
+      </c>
+      <c r="L6" s="40" t="n">
+        <v>0.6106194690265486</v>
+      </c>
+      <c r="M6" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>Balau Homes 2C</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>22' x 70'</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D7" s="31" t="n">
+        <v>46313</v>
+      </c>
+      <c r="E7" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="32" t="n">
+        <v>21</v>
+      </c>
+      <c r="G7" s="32" t="n">
+        <v>21</v>
+      </c>
+      <c r="H7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="32" t="n">
+        <v>48</v>
+      </c>
+      <c r="J7" s="32" t="n">
+        <v>48</v>
+      </c>
+      <c r="K7" s="34" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="L7" s="34" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="M7" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="36" t="inlineStr">
+        <is>
+          <t>Banyan @Setia Ecohill 2</t>
+        </is>
+      </c>
+      <c r="B8" s="36" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="C8" s="37" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D8" s="37" t="n">
+        <v>46313</v>
+      </c>
+      <c r="E8" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="38" t="n">
+        <v>71</v>
+      </c>
+      <c r="G8" s="38" t="n">
+        <v>71</v>
+      </c>
+      <c r="H8" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="38" t="n">
+        <v>113</v>
+      </c>
+      <c r="J8" s="38" t="n">
+        <v>113</v>
+      </c>
+      <c r="K8" s="40" t="n">
+        <v>0.6283185840707964</v>
+      </c>
+      <c r="L8" s="40" t="n">
+        <v>0.6283185840707964</v>
+      </c>
+      <c r="M8" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="B9" s="30" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="C9" s="31" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D9" s="31" t="n">
+        <v>46313</v>
+      </c>
+      <c r="E9" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="32" t="n">
+        <v>46</v>
+      </c>
+      <c r="G9" s="32" t="n">
+        <v>46</v>
+      </c>
+      <c r="H9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="32" t="n">
+        <v>46</v>
+      </c>
+      <c r="J9" s="32" t="n">
+        <v>46</v>
+      </c>
+      <c r="K9" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="36" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="B10" s="36" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="C10" s="37" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D10" s="37" t="n">
+        <v>46313</v>
+      </c>
+      <c r="E10" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="38" t="n">
+        <v>56</v>
+      </c>
+      <c r="G10" s="38" t="n">
+        <v>56</v>
+      </c>
+      <c r="H10" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="38" t="n">
+        <v>56</v>
+      </c>
+      <c r="J10" s="38" t="n">
+        <v>56</v>
+      </c>
+      <c r="K10" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="30" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="B11" s="30" t="inlineStr">
+        <is>
+          <t>20' x 75'</t>
+        </is>
+      </c>
+      <c r="C11" s="31" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D11" s="31" t="n">
+        <v>46313</v>
+      </c>
+      <c r="E11" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="32" t="n">
+        <v>24</v>
+      </c>
+      <c r="G11" s="32" t="n">
+        <v>24</v>
+      </c>
+      <c r="H11" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="32" t="n">
+        <v>25</v>
+      </c>
+      <c r="J11" s="32" t="n">
+        <v>25</v>
+      </c>
+      <c r="K11" s="34" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L11" s="34" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="M11" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="36" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="B12" s="36" t="inlineStr">
+        <is>
+          <t>20' x 80'</t>
+        </is>
+      </c>
+      <c r="C12" s="37" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D12" s="37" t="n">
+        <v>46313</v>
+      </c>
+      <c r="E12" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="38" t="n">
+        <v>25</v>
+      </c>
+      <c r="J12" s="38" t="n">
+        <v>25</v>
+      </c>
+      <c r="K12" s="40" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L12" s="40" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M12" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="30" t="inlineStr">
+        <is>
+          <t>Chorus @Setia Ecohill 2</t>
+        </is>
+      </c>
+      <c r="B13" s="30" t="inlineStr">
+        <is>
+          <t>22' x 70'</t>
+        </is>
+      </c>
+      <c r="C13" s="31" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D13" s="31" t="n">
+        <v>46313</v>
+      </c>
+      <c r="E13" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="32" t="n">
+        <v>77</v>
+      </c>
+      <c r="G13" s="32" t="n">
+        <v>77</v>
+      </c>
+      <c r="H13" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="32" t="n">
+        <v>99</v>
+      </c>
+      <c r="J13" s="32" t="n">
+        <v>99</v>
+      </c>
+      <c r="K13" s="34" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="L13" s="34" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="M13" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="B14" s="36" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="C14" s="37" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D14" s="37" t="n">
+        <v>46313</v>
+      </c>
+      <c r="E14" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="38" t="n">
+        <v>111</v>
+      </c>
+      <c r="G14" s="38" t="n">
+        <v>111</v>
+      </c>
+      <c r="H14" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="38" t="n">
+        <v>111</v>
+      </c>
+      <c r="J14" s="38" t="n">
+        <v>111</v>
+      </c>
+      <c r="K14" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="B15" s="30" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="C15" s="31" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D15" s="31" t="n">
+        <v>46313</v>
+      </c>
+      <c r="E15" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="32" t="n">
+        <v>134</v>
+      </c>
+      <c r="G15" s="32" t="n">
+        <v>134</v>
+      </c>
+      <c r="H15" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="32" t="n">
+        <v>138</v>
+      </c>
+      <c r="J15" s="32" t="n">
+        <v>138</v>
+      </c>
+      <c r="K15" s="34" t="n">
+        <v>0.9710144927536232</v>
+      </c>
+      <c r="L15" s="34" t="n">
+        <v>0.9710144927536232</v>
+      </c>
+      <c r="M15" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="B16" s="36" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="C16" s="37" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D16" s="37" t="n">
+        <v>46313</v>
+      </c>
+      <c r="E16" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="38" t="n">
+        <v>79</v>
+      </c>
+      <c r="G16" s="38" t="n">
+        <v>79</v>
+      </c>
+      <c r="H16" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="38" t="n">
+        <v>81</v>
+      </c>
+      <c r="J16" s="38" t="n">
+        <v>81</v>
+      </c>
+      <c r="K16" s="40" t="n">
+        <v>0.9753086419753086</v>
+      </c>
+      <c r="L16" s="40" t="n">
+        <v>0.9753086419753086</v>
+      </c>
+      <c r="M16" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="B17" s="30" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="C17" s="31" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D17" s="31" t="n">
+        <v>46313</v>
+      </c>
+      <c r="E17" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="32" t="n">
+        <v>23</v>
+      </c>
+      <c r="G17" s="32" t="n">
+        <v>23</v>
+      </c>
+      <c r="H17" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="32" t="n">
+        <v>26</v>
+      </c>
+      <c r="J17" s="32" t="n">
+        <v>26</v>
+      </c>
+      <c r="K17" s="34" t="n">
+        <v>0.8846153846153846</v>
+      </c>
+      <c r="L17" s="34" t="n">
+        <v>0.8846153846153846</v>
+      </c>
+      <c r="M17" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="B18" s="36" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="C18" s="37" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D18" s="37" t="n">
+        <v>46313</v>
+      </c>
+      <c r="E18" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="38" t="n">
+        <v>124</v>
+      </c>
+      <c r="G18" s="38" t="n">
+        <v>124</v>
+      </c>
+      <c r="H18" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="38" t="n">
+        <v>126</v>
+      </c>
+      <c r="J18" s="38" t="n">
+        <v>126</v>
+      </c>
+      <c r="K18" s="40" t="n">
+        <v>0.9841269841269841</v>
+      </c>
+      <c r="L18" s="40" t="n">
+        <v>0.9841269841269841</v>
+      </c>
+      <c r="M18" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D19" s="31" t="n">
+        <v>46313</v>
+      </c>
+      <c r="E19" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="32" t="n">
+        <v>98</v>
+      </c>
+      <c r="G19" s="32" t="n">
+        <v>98</v>
+      </c>
+      <c r="H19" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="32" t="n">
+        <v>104</v>
+      </c>
+      <c r="J19" s="32" t="n">
+        <v>104</v>
+      </c>
+      <c r="K19" s="34" t="n">
+        <v>0.9423076923076923</v>
+      </c>
+      <c r="L19" s="34" t="n">
+        <v>0.9423076923076923</v>
+      </c>
+      <c r="M19" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 3</t>
+        </is>
+      </c>
+      <c r="B20" s="36" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="C20" s="37" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D20" s="37" t="n">
+        <v>46313</v>
+      </c>
+      <c r="E20" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="38" t="n">
+        <v>29</v>
+      </c>
+      <c r="G20" s="38" t="n">
+        <v>29</v>
+      </c>
+      <c r="H20" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="38" t="n">
+        <v>44</v>
+      </c>
+      <c r="J20" s="38" t="n">
+        <v>44</v>
+      </c>
+      <c r="K20" s="40" t="n">
+        <v>0.6590909090909091</v>
+      </c>
+      <c r="L20" s="40" t="n">
+        <v>0.6590909090909091</v>
+      </c>
+      <c r="M20" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 3</t>
+        </is>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D21" s="31" t="n">
+        <v>46313</v>
+      </c>
+      <c r="E21" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="32" t="n">
+        <v>65</v>
+      </c>
+      <c r="G21" s="32" t="n">
+        <v>65</v>
+      </c>
+      <c r="H21" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="32" t="n">
+        <v>85</v>
+      </c>
+      <c r="J21" s="32" t="n">
+        <v>85</v>
+      </c>
+      <c r="K21" s="34" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="L21" s="34" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="M21" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 3</t>
+        </is>
+      </c>
+      <c r="B22" s="36" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="C22" s="37" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D22" s="37" t="n">
+        <v>46313</v>
+      </c>
+      <c r="E22" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="38" t="n">
+        <v>24</v>
+      </c>
+      <c r="G22" s="38" t="n">
+        <v>24</v>
+      </c>
+      <c r="H22" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="38" t="n">
+        <v>102</v>
+      </c>
+      <c r="J22" s="38" t="n">
+        <v>102</v>
+      </c>
+      <c r="K22" s="40" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="L22" s="40" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="M22" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="30" t="inlineStr">
+        <is>
+          <t>Sapphire Residence @Diamond City</t>
+        </is>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D23" s="31" t="n">
+        <v>46313</v>
+      </c>
+      <c r="E23" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="32" t="n">
+        <v>45</v>
+      </c>
+      <c r="G23" s="32" t="n">
+        <v>45</v>
+      </c>
+      <c r="H23" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="32" t="n">
+        <v>136</v>
+      </c>
+      <c r="J23" s="32" t="n">
+        <v>136</v>
+      </c>
+      <c r="K23" s="34" t="n">
+        <v>0.3308823529411765</v>
+      </c>
+      <c r="L23" s="34" t="n">
+        <v>0.3308823529411765</v>
+      </c>
+      <c r="M23" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="36" t="inlineStr">
+        <is>
+          <t>Springvale Sempurna Heights</t>
+        </is>
+      </c>
+      <c r="B24" s="36" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C24" s="37" t="n">
+        <v>46213</v>
+      </c>
+      <c r="D24" s="37" t="n">
+        <v>46181</v>
+      </c>
+      <c r="E24" s="38" t="n">
+        <v>32</v>
+      </c>
+      <c r="F24" s="38" t="n">
+        <v>154</v>
+      </c>
+      <c r="G24" s="38" t="n">
+        <v>148</v>
+      </c>
+      <c r="H24" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="I24" s="38" t="n">
+        <v>189</v>
+      </c>
+      <c r="J24" s="38" t="n">
+        <v>189</v>
+      </c>
+      <c r="K24" s="40" t="n">
+        <v>0.8148148148148148</v>
+      </c>
+      <c r="L24" s="40" t="n">
+        <v>0.783068783068783</v>
+      </c>
+      <c r="M24" s="41" t="n">
+        <v>3.174603174603174</v>
+      </c>
+      <c r="N24" s="36" t="inlineStr">
+        <is>
+          <t>32-day observation gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="30" t="inlineStr">
+        <is>
+          <t>Springvale Sempurna Heights</t>
+        </is>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Group A · front-kitchen layout</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D25" s="31" t="n">
+        <v>46313</v>
+      </c>
+      <c r="E25" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="32" t="n">
+        <v>27</v>
+      </c>
+      <c r="J25" s="32" t="n">
+        <v>27</v>
+      </c>
+      <c r="K25" s="34" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="L25" s="34" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="M25" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="36" t="inlineStr">
+        <is>
+          <t>Springvale Sempurna Heights</t>
+        </is>
+      </c>
+      <c r="B26" s="36" t="inlineStr">
+        <is>
+          <t>Group B · rear-kitchen layout</t>
+        </is>
+      </c>
+      <c r="C26" s="37" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D26" s="37" t="n">
+        <v>46313</v>
+      </c>
+      <c r="E26" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="38" t="n">
+        <v>161</v>
+      </c>
+      <c r="G26" s="38" t="n">
+        <v>161</v>
+      </c>
+      <c r="H26" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="38" t="n">
+        <v>308</v>
+      </c>
+      <c r="J26" s="38" t="n">
+        <v>308</v>
+      </c>
+      <c r="K26" s="40" t="n">
+        <v>0.5227272727272727</v>
+      </c>
+      <c r="L26" s="40" t="n">
+        <v>0.5227272727272727</v>
+      </c>
+      <c r="M26" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t>Zinnia Residences</t>
+        </is>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D27" s="31" t="n">
+        <v>46313</v>
+      </c>
+      <c r="E27" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="32" t="n">
+        <v>34</v>
+      </c>
+      <c r="G27" s="32" t="n">
+        <v>34</v>
+      </c>
+      <c r="H27" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="32" t="n">
+        <v>149</v>
+      </c>
+      <c r="J27" s="32" t="n">
+        <v>149</v>
+      </c>
+      <c r="K27" s="34" t="n">
+        <v>0.2281879194630873</v>
+      </c>
+      <c r="L27" s="34" t="n">
+        <v>0.2281879194630873</v>
+      </c>
+      <c r="M27" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation pair</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:N27"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:X17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -712,9 +2092,9 @@
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="5" t="n"/>
+      <c r="G2" s="42" t="n"/>
+      <c r="H2" s="42" t="n"/>
+      <c r="I2" s="43" t="n"/>
       <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Chorus @Setia Ecohill 2</t>
@@ -725,22 +2105,22 @@
           <t>M Legasi Phase 1</t>
         </is>
       </c>
-      <c r="L2" s="2" t="n"/>
-      <c r="M2" s="5" t="n"/>
+      <c r="L2" s="42" t="n"/>
+      <c r="M2" s="43" t="n"/>
       <c r="N2" s="4" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n"/>
-      <c r="P2" s="5" t="n"/>
+      <c r="O2" s="42" t="n"/>
+      <c r="P2" s="43" t="n"/>
       <c r="Q2" s="4" t="inlineStr">
         <is>
           <t>M Legasi Phase 3</t>
         </is>
       </c>
-      <c r="R2" s="2" t="n"/>
-      <c r="S2" s="5" t="n"/>
+      <c r="R2" s="42" t="n"/>
+      <c r="S2" s="43" t="n"/>
       <c r="T2" s="3" t="inlineStr">
         <is>
           <t>Sapphire Residence @Diamond City</t>
@@ -751,8 +2131,8 @@
           <t>Springvale Sempurna Heights</t>
         </is>
       </c>
-      <c r="V2" s="2" t="n"/>
-      <c r="W2" s="5" t="n"/>
+      <c r="V2" s="42" t="n"/>
+      <c r="W2" s="43" t="n"/>
       <c r="X2" s="3" t="inlineStr">
         <is>
           <t>Zinnia Residences</t>
@@ -882,28 +2262,12 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>WEEK · 5 Oct 2026 – 11 Oct 2026</t>
         </is>
       </c>
-      <c r="B4" s="11" t="n"/>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="12" t="n"/>
-      <c r="I4" s="13" t="n"/>
-      <c r="J4" s="11" t="n"/>
-      <c r="K4" s="12" t="n"/>
-      <c r="M4" s="13" t="n"/>
-      <c r="N4" s="12" t="n"/>
-      <c r="P4" s="13" t="n"/>
-      <c r="Q4" s="12" t="n"/>
-      <c r="S4" s="13" t="n"/>
-      <c r="T4" s="11" t="n"/>
-      <c r="U4" s="12" t="n"/>
-      <c r="W4" s="13" t="n"/>
-      <c r="X4" s="11" t="n"/>
+      <c r="X4" s="45" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
@@ -1150,28 +2514,12 @@
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="44" t="inlineStr">
         <is>
           <t>WEEK · 12 Oct 2026 – 18 Oct 2026</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="12" t="n"/>
-      <c r="I7" s="13" t="n"/>
-      <c r="J7" s="11" t="n"/>
-      <c r="K7" s="12" t="n"/>
-      <c r="M7" s="13" t="n"/>
-      <c r="N7" s="12" t="n"/>
-      <c r="P7" s="13" t="n"/>
-      <c r="Q7" s="12" t="n"/>
-      <c r="S7" s="13" t="n"/>
-      <c r="T7" s="11" t="n"/>
-      <c r="U7" s="12" t="n"/>
-      <c r="W7" s="13" t="n"/>
-      <c r="X7" s="11" t="n"/>
+      <c r="X7" s="45" t="n"/>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
@@ -1418,28 +2766,12 @@
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="44" t="inlineStr">
         <is>
           <t>WEEK · 19 Oct 2026 – 25 Oct 2026</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="11" t="n"/>
-      <c r="F10" s="12" t="n"/>
-      <c r="I10" s="13" t="n"/>
-      <c r="J10" s="11" t="n"/>
-      <c r="K10" s="12" t="n"/>
-      <c r="M10" s="13" t="n"/>
-      <c r="N10" s="12" t="n"/>
-      <c r="P10" s="13" t="n"/>
-      <c r="Q10" s="12" t="n"/>
-      <c r="S10" s="13" t="n"/>
-      <c r="T10" s="11" t="n"/>
-      <c r="U10" s="12" t="n"/>
-      <c r="W10" s="13" t="n"/>
-      <c r="X10" s="11" t="n"/>
+      <c r="X10" s="45" t="n"/>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="14" t="inlineStr">
@@ -1569,99 +2901,99 @@
           <t>Weekly Change</t>
         </is>
       </c>
-      <c r="B12" s="28" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="C12" s="28" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="D12" s="28" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="E12" s="28" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="F12" s="29" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="G12" s="30" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="H12" s="30" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="I12" s="31" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="J12" s="28" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="K12" s="29" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="L12" s="30" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="M12" s="31" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="N12" s="29" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="O12" s="30" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="P12" s="31" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="Q12" s="29" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="R12" s="30" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="S12" s="31" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="T12" s="28" t="inlineStr">
-        <is>
-          <t>No change</t>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="I12" s="23" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="K12" s="21" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="L12" s="22" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="M12" s="23" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="O12" s="22" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="P12" s="23" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="Q12" s="21" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="R12" s="22" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="S12" s="23" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="T12" s="20" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
         </is>
       </c>
       <c r="U12" s="21" t="inlineStr">
@@ -1669,45 +3001,29 @@
           <t>In progress</t>
         </is>
       </c>
-      <c r="V12" s="30" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="W12" s="31" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="X12" s="28" t="inlineStr">
-        <is>
-          <t>No change</t>
+      <c r="V12" s="22" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="W12" s="23" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="X12" s="20" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="44" t="inlineStr">
         <is>
           <t>WEEK · 26 Oct 2026 – 1 Nov 2026</t>
         </is>
       </c>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="12" t="n"/>
-      <c r="I13" s="13" t="n"/>
-      <c r="J13" s="11" t="n"/>
-      <c r="K13" s="12" t="n"/>
-      <c r="M13" s="13" t="n"/>
-      <c r="N13" s="12" t="n"/>
-      <c r="P13" s="13" t="n"/>
-      <c r="Q13" s="12" t="n"/>
-      <c r="S13" s="13" t="n"/>
-      <c r="T13" s="11" t="n"/>
-      <c r="U13" s="12" t="n"/>
-      <c r="W13" s="13" t="n"/>
-      <c r="X13" s="11" t="n"/>
+      <c r="X13" s="45" t="n"/>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="14" t="inlineStr">
@@ -1973,36 +3289,20 @@
       <c r="X16" s="11" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="32" t="inlineStr">
+      <c r="A17" s="46" t="inlineStr">
         <is>
           <t>Monthly tabs are generated from available history. Weeks are Monday–Sunday; weeks spanning month boundaries are shown in each month they overlap.</t>
         </is>
       </c>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="I17" s="13" t="n"/>
-      <c r="J17" s="11" t="n"/>
-      <c r="K17" s="12" t="n"/>
-      <c r="M17" s="13" t="n"/>
-      <c r="N17" s="12" t="n"/>
-      <c r="P17" s="13" t="n"/>
-      <c r="Q17" s="12" t="n"/>
-      <c r="S17" s="13" t="n"/>
-      <c r="T17" s="11" t="n"/>
-      <c r="U17" s="12" t="n"/>
-      <c r="W17" s="13" t="n"/>
-      <c r="X17" s="11" t="n"/>
+      <c r="X17" s="45" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="K2:M2"/>
     <mergeCell ref="N2:P2"/>
+    <mergeCell ref="A7:X7"/>
     <mergeCell ref="A4:X4"/>
-    <mergeCell ref="A7:X7"/>
     <mergeCell ref="F2:I2"/>
     <mergeCell ref="A10:X10"/>
     <mergeCell ref="A17:X17"/>

--- a/Broga_Weekly_Tracking.xlsx
+++ b/Broga_Weekly_Tracking.xlsx
@@ -8,12 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="Latest Snapshot Comparison" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Oct 2026" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Snapshot History" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Oct 2026" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Latest Snapshot Comparison'!$A$4:$N$27</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Latest Snapshot Comparison'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Oct 2026'!$1:$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Snapshot History'!$A$4:$K$209</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Snapshot History'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Oct 2026'!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,13 +25,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="dd mmm yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd mmm yyyy"/>
+    <numFmt numFmtId="165" formatCode="+0;-0;0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="+0.0;-0.0;0.0"/>
-    <numFmt numFmtId="168" formatCode="+0;-0;0"/>
+    <numFmt numFmtId="168" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -73,6 +76,12 @@
       <i val="1"/>
       <color rgb="008B5E34"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="8">
@@ -260,7 +269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -346,13 +355,13 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -364,13 +373,13 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -387,6 +396,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -869,10 +908,10 @@
           <t>Terrace houses</t>
         </is>
       </c>
-      <c r="C5" s="31" t="n">
+      <c r="C5" s="47" t="n">
         <v>46314</v>
       </c>
-      <c r="D5" s="31" t="n">
+      <c r="D5" s="47" t="n">
         <v>46313</v>
       </c>
       <c r="E5" s="32" t="n">
@@ -884,7 +923,7 @@
       <c r="G5" s="32" t="n">
         <v>74</v>
       </c>
-      <c r="H5" s="33" t="n">
+      <c r="H5" s="48" t="n">
         <v>0</v>
       </c>
       <c r="I5" s="32" t="n">
@@ -919,10 +958,10 @@
           <t>20' x 60'</t>
         </is>
       </c>
-      <c r="C6" s="37" t="n">
+      <c r="C6" s="49" t="n">
         <v>46314</v>
       </c>
-      <c r="D6" s="37" t="n">
+      <c r="D6" s="49" t="n">
         <v>46313</v>
       </c>
       <c r="E6" s="38" t="n">
@@ -934,7 +973,7 @@
       <c r="G6" s="38" t="n">
         <v>69</v>
       </c>
-      <c r="H6" s="39" t="n">
+      <c r="H6" s="50" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="38" t="n">
@@ -969,10 +1008,10 @@
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="C7" s="31" t="n">
+      <c r="C7" s="47" t="n">
         <v>46314</v>
       </c>
-      <c r="D7" s="31" t="n">
+      <c r="D7" s="47" t="n">
         <v>46313</v>
       </c>
       <c r="E7" s="32" t="n">
@@ -984,7 +1023,7 @@
       <c r="G7" s="32" t="n">
         <v>21</v>
       </c>
-      <c r="H7" s="33" t="n">
+      <c r="H7" s="48" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="32" t="n">
@@ -1019,10 +1058,10 @@
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="C8" s="37" t="n">
+      <c r="C8" s="49" t="n">
         <v>46314</v>
       </c>
-      <c r="D8" s="37" t="n">
+      <c r="D8" s="49" t="n">
         <v>46313</v>
       </c>
       <c r="E8" s="38" t="n">
@@ -1034,7 +1073,7 @@
       <c r="G8" s="38" t="n">
         <v>71</v>
       </c>
-      <c r="H8" s="39" t="n">
+      <c r="H8" s="50" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="38" t="n">
@@ -1069,10 +1108,10 @@
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="C9" s="31" t="n">
+      <c r="C9" s="47" t="n">
         <v>46314</v>
       </c>
-      <c r="D9" s="31" t="n">
+      <c r="D9" s="47" t="n">
         <v>46313</v>
       </c>
       <c r="E9" s="32" t="n">
@@ -1084,7 +1123,7 @@
       <c r="G9" s="32" t="n">
         <v>46</v>
       </c>
-      <c r="H9" s="33" t="n">
+      <c r="H9" s="48" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="32" t="n">
@@ -1119,10 +1158,10 @@
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="C10" s="37" t="n">
+      <c r="C10" s="49" t="n">
         <v>46314</v>
       </c>
-      <c r="D10" s="37" t="n">
+      <c r="D10" s="49" t="n">
         <v>46313</v>
       </c>
       <c r="E10" s="38" t="n">
@@ -1134,7 +1173,7 @@
       <c r="G10" s="38" t="n">
         <v>56</v>
       </c>
-      <c r="H10" s="39" t="n">
+      <c r="H10" s="50" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="38" t="n">
@@ -1169,10 +1208,10 @@
           <t>20' x 75'</t>
         </is>
       </c>
-      <c r="C11" s="31" t="n">
+      <c r="C11" s="47" t="n">
         <v>46314</v>
       </c>
-      <c r="D11" s="31" t="n">
+      <c r="D11" s="47" t="n">
         <v>46313</v>
       </c>
       <c r="E11" s="32" t="n">
@@ -1184,7 +1223,7 @@
       <c r="G11" s="32" t="n">
         <v>24</v>
       </c>
-      <c r="H11" s="33" t="n">
+      <c r="H11" s="48" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="32" t="n">
@@ -1219,10 +1258,10 @@
           <t>20' x 80'</t>
         </is>
       </c>
-      <c r="C12" s="37" t="n">
+      <c r="C12" s="49" t="n">
         <v>46314</v>
       </c>
-      <c r="D12" s="37" t="n">
+      <c r="D12" s="49" t="n">
         <v>46313</v>
       </c>
       <c r="E12" s="38" t="n">
@@ -1234,7 +1273,7 @@
       <c r="G12" s="38" t="n">
         <v>10</v>
       </c>
-      <c r="H12" s="39" t="n">
+      <c r="H12" s="50" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="38" t="n">
@@ -1269,10 +1308,10 @@
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="C13" s="31" t="n">
+      <c r="C13" s="47" t="n">
         <v>46314</v>
       </c>
-      <c r="D13" s="31" t="n">
+      <c r="D13" s="47" t="n">
         <v>46313</v>
       </c>
       <c r="E13" s="32" t="n">
@@ -1284,7 +1323,7 @@
       <c r="G13" s="32" t="n">
         <v>77</v>
       </c>
-      <c r="H13" s="33" t="n">
+      <c r="H13" s="48" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="32" t="n">
@@ -1319,10 +1358,10 @@
           <t>20' x 60'</t>
         </is>
       </c>
-      <c r="C14" s="37" t="n">
+      <c r="C14" s="49" t="n">
         <v>46314</v>
       </c>
-      <c r="D14" s="37" t="n">
+      <c r="D14" s="49" t="n">
         <v>46313</v>
       </c>
       <c r="E14" s="38" t="n">
@@ -1334,7 +1373,7 @@
       <c r="G14" s="38" t="n">
         <v>111</v>
       </c>
-      <c r="H14" s="39" t="n">
+      <c r="H14" s="50" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="38" t="n">
@@ -1369,10 +1408,10 @@
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="C15" s="31" t="n">
+      <c r="C15" s="47" t="n">
         <v>46314</v>
       </c>
-      <c r="D15" s="31" t="n">
+      <c r="D15" s="47" t="n">
         <v>46313</v>
       </c>
       <c r="E15" s="32" t="n">
@@ -1384,7 +1423,7 @@
       <c r="G15" s="32" t="n">
         <v>134</v>
       </c>
-      <c r="H15" s="33" t="n">
+      <c r="H15" s="48" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="32" t="n">
@@ -1419,10 +1458,10 @@
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="C16" s="37" t="n">
+      <c r="C16" s="49" t="n">
         <v>46314</v>
       </c>
-      <c r="D16" s="37" t="n">
+      <c r="D16" s="49" t="n">
         <v>46313</v>
       </c>
       <c r="E16" s="38" t="n">
@@ -1434,7 +1473,7 @@
       <c r="G16" s="38" t="n">
         <v>79</v>
       </c>
-      <c r="H16" s="39" t="n">
+      <c r="H16" s="50" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="38" t="n">
@@ -1469,10 +1508,10 @@
           <t>20' x 60'</t>
         </is>
       </c>
-      <c r="C17" s="31" t="n">
+      <c r="C17" s="47" t="n">
         <v>46314</v>
       </c>
-      <c r="D17" s="31" t="n">
+      <c r="D17" s="47" t="n">
         <v>46313</v>
       </c>
       <c r="E17" s="32" t="n">
@@ -1484,7 +1523,7 @@
       <c r="G17" s="32" t="n">
         <v>23</v>
       </c>
-      <c r="H17" s="33" t="n">
+      <c r="H17" s="48" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="32" t="n">
@@ -1519,10 +1558,10 @@
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="C18" s="37" t="n">
+      <c r="C18" s="49" t="n">
         <v>46314</v>
       </c>
-      <c r="D18" s="37" t="n">
+      <c r="D18" s="49" t="n">
         <v>46313</v>
       </c>
       <c r="E18" s="38" t="n">
@@ -1534,7 +1573,7 @@
       <c r="G18" s="38" t="n">
         <v>124</v>
       </c>
-      <c r="H18" s="39" t="n">
+      <c r="H18" s="50" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="38" t="n">
@@ -1569,10 +1608,10 @@
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="C19" s="31" t="n">
+      <c r="C19" s="47" t="n">
         <v>46314</v>
       </c>
-      <c r="D19" s="31" t="n">
+      <c r="D19" s="47" t="n">
         <v>46313</v>
       </c>
       <c r="E19" s="32" t="n">
@@ -1584,7 +1623,7 @@
       <c r="G19" s="32" t="n">
         <v>98</v>
       </c>
-      <c r="H19" s="33" t="n">
+      <c r="H19" s="48" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="32" t="n">
@@ -1619,10 +1658,10 @@
           <t>20' x 60'</t>
         </is>
       </c>
-      <c r="C20" s="37" t="n">
+      <c r="C20" s="49" t="n">
         <v>46314</v>
       </c>
-      <c r="D20" s="37" t="n">
+      <c r="D20" s="49" t="n">
         <v>46313</v>
       </c>
       <c r="E20" s="38" t="n">
@@ -1634,7 +1673,7 @@
       <c r="G20" s="38" t="n">
         <v>29</v>
       </c>
-      <c r="H20" s="39" t="n">
+      <c r="H20" s="50" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="38" t="n">
@@ -1669,10 +1708,10 @@
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="C21" s="31" t="n">
+      <c r="C21" s="47" t="n">
         <v>46314</v>
       </c>
-      <c r="D21" s="31" t="n">
+      <c r="D21" s="47" t="n">
         <v>46313</v>
       </c>
       <c r="E21" s="32" t="n">
@@ -1684,7 +1723,7 @@
       <c r="G21" s="32" t="n">
         <v>65</v>
       </c>
-      <c r="H21" s="33" t="n">
+      <c r="H21" s="48" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="32" t="n">
@@ -1719,10 +1758,10 @@
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="C22" s="37" t="n">
+      <c r="C22" s="49" t="n">
         <v>46314</v>
       </c>
-      <c r="D22" s="37" t="n">
+      <c r="D22" s="49" t="n">
         <v>46313</v>
       </c>
       <c r="E22" s="38" t="n">
@@ -1734,7 +1773,7 @@
       <c r="G22" s="38" t="n">
         <v>24</v>
       </c>
-      <c r="H22" s="39" t="n">
+      <c r="H22" s="50" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="38" t="n">
@@ -1769,10 +1808,10 @@
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="C23" s="31" t="n">
+      <c r="C23" s="47" t="n">
         <v>46314</v>
       </c>
-      <c r="D23" s="31" t="n">
+      <c r="D23" s="47" t="n">
         <v>46313</v>
       </c>
       <c r="E23" s="32" t="n">
@@ -1784,7 +1823,7 @@
       <c r="G23" s="32" t="n">
         <v>45</v>
       </c>
-      <c r="H23" s="33" t="n">
+      <c r="H23" s="48" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="32" t="n">
@@ -1819,10 +1858,10 @@
           <t>Group 1</t>
         </is>
       </c>
-      <c r="C24" s="37" t="n">
+      <c r="C24" s="49" t="n">
         <v>46213</v>
       </c>
-      <c r="D24" s="37" t="n">
+      <c r="D24" s="49" t="n">
         <v>46181</v>
       </c>
       <c r="E24" s="38" t="n">
@@ -1834,7 +1873,7 @@
       <c r="G24" s="38" t="n">
         <v>148</v>
       </c>
-      <c r="H24" s="39" t="n">
+      <c r="H24" s="50" t="n">
         <v>6</v>
       </c>
       <c r="I24" s="38" t="n">
@@ -1869,10 +1908,10 @@
           <t>Group A · front-kitchen layout</t>
         </is>
       </c>
-      <c r="C25" s="31" t="n">
+      <c r="C25" s="47" t="n">
         <v>46314</v>
       </c>
-      <c r="D25" s="31" t="n">
+      <c r="D25" s="47" t="n">
         <v>46313</v>
       </c>
       <c r="E25" s="32" t="n">
@@ -1884,7 +1923,7 @@
       <c r="G25" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="33" t="n">
+      <c r="H25" s="48" t="n">
         <v>0</v>
       </c>
       <c r="I25" s="32" t="n">
@@ -1919,10 +1958,10 @@
           <t>Group B · rear-kitchen layout</t>
         </is>
       </c>
-      <c r="C26" s="37" t="n">
+      <c r="C26" s="49" t="n">
         <v>46314</v>
       </c>
-      <c r="D26" s="37" t="n">
+      <c r="D26" s="49" t="n">
         <v>46313</v>
       </c>
       <c r="E26" s="38" t="n">
@@ -1934,7 +1973,7 @@
       <c r="G26" s="38" t="n">
         <v>161</v>
       </c>
-      <c r="H26" s="39" t="n">
+      <c r="H26" s="50" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="38" t="n">
@@ -1969,10 +2008,10 @@
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="C27" s="31" t="n">
+      <c r="C27" s="47" t="n">
         <v>46314</v>
       </c>
-      <c r="D27" s="31" t="n">
+      <c r="D27" s="47" t="n">
         <v>46313</v>
       </c>
       <c r="E27" s="32" t="n">
@@ -1984,7 +2023,7 @@
       <c r="G27" s="32" t="n">
         <v>34</v>
       </c>
-      <c r="H27" s="33" t="n">
+      <c r="H27" s="48" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="32" t="n">
@@ -2020,6 +2059,8331 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K209"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="52" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BROGA COMPETITOR SALES ANALYSIS | SNAPSHOT HISTORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>One row per valid signed observation from Historical Records. Use the filter on Observation Date to select dates available in the original history; date filters cannot create missing observations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Observation Date</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Unit Group / Layout</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Signed Units</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Total Units</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Signed %</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Previous Observation Date</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Days Since Previous Observation</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Change in Signed Units</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Change in Signed Percentage Points</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>Data Quality / Interpretation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="47" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B5" s="30" t="inlineStr">
+        <is>
+          <t>Amani Gallery Homes</t>
+        </is>
+      </c>
+      <c r="C5" s="30" t="inlineStr">
+        <is>
+          <t>Terrace houses</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="n">
+        <v>48</v>
+      </c>
+      <c r="E5" s="32" t="n">
+        <v>81</v>
+      </c>
+      <c r="F5" s="34" t="n">
+        <v>0.5925925925925926</v>
+      </c>
+      <c r="G5" s="47" t="n"/>
+      <c r="H5" s="32" t="n"/>
+      <c r="I5" s="32" t="n"/>
+      <c r="J5" s="51" t="n"/>
+      <c r="K5" s="30" t="inlineStr">
+        <is>
+          <t>Baseline: no earlier observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="49" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B6" s="36" t="inlineStr">
+        <is>
+          <t>Amani Gallery Homes</t>
+        </is>
+      </c>
+      <c r="C6" s="36" t="inlineStr">
+        <is>
+          <t>Terrace houses</t>
+        </is>
+      </c>
+      <c r="D6" s="38" t="n">
+        <v>53</v>
+      </c>
+      <c r="E6" s="38" t="n">
+        <v>81</v>
+      </c>
+      <c r="F6" s="40" t="n">
+        <v>0.654320987654321</v>
+      </c>
+      <c r="G6" s="49" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H6" s="38" t="n">
+        <v>32</v>
+      </c>
+      <c r="I6" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" s="41" t="n">
+        <v>6.172839506172845</v>
+      </c>
+      <c r="K6" s="36" t="inlineStr">
+        <is>
+          <t>32-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="47" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>Amani Gallery Homes</t>
+        </is>
+      </c>
+      <c r="C7" s="30" t="inlineStr">
+        <is>
+          <t>Terrace houses</t>
+        </is>
+      </c>
+      <c r="D7" s="32" t="n">
+        <v>72</v>
+      </c>
+      <c r="E7" s="32" t="n">
+        <v>81</v>
+      </c>
+      <c r="F7" s="34" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="G7" s="47" t="n">
+        <v>46213</v>
+      </c>
+      <c r="H7" s="32" t="n">
+        <v>95</v>
+      </c>
+      <c r="I7" s="48" t="n">
+        <v>19</v>
+      </c>
+      <c r="J7" s="35" t="n">
+        <v>23.45679012345678</v>
+      </c>
+      <c r="K7" s="30" t="inlineStr">
+        <is>
+          <t>95-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="49" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B8" s="36" t="inlineStr">
+        <is>
+          <t>Amani Gallery Homes</t>
+        </is>
+      </c>
+      <c r="C8" s="36" t="inlineStr">
+        <is>
+          <t>Terrace houses</t>
+        </is>
+      </c>
+      <c r="D8" s="38" t="n">
+        <v>74</v>
+      </c>
+      <c r="E8" s="38" t="n">
+        <v>81</v>
+      </c>
+      <c r="F8" s="40" t="n">
+        <v>0.9135802469135802</v>
+      </c>
+      <c r="G8" s="49" t="n">
+        <v>46308</v>
+      </c>
+      <c r="H8" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" s="41" t="n">
+        <v>2.469135802469136</v>
+      </c>
+      <c r="K8" s="36" t="inlineStr">
+        <is>
+          <t>2-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="47" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B9" s="30" t="inlineStr">
+        <is>
+          <t>Amani Gallery Homes</t>
+        </is>
+      </c>
+      <c r="C9" s="30" t="inlineStr">
+        <is>
+          <t>Terrace houses</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="n">
+        <v>74</v>
+      </c>
+      <c r="E9" s="32" t="n">
+        <v>81</v>
+      </c>
+      <c r="F9" s="34" t="n">
+        <v>0.9135802469135802</v>
+      </c>
+      <c r="G9" s="47" t="n">
+        <v>46310</v>
+      </c>
+      <c r="H9" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="49" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B10" s="36" t="inlineStr">
+        <is>
+          <t>Amani Gallery Homes</t>
+        </is>
+      </c>
+      <c r="C10" s="36" t="inlineStr">
+        <is>
+          <t>Terrace houses</t>
+        </is>
+      </c>
+      <c r="D10" s="38" t="n">
+        <v>74</v>
+      </c>
+      <c r="E10" s="38" t="n">
+        <v>81</v>
+      </c>
+      <c r="F10" s="40" t="n">
+        <v>0.9135802469135802</v>
+      </c>
+      <c r="G10" s="49" t="n">
+        <v>46311</v>
+      </c>
+      <c r="H10" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="47" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B11" s="30" t="inlineStr">
+        <is>
+          <t>Amani Gallery Homes</t>
+        </is>
+      </c>
+      <c r="C11" s="30" t="inlineStr">
+        <is>
+          <t>Terrace houses</t>
+        </is>
+      </c>
+      <c r="D11" s="32" t="n">
+        <v>74</v>
+      </c>
+      <c r="E11" s="32" t="n">
+        <v>81</v>
+      </c>
+      <c r="F11" s="34" t="n">
+        <v>0.9135802469135802</v>
+      </c>
+      <c r="G11" s="47" t="n">
+        <v>46312</v>
+      </c>
+      <c r="H11" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="49" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B12" s="36" t="inlineStr">
+        <is>
+          <t>Amani Gallery Homes</t>
+        </is>
+      </c>
+      <c r="C12" s="36" t="inlineStr">
+        <is>
+          <t>Terrace houses</t>
+        </is>
+      </c>
+      <c r="D12" s="38" t="n">
+        <v>74</v>
+      </c>
+      <c r="E12" s="38" t="n">
+        <v>81</v>
+      </c>
+      <c r="F12" s="40" t="n">
+        <v>0.9135802469135802</v>
+      </c>
+      <c r="G12" s="49" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H12" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="47" t="n">
+        <v>45889</v>
+      </c>
+      <c r="B13" s="30" t="inlineStr">
+        <is>
+          <t>Balau Homes 2A</t>
+        </is>
+      </c>
+      <c r="C13" s="30" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D13" s="32" t="n">
+        <v>34</v>
+      </c>
+      <c r="E13" s="32" t="n">
+        <v>113</v>
+      </c>
+      <c r="F13" s="34" t="n">
+        <v>0.3008849557522124</v>
+      </c>
+      <c r="G13" s="47" t="n"/>
+      <c r="H13" s="32" t="n"/>
+      <c r="I13" s="32" t="n"/>
+      <c r="J13" s="51" t="n"/>
+      <c r="K13" s="30" t="inlineStr">
+        <is>
+          <t>Baseline: no earlier observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="49" t="n">
+        <v>45911</v>
+      </c>
+      <c r="B14" s="36" t="inlineStr">
+        <is>
+          <t>Balau Homes 2A</t>
+        </is>
+      </c>
+      <c r="C14" s="36" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D14" s="38" t="n">
+        <v>37</v>
+      </c>
+      <c r="E14" s="38" t="n">
+        <v>113</v>
+      </c>
+      <c r="F14" s="40" t="n">
+        <v>0.3274336283185841</v>
+      </c>
+      <c r="G14" s="49" t="n">
+        <v>45889</v>
+      </c>
+      <c r="H14" s="38" t="n">
+        <v>22</v>
+      </c>
+      <c r="I14" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" s="41" t="n">
+        <v>2.654867256637167</v>
+      </c>
+      <c r="K14" s="36" t="inlineStr">
+        <is>
+          <t>22-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="47" t="n">
+        <v>45936</v>
+      </c>
+      <c r="B15" s="30" t="inlineStr">
+        <is>
+          <t>Balau Homes 2A</t>
+        </is>
+      </c>
+      <c r="C15" s="30" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="n">
+        <v>37</v>
+      </c>
+      <c r="E15" s="32" t="n">
+        <v>113</v>
+      </c>
+      <c r="F15" s="34" t="n">
+        <v>0.3274336283185841</v>
+      </c>
+      <c r="G15" s="47" t="n">
+        <v>45911</v>
+      </c>
+      <c r="H15" s="32" t="n">
+        <v>25</v>
+      </c>
+      <c r="I15" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="30" t="inlineStr">
+        <is>
+          <t>25-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="49" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B16" s="36" t="inlineStr">
+        <is>
+          <t>Balau Homes 2A</t>
+        </is>
+      </c>
+      <c r="C16" s="36" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D16" s="38" t="n">
+        <v>54</v>
+      </c>
+      <c r="E16" s="38" t="n">
+        <v>113</v>
+      </c>
+      <c r="F16" s="40" t="n">
+        <v>0.4778761061946903</v>
+      </c>
+      <c r="G16" s="49" t="n">
+        <v>45936</v>
+      </c>
+      <c r="H16" s="38" t="n">
+        <v>144</v>
+      </c>
+      <c r="I16" s="50" t="n">
+        <v>17</v>
+      </c>
+      <c r="J16" s="41" t="n">
+        <v>15.04424778761062</v>
+      </c>
+      <c r="K16" s="36" t="inlineStr">
+        <is>
+          <t>144-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="47" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B17" s="30" t="inlineStr">
+        <is>
+          <t>Balau Homes 2A</t>
+        </is>
+      </c>
+      <c r="C17" s="30" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D17" s="32" t="n">
+        <v>63</v>
+      </c>
+      <c r="E17" s="32" t="n">
+        <v>113</v>
+      </c>
+      <c r="F17" s="34" t="n">
+        <v>0.5575221238938053</v>
+      </c>
+      <c r="G17" s="47" t="n">
+        <v>46080</v>
+      </c>
+      <c r="H17" s="32" t="n">
+        <v>101</v>
+      </c>
+      <c r="I17" s="48" t="n">
+        <v>9</v>
+      </c>
+      <c r="J17" s="35" t="n">
+        <v>7.9646017699115</v>
+      </c>
+      <c r="K17" s="30" t="inlineStr">
+        <is>
+          <t>101-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="49" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B18" s="36" t="inlineStr">
+        <is>
+          <t>Balau Homes 2A</t>
+        </is>
+      </c>
+      <c r="C18" s="36" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D18" s="38" t="n">
+        <v>68</v>
+      </c>
+      <c r="E18" s="38" t="n">
+        <v>113</v>
+      </c>
+      <c r="F18" s="40" t="n">
+        <v>0.6017699115044248</v>
+      </c>
+      <c r="G18" s="49" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H18" s="38" t="n">
+        <v>32</v>
+      </c>
+      <c r="I18" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" s="41" t="n">
+        <v>4.424778761061954</v>
+      </c>
+      <c r="K18" s="36" t="inlineStr">
+        <is>
+          <t>32-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="47" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Balau Homes 2A</t>
+        </is>
+      </c>
+      <c r="C19" s="30" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D19" s="32" t="n">
+        <v>68</v>
+      </c>
+      <c r="E19" s="32" t="n">
+        <v>113</v>
+      </c>
+      <c r="F19" s="34" t="n">
+        <v>0.6017699115044248</v>
+      </c>
+      <c r="G19" s="47" t="n">
+        <v>46213</v>
+      </c>
+      <c r="H19" s="32" t="n">
+        <v>95</v>
+      </c>
+      <c r="I19" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="30" t="inlineStr">
+        <is>
+          <t>95-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="49" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B20" s="36" t="inlineStr">
+        <is>
+          <t>Balau Homes 2A</t>
+        </is>
+      </c>
+      <c r="C20" s="36" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D20" s="38" t="n">
+        <v>68</v>
+      </c>
+      <c r="E20" s="38" t="n">
+        <v>113</v>
+      </c>
+      <c r="F20" s="40" t="n">
+        <v>0.6017699115044248</v>
+      </c>
+      <c r="G20" s="49" t="n">
+        <v>46308</v>
+      </c>
+      <c r="H20" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="36" t="inlineStr">
+        <is>
+          <t>2-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="47" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Balau Homes 2A</t>
+        </is>
+      </c>
+      <c r="C21" s="30" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D21" s="32" t="n">
+        <v>68</v>
+      </c>
+      <c r="E21" s="32" t="n">
+        <v>113</v>
+      </c>
+      <c r="F21" s="34" t="n">
+        <v>0.6017699115044248</v>
+      </c>
+      <c r="G21" s="47" t="n">
+        <v>46310</v>
+      </c>
+      <c r="H21" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="49" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B22" s="36" t="inlineStr">
+        <is>
+          <t>Balau Homes 2A</t>
+        </is>
+      </c>
+      <c r="C22" s="36" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D22" s="38" t="n">
+        <v>69</v>
+      </c>
+      <c r="E22" s="38" t="n">
+        <v>113</v>
+      </c>
+      <c r="F22" s="40" t="n">
+        <v>0.6106194690265486</v>
+      </c>
+      <c r="G22" s="49" t="n">
+        <v>46311</v>
+      </c>
+      <c r="H22" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="41" t="n">
+        <v>0.8849557522123797</v>
+      </c>
+      <c r="K22" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="47" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Balau Homes 2A</t>
+        </is>
+      </c>
+      <c r="C23" s="30" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D23" s="32" t="n">
+        <v>69</v>
+      </c>
+      <c r="E23" s="32" t="n">
+        <v>113</v>
+      </c>
+      <c r="F23" s="34" t="n">
+        <v>0.6106194690265486</v>
+      </c>
+      <c r="G23" s="47" t="n">
+        <v>46312</v>
+      </c>
+      <c r="H23" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="49" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B24" s="36" t="inlineStr">
+        <is>
+          <t>Balau Homes 2A</t>
+        </is>
+      </c>
+      <c r="C24" s="36" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D24" s="38" t="n">
+        <v>69</v>
+      </c>
+      <c r="E24" s="38" t="n">
+        <v>113</v>
+      </c>
+      <c r="F24" s="40" t="n">
+        <v>0.6106194690265486</v>
+      </c>
+      <c r="G24" s="49" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H24" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="47" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Balau Homes 2C</t>
+        </is>
+      </c>
+      <c r="C25" s="30" t="inlineStr">
+        <is>
+          <t>22' x 70'</t>
+        </is>
+      </c>
+      <c r="D25" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="E25" s="32" t="n">
+        <v>48</v>
+      </c>
+      <c r="F25" s="34" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="G25" s="47" t="n"/>
+      <c r="H25" s="32" t="n"/>
+      <c r="I25" s="32" t="n"/>
+      <c r="J25" s="51" t="n"/>
+      <c r="K25" s="30" t="inlineStr">
+        <is>
+          <t>Baseline: no earlier observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="49" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B26" s="36" t="inlineStr">
+        <is>
+          <t>Balau Homes 2C</t>
+        </is>
+      </c>
+      <c r="C26" s="36" t="inlineStr">
+        <is>
+          <t>22' x 70'</t>
+        </is>
+      </c>
+      <c r="D26" s="38" t="n">
+        <v>19</v>
+      </c>
+      <c r="E26" s="38" t="n">
+        <v>48</v>
+      </c>
+      <c r="F26" s="40" t="n">
+        <v>0.3958333333333333</v>
+      </c>
+      <c r="G26" s="49" t="n">
+        <v>46080</v>
+      </c>
+      <c r="H26" s="38" t="n">
+        <v>101</v>
+      </c>
+      <c r="I26" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="J26" s="41" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="K26" s="36" t="inlineStr">
+        <is>
+          <t>101-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="47" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Balau Homes 2C</t>
+        </is>
+      </c>
+      <c r="C27" s="30" t="inlineStr">
+        <is>
+          <t>22' x 70'</t>
+        </is>
+      </c>
+      <c r="D27" s="32" t="n">
+        <v>19</v>
+      </c>
+      <c r="E27" s="32" t="n">
+        <v>48</v>
+      </c>
+      <c r="F27" s="34" t="n">
+        <v>0.3958333333333333</v>
+      </c>
+      <c r="G27" s="47" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H27" s="32" t="n">
+        <v>32</v>
+      </c>
+      <c r="I27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="30" t="inlineStr">
+        <is>
+          <t>32-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="49" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B28" s="36" t="inlineStr">
+        <is>
+          <t>Balau Homes 2C</t>
+        </is>
+      </c>
+      <c r="C28" s="36" t="inlineStr">
+        <is>
+          <t>22' x 70'</t>
+        </is>
+      </c>
+      <c r="D28" s="38" t="n">
+        <v>21</v>
+      </c>
+      <c r="E28" s="38" t="n">
+        <v>48</v>
+      </c>
+      <c r="F28" s="40" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="G28" s="49" t="n">
+        <v>46213</v>
+      </c>
+      <c r="H28" s="38" t="n">
+        <v>95</v>
+      </c>
+      <c r="I28" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" s="41" t="n">
+        <v>4.166666666666669</v>
+      </c>
+      <c r="K28" s="36" t="inlineStr">
+        <is>
+          <t>95-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="47" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Balau Homes 2C</t>
+        </is>
+      </c>
+      <c r="C29" s="30" t="inlineStr">
+        <is>
+          <t>22' x 70'</t>
+        </is>
+      </c>
+      <c r="D29" s="32" t="n">
+        <v>21</v>
+      </c>
+      <c r="E29" s="32" t="n">
+        <v>48</v>
+      </c>
+      <c r="F29" s="34" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="G29" s="47" t="n">
+        <v>46308</v>
+      </c>
+      <c r="H29" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="30" t="inlineStr">
+        <is>
+          <t>2-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="49" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B30" s="36" t="inlineStr">
+        <is>
+          <t>Balau Homes 2C</t>
+        </is>
+      </c>
+      <c r="C30" s="36" t="inlineStr">
+        <is>
+          <t>22' x 70'</t>
+        </is>
+      </c>
+      <c r="D30" s="38" t="n">
+        <v>21</v>
+      </c>
+      <c r="E30" s="38" t="n">
+        <v>48</v>
+      </c>
+      <c r="F30" s="40" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="G30" s="49" t="n">
+        <v>46310</v>
+      </c>
+      <c r="H30" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="47" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>Balau Homes 2C</t>
+        </is>
+      </c>
+      <c r="C31" s="30" t="inlineStr">
+        <is>
+          <t>22' x 70'</t>
+        </is>
+      </c>
+      <c r="D31" s="32" t="n">
+        <v>21</v>
+      </c>
+      <c r="E31" s="32" t="n">
+        <v>48</v>
+      </c>
+      <c r="F31" s="34" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="G31" s="47" t="n">
+        <v>46311</v>
+      </c>
+      <c r="H31" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="49" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B32" s="36" t="inlineStr">
+        <is>
+          <t>Balau Homes 2C</t>
+        </is>
+      </c>
+      <c r="C32" s="36" t="inlineStr">
+        <is>
+          <t>22' x 70'</t>
+        </is>
+      </c>
+      <c r="D32" s="38" t="n">
+        <v>21</v>
+      </c>
+      <c r="E32" s="38" t="n">
+        <v>48</v>
+      </c>
+      <c r="F32" s="40" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="G32" s="49" t="n">
+        <v>46312</v>
+      </c>
+      <c r="H32" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="47" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B33" s="30" t="inlineStr">
+        <is>
+          <t>Balau Homes 2C</t>
+        </is>
+      </c>
+      <c r="C33" s="30" t="inlineStr">
+        <is>
+          <t>22' x 70'</t>
+        </is>
+      </c>
+      <c r="D33" s="32" t="n">
+        <v>21</v>
+      </c>
+      <c r="E33" s="32" t="n">
+        <v>48</v>
+      </c>
+      <c r="F33" s="34" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="G33" s="47" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H33" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="49" t="n">
+        <v>45936</v>
+      </c>
+      <c r="B34" s="36" t="inlineStr">
+        <is>
+          <t>Banyan @Setia Ecohill 2</t>
+        </is>
+      </c>
+      <c r="C34" s="36" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D34" s="38" t="n">
+        <v>83</v>
+      </c>
+      <c r="E34" s="38" t="n">
+        <v>99</v>
+      </c>
+      <c r="F34" s="40" t="n">
+        <v>0.8383838383838383</v>
+      </c>
+      <c r="G34" s="49" t="n"/>
+      <c r="H34" s="38" t="n"/>
+      <c r="I34" s="38" t="n"/>
+      <c r="J34" s="52" t="n"/>
+      <c r="K34" s="36" t="inlineStr">
+        <is>
+          <t>Baseline: no earlier observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="47" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B35" s="30" t="inlineStr">
+        <is>
+          <t>Banyan @Setia Ecohill 2</t>
+        </is>
+      </c>
+      <c r="C35" s="30" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D35" s="32" t="n">
+        <v>70</v>
+      </c>
+      <c r="E35" s="32" t="n">
+        <v>113</v>
+      </c>
+      <c r="F35" s="34" t="n">
+        <v>0.6194690265486725</v>
+      </c>
+      <c r="G35" s="47" t="n">
+        <v>45936</v>
+      </c>
+      <c r="H35" s="32" t="n">
+        <v>245</v>
+      </c>
+      <c r="I35" s="53" t="n">
+        <v>-13</v>
+      </c>
+      <c r="J35" s="54" t="n">
+        <v>-21.89148118351658</v>
+      </c>
+      <c r="K35" s="30" t="inlineStr">
+        <is>
+          <t>Total-unit denominator changed; review scope/release changes; 245-day gap; change is not daily movement; Signed count decreased; verify source/status correction</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="49" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B36" s="36" t="inlineStr">
+        <is>
+          <t>Banyan @Setia Ecohill 2</t>
+        </is>
+      </c>
+      <c r="C36" s="36" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D36" s="38" t="n">
+        <v>70</v>
+      </c>
+      <c r="E36" s="38" t="n">
+        <v>113</v>
+      </c>
+      <c r="F36" s="40" t="n">
+        <v>0.6194690265486725</v>
+      </c>
+      <c r="G36" s="49" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H36" s="38" t="n">
+        <v>32</v>
+      </c>
+      <c r="I36" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="36" t="inlineStr">
+        <is>
+          <t>32-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="47" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B37" s="30" t="inlineStr">
+        <is>
+          <t>Banyan @Setia Ecohill 2</t>
+        </is>
+      </c>
+      <c r="C37" s="30" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D37" s="32" t="n">
+        <v>71</v>
+      </c>
+      <c r="E37" s="32" t="n">
+        <v>113</v>
+      </c>
+      <c r="F37" s="34" t="n">
+        <v>0.6283185840707964</v>
+      </c>
+      <c r="G37" s="47" t="n">
+        <v>46213</v>
+      </c>
+      <c r="H37" s="32" t="n">
+        <v>95</v>
+      </c>
+      <c r="I37" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" s="35" t="n">
+        <v>0.8849557522123908</v>
+      </c>
+      <c r="K37" s="30" t="inlineStr">
+        <is>
+          <t>95-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="49" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B38" s="36" t="inlineStr">
+        <is>
+          <t>Banyan @Setia Ecohill 2</t>
+        </is>
+      </c>
+      <c r="C38" s="36" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D38" s="38" t="n">
+        <v>71</v>
+      </c>
+      <c r="E38" s="38" t="n">
+        <v>113</v>
+      </c>
+      <c r="F38" s="40" t="n">
+        <v>0.6283185840707964</v>
+      </c>
+      <c r="G38" s="49" t="n">
+        <v>46308</v>
+      </c>
+      <c r="H38" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="36" t="inlineStr">
+        <is>
+          <t>2-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="47" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B39" s="30" t="inlineStr">
+        <is>
+          <t>Banyan @Setia Ecohill 2</t>
+        </is>
+      </c>
+      <c r="C39" s="30" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D39" s="32" t="n">
+        <v>71</v>
+      </c>
+      <c r="E39" s="32" t="n">
+        <v>113</v>
+      </c>
+      <c r="F39" s="34" t="n">
+        <v>0.6283185840707964</v>
+      </c>
+      <c r="G39" s="47" t="n">
+        <v>46310</v>
+      </c>
+      <c r="H39" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="49" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B40" s="36" t="inlineStr">
+        <is>
+          <t>Banyan @Setia Ecohill 2</t>
+        </is>
+      </c>
+      <c r="C40" s="36" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D40" s="38" t="n">
+        <v>71</v>
+      </c>
+      <c r="E40" s="38" t="n">
+        <v>113</v>
+      </c>
+      <c r="F40" s="40" t="n">
+        <v>0.6283185840707964</v>
+      </c>
+      <c r="G40" s="49" t="n">
+        <v>46311</v>
+      </c>
+      <c r="H40" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="47" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B41" s="30" t="inlineStr">
+        <is>
+          <t>Banyan @Setia Ecohill 2</t>
+        </is>
+      </c>
+      <c r="C41" s="30" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D41" s="32" t="n">
+        <v>71</v>
+      </c>
+      <c r="E41" s="32" t="n">
+        <v>113</v>
+      </c>
+      <c r="F41" s="34" t="n">
+        <v>0.6283185840707964</v>
+      </c>
+      <c r="G41" s="47" t="n">
+        <v>46312</v>
+      </c>
+      <c r="H41" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="49" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B42" s="36" t="inlineStr">
+        <is>
+          <t>Banyan @Setia Ecohill 2</t>
+        </is>
+      </c>
+      <c r="C42" s="36" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D42" s="38" t="n">
+        <v>71</v>
+      </c>
+      <c r="E42" s="38" t="n">
+        <v>113</v>
+      </c>
+      <c r="F42" s="40" t="n">
+        <v>0.6283185840707964</v>
+      </c>
+      <c r="G42" s="49" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H42" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="47" t="n">
+        <v>45936</v>
+      </c>
+      <c r="B43" s="30" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C43" s="30" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D43" s="32" t="n">
+        <v>45</v>
+      </c>
+      <c r="E43" s="32" t="n">
+        <v>46</v>
+      </c>
+      <c r="F43" s="34" t="n">
+        <v>0.9782608695652174</v>
+      </c>
+      <c r="G43" s="47" t="n"/>
+      <c r="H43" s="32" t="n"/>
+      <c r="I43" s="32" t="n"/>
+      <c r="J43" s="51" t="n"/>
+      <c r="K43" s="30" t="inlineStr">
+        <is>
+          <t>Baseline: no earlier observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="49" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B44" s="36" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C44" s="36" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D44" s="38" t="n">
+        <v>46</v>
+      </c>
+      <c r="E44" s="38" t="n">
+        <v>46</v>
+      </c>
+      <c r="F44" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="49" t="n">
+        <v>45936</v>
+      </c>
+      <c r="H44" s="38" t="n">
+        <v>245</v>
+      </c>
+      <c r="I44" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="41" t="n">
+        <v>2.173913043478259</v>
+      </c>
+      <c r="K44" s="36" t="inlineStr">
+        <is>
+          <t>245-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="47" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B45" s="30" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C45" s="30" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D45" s="32" t="n">
+        <v>46</v>
+      </c>
+      <c r="E45" s="32" t="n">
+        <v>46</v>
+      </c>
+      <c r="F45" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="47" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H45" s="32" t="n">
+        <v>32</v>
+      </c>
+      <c r="I45" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="30" t="inlineStr">
+        <is>
+          <t>32-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="49" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B46" s="36" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C46" s="36" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D46" s="38" t="n">
+        <v>46</v>
+      </c>
+      <c r="E46" s="38" t="n">
+        <v>46</v>
+      </c>
+      <c r="F46" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="49" t="n">
+        <v>46213</v>
+      </c>
+      <c r="H46" s="38" t="n">
+        <v>95</v>
+      </c>
+      <c r="I46" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="36" t="inlineStr">
+        <is>
+          <t>95-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="47" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B47" s="30" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C47" s="30" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D47" s="32" t="n">
+        <v>46</v>
+      </c>
+      <c r="E47" s="32" t="n">
+        <v>46</v>
+      </c>
+      <c r="F47" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="47" t="n">
+        <v>46308</v>
+      </c>
+      <c r="H47" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I47" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="30" t="inlineStr">
+        <is>
+          <t>2-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="49" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B48" s="36" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C48" s="36" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D48" s="38" t="n">
+        <v>46</v>
+      </c>
+      <c r="E48" s="38" t="n">
+        <v>46</v>
+      </c>
+      <c r="F48" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="49" t="n">
+        <v>46310</v>
+      </c>
+      <c r="H48" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="47" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B49" s="30" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C49" s="30" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D49" s="32" t="n">
+        <v>46</v>
+      </c>
+      <c r="E49" s="32" t="n">
+        <v>46</v>
+      </c>
+      <c r="F49" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="47" t="n">
+        <v>46311</v>
+      </c>
+      <c r="H49" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="49" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B50" s="36" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C50" s="36" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D50" s="38" t="n">
+        <v>46</v>
+      </c>
+      <c r="E50" s="38" t="n">
+        <v>46</v>
+      </c>
+      <c r="F50" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="49" t="n">
+        <v>46312</v>
+      </c>
+      <c r="H50" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="47" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B51" s="30" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C51" s="30" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D51" s="32" t="n">
+        <v>46</v>
+      </c>
+      <c r="E51" s="32" t="n">
+        <v>46</v>
+      </c>
+      <c r="F51" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="47" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H51" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="49" t="n">
+        <v>45936</v>
+      </c>
+      <c r="B52" s="36" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C52" s="36" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D52" s="38" t="n">
+        <v>47</v>
+      </c>
+      <c r="E52" s="38" t="n">
+        <v>56</v>
+      </c>
+      <c r="F52" s="40" t="n">
+        <v>0.8392857142857143</v>
+      </c>
+      <c r="G52" s="49" t="n"/>
+      <c r="H52" s="38" t="n"/>
+      <c r="I52" s="38" t="n"/>
+      <c r="J52" s="52" t="n"/>
+      <c r="K52" s="36" t="inlineStr">
+        <is>
+          <t>Baseline: no earlier observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="47" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B53" s="30" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C53" s="30" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D53" s="32" t="n">
+        <v>56</v>
+      </c>
+      <c r="E53" s="32" t="n">
+        <v>56</v>
+      </c>
+      <c r="F53" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="47" t="n">
+        <v>45936</v>
+      </c>
+      <c r="H53" s="32" t="n">
+        <v>245</v>
+      </c>
+      <c r="I53" s="48" t="n">
+        <v>9</v>
+      </c>
+      <c r="J53" s="35" t="n">
+        <v>16.07142857142857</v>
+      </c>
+      <c r="K53" s="30" t="inlineStr">
+        <is>
+          <t>245-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="49" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B54" s="36" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C54" s="36" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D54" s="38" t="n">
+        <v>56</v>
+      </c>
+      <c r="E54" s="38" t="n">
+        <v>56</v>
+      </c>
+      <c r="F54" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="49" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H54" s="38" t="n">
+        <v>32</v>
+      </c>
+      <c r="I54" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="36" t="inlineStr">
+        <is>
+          <t>32-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="47" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B55" s="30" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C55" s="30" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D55" s="32" t="n">
+        <v>56</v>
+      </c>
+      <c r="E55" s="32" t="n">
+        <v>56</v>
+      </c>
+      <c r="F55" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="47" t="n">
+        <v>46213</v>
+      </c>
+      <c r="H55" s="32" t="n">
+        <v>95</v>
+      </c>
+      <c r="I55" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="30" t="inlineStr">
+        <is>
+          <t>95-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="49" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B56" s="36" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C56" s="36" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D56" s="38" t="n">
+        <v>56</v>
+      </c>
+      <c r="E56" s="38" t="n">
+        <v>56</v>
+      </c>
+      <c r="F56" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="49" t="n">
+        <v>46308</v>
+      </c>
+      <c r="H56" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="I56" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="36" t="inlineStr">
+        <is>
+          <t>2-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="47" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B57" s="30" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C57" s="30" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D57" s="32" t="n">
+        <v>56</v>
+      </c>
+      <c r="E57" s="32" t="n">
+        <v>56</v>
+      </c>
+      <c r="F57" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="47" t="n">
+        <v>46310</v>
+      </c>
+      <c r="H57" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="49" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B58" s="36" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C58" s="36" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D58" s="38" t="n">
+        <v>56</v>
+      </c>
+      <c r="E58" s="38" t="n">
+        <v>56</v>
+      </c>
+      <c r="F58" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="49" t="n">
+        <v>46311</v>
+      </c>
+      <c r="H58" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="47" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B59" s="30" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C59" s="30" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D59" s="32" t="n">
+        <v>56</v>
+      </c>
+      <c r="E59" s="32" t="n">
+        <v>56</v>
+      </c>
+      <c r="F59" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="47" t="n">
+        <v>46312</v>
+      </c>
+      <c r="H59" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="49" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B60" s="36" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C60" s="36" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D60" s="38" t="n">
+        <v>56</v>
+      </c>
+      <c r="E60" s="38" t="n">
+        <v>56</v>
+      </c>
+      <c r="F60" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="49" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H60" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="47" t="n">
+        <v>45936</v>
+      </c>
+      <c r="B61" s="30" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C61" s="30" t="inlineStr">
+        <is>
+          <t>20' x 75'</t>
+        </is>
+      </c>
+      <c r="D61" s="32" t="n">
+        <v>13</v>
+      </c>
+      <c r="E61" s="32" t="n">
+        <v>25</v>
+      </c>
+      <c r="F61" s="34" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G61" s="47" t="n"/>
+      <c r="H61" s="32" t="n"/>
+      <c r="I61" s="32" t="n"/>
+      <c r="J61" s="51" t="n"/>
+      <c r="K61" s="30" t="inlineStr">
+        <is>
+          <t>Baseline: no earlier observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="49" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B62" s="36" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C62" s="36" t="inlineStr">
+        <is>
+          <t>20' x 75'</t>
+        </is>
+      </c>
+      <c r="D62" s="38" t="n">
+        <v>24</v>
+      </c>
+      <c r="E62" s="38" t="n">
+        <v>25</v>
+      </c>
+      <c r="F62" s="40" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G62" s="49" t="n">
+        <v>45936</v>
+      </c>
+      <c r="H62" s="38" t="n">
+        <v>245</v>
+      </c>
+      <c r="I62" s="50" t="n">
+        <v>11</v>
+      </c>
+      <c r="J62" s="41" t="n">
+        <v>43.99999999999999</v>
+      </c>
+      <c r="K62" s="36" t="inlineStr">
+        <is>
+          <t>245-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="47" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B63" s="30" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C63" s="30" t="inlineStr">
+        <is>
+          <t>20' x 75'</t>
+        </is>
+      </c>
+      <c r="D63" s="32" t="n">
+        <v>24</v>
+      </c>
+      <c r="E63" s="32" t="n">
+        <v>25</v>
+      </c>
+      <c r="F63" s="34" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G63" s="47" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H63" s="32" t="n">
+        <v>32</v>
+      </c>
+      <c r="I63" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="30" t="inlineStr">
+        <is>
+          <t>32-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="49" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B64" s="36" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C64" s="36" t="inlineStr">
+        <is>
+          <t>20' x 75'</t>
+        </is>
+      </c>
+      <c r="D64" s="38" t="n">
+        <v>24</v>
+      </c>
+      <c r="E64" s="38" t="n">
+        <v>25</v>
+      </c>
+      <c r="F64" s="40" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G64" s="49" t="n">
+        <v>46213</v>
+      </c>
+      <c r="H64" s="38" t="n">
+        <v>95</v>
+      </c>
+      <c r="I64" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="36" t="inlineStr">
+        <is>
+          <t>95-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="47" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B65" s="30" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C65" s="30" t="inlineStr">
+        <is>
+          <t>20' x 75'</t>
+        </is>
+      </c>
+      <c r="D65" s="32" t="n">
+        <v>24</v>
+      </c>
+      <c r="E65" s="32" t="n">
+        <v>25</v>
+      </c>
+      <c r="F65" s="34" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G65" s="47" t="n">
+        <v>46308</v>
+      </c>
+      <c r="H65" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I65" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="30" t="inlineStr">
+        <is>
+          <t>2-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="49" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B66" s="36" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C66" s="36" t="inlineStr">
+        <is>
+          <t>20' x 75'</t>
+        </is>
+      </c>
+      <c r="D66" s="38" t="n">
+        <v>24</v>
+      </c>
+      <c r="E66" s="38" t="n">
+        <v>25</v>
+      </c>
+      <c r="F66" s="40" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G66" s="49" t="n">
+        <v>46310</v>
+      </c>
+      <c r="H66" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="47" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B67" s="30" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C67" s="30" t="inlineStr">
+        <is>
+          <t>20' x 75'</t>
+        </is>
+      </c>
+      <c r="D67" s="32" t="n">
+        <v>24</v>
+      </c>
+      <c r="E67" s="32" t="n">
+        <v>25</v>
+      </c>
+      <c r="F67" s="34" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G67" s="47" t="n">
+        <v>46311</v>
+      </c>
+      <c r="H67" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="49" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B68" s="36" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C68" s="36" t="inlineStr">
+        <is>
+          <t>20' x 75'</t>
+        </is>
+      </c>
+      <c r="D68" s="38" t="n">
+        <v>24</v>
+      </c>
+      <c r="E68" s="38" t="n">
+        <v>25</v>
+      </c>
+      <c r="F68" s="40" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G68" s="49" t="n">
+        <v>46312</v>
+      </c>
+      <c r="H68" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="47" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B69" s="30" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C69" s="30" t="inlineStr">
+        <is>
+          <t>20' x 75'</t>
+        </is>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>24</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>25</v>
+      </c>
+      <c r="F69" s="34" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G69" s="47" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H69" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="49" t="n">
+        <v>45936</v>
+      </c>
+      <c r="B70" s="36" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C70" s="36" t="inlineStr">
+        <is>
+          <t>20' x 80'</t>
+        </is>
+      </c>
+      <c r="D70" s="38" t="n">
+        <v>3</v>
+      </c>
+      <c r="E70" s="38" t="n">
+        <v>25</v>
+      </c>
+      <c r="F70" s="40" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G70" s="49" t="n"/>
+      <c r="H70" s="38" t="n"/>
+      <c r="I70" s="38" t="n"/>
+      <c r="J70" s="52" t="n"/>
+      <c r="K70" s="36" t="inlineStr">
+        <is>
+          <t>Baseline: no earlier observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="47" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B71" s="30" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C71" s="30" t="inlineStr">
+        <is>
+          <t>20' x 80'</t>
+        </is>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>25</v>
+      </c>
+      <c r="F71" s="34" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G71" s="47" t="n">
+        <v>45936</v>
+      </c>
+      <c r="H71" s="32" t="n">
+        <v>245</v>
+      </c>
+      <c r="I71" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="J71" s="35" t="n">
+        <v>16</v>
+      </c>
+      <c r="K71" s="30" t="inlineStr">
+        <is>
+          <t>245-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="49" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B72" s="36" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C72" s="36" t="inlineStr">
+        <is>
+          <t>20' x 80'</t>
+        </is>
+      </c>
+      <c r="D72" s="38" t="n">
+        <v>8</v>
+      </c>
+      <c r="E72" s="38" t="n">
+        <v>25</v>
+      </c>
+      <c r="F72" s="40" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G72" s="49" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H72" s="38" t="n">
+        <v>32</v>
+      </c>
+      <c r="I72" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" s="41" t="n">
+        <v>3.999999999999998</v>
+      </c>
+      <c r="K72" s="36" t="inlineStr">
+        <is>
+          <t>32-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="47" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B73" s="30" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C73" s="30" t="inlineStr">
+        <is>
+          <t>20' x 80'</t>
+        </is>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E73" s="32" t="n">
+        <v>25</v>
+      </c>
+      <c r="F73" s="34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G73" s="47" t="n">
+        <v>46213</v>
+      </c>
+      <c r="H73" s="32" t="n">
+        <v>95</v>
+      </c>
+      <c r="I73" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="J73" s="35" t="n">
+        <v>8.000000000000002</v>
+      </c>
+      <c r="K73" s="30" t="inlineStr">
+        <is>
+          <t>95-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="49" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B74" s="36" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C74" s="36" t="inlineStr">
+        <is>
+          <t>20' x 80'</t>
+        </is>
+      </c>
+      <c r="D74" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E74" s="38" t="n">
+        <v>25</v>
+      </c>
+      <c r="F74" s="40" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G74" s="49" t="n">
+        <v>46308</v>
+      </c>
+      <c r="H74" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="I74" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="36" t="inlineStr">
+        <is>
+          <t>2-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="47" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B75" s="30" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C75" s="30" t="inlineStr">
+        <is>
+          <t>20' x 80'</t>
+        </is>
+      </c>
+      <c r="D75" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" s="32" t="n">
+        <v>25</v>
+      </c>
+      <c r="F75" s="34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G75" s="47" t="n">
+        <v>46310</v>
+      </c>
+      <c r="H75" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="49" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B76" s="36" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C76" s="36" t="inlineStr">
+        <is>
+          <t>20' x 80'</t>
+        </is>
+      </c>
+      <c r="D76" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" s="38" t="n">
+        <v>25</v>
+      </c>
+      <c r="F76" s="40" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G76" s="49" t="n">
+        <v>46311</v>
+      </c>
+      <c r="H76" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="47" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B77" s="30" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C77" s="30" t="inlineStr">
+        <is>
+          <t>20' x 80'</t>
+        </is>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>25</v>
+      </c>
+      <c r="F77" s="34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G77" s="47" t="n">
+        <v>46312</v>
+      </c>
+      <c r="H77" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I77" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="49" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B78" s="36" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C78" s="36" t="inlineStr">
+        <is>
+          <t>20' x 80'</t>
+        </is>
+      </c>
+      <c r="D78" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E78" s="38" t="n">
+        <v>25</v>
+      </c>
+      <c r="F78" s="40" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G78" s="49" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H78" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="47" t="n">
+        <v>45936</v>
+      </c>
+      <c r="B79" s="30" t="inlineStr">
+        <is>
+          <t>Chorus @Setia Ecohill 2</t>
+        </is>
+      </c>
+      <c r="C79" s="30" t="inlineStr">
+        <is>
+          <t>22' x 70'</t>
+        </is>
+      </c>
+      <c r="D79" s="32" t="n">
+        <v>87</v>
+      </c>
+      <c r="E79" s="32" t="n">
+        <v>99</v>
+      </c>
+      <c r="F79" s="34" t="n">
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="G79" s="47" t="n"/>
+      <c r="H79" s="32" t="n"/>
+      <c r="I79" s="32" t="n"/>
+      <c r="J79" s="51" t="n"/>
+      <c r="K79" s="30" t="inlineStr">
+        <is>
+          <t>Baseline: no earlier observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="49" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B80" s="36" t="inlineStr">
+        <is>
+          <t>Chorus @Setia Ecohill 2</t>
+        </is>
+      </c>
+      <c r="C80" s="36" t="inlineStr">
+        <is>
+          <t>22' x 70'</t>
+        </is>
+      </c>
+      <c r="D80" s="38" t="n">
+        <v>77</v>
+      </c>
+      <c r="E80" s="38" t="n">
+        <v>99</v>
+      </c>
+      <c r="F80" s="40" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="G80" s="49" t="n">
+        <v>45936</v>
+      </c>
+      <c r="H80" s="38" t="n">
+        <v>245</v>
+      </c>
+      <c r="I80" s="55" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J80" s="56" t="n">
+        <v>-10.1010101010101</v>
+      </c>
+      <c r="K80" s="36" t="inlineStr">
+        <is>
+          <t>245-day gap; change is not daily movement; Signed count decreased; verify source/status correction</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="47" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B81" s="30" t="inlineStr">
+        <is>
+          <t>Chorus @Setia Ecohill 2</t>
+        </is>
+      </c>
+      <c r="C81" s="30" t="inlineStr">
+        <is>
+          <t>22' x 70'</t>
+        </is>
+      </c>
+      <c r="D81" s="32" t="n">
+        <v>77</v>
+      </c>
+      <c r="E81" s="32" t="n">
+        <v>99</v>
+      </c>
+      <c r="F81" s="34" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="G81" s="47" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H81" s="32" t="n">
+        <v>32</v>
+      </c>
+      <c r="I81" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="30" t="inlineStr">
+        <is>
+          <t>32-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="49" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B82" s="36" t="inlineStr">
+        <is>
+          <t>Chorus @Setia Ecohill 2</t>
+        </is>
+      </c>
+      <c r="C82" s="36" t="inlineStr">
+        <is>
+          <t>22' x 70'</t>
+        </is>
+      </c>
+      <c r="D82" s="38" t="n">
+        <v>77</v>
+      </c>
+      <c r="E82" s="38" t="n">
+        <v>99</v>
+      </c>
+      <c r="F82" s="40" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="G82" s="49" t="n">
+        <v>46213</v>
+      </c>
+      <c r="H82" s="38" t="n">
+        <v>95</v>
+      </c>
+      <c r="I82" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" s="36" t="inlineStr">
+        <is>
+          <t>95-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="47" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B83" s="30" t="inlineStr">
+        <is>
+          <t>Chorus @Setia Ecohill 2</t>
+        </is>
+      </c>
+      <c r="C83" s="30" t="inlineStr">
+        <is>
+          <t>22' x 70'</t>
+        </is>
+      </c>
+      <c r="D83" s="32" t="n">
+        <v>77</v>
+      </c>
+      <c r="E83" s="32" t="n">
+        <v>99</v>
+      </c>
+      <c r="F83" s="34" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="G83" s="47" t="n">
+        <v>46308</v>
+      </c>
+      <c r="H83" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I83" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" s="30" t="inlineStr">
+        <is>
+          <t>2-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="49" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B84" s="36" t="inlineStr">
+        <is>
+          <t>Chorus @Setia Ecohill 2</t>
+        </is>
+      </c>
+      <c r="C84" s="36" t="inlineStr">
+        <is>
+          <t>22' x 70'</t>
+        </is>
+      </c>
+      <c r="D84" s="38" t="n">
+        <v>77</v>
+      </c>
+      <c r="E84" s="38" t="n">
+        <v>99</v>
+      </c>
+      <c r="F84" s="40" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="G84" s="49" t="n">
+        <v>46310</v>
+      </c>
+      <c r="H84" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I84" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="47" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B85" s="30" t="inlineStr">
+        <is>
+          <t>Chorus @Setia Ecohill 2</t>
+        </is>
+      </c>
+      <c r="C85" s="30" t="inlineStr">
+        <is>
+          <t>22' x 70'</t>
+        </is>
+      </c>
+      <c r="D85" s="32" t="n">
+        <v>77</v>
+      </c>
+      <c r="E85" s="32" t="n">
+        <v>99</v>
+      </c>
+      <c r="F85" s="34" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="G85" s="47" t="n">
+        <v>46311</v>
+      </c>
+      <c r="H85" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="49" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B86" s="36" t="inlineStr">
+        <is>
+          <t>Chorus @Setia Ecohill 2</t>
+        </is>
+      </c>
+      <c r="C86" s="36" t="inlineStr">
+        <is>
+          <t>22' x 70'</t>
+        </is>
+      </c>
+      <c r="D86" s="38" t="n">
+        <v>77</v>
+      </c>
+      <c r="E86" s="38" t="n">
+        <v>99</v>
+      </c>
+      <c r="F86" s="40" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="G86" s="49" t="n">
+        <v>46312</v>
+      </c>
+      <c r="H86" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I86" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="47" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B87" s="30" t="inlineStr">
+        <is>
+          <t>Chorus @Setia Ecohill 2</t>
+        </is>
+      </c>
+      <c r="C87" s="30" t="inlineStr">
+        <is>
+          <t>22' x 70'</t>
+        </is>
+      </c>
+      <c r="D87" s="32" t="n">
+        <v>77</v>
+      </c>
+      <c r="E87" s="32" t="n">
+        <v>99</v>
+      </c>
+      <c r="F87" s="34" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="G87" s="47" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H87" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I87" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="49" t="n">
+        <v>45715</v>
+      </c>
+      <c r="B88" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C88" s="36" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D88" s="38" t="n">
+        <v>101</v>
+      </c>
+      <c r="E88" s="38" t="n">
+        <v>111</v>
+      </c>
+      <c r="F88" s="40" t="n">
+        <v>0.9099099099099099</v>
+      </c>
+      <c r="G88" s="49" t="n"/>
+      <c r="H88" s="38" t="n"/>
+      <c r="I88" s="38" t="n"/>
+      <c r="J88" s="52" t="n"/>
+      <c r="K88" s="36" t="inlineStr">
+        <is>
+          <t>Baseline: no earlier observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="47" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B89" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C89" s="30" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D89" s="32" t="n">
+        <v>57</v>
+      </c>
+      <c r="E89" s="32" t="n">
+        <v>111</v>
+      </c>
+      <c r="F89" s="34" t="n">
+        <v>0.5135135135135135</v>
+      </c>
+      <c r="G89" s="47" t="n">
+        <v>45715</v>
+      </c>
+      <c r="H89" s="32" t="n">
+        <v>179</v>
+      </c>
+      <c r="I89" s="53" t="n">
+        <v>-44</v>
+      </c>
+      <c r="J89" s="54" t="n">
+        <v>-39.63963963963965</v>
+      </c>
+      <c r="K89" s="30" t="inlineStr">
+        <is>
+          <t>179-day gap; change is not daily movement; Signed count decreased; verify source/status correction</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="49" t="n">
+        <v>45936</v>
+      </c>
+      <c r="B90" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C90" s="36" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D90" s="38" t="n">
+        <v>62</v>
+      </c>
+      <c r="E90" s="38" t="n">
+        <v>111</v>
+      </c>
+      <c r="F90" s="40" t="n">
+        <v>0.5585585585585585</v>
+      </c>
+      <c r="G90" s="49" t="n">
+        <v>45894</v>
+      </c>
+      <c r="H90" s="38" t="n">
+        <v>42</v>
+      </c>
+      <c r="I90" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="J90" s="41" t="n">
+        <v>4.504504504504503</v>
+      </c>
+      <c r="K90" s="36" t="inlineStr">
+        <is>
+          <t>42-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="47" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B91" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C91" s="30" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D91" s="32" t="n">
+        <v>102</v>
+      </c>
+      <c r="E91" s="32" t="n">
+        <v>111</v>
+      </c>
+      <c r="F91" s="34" t="n">
+        <v>0.918918918918919</v>
+      </c>
+      <c r="G91" s="47" t="n">
+        <v>45936</v>
+      </c>
+      <c r="H91" s="32" t="n">
+        <v>245</v>
+      </c>
+      <c r="I91" s="48" t="n">
+        <v>40</v>
+      </c>
+      <c r="J91" s="35" t="n">
+        <v>36.03603603603604</v>
+      </c>
+      <c r="K91" s="30" t="inlineStr">
+        <is>
+          <t>245-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="49" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B92" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C92" s="36" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D92" s="38" t="n">
+        <v>102</v>
+      </c>
+      <c r="E92" s="38" t="n">
+        <v>111</v>
+      </c>
+      <c r="F92" s="40" t="n">
+        <v>0.918918918918919</v>
+      </c>
+      <c r="G92" s="49" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H92" s="38" t="n">
+        <v>32</v>
+      </c>
+      <c r="I92" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" s="36" t="inlineStr">
+        <is>
+          <t>32-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="47" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B93" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C93" s="30" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D93" s="32" t="n">
+        <v>111</v>
+      </c>
+      <c r="E93" s="32" t="n">
+        <v>111</v>
+      </c>
+      <c r="F93" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="47" t="n">
+        <v>46213</v>
+      </c>
+      <c r="H93" s="32" t="n">
+        <v>95</v>
+      </c>
+      <c r="I93" s="48" t="n">
+        <v>9</v>
+      </c>
+      <c r="J93" s="35" t="n">
+        <v>8.108108108108103</v>
+      </c>
+      <c r="K93" s="30" t="inlineStr">
+        <is>
+          <t>95-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="49" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B94" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C94" s="36" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D94" s="38" t="n">
+        <v>111</v>
+      </c>
+      <c r="E94" s="38" t="n">
+        <v>111</v>
+      </c>
+      <c r="F94" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="49" t="n">
+        <v>46308</v>
+      </c>
+      <c r="H94" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="I94" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="36" t="inlineStr">
+        <is>
+          <t>2-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="47" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B95" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C95" s="30" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D95" s="32" t="n">
+        <v>111</v>
+      </c>
+      <c r="E95" s="32" t="n">
+        <v>111</v>
+      </c>
+      <c r="F95" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="47" t="n">
+        <v>46310</v>
+      </c>
+      <c r="H95" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I95" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="49" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B96" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C96" s="36" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D96" s="38" t="n">
+        <v>111</v>
+      </c>
+      <c r="E96" s="38" t="n">
+        <v>111</v>
+      </c>
+      <c r="F96" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="49" t="n">
+        <v>46311</v>
+      </c>
+      <c r="H96" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I96" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="47" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B97" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C97" s="30" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D97" s="32" t="n">
+        <v>111</v>
+      </c>
+      <c r="E97" s="32" t="n">
+        <v>111</v>
+      </c>
+      <c r="F97" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="47" t="n">
+        <v>46312</v>
+      </c>
+      <c r="H97" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I97" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="49" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B98" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C98" s="36" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D98" s="38" t="n">
+        <v>111</v>
+      </c>
+      <c r="E98" s="38" t="n">
+        <v>111</v>
+      </c>
+      <c r="F98" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" s="49" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H98" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I98" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="47" t="n">
+        <v>45715</v>
+      </c>
+      <c r="B99" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C99" s="30" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D99" s="32" t="n">
+        <v>131</v>
+      </c>
+      <c r="E99" s="32" t="n">
+        <v>138</v>
+      </c>
+      <c r="F99" s="34" t="n">
+        <v>0.9492753623188406</v>
+      </c>
+      <c r="G99" s="47" t="n"/>
+      <c r="H99" s="32" t="n"/>
+      <c r="I99" s="32" t="n"/>
+      <c r="J99" s="51" t="n"/>
+      <c r="K99" s="30" t="inlineStr">
+        <is>
+          <t>Baseline: no earlier observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="49" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B100" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C100" s="36" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D100" s="38" t="n">
+        <v>93</v>
+      </c>
+      <c r="E100" s="38" t="n">
+        <v>138</v>
+      </c>
+      <c r="F100" s="40" t="n">
+        <v>0.6739130434782609</v>
+      </c>
+      <c r="G100" s="49" t="n">
+        <v>45715</v>
+      </c>
+      <c r="H100" s="38" t="n">
+        <v>179</v>
+      </c>
+      <c r="I100" s="55" t="n">
+        <v>-38</v>
+      </c>
+      <c r="J100" s="56" t="n">
+        <v>-27.53623188405797</v>
+      </c>
+      <c r="K100" s="36" t="inlineStr">
+        <is>
+          <t>179-day gap; change is not daily movement; Signed count decreased; verify source/status correction</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="47" t="n">
+        <v>45936</v>
+      </c>
+      <c r="B101" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C101" s="30" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D101" s="32" t="n">
+        <v>98</v>
+      </c>
+      <c r="E101" s="32" t="n">
+        <v>138</v>
+      </c>
+      <c r="F101" s="34" t="n">
+        <v>0.7101449275362319</v>
+      </c>
+      <c r="G101" s="47" t="n">
+        <v>45894</v>
+      </c>
+      <c r="H101" s="32" t="n">
+        <v>42</v>
+      </c>
+      <c r="I101" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="J101" s="35" t="n">
+        <v>3.623188405797106</v>
+      </c>
+      <c r="K101" s="30" t="inlineStr">
+        <is>
+          <t>42-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="49" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B102" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C102" s="36" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D102" s="38" t="n">
+        <v>131</v>
+      </c>
+      <c r="E102" s="38" t="n">
+        <v>138</v>
+      </c>
+      <c r="F102" s="40" t="n">
+        <v>0.9492753623188406</v>
+      </c>
+      <c r="G102" s="49" t="n">
+        <v>45936</v>
+      </c>
+      <c r="H102" s="38" t="n">
+        <v>245</v>
+      </c>
+      <c r="I102" s="50" t="n">
+        <v>33</v>
+      </c>
+      <c r="J102" s="41" t="n">
+        <v>23.91304347826086</v>
+      </c>
+      <c r="K102" s="36" t="inlineStr">
+        <is>
+          <t>245-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="47" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B103" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C103" s="30" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D103" s="32" t="n">
+        <v>131</v>
+      </c>
+      <c r="E103" s="32" t="n">
+        <v>138</v>
+      </c>
+      <c r="F103" s="34" t="n">
+        <v>0.9492753623188406</v>
+      </c>
+      <c r="G103" s="47" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H103" s="32" t="n">
+        <v>32</v>
+      </c>
+      <c r="I103" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" s="30" t="inlineStr">
+        <is>
+          <t>32-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="49" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B104" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C104" s="36" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D104" s="38" t="n">
+        <v>134</v>
+      </c>
+      <c r="E104" s="38" t="n">
+        <v>138</v>
+      </c>
+      <c r="F104" s="40" t="n">
+        <v>0.9710144927536232</v>
+      </c>
+      <c r="G104" s="49" t="n">
+        <v>46213</v>
+      </c>
+      <c r="H104" s="38" t="n">
+        <v>95</v>
+      </c>
+      <c r="I104" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="J104" s="41" t="n">
+        <v>2.173913043478259</v>
+      </c>
+      <c r="K104" s="36" t="inlineStr">
+        <is>
+          <t>95-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="47" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B105" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C105" s="30" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D105" s="32" t="n">
+        <v>134</v>
+      </c>
+      <c r="E105" s="32" t="n">
+        <v>138</v>
+      </c>
+      <c r="F105" s="34" t="n">
+        <v>0.9710144927536232</v>
+      </c>
+      <c r="G105" s="47" t="n">
+        <v>46308</v>
+      </c>
+      <c r="H105" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I105" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" s="30" t="inlineStr">
+        <is>
+          <t>2-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="49" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B106" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C106" s="36" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D106" s="38" t="n">
+        <v>134</v>
+      </c>
+      <c r="E106" s="38" t="n">
+        <v>138</v>
+      </c>
+      <c r="F106" s="40" t="n">
+        <v>0.9710144927536232</v>
+      </c>
+      <c r="G106" s="49" t="n">
+        <v>46310</v>
+      </c>
+      <c r="H106" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I106" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="47" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B107" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C107" s="30" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D107" s="32" t="n">
+        <v>134</v>
+      </c>
+      <c r="E107" s="32" t="n">
+        <v>138</v>
+      </c>
+      <c r="F107" s="34" t="n">
+        <v>0.9710144927536232</v>
+      </c>
+      <c r="G107" s="47" t="n">
+        <v>46311</v>
+      </c>
+      <c r="H107" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I107" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="49" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B108" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C108" s="36" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D108" s="38" t="n">
+        <v>134</v>
+      </c>
+      <c r="E108" s="38" t="n">
+        <v>138</v>
+      </c>
+      <c r="F108" s="40" t="n">
+        <v>0.9710144927536232</v>
+      </c>
+      <c r="G108" s="49" t="n">
+        <v>46312</v>
+      </c>
+      <c r="H108" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I108" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="47" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B109" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C109" s="30" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D109" s="32" t="n">
+        <v>134</v>
+      </c>
+      <c r="E109" s="32" t="n">
+        <v>138</v>
+      </c>
+      <c r="F109" s="34" t="n">
+        <v>0.9710144927536232</v>
+      </c>
+      <c r="G109" s="47" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H109" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I109" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="49" t="n">
+        <v>45715</v>
+      </c>
+      <c r="B110" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C110" s="36" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D110" s="38" t="n">
+        <v>78</v>
+      </c>
+      <c r="E110" s="38" t="n">
+        <v>81</v>
+      </c>
+      <c r="F110" s="40" t="n">
+        <v>0.9629629629629629</v>
+      </c>
+      <c r="G110" s="49" t="n"/>
+      <c r="H110" s="38" t="n"/>
+      <c r="I110" s="38" t="n"/>
+      <c r="J110" s="52" t="n"/>
+      <c r="K110" s="36" t="inlineStr">
+        <is>
+          <t>Baseline: no earlier observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="47" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B111" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C111" s="30" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D111" s="32" t="n">
+        <v>44</v>
+      </c>
+      <c r="E111" s="32" t="n">
+        <v>81</v>
+      </c>
+      <c r="F111" s="34" t="n">
+        <v>0.5432098765432098</v>
+      </c>
+      <c r="G111" s="47" t="n">
+        <v>45715</v>
+      </c>
+      <c r="H111" s="32" t="n">
+        <v>179</v>
+      </c>
+      <c r="I111" s="53" t="n">
+        <v>-34</v>
+      </c>
+      <c r="J111" s="54" t="n">
+        <v>-41.9753086419753</v>
+      </c>
+      <c r="K111" s="30" t="inlineStr">
+        <is>
+          <t>179-day gap; change is not daily movement; Signed count decreased; verify source/status correction</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="49" t="n">
+        <v>45936</v>
+      </c>
+      <c r="B112" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C112" s="36" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D112" s="38" t="n">
+        <v>52</v>
+      </c>
+      <c r="E112" s="38" t="n">
+        <v>81</v>
+      </c>
+      <c r="F112" s="40" t="n">
+        <v>0.6419753086419753</v>
+      </c>
+      <c r="G112" s="49" t="n">
+        <v>45894</v>
+      </c>
+      <c r="H112" s="38" t="n">
+        <v>42</v>
+      </c>
+      <c r="I112" s="50" t="n">
+        <v>8</v>
+      </c>
+      <c r="J112" s="41" t="n">
+        <v>9.876543209876543</v>
+      </c>
+      <c r="K112" s="36" t="inlineStr">
+        <is>
+          <t>42-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="47" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B113" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C113" s="30" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D113" s="32" t="n">
+        <v>78</v>
+      </c>
+      <c r="E113" s="32" t="n">
+        <v>81</v>
+      </c>
+      <c r="F113" s="34" t="n">
+        <v>0.9629629629629629</v>
+      </c>
+      <c r="G113" s="47" t="n">
+        <v>45936</v>
+      </c>
+      <c r="H113" s="32" t="n">
+        <v>245</v>
+      </c>
+      <c r="I113" s="48" t="n">
+        <v>26</v>
+      </c>
+      <c r="J113" s="35" t="n">
+        <v>32.09876543209877</v>
+      </c>
+      <c r="K113" s="30" t="inlineStr">
+        <is>
+          <t>245-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="49" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B114" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C114" s="36" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D114" s="38" t="n">
+        <v>78</v>
+      </c>
+      <c r="E114" s="38" t="n">
+        <v>81</v>
+      </c>
+      <c r="F114" s="40" t="n">
+        <v>0.9629629629629629</v>
+      </c>
+      <c r="G114" s="49" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H114" s="38" t="n">
+        <v>32</v>
+      </c>
+      <c r="I114" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" s="36" t="inlineStr">
+        <is>
+          <t>32-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="47" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B115" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C115" s="30" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D115" s="32" t="n">
+        <v>79</v>
+      </c>
+      <c r="E115" s="32" t="n">
+        <v>81</v>
+      </c>
+      <c r="F115" s="34" t="n">
+        <v>0.9753086419753086</v>
+      </c>
+      <c r="G115" s="47" t="n">
+        <v>46213</v>
+      </c>
+      <c r="H115" s="32" t="n">
+        <v>95</v>
+      </c>
+      <c r="I115" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J115" s="35" t="n">
+        <v>1.234567901234573</v>
+      </c>
+      <c r="K115" s="30" t="inlineStr">
+        <is>
+          <t>95-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="49" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B116" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C116" s="36" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D116" s="38" t="n">
+        <v>79</v>
+      </c>
+      <c r="E116" s="38" t="n">
+        <v>81</v>
+      </c>
+      <c r="F116" s="40" t="n">
+        <v>0.9753086419753086</v>
+      </c>
+      <c r="G116" s="49" t="n">
+        <v>46308</v>
+      </c>
+      <c r="H116" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="I116" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" s="36" t="inlineStr">
+        <is>
+          <t>2-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="47" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B117" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C117" s="30" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D117" s="32" t="n">
+        <v>79</v>
+      </c>
+      <c r="E117" s="32" t="n">
+        <v>81</v>
+      </c>
+      <c r="F117" s="34" t="n">
+        <v>0.9753086419753086</v>
+      </c>
+      <c r="G117" s="47" t="n">
+        <v>46310</v>
+      </c>
+      <c r="H117" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I117" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="49" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B118" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C118" s="36" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D118" s="38" t="n">
+        <v>79</v>
+      </c>
+      <c r="E118" s="38" t="n">
+        <v>81</v>
+      </c>
+      <c r="F118" s="40" t="n">
+        <v>0.9753086419753086</v>
+      </c>
+      <c r="G118" s="49" t="n">
+        <v>46311</v>
+      </c>
+      <c r="H118" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I118" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="47" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B119" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C119" s="30" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D119" s="32" t="n">
+        <v>79</v>
+      </c>
+      <c r="E119" s="32" t="n">
+        <v>81</v>
+      </c>
+      <c r="F119" s="34" t="n">
+        <v>0.9753086419753086</v>
+      </c>
+      <c r="G119" s="47" t="n">
+        <v>46312</v>
+      </c>
+      <c r="H119" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I119" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="49" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B120" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C120" s="36" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D120" s="38" t="n">
+        <v>79</v>
+      </c>
+      <c r="E120" s="38" t="n">
+        <v>81</v>
+      </c>
+      <c r="F120" s="40" t="n">
+        <v>0.9753086419753086</v>
+      </c>
+      <c r="G120" s="49" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H120" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I120" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="47" t="n">
+        <v>45715</v>
+      </c>
+      <c r="B121" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="C121" s="30" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D121" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E121" s="32" t="n">
+        <v>26</v>
+      </c>
+      <c r="F121" s="34" t="n">
+        <v>0.1153846153846154</v>
+      </c>
+      <c r="G121" s="47" t="n"/>
+      <c r="H121" s="32" t="n"/>
+      <c r="I121" s="32" t="n"/>
+      <c r="J121" s="51" t="n"/>
+      <c r="K121" s="30" t="inlineStr">
+        <is>
+          <t>Baseline: no earlier observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="49" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B122" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="C122" s="36" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D122" s="38" t="n">
+        <v>17</v>
+      </c>
+      <c r="E122" s="38" t="n">
+        <v>26</v>
+      </c>
+      <c r="F122" s="40" t="n">
+        <v>0.6538461538461539</v>
+      </c>
+      <c r="G122" s="49" t="n">
+        <v>45715</v>
+      </c>
+      <c r="H122" s="38" t="n">
+        <v>466</v>
+      </c>
+      <c r="I122" s="50" t="n">
+        <v>14</v>
+      </c>
+      <c r="J122" s="41" t="n">
+        <v>53.84615384615385</v>
+      </c>
+      <c r="K122" s="36" t="inlineStr">
+        <is>
+          <t>466-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="47" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B123" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="C123" s="30" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D123" s="32" t="n">
+        <v>17</v>
+      </c>
+      <c r="E123" s="32" t="n">
+        <v>26</v>
+      </c>
+      <c r="F123" s="34" t="n">
+        <v>0.6538461538461539</v>
+      </c>
+      <c r="G123" s="47" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H123" s="32" t="n">
+        <v>32</v>
+      </c>
+      <c r="I123" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" s="30" t="inlineStr">
+        <is>
+          <t>32-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="49" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B124" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="C124" s="36" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D124" s="38" t="n">
+        <v>23</v>
+      </c>
+      <c r="E124" s="38" t="n">
+        <v>26</v>
+      </c>
+      <c r="F124" s="40" t="n">
+        <v>0.8846153846153846</v>
+      </c>
+      <c r="G124" s="49" t="n">
+        <v>46213</v>
+      </c>
+      <c r="H124" s="38" t="n">
+        <v>95</v>
+      </c>
+      <c r="I124" s="50" t="n">
+        <v>6</v>
+      </c>
+      <c r="J124" s="41" t="n">
+        <v>23.07692307692307</v>
+      </c>
+      <c r="K124" s="36" t="inlineStr">
+        <is>
+          <t>95-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="47" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B125" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="C125" s="30" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D125" s="32" t="n">
+        <v>23</v>
+      </c>
+      <c r="E125" s="32" t="n">
+        <v>26</v>
+      </c>
+      <c r="F125" s="34" t="n">
+        <v>0.8846153846153846</v>
+      </c>
+      <c r="G125" s="47" t="n">
+        <v>46308</v>
+      </c>
+      <c r="H125" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I125" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" s="30" t="inlineStr">
+        <is>
+          <t>2-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="49" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B126" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="C126" s="36" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D126" s="38" t="n">
+        <v>23</v>
+      </c>
+      <c r="E126" s="38" t="n">
+        <v>26</v>
+      </c>
+      <c r="F126" s="40" t="n">
+        <v>0.8846153846153846</v>
+      </c>
+      <c r="G126" s="49" t="n">
+        <v>46310</v>
+      </c>
+      <c r="H126" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I126" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="47" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B127" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="C127" s="30" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D127" s="32" t="n">
+        <v>23</v>
+      </c>
+      <c r="E127" s="32" t="n">
+        <v>26</v>
+      </c>
+      <c r="F127" s="34" t="n">
+        <v>0.8846153846153846</v>
+      </c>
+      <c r="G127" s="47" t="n">
+        <v>46311</v>
+      </c>
+      <c r="H127" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I127" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="49" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B128" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="C128" s="36" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D128" s="38" t="n">
+        <v>23</v>
+      </c>
+      <c r="E128" s="38" t="n">
+        <v>26</v>
+      </c>
+      <c r="F128" s="40" t="n">
+        <v>0.8846153846153846</v>
+      </c>
+      <c r="G128" s="49" t="n">
+        <v>46312</v>
+      </c>
+      <c r="H128" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I128" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="47" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B129" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="C129" s="30" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D129" s="32" t="n">
+        <v>23</v>
+      </c>
+      <c r="E129" s="32" t="n">
+        <v>26</v>
+      </c>
+      <c r="F129" s="34" t="n">
+        <v>0.8846153846153846</v>
+      </c>
+      <c r="G129" s="47" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H129" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I129" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="49" t="n">
+        <v>45715</v>
+      </c>
+      <c r="B130" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="C130" s="36" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D130" s="38" t="n">
+        <v>77</v>
+      </c>
+      <c r="E130" s="38" t="n">
+        <v>126</v>
+      </c>
+      <c r="F130" s="40" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="G130" s="49" t="n"/>
+      <c r="H130" s="38" t="n"/>
+      <c r="I130" s="38" t="n"/>
+      <c r="J130" s="52" t="n"/>
+      <c r="K130" s="36" t="inlineStr">
+        <is>
+          <t>Baseline: no earlier observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="47" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B131" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="C131" s="30" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D131" s="32" t="n">
+        <v>111</v>
+      </c>
+      <c r="E131" s="32" t="n">
+        <v>126</v>
+      </c>
+      <c r="F131" s="34" t="n">
+        <v>0.8809523809523809</v>
+      </c>
+      <c r="G131" s="47" t="n">
+        <v>45715</v>
+      </c>
+      <c r="H131" s="32" t="n">
+        <v>466</v>
+      </c>
+      <c r="I131" s="48" t="n">
+        <v>34</v>
+      </c>
+      <c r="J131" s="35" t="n">
+        <v>26.98412698412698</v>
+      </c>
+      <c r="K131" s="30" t="inlineStr">
+        <is>
+          <t>466-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="49" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B132" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="C132" s="36" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D132" s="38" t="n">
+        <v>116</v>
+      </c>
+      <c r="E132" s="38" t="n">
+        <v>126</v>
+      </c>
+      <c r="F132" s="40" t="n">
+        <v>0.9206349206349206</v>
+      </c>
+      <c r="G132" s="49" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H132" s="38" t="n">
+        <v>32</v>
+      </c>
+      <c r="I132" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="J132" s="41" t="n">
+        <v>3.968253968253965</v>
+      </c>
+      <c r="K132" s="36" t="inlineStr">
+        <is>
+          <t>32-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="47" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B133" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="C133" s="30" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D133" s="32" t="n">
+        <v>124</v>
+      </c>
+      <c r="E133" s="32" t="n">
+        <v>126</v>
+      </c>
+      <c r="F133" s="34" t="n">
+        <v>0.9841269841269841</v>
+      </c>
+      <c r="G133" s="47" t="n">
+        <v>46213</v>
+      </c>
+      <c r="H133" s="32" t="n">
+        <v>95</v>
+      </c>
+      <c r="I133" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J133" s="35" t="n">
+        <v>6.349206349206349</v>
+      </c>
+      <c r="K133" s="30" t="inlineStr">
+        <is>
+          <t>95-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="49" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B134" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="C134" s="36" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D134" s="38" t="n">
+        <v>124</v>
+      </c>
+      <c r="E134" s="38" t="n">
+        <v>126</v>
+      </c>
+      <c r="F134" s="40" t="n">
+        <v>0.9841269841269841</v>
+      </c>
+      <c r="G134" s="49" t="n">
+        <v>46308</v>
+      </c>
+      <c r="H134" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="I134" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" s="36" t="inlineStr">
+        <is>
+          <t>2-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="47" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B135" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="C135" s="30" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D135" s="32" t="n">
+        <v>124</v>
+      </c>
+      <c r="E135" s="32" t="n">
+        <v>126</v>
+      </c>
+      <c r="F135" s="34" t="n">
+        <v>0.9841269841269841</v>
+      </c>
+      <c r="G135" s="47" t="n">
+        <v>46310</v>
+      </c>
+      <c r="H135" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I135" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="49" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B136" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="C136" s="36" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D136" s="38" t="n">
+        <v>124</v>
+      </c>
+      <c r="E136" s="38" t="n">
+        <v>126</v>
+      </c>
+      <c r="F136" s="40" t="n">
+        <v>0.9841269841269841</v>
+      </c>
+      <c r="G136" s="49" t="n">
+        <v>46311</v>
+      </c>
+      <c r="H136" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I136" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="47" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B137" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="C137" s="30" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D137" s="32" t="n">
+        <v>124</v>
+      </c>
+      <c r="E137" s="32" t="n">
+        <v>126</v>
+      </c>
+      <c r="F137" s="34" t="n">
+        <v>0.9841269841269841</v>
+      </c>
+      <c r="G137" s="47" t="n">
+        <v>46312</v>
+      </c>
+      <c r="H137" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I137" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="49" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B138" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="C138" s="36" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D138" s="38" t="n">
+        <v>124</v>
+      </c>
+      <c r="E138" s="38" t="n">
+        <v>126</v>
+      </c>
+      <c r="F138" s="40" t="n">
+        <v>0.9841269841269841</v>
+      </c>
+      <c r="G138" s="49" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H138" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I138" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="47" t="n">
+        <v>45715</v>
+      </c>
+      <c r="B139" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="C139" s="30" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D139" s="32" t="n">
+        <v>17</v>
+      </c>
+      <c r="E139" s="32" t="n">
+        <v>104</v>
+      </c>
+      <c r="F139" s="34" t="n">
+        <v>0.1634615384615385</v>
+      </c>
+      <c r="G139" s="47" t="n"/>
+      <c r="H139" s="32" t="n"/>
+      <c r="I139" s="32" t="n"/>
+      <c r="J139" s="51" t="n"/>
+      <c r="K139" s="30" t="inlineStr">
+        <is>
+          <t>Baseline: no earlier observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="49" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B140" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="C140" s="36" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D140" s="38" t="n">
+        <v>71</v>
+      </c>
+      <c r="E140" s="38" t="n">
+        <v>104</v>
+      </c>
+      <c r="F140" s="40" t="n">
+        <v>0.6826923076923077</v>
+      </c>
+      <c r="G140" s="49" t="n">
+        <v>45715</v>
+      </c>
+      <c r="H140" s="38" t="n">
+        <v>466</v>
+      </c>
+      <c r="I140" s="50" t="n">
+        <v>54</v>
+      </c>
+      <c r="J140" s="41" t="n">
+        <v>51.92307692307693</v>
+      </c>
+      <c r="K140" s="36" t="inlineStr">
+        <is>
+          <t>466-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="47" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B141" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="C141" s="30" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D141" s="32" t="n">
+        <v>89</v>
+      </c>
+      <c r="E141" s="32" t="n">
+        <v>104</v>
+      </c>
+      <c r="F141" s="34" t="n">
+        <v>0.8557692307692307</v>
+      </c>
+      <c r="G141" s="47" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H141" s="32" t="n">
+        <v>32</v>
+      </c>
+      <c r="I141" s="48" t="n">
+        <v>18</v>
+      </c>
+      <c r="J141" s="35" t="n">
+        <v>17.3076923076923</v>
+      </c>
+      <c r="K141" s="30" t="inlineStr">
+        <is>
+          <t>32-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="49" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B142" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="C142" s="36" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D142" s="38" t="n">
+        <v>98</v>
+      </c>
+      <c r="E142" s="38" t="n">
+        <v>104</v>
+      </c>
+      <c r="F142" s="40" t="n">
+        <v>0.9423076923076923</v>
+      </c>
+      <c r="G142" s="49" t="n">
+        <v>46213</v>
+      </c>
+      <c r="H142" s="38" t="n">
+        <v>95</v>
+      </c>
+      <c r="I142" s="50" t="n">
+        <v>9</v>
+      </c>
+      <c r="J142" s="41" t="n">
+        <v>8.653846153846157</v>
+      </c>
+      <c r="K142" s="36" t="inlineStr">
+        <is>
+          <t>95-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="47" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B143" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="C143" s="30" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D143" s="32" t="n">
+        <v>98</v>
+      </c>
+      <c r="E143" s="32" t="n">
+        <v>104</v>
+      </c>
+      <c r="F143" s="34" t="n">
+        <v>0.9423076923076923</v>
+      </c>
+      <c r="G143" s="47" t="n">
+        <v>46308</v>
+      </c>
+      <c r="H143" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I143" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" s="30" t="inlineStr">
+        <is>
+          <t>2-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="49" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B144" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="C144" s="36" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D144" s="38" t="n">
+        <v>98</v>
+      </c>
+      <c r="E144" s="38" t="n">
+        <v>104</v>
+      </c>
+      <c r="F144" s="40" t="n">
+        <v>0.9423076923076923</v>
+      </c>
+      <c r="G144" s="49" t="n">
+        <v>46310</v>
+      </c>
+      <c r="H144" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I144" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="47" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B145" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="C145" s="30" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D145" s="32" t="n">
+        <v>98</v>
+      </c>
+      <c r="E145" s="32" t="n">
+        <v>104</v>
+      </c>
+      <c r="F145" s="34" t="n">
+        <v>0.9423076923076923</v>
+      </c>
+      <c r="G145" s="47" t="n">
+        <v>46311</v>
+      </c>
+      <c r="H145" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I145" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="49" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B146" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="C146" s="36" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D146" s="38" t="n">
+        <v>98</v>
+      </c>
+      <c r="E146" s="38" t="n">
+        <v>104</v>
+      </c>
+      <c r="F146" s="40" t="n">
+        <v>0.9423076923076923</v>
+      </c>
+      <c r="G146" s="49" t="n">
+        <v>46312</v>
+      </c>
+      <c r="H146" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I146" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="47" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B147" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="C147" s="30" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D147" s="32" t="n">
+        <v>98</v>
+      </c>
+      <c r="E147" s="32" t="n">
+        <v>104</v>
+      </c>
+      <c r="F147" s="34" t="n">
+        <v>0.9423076923076923</v>
+      </c>
+      <c r="G147" s="47" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H147" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I147" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="49" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B148" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 3</t>
+        </is>
+      </c>
+      <c r="C148" s="36" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D148" s="38" t="n">
+        <v>16</v>
+      </c>
+      <c r="E148" s="38" t="n">
+        <v>44</v>
+      </c>
+      <c r="F148" s="40" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="G148" s="49" t="n"/>
+      <c r="H148" s="38" t="n"/>
+      <c r="I148" s="38" t="n"/>
+      <c r="J148" s="52" t="n"/>
+      <c r="K148" s="36" t="inlineStr">
+        <is>
+          <t>Baseline: no earlier observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="47" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B149" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 3</t>
+        </is>
+      </c>
+      <c r="C149" s="30" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D149" s="32" t="n">
+        <v>29</v>
+      </c>
+      <c r="E149" s="32" t="n">
+        <v>44</v>
+      </c>
+      <c r="F149" s="34" t="n">
+        <v>0.6590909090909091</v>
+      </c>
+      <c r="G149" s="47" t="n">
+        <v>46213</v>
+      </c>
+      <c r="H149" s="32" t="n">
+        <v>95</v>
+      </c>
+      <c r="I149" s="48" t="n">
+        <v>13</v>
+      </c>
+      <c r="J149" s="35" t="n">
+        <v>29.54545454545454</v>
+      </c>
+      <c r="K149" s="30" t="inlineStr">
+        <is>
+          <t>95-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="49" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B150" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 3</t>
+        </is>
+      </c>
+      <c r="C150" s="36" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D150" s="38" t="n">
+        <v>29</v>
+      </c>
+      <c r="E150" s="38" t="n">
+        <v>44</v>
+      </c>
+      <c r="F150" s="40" t="n">
+        <v>0.6590909090909091</v>
+      </c>
+      <c r="G150" s="49" t="n">
+        <v>46308</v>
+      </c>
+      <c r="H150" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="I150" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" s="36" t="inlineStr">
+        <is>
+          <t>2-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="47" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B151" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 3</t>
+        </is>
+      </c>
+      <c r="C151" s="30" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D151" s="32" t="n">
+        <v>29</v>
+      </c>
+      <c r="E151" s="32" t="n">
+        <v>44</v>
+      </c>
+      <c r="F151" s="34" t="n">
+        <v>0.6590909090909091</v>
+      </c>
+      <c r="G151" s="47" t="n">
+        <v>46310</v>
+      </c>
+      <c r="H151" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I151" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="49" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B152" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 3</t>
+        </is>
+      </c>
+      <c r="C152" s="36" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D152" s="38" t="n">
+        <v>29</v>
+      </c>
+      <c r="E152" s="38" t="n">
+        <v>44</v>
+      </c>
+      <c r="F152" s="40" t="n">
+        <v>0.6590909090909091</v>
+      </c>
+      <c r="G152" s="49" t="n">
+        <v>46311</v>
+      </c>
+      <c r="H152" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I152" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K152" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="47" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B153" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 3</t>
+        </is>
+      </c>
+      <c r="C153" s="30" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D153" s="32" t="n">
+        <v>29</v>
+      </c>
+      <c r="E153" s="32" t="n">
+        <v>44</v>
+      </c>
+      <c r="F153" s="34" t="n">
+        <v>0.6590909090909091</v>
+      </c>
+      <c r="G153" s="47" t="n">
+        <v>46312</v>
+      </c>
+      <c r="H153" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I153" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="49" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B154" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 3</t>
+        </is>
+      </c>
+      <c r="C154" s="36" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D154" s="38" t="n">
+        <v>29</v>
+      </c>
+      <c r="E154" s="38" t="n">
+        <v>44</v>
+      </c>
+      <c r="F154" s="40" t="n">
+        <v>0.6590909090909091</v>
+      </c>
+      <c r="G154" s="49" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H154" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I154" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K154" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="47" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B155" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 3</t>
+        </is>
+      </c>
+      <c r="C155" s="30" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D155" s="32" t="n">
+        <v>39</v>
+      </c>
+      <c r="E155" s="32" t="n">
+        <v>85</v>
+      </c>
+      <c r="F155" s="34" t="n">
+        <v>0.4588235294117647</v>
+      </c>
+      <c r="G155" s="47" t="n"/>
+      <c r="H155" s="32" t="n"/>
+      <c r="I155" s="32" t="n"/>
+      <c r="J155" s="51" t="n"/>
+      <c r="K155" s="30" t="inlineStr">
+        <is>
+          <t>Baseline: no earlier observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="49" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B156" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 3</t>
+        </is>
+      </c>
+      <c r="C156" s="36" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D156" s="38" t="n">
+        <v>63</v>
+      </c>
+      <c r="E156" s="38" t="n">
+        <v>85</v>
+      </c>
+      <c r="F156" s="40" t="n">
+        <v>0.7411764705882353</v>
+      </c>
+      <c r="G156" s="49" t="n">
+        <v>46213</v>
+      </c>
+      <c r="H156" s="38" t="n">
+        <v>95</v>
+      </c>
+      <c r="I156" s="50" t="n">
+        <v>24</v>
+      </c>
+      <c r="J156" s="41" t="n">
+        <v>28.23529411764707</v>
+      </c>
+      <c r="K156" s="36" t="inlineStr">
+        <is>
+          <t>95-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="47" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B157" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 3</t>
+        </is>
+      </c>
+      <c r="C157" s="30" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D157" s="32" t="n">
+        <v>63</v>
+      </c>
+      <c r="E157" s="32" t="n">
+        <v>85</v>
+      </c>
+      <c r="F157" s="34" t="n">
+        <v>0.7411764705882353</v>
+      </c>
+      <c r="G157" s="47" t="n">
+        <v>46308</v>
+      </c>
+      <c r="H157" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I157" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" s="30" t="inlineStr">
+        <is>
+          <t>2-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="49" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B158" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 3</t>
+        </is>
+      </c>
+      <c r="C158" s="36" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D158" s="38" t="n">
+        <v>63</v>
+      </c>
+      <c r="E158" s="38" t="n">
+        <v>85</v>
+      </c>
+      <c r="F158" s="40" t="n">
+        <v>0.7411764705882353</v>
+      </c>
+      <c r="G158" s="49" t="n">
+        <v>46310</v>
+      </c>
+      <c r="H158" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I158" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="47" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B159" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 3</t>
+        </is>
+      </c>
+      <c r="C159" s="30" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D159" s="32" t="n">
+        <v>65</v>
+      </c>
+      <c r="E159" s="32" t="n">
+        <v>85</v>
+      </c>
+      <c r="F159" s="34" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="G159" s="47" t="n">
+        <v>46311</v>
+      </c>
+      <c r="H159" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I159" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="J159" s="35" t="n">
+        <v>2.35294117647058</v>
+      </c>
+      <c r="K159" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="49" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B160" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 3</t>
+        </is>
+      </c>
+      <c r="C160" s="36" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D160" s="38" t="n">
+        <v>65</v>
+      </c>
+      <c r="E160" s="38" t="n">
+        <v>85</v>
+      </c>
+      <c r="F160" s="40" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="G160" s="49" t="n">
+        <v>46312</v>
+      </c>
+      <c r="H160" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I160" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="47" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B161" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 3</t>
+        </is>
+      </c>
+      <c r="C161" s="30" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D161" s="32" t="n">
+        <v>65</v>
+      </c>
+      <c r="E161" s="32" t="n">
+        <v>85</v>
+      </c>
+      <c r="F161" s="34" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="G161" s="47" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H161" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I161" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="49" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B162" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 3</t>
+        </is>
+      </c>
+      <c r="C162" s="36" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D162" s="38" t="n">
+        <v>11</v>
+      </c>
+      <c r="E162" s="38" t="n">
+        <v>102</v>
+      </c>
+      <c r="F162" s="40" t="n">
+        <v>0.107843137254902</v>
+      </c>
+      <c r="G162" s="49" t="n"/>
+      <c r="H162" s="38" t="n"/>
+      <c r="I162" s="38" t="n"/>
+      <c r="J162" s="52" t="n"/>
+      <c r="K162" s="36" t="inlineStr">
+        <is>
+          <t>Baseline: no earlier observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="47" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B163" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 3</t>
+        </is>
+      </c>
+      <c r="C163" s="30" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D163" s="32" t="n">
+        <v>22</v>
+      </c>
+      <c r="E163" s="32" t="n">
+        <v>102</v>
+      </c>
+      <c r="F163" s="34" t="n">
+        <v>0.2156862745098039</v>
+      </c>
+      <c r="G163" s="47" t="n">
+        <v>46213</v>
+      </c>
+      <c r="H163" s="32" t="n">
+        <v>95</v>
+      </c>
+      <c r="I163" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="J163" s="35" t="n">
+        <v>10.7843137254902</v>
+      </c>
+      <c r="K163" s="30" t="inlineStr">
+        <is>
+          <t>95-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="49" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B164" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 3</t>
+        </is>
+      </c>
+      <c r="C164" s="36" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D164" s="38" t="n">
+        <v>23</v>
+      </c>
+      <c r="E164" s="38" t="n">
+        <v>102</v>
+      </c>
+      <c r="F164" s="40" t="n">
+        <v>0.2254901960784314</v>
+      </c>
+      <c r="G164" s="49" t="n">
+        <v>46308</v>
+      </c>
+      <c r="H164" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="I164" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J164" s="41" t="n">
+        <v>0.9803921568627444</v>
+      </c>
+      <c r="K164" s="36" t="inlineStr">
+        <is>
+          <t>2-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="47" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B165" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 3</t>
+        </is>
+      </c>
+      <c r="C165" s="30" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D165" s="32" t="n">
+        <v>23</v>
+      </c>
+      <c r="E165" s="32" t="n">
+        <v>102</v>
+      </c>
+      <c r="F165" s="34" t="n">
+        <v>0.2254901960784314</v>
+      </c>
+      <c r="G165" s="47" t="n">
+        <v>46310</v>
+      </c>
+      <c r="H165" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I165" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="49" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B166" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 3</t>
+        </is>
+      </c>
+      <c r="C166" s="36" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D166" s="38" t="n">
+        <v>24</v>
+      </c>
+      <c r="E166" s="38" t="n">
+        <v>102</v>
+      </c>
+      <c r="F166" s="40" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="G166" s="49" t="n">
+        <v>46311</v>
+      </c>
+      <c r="H166" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I166" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J166" s="41" t="n">
+        <v>0.9803921568627444</v>
+      </c>
+      <c r="K166" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="47" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B167" s="30" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 3</t>
+        </is>
+      </c>
+      <c r="C167" s="30" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D167" s="32" t="n">
+        <v>24</v>
+      </c>
+      <c r="E167" s="32" t="n">
+        <v>102</v>
+      </c>
+      <c r="F167" s="34" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="G167" s="47" t="n">
+        <v>46312</v>
+      </c>
+      <c r="H167" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I167" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="49" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B168" s="36" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 3</t>
+        </is>
+      </c>
+      <c r="C168" s="36" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D168" s="38" t="n">
+        <v>24</v>
+      </c>
+      <c r="E168" s="38" t="n">
+        <v>102</v>
+      </c>
+      <c r="F168" s="40" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="G168" s="49" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H168" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I168" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="47" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B169" s="30" t="inlineStr">
+        <is>
+          <t>Sapphire Residence @Diamond City</t>
+        </is>
+      </c>
+      <c r="C169" s="30" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D169" s="32" t="n">
+        <v>24</v>
+      </c>
+      <c r="E169" s="32" t="n">
+        <v>136</v>
+      </c>
+      <c r="F169" s="34" t="n">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="G169" s="47" t="n"/>
+      <c r="H169" s="32" t="n"/>
+      <c r="I169" s="32" t="n"/>
+      <c r="J169" s="51" t="n"/>
+      <c r="K169" s="30" t="inlineStr">
+        <is>
+          <t>Baseline: no earlier observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="49" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B170" s="36" t="inlineStr">
+        <is>
+          <t>Sapphire Residence @Diamond City</t>
+        </is>
+      </c>
+      <c r="C170" s="36" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D170" s="38" t="n">
+        <v>30</v>
+      </c>
+      <c r="E170" s="38" t="n">
+        <v>136</v>
+      </c>
+      <c r="F170" s="40" t="n">
+        <v>0.2205882352941176</v>
+      </c>
+      <c r="G170" s="49" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H170" s="38" t="n">
+        <v>32</v>
+      </c>
+      <c r="I170" s="50" t="n">
+        <v>6</v>
+      </c>
+      <c r="J170" s="41" t="n">
+        <v>4.411764705882351</v>
+      </c>
+      <c r="K170" s="36" t="inlineStr">
+        <is>
+          <t>32-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="47" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B171" s="30" t="inlineStr">
+        <is>
+          <t>Sapphire Residence @Diamond City</t>
+        </is>
+      </c>
+      <c r="C171" s="30" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D171" s="32" t="n">
+        <v>45</v>
+      </c>
+      <c r="E171" s="32" t="n">
+        <v>136</v>
+      </c>
+      <c r="F171" s="34" t="n">
+        <v>0.3308823529411765</v>
+      </c>
+      <c r="G171" s="47" t="n">
+        <v>46213</v>
+      </c>
+      <c r="H171" s="32" t="n">
+        <v>95</v>
+      </c>
+      <c r="I171" s="48" t="n">
+        <v>15</v>
+      </c>
+      <c r="J171" s="35" t="n">
+        <v>11.02941176470588</v>
+      </c>
+      <c r="K171" s="30" t="inlineStr">
+        <is>
+          <t>95-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="49" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B172" s="36" t="inlineStr">
+        <is>
+          <t>Sapphire Residence @Diamond City</t>
+        </is>
+      </c>
+      <c r="C172" s="36" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D172" s="38" t="n">
+        <v>45</v>
+      </c>
+      <c r="E172" s="38" t="n">
+        <v>136</v>
+      </c>
+      <c r="F172" s="40" t="n">
+        <v>0.3308823529411765</v>
+      </c>
+      <c r="G172" s="49" t="n">
+        <v>46308</v>
+      </c>
+      <c r="H172" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="I172" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" s="36" t="inlineStr">
+        <is>
+          <t>2-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="47" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B173" s="30" t="inlineStr">
+        <is>
+          <t>Sapphire Residence @Diamond City</t>
+        </is>
+      </c>
+      <c r="C173" s="30" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D173" s="32" t="n">
+        <v>45</v>
+      </c>
+      <c r="E173" s="32" t="n">
+        <v>136</v>
+      </c>
+      <c r="F173" s="34" t="n">
+        <v>0.3308823529411765</v>
+      </c>
+      <c r="G173" s="47" t="n">
+        <v>46310</v>
+      </c>
+      <c r="H173" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I173" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K173" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="49" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B174" s="36" t="inlineStr">
+        <is>
+          <t>Sapphire Residence @Diamond City</t>
+        </is>
+      </c>
+      <c r="C174" s="36" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D174" s="38" t="n">
+        <v>45</v>
+      </c>
+      <c r="E174" s="38" t="n">
+        <v>136</v>
+      </c>
+      <c r="F174" s="40" t="n">
+        <v>0.3308823529411765</v>
+      </c>
+      <c r="G174" s="49" t="n">
+        <v>46311</v>
+      </c>
+      <c r="H174" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I174" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J174" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K174" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="47" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B175" s="30" t="inlineStr">
+        <is>
+          <t>Sapphire Residence @Diamond City</t>
+        </is>
+      </c>
+      <c r="C175" s="30" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D175" s="32" t="n">
+        <v>45</v>
+      </c>
+      <c r="E175" s="32" t="n">
+        <v>136</v>
+      </c>
+      <c r="F175" s="34" t="n">
+        <v>0.3308823529411765</v>
+      </c>
+      <c r="G175" s="47" t="n">
+        <v>46312</v>
+      </c>
+      <c r="H175" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I175" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K175" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="49" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B176" s="36" t="inlineStr">
+        <is>
+          <t>Sapphire Residence @Diamond City</t>
+        </is>
+      </c>
+      <c r="C176" s="36" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D176" s="38" t="n">
+        <v>45</v>
+      </c>
+      <c r="E176" s="38" t="n">
+        <v>136</v>
+      </c>
+      <c r="F176" s="40" t="n">
+        <v>0.3308823529411765</v>
+      </c>
+      <c r="G176" s="49" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H176" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I176" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K176" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="47" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B177" s="30" t="inlineStr">
+        <is>
+          <t>Springvale Sempurna Heights</t>
+        </is>
+      </c>
+      <c r="C177" s="30" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="D177" s="32" t="n">
+        <v>81</v>
+      </c>
+      <c r="E177" s="32" t="n">
+        <v>189</v>
+      </c>
+      <c r="F177" s="34" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="G177" s="47" t="n"/>
+      <c r="H177" s="32" t="n"/>
+      <c r="I177" s="32" t="n"/>
+      <c r="J177" s="51" t="n"/>
+      <c r="K177" s="30" t="inlineStr">
+        <is>
+          <t>Baseline: no earlier observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="49" t="n">
+        <v>45936</v>
+      </c>
+      <c r="B178" s="36" t="inlineStr">
+        <is>
+          <t>Springvale Sempurna Heights</t>
+        </is>
+      </c>
+      <c r="C178" s="36" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="D178" s="38" t="n">
+        <v>84</v>
+      </c>
+      <c r="E178" s="38" t="n">
+        <v>189</v>
+      </c>
+      <c r="F178" s="40" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="G178" s="49" t="n">
+        <v>45894</v>
+      </c>
+      <c r="H178" s="38" t="n">
+        <v>42</v>
+      </c>
+      <c r="I178" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="J178" s="41" t="n">
+        <v>1.587301587301587</v>
+      </c>
+      <c r="K178" s="36" t="inlineStr">
+        <is>
+          <t>42-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="47" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B179" s="30" t="inlineStr">
+        <is>
+          <t>Springvale Sempurna Heights</t>
+        </is>
+      </c>
+      <c r="C179" s="30" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="D179" s="32" t="n">
+        <v>124</v>
+      </c>
+      <c r="E179" s="32" t="n">
+        <v>189</v>
+      </c>
+      <c r="F179" s="34" t="n">
+        <v>0.656084656084656</v>
+      </c>
+      <c r="G179" s="47" t="n">
+        <v>45936</v>
+      </c>
+      <c r="H179" s="32" t="n">
+        <v>144</v>
+      </c>
+      <c r="I179" s="48" t="n">
+        <v>40</v>
+      </c>
+      <c r="J179" s="35" t="n">
+        <v>21.16402116402116</v>
+      </c>
+      <c r="K179" s="30" t="inlineStr">
+        <is>
+          <t>144-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="49" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B180" s="36" t="inlineStr">
+        <is>
+          <t>Springvale Sempurna Heights</t>
+        </is>
+      </c>
+      <c r="C180" s="36" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="D180" s="38" t="n">
+        <v>148</v>
+      </c>
+      <c r="E180" s="38" t="n">
+        <v>189</v>
+      </c>
+      <c r="F180" s="40" t="n">
+        <v>0.783068783068783</v>
+      </c>
+      <c r="G180" s="49" t="n">
+        <v>46080</v>
+      </c>
+      <c r="H180" s="38" t="n">
+        <v>101</v>
+      </c>
+      <c r="I180" s="50" t="n">
+        <v>24</v>
+      </c>
+      <c r="J180" s="41" t="n">
+        <v>12.6984126984127</v>
+      </c>
+      <c r="K180" s="36" t="inlineStr">
+        <is>
+          <t>101-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="47" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B181" s="30" t="inlineStr">
+        <is>
+          <t>Springvale Sempurna Heights</t>
+        </is>
+      </c>
+      <c r="C181" s="30" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="D181" s="32" t="n">
+        <v>154</v>
+      </c>
+      <c r="E181" s="32" t="n">
+        <v>189</v>
+      </c>
+      <c r="F181" s="34" t="n">
+        <v>0.8148148148148148</v>
+      </c>
+      <c r="G181" s="47" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H181" s="32" t="n">
+        <v>32</v>
+      </c>
+      <c r="I181" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="J181" s="35" t="n">
+        <v>3.174603174603174</v>
+      </c>
+      <c r="K181" s="30" t="inlineStr">
+        <is>
+          <t>32-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="49" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B182" s="36" t="inlineStr">
+        <is>
+          <t>Springvale Sempurna Heights</t>
+        </is>
+      </c>
+      <c r="C182" s="36" t="inlineStr">
+        <is>
+          <t>Group A · front-kitchen layout</t>
+        </is>
+      </c>
+      <c r="D182" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E182" s="38" t="n">
+        <v>27</v>
+      </c>
+      <c r="F182" s="40" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="G182" s="49" t="n"/>
+      <c r="H182" s="38" t="n"/>
+      <c r="I182" s="38" t="n"/>
+      <c r="J182" s="52" t="n"/>
+      <c r="K182" s="36" t="inlineStr">
+        <is>
+          <t>Baseline: no earlier observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="47" t="n">
+        <v>45936</v>
+      </c>
+      <c r="B183" s="30" t="inlineStr">
+        <is>
+          <t>Springvale Sempurna Heights</t>
+        </is>
+      </c>
+      <c r="C183" s="30" t="inlineStr">
+        <is>
+          <t>Group A · front-kitchen layout</t>
+        </is>
+      </c>
+      <c r="D183" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E183" s="32" t="n">
+        <v>27</v>
+      </c>
+      <c r="F183" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G183" s="47" t="n">
+        <v>45894</v>
+      </c>
+      <c r="H183" s="32" t="n">
+        <v>42</v>
+      </c>
+      <c r="I183" s="53" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J183" s="54" t="n">
+        <v>-3.703703703703703</v>
+      </c>
+      <c r="K183" s="30" t="inlineStr">
+        <is>
+          <t>42-day gap; change is not daily movement; Signed count decreased; verify source/status correction</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="49" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B184" s="36" t="inlineStr">
+        <is>
+          <t>Springvale Sempurna Heights</t>
+        </is>
+      </c>
+      <c r="C184" s="36" t="inlineStr">
+        <is>
+          <t>Group A · front-kitchen layout</t>
+        </is>
+      </c>
+      <c r="D184" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E184" s="38" t="n">
+        <v>27</v>
+      </c>
+      <c r="F184" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G184" s="49" t="n">
+        <v>45936</v>
+      </c>
+      <c r="H184" s="38" t="n">
+        <v>144</v>
+      </c>
+      <c r="I184" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J184" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K184" s="36" t="inlineStr">
+        <is>
+          <t>144-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="47" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B185" s="30" t="inlineStr">
+        <is>
+          <t>Springvale Sempurna Heights</t>
+        </is>
+      </c>
+      <c r="C185" s="30" t="inlineStr">
+        <is>
+          <t>Group A · front-kitchen layout</t>
+        </is>
+      </c>
+      <c r="D185" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E185" s="32" t="n">
+        <v>27</v>
+      </c>
+      <c r="F185" s="34" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="G185" s="47" t="n">
+        <v>46080</v>
+      </c>
+      <c r="H185" s="32" t="n">
+        <v>101</v>
+      </c>
+      <c r="I185" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J185" s="35" t="n">
+        <v>3.703703703703703</v>
+      </c>
+      <c r="K185" s="30" t="inlineStr">
+        <is>
+          <t>101-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="49" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B186" s="36" t="inlineStr">
+        <is>
+          <t>Springvale Sempurna Heights</t>
+        </is>
+      </c>
+      <c r="C186" s="36" t="inlineStr">
+        <is>
+          <t>Group A · front-kitchen layout</t>
+        </is>
+      </c>
+      <c r="D186" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E186" s="38" t="n">
+        <v>27</v>
+      </c>
+      <c r="F186" s="40" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="G186" s="49" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H186" s="38" t="n">
+        <v>32</v>
+      </c>
+      <c r="I186" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K186" s="36" t="inlineStr">
+        <is>
+          <t>32-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="47" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B187" s="30" t="inlineStr">
+        <is>
+          <t>Springvale Sempurna Heights</t>
+        </is>
+      </c>
+      <c r="C187" s="30" t="inlineStr">
+        <is>
+          <t>Group A · front-kitchen layout</t>
+        </is>
+      </c>
+      <c r="D187" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E187" s="32" t="n">
+        <v>27</v>
+      </c>
+      <c r="F187" s="34" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="G187" s="47" t="n">
+        <v>46213</v>
+      </c>
+      <c r="H187" s="32" t="n">
+        <v>95</v>
+      </c>
+      <c r="I187" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J187" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K187" s="30" t="inlineStr">
+        <is>
+          <t>95-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="49" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B188" s="36" t="inlineStr">
+        <is>
+          <t>Springvale Sempurna Heights</t>
+        </is>
+      </c>
+      <c r="C188" s="36" t="inlineStr">
+        <is>
+          <t>Group A · front-kitchen layout</t>
+        </is>
+      </c>
+      <c r="D188" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E188" s="38" t="n">
+        <v>27</v>
+      </c>
+      <c r="F188" s="40" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="G188" s="49" t="n">
+        <v>46308</v>
+      </c>
+      <c r="H188" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="I188" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J188" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K188" s="36" t="inlineStr">
+        <is>
+          <t>2-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="47" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B189" s="30" t="inlineStr">
+        <is>
+          <t>Springvale Sempurna Heights</t>
+        </is>
+      </c>
+      <c r="C189" s="30" t="inlineStr">
+        <is>
+          <t>Group A · front-kitchen layout</t>
+        </is>
+      </c>
+      <c r="D189" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E189" s="32" t="n">
+        <v>27</v>
+      </c>
+      <c r="F189" s="34" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="G189" s="47" t="n">
+        <v>46310</v>
+      </c>
+      <c r="H189" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I189" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J189" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K189" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="49" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B190" s="36" t="inlineStr">
+        <is>
+          <t>Springvale Sempurna Heights</t>
+        </is>
+      </c>
+      <c r="C190" s="36" t="inlineStr">
+        <is>
+          <t>Group A · front-kitchen layout</t>
+        </is>
+      </c>
+      <c r="D190" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E190" s="38" t="n">
+        <v>27</v>
+      </c>
+      <c r="F190" s="40" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="G190" s="49" t="n">
+        <v>46311</v>
+      </c>
+      <c r="H190" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I190" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K190" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="47" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B191" s="30" t="inlineStr">
+        <is>
+          <t>Springvale Sempurna Heights</t>
+        </is>
+      </c>
+      <c r="C191" s="30" t="inlineStr">
+        <is>
+          <t>Group A · front-kitchen layout</t>
+        </is>
+      </c>
+      <c r="D191" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E191" s="32" t="n">
+        <v>27</v>
+      </c>
+      <c r="F191" s="34" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="G191" s="47" t="n">
+        <v>46312</v>
+      </c>
+      <c r="H191" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I191" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J191" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K191" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="49" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B192" s="36" t="inlineStr">
+        <is>
+          <t>Springvale Sempurna Heights</t>
+        </is>
+      </c>
+      <c r="C192" s="36" t="inlineStr">
+        <is>
+          <t>Group A · front-kitchen layout</t>
+        </is>
+      </c>
+      <c r="D192" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E192" s="38" t="n">
+        <v>27</v>
+      </c>
+      <c r="F192" s="40" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="G192" s="49" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H192" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I192" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J192" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K192" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="47" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B193" s="30" t="inlineStr">
+        <is>
+          <t>Springvale Sempurna Heights</t>
+        </is>
+      </c>
+      <c r="C193" s="30" t="inlineStr">
+        <is>
+          <t>Group B · rear-kitchen layout</t>
+        </is>
+      </c>
+      <c r="D193" s="32" t="n">
+        <v>160</v>
+      </c>
+      <c r="E193" s="32" t="n">
+        <v>308</v>
+      </c>
+      <c r="F193" s="34" t="n">
+        <v>0.5194805194805194</v>
+      </c>
+      <c r="G193" s="47" t="n"/>
+      <c r="H193" s="32" t="n"/>
+      <c r="I193" s="32" t="n"/>
+      <c r="J193" s="51" t="n"/>
+      <c r="K193" s="30" t="inlineStr">
+        <is>
+          <t>Baseline: no earlier observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="49" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B194" s="36" t="inlineStr">
+        <is>
+          <t>Springvale Sempurna Heights</t>
+        </is>
+      </c>
+      <c r="C194" s="36" t="inlineStr">
+        <is>
+          <t>Group B · rear-kitchen layout</t>
+        </is>
+      </c>
+      <c r="D194" s="38" t="n">
+        <v>161</v>
+      </c>
+      <c r="E194" s="38" t="n">
+        <v>308</v>
+      </c>
+      <c r="F194" s="40" t="n">
+        <v>0.5227272727272727</v>
+      </c>
+      <c r="G194" s="49" t="n">
+        <v>46308</v>
+      </c>
+      <c r="H194" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="I194" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J194" s="41" t="n">
+        <v>0.3246753246753276</v>
+      </c>
+      <c r="K194" s="36" t="inlineStr">
+        <is>
+          <t>2-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="47" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B195" s="30" t="inlineStr">
+        <is>
+          <t>Springvale Sempurna Heights</t>
+        </is>
+      </c>
+      <c r="C195" s="30" t="inlineStr">
+        <is>
+          <t>Group B · rear-kitchen layout</t>
+        </is>
+      </c>
+      <c r="D195" s="32" t="n">
+        <v>161</v>
+      </c>
+      <c r="E195" s="32" t="n">
+        <v>308</v>
+      </c>
+      <c r="F195" s="34" t="n">
+        <v>0.5227272727272727</v>
+      </c>
+      <c r="G195" s="47" t="n">
+        <v>46310</v>
+      </c>
+      <c r="H195" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I195" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K195" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="49" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B196" s="36" t="inlineStr">
+        <is>
+          <t>Springvale Sempurna Heights</t>
+        </is>
+      </c>
+      <c r="C196" s="36" t="inlineStr">
+        <is>
+          <t>Group B · rear-kitchen layout</t>
+        </is>
+      </c>
+      <c r="D196" s="38" t="n">
+        <v>161</v>
+      </c>
+      <c r="E196" s="38" t="n">
+        <v>308</v>
+      </c>
+      <c r="F196" s="40" t="n">
+        <v>0.5227272727272727</v>
+      </c>
+      <c r="G196" s="49" t="n">
+        <v>46311</v>
+      </c>
+      <c r="H196" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I196" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K196" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="47" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B197" s="30" t="inlineStr">
+        <is>
+          <t>Springvale Sempurna Heights</t>
+        </is>
+      </c>
+      <c r="C197" s="30" t="inlineStr">
+        <is>
+          <t>Group B · rear-kitchen layout</t>
+        </is>
+      </c>
+      <c r="D197" s="32" t="n">
+        <v>161</v>
+      </c>
+      <c r="E197" s="32" t="n">
+        <v>308</v>
+      </c>
+      <c r="F197" s="34" t="n">
+        <v>0.5227272727272727</v>
+      </c>
+      <c r="G197" s="47" t="n">
+        <v>46312</v>
+      </c>
+      <c r="H197" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I197" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J197" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K197" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="49" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B198" s="36" t="inlineStr">
+        <is>
+          <t>Springvale Sempurna Heights</t>
+        </is>
+      </c>
+      <c r="C198" s="36" t="inlineStr">
+        <is>
+          <t>Group B · rear-kitchen layout</t>
+        </is>
+      </c>
+      <c r="D198" s="38" t="n">
+        <v>161</v>
+      </c>
+      <c r="E198" s="38" t="n">
+        <v>308</v>
+      </c>
+      <c r="F198" s="40" t="n">
+        <v>0.5227272727272727</v>
+      </c>
+      <c r="G198" s="49" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H198" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I198" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J198" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K198" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="47" t="n">
+        <v>45733</v>
+      </c>
+      <c r="B199" s="30" t="inlineStr">
+        <is>
+          <t>Zinnia Residences</t>
+        </is>
+      </c>
+      <c r="C199" s="30" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D199" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="E199" s="32" t="n">
+        <v>149</v>
+      </c>
+      <c r="F199" s="34" t="n">
+        <v>0.06040268456375839</v>
+      </c>
+      <c r="G199" s="47" t="n"/>
+      <c r="H199" s="32" t="n"/>
+      <c r="I199" s="32" t="n"/>
+      <c r="J199" s="51" t="n"/>
+      <c r="K199" s="30" t="inlineStr">
+        <is>
+          <t>Baseline: no earlier observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="49" t="n">
+        <v>45889</v>
+      </c>
+      <c r="B200" s="36" t="inlineStr">
+        <is>
+          <t>Zinnia Residences</t>
+        </is>
+      </c>
+      <c r="C200" s="36" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D200" s="38" t="n">
+        <v>21</v>
+      </c>
+      <c r="E200" s="38" t="n">
+        <v>149</v>
+      </c>
+      <c r="F200" s="40" t="n">
+        <v>0.1409395973154362</v>
+      </c>
+      <c r="G200" s="49" t="n">
+        <v>45733</v>
+      </c>
+      <c r="H200" s="38" t="n">
+        <v>156</v>
+      </c>
+      <c r="I200" s="50" t="n">
+        <v>12</v>
+      </c>
+      <c r="J200" s="41" t="n">
+        <v>8.053691275167784</v>
+      </c>
+      <c r="K200" s="36" t="inlineStr">
+        <is>
+          <t>156-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="47" t="n">
+        <v>45936</v>
+      </c>
+      <c r="B201" s="30" t="inlineStr">
+        <is>
+          <t>Zinnia Residences</t>
+        </is>
+      </c>
+      <c r="C201" s="30" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D201" s="32" t="n">
+        <v>23</v>
+      </c>
+      <c r="E201" s="32" t="n">
+        <v>149</v>
+      </c>
+      <c r="F201" s="34" t="n">
+        <v>0.1543624161073825</v>
+      </c>
+      <c r="G201" s="47" t="n">
+        <v>45889</v>
+      </c>
+      <c r="H201" s="32" t="n">
+        <v>47</v>
+      </c>
+      <c r="I201" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="J201" s="35" t="n">
+        <v>1.342281879194632</v>
+      </c>
+      <c r="K201" s="30" t="inlineStr">
+        <is>
+          <t>47-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="49" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B202" s="36" t="inlineStr">
+        <is>
+          <t>Zinnia Residences</t>
+        </is>
+      </c>
+      <c r="C202" s="36" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D202" s="38" t="n">
+        <v>31</v>
+      </c>
+      <c r="E202" s="38" t="n">
+        <v>149</v>
+      </c>
+      <c r="F202" s="40" t="n">
+        <v>0.2080536912751678</v>
+      </c>
+      <c r="G202" s="49" t="n">
+        <v>45936</v>
+      </c>
+      <c r="H202" s="38" t="n">
+        <v>245</v>
+      </c>
+      <c r="I202" s="50" t="n">
+        <v>8</v>
+      </c>
+      <c r="J202" s="41" t="n">
+        <v>5.369127516778524</v>
+      </c>
+      <c r="K202" s="36" t="inlineStr">
+        <is>
+          <t>245-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="47" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B203" s="30" t="inlineStr">
+        <is>
+          <t>Zinnia Residences</t>
+        </is>
+      </c>
+      <c r="C203" s="30" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D203" s="32" t="n">
+        <v>34</v>
+      </c>
+      <c r="E203" s="32" t="n">
+        <v>149</v>
+      </c>
+      <c r="F203" s="34" t="n">
+        <v>0.2281879194630873</v>
+      </c>
+      <c r="G203" s="47" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H203" s="32" t="n">
+        <v>32</v>
+      </c>
+      <c r="I203" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="J203" s="35" t="n">
+        <v>2.013422818791946</v>
+      </c>
+      <c r="K203" s="30" t="inlineStr">
+        <is>
+          <t>32-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="49" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B204" s="36" t="inlineStr">
+        <is>
+          <t>Zinnia Residences</t>
+        </is>
+      </c>
+      <c r="C204" s="36" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D204" s="38" t="n">
+        <v>34</v>
+      </c>
+      <c r="E204" s="38" t="n">
+        <v>149</v>
+      </c>
+      <c r="F204" s="40" t="n">
+        <v>0.2281879194630873</v>
+      </c>
+      <c r="G204" s="49" t="n">
+        <v>46213</v>
+      </c>
+      <c r="H204" s="38" t="n">
+        <v>95</v>
+      </c>
+      <c r="I204" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K204" s="36" t="inlineStr">
+        <is>
+          <t>95-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="47" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B205" s="30" t="inlineStr">
+        <is>
+          <t>Zinnia Residences</t>
+        </is>
+      </c>
+      <c r="C205" s="30" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D205" s="32" t="n">
+        <v>34</v>
+      </c>
+      <c r="E205" s="32" t="n">
+        <v>149</v>
+      </c>
+      <c r="F205" s="34" t="n">
+        <v>0.2281879194630873</v>
+      </c>
+      <c r="G205" s="47" t="n">
+        <v>46308</v>
+      </c>
+      <c r="H205" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I205" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K205" s="30" t="inlineStr">
+        <is>
+          <t>2-day gap; change is not daily movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="49" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B206" s="36" t="inlineStr">
+        <is>
+          <t>Zinnia Residences</t>
+        </is>
+      </c>
+      <c r="C206" s="36" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D206" s="38" t="n">
+        <v>34</v>
+      </c>
+      <c r="E206" s="38" t="n">
+        <v>149</v>
+      </c>
+      <c r="F206" s="40" t="n">
+        <v>0.2281879194630873</v>
+      </c>
+      <c r="G206" s="49" t="n">
+        <v>46310</v>
+      </c>
+      <c r="H206" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I206" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J206" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K206" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="47" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B207" s="30" t="inlineStr">
+        <is>
+          <t>Zinnia Residences</t>
+        </is>
+      </c>
+      <c r="C207" s="30" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D207" s="32" t="n">
+        <v>34</v>
+      </c>
+      <c r="E207" s="32" t="n">
+        <v>149</v>
+      </c>
+      <c r="F207" s="34" t="n">
+        <v>0.2281879194630873</v>
+      </c>
+      <c r="G207" s="47" t="n">
+        <v>46311</v>
+      </c>
+      <c r="H207" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I207" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J207" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K207" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="49" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B208" s="36" t="inlineStr">
+        <is>
+          <t>Zinnia Residences</t>
+        </is>
+      </c>
+      <c r="C208" s="36" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D208" s="38" t="n">
+        <v>34</v>
+      </c>
+      <c r="E208" s="38" t="n">
+        <v>149</v>
+      </c>
+      <c r="F208" s="40" t="n">
+        <v>0.2281879194630873</v>
+      </c>
+      <c r="G208" s="49" t="n">
+        <v>46312</v>
+      </c>
+      <c r="H208" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I208" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J208" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K208" s="36" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="47" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B209" s="30" t="inlineStr">
+        <is>
+          <t>Zinnia Residences</t>
+        </is>
+      </c>
+      <c r="C209" s="30" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D209" s="32" t="n">
+        <v>34</v>
+      </c>
+      <c r="E209" s="32" t="n">
+        <v>149</v>
+      </c>
+      <c r="F209" s="34" t="n">
+        <v>0.2281879194630873</v>
+      </c>
+      <c r="G209" s="47" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H209" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I209" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K209" s="30" t="inlineStr">
+        <is>
+          <t>Comparable observation</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:K209"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3301,8 +11665,8 @@
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="K2:M2"/>
     <mergeCell ref="N2:P2"/>
+    <mergeCell ref="A4:X4"/>
     <mergeCell ref="A7:X7"/>
-    <mergeCell ref="A4:X4"/>
     <mergeCell ref="F2:I2"/>
     <mergeCell ref="A10:X10"/>
     <mergeCell ref="A17:X17"/>

--- a/Broga_Weekly_Tracking.xlsx
+++ b/Broga_Weekly_Tracking.xlsx
@@ -130,12 +130,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6E5C9"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00F6E5C9"/>
       </patternFill>
     </fill>
     <fill>
@@ -291,7 +291,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -413,31 +413,28 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2031,74 +2028,74 @@
       </c>
     </row>
     <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="43" t="n">
+      <c r="A35" s="37" t="n">
         <v>45936</v>
       </c>
-      <c r="B35" s="44" t="inlineStr">
+      <c r="B35" s="38" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C35" s="44" t="inlineStr">
+      <c r="C35" s="38" t="inlineStr">
         <is>
           <t>No group details</t>
         </is>
       </c>
-      <c r="D35" s="45" t="inlineStr">
-        <is>
-          <t>Unclassified</t>
-        </is>
-      </c>
-      <c r="E35" s="45" t="inlineStr">
+      <c r="D35" s="39" t="inlineStr">
+        <is>
+          <t>Yet to sign</t>
+        </is>
+      </c>
+      <c r="E35" s="39" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F35" s="46" t="n"/>
-      <c r="G35" s="47" t="inlineStr">
+      <c r="F35" s="40" t="n"/>
+      <c r="G35" s="41" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="H35" s="44" t="inlineStr">
-        <is>
-          <t>No parseable group-level values: Yet to sign; Blank/unclassified status; verify source</t>
+      <c r="H35" s="38" t="inlineStr">
+        <is>
+          <t>Yet to sign; Non-signed status retained for audit; excluded from signed trend</t>
         </is>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="43" t="n">
+      <c r="A36" s="32" t="n">
         <v>45936</v>
       </c>
-      <c r="B36" s="44" t="inlineStr">
+      <c r="B36" s="33" t="inlineStr">
         <is>
           <t>Sapphire Residence @Diamond City</t>
         </is>
       </c>
-      <c r="C36" s="44" t="inlineStr">
+      <c r="C36" s="33" t="inlineStr">
         <is>
           <t>No group details</t>
         </is>
       </c>
-      <c r="D36" s="45" t="inlineStr">
-        <is>
-          <t>Unclassified</t>
-        </is>
-      </c>
-      <c r="E36" s="45" t="inlineStr">
+      <c r="D36" s="34" t="inlineStr">
+        <is>
+          <t>Yet to sign</t>
+        </is>
+      </c>
+      <c r="E36" s="34" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F36" s="46" t="n"/>
-      <c r="G36" s="47" t="inlineStr">
+      <c r="F36" s="35" t="n"/>
+      <c r="G36" s="36" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="H36" s="44" t="inlineStr">
-        <is>
-          <t>No parseable group-level values: Yet to sign; Blank/unclassified status; verify source</t>
+      <c r="H36" s="33" t="inlineStr">
+        <is>
+          <t>Yet to sign; Non-signed status retained for audit; excluded from signed trend</t>
         </is>
       </c>
     </row>
@@ -2129,7 +2126,7 @@
       <c r="F37" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="G37" s="48" t="inlineStr">
+      <c r="G37" s="43" t="inlineStr">
         <is>
           <t>-1 signed · -3.7 pp</t>
         </is>
@@ -2635,38 +2632,38 @@
       </c>
     </row>
     <row r="51" ht="24" customHeight="1">
-      <c r="A51" s="43" t="n">
+      <c r="A51" s="37" t="n">
         <v>46181</v>
       </c>
-      <c r="B51" s="44" t="inlineStr">
+      <c r="B51" s="38" t="inlineStr">
         <is>
           <t>Astrea @Eco Radiance</t>
         </is>
       </c>
-      <c r="C51" s="44" t="inlineStr">
+      <c r="C51" s="38" t="inlineStr">
         <is>
           <t>No group details</t>
         </is>
       </c>
-      <c r="D51" s="45" t="inlineStr">
-        <is>
-          <t>Unclassified</t>
-        </is>
-      </c>
-      <c r="E51" s="45" t="inlineStr">
+      <c r="D51" s="39" t="inlineStr">
+        <is>
+          <t>Yet to launch</t>
+        </is>
+      </c>
+      <c r="E51" s="39" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F51" s="46" t="n"/>
-      <c r="G51" s="47" t="inlineStr">
+      <c r="F51" s="40" t="n"/>
+      <c r="G51" s="41" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="H51" s="44" t="inlineStr">
-        <is>
-          <t>No parseable group-level values: Yet to Launch; Blank/unclassified status; verify source</t>
+      <c r="H51" s="38" t="inlineStr">
+        <is>
+          <t>Yet to Launch; Non-signed status retained for audit; excluded from signed trend</t>
         </is>
       </c>
     </row>
@@ -2747,38 +2744,38 @@
       </c>
     </row>
     <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="43" t="n">
+      <c r="A54" s="44" t="n">
         <v>46181</v>
       </c>
-      <c r="B54" s="44" t="inlineStr">
+      <c r="B54" s="45" t="inlineStr">
         <is>
           <t>Banyan @Setia Ecohill 2</t>
         </is>
       </c>
-      <c r="C54" s="44" t="inlineStr">
+      <c r="C54" s="45" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D54" s="45" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E54" s="45" t="inlineStr">
+      <c r="D54" s="46" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E54" s="46" t="inlineStr">
         <is>
           <t>70 / 113</t>
         </is>
       </c>
-      <c r="F54" s="46" t="n">
+      <c r="F54" s="47" t="n">
         <v>0.6194690265486725</v>
       </c>
-      <c r="G54" s="49" t="inlineStr">
+      <c r="G54" s="48" t="inlineStr">
         <is>
           <t>-13 signed · -21.9 pp</t>
         </is>
       </c>
-      <c r="H54" s="50" t="inlineStr">
+      <c r="H54" s="49" t="inlineStr">
         <is>
           <t>62% Signed (70/113 units); TOTAL CHANGED: 99 → 113 (+14); percentage recalculated; 245-day gap; not daily movement; Signed count decreased; verify source/status correction</t>
         </is>
@@ -2963,7 +2960,7 @@
       <c r="F59" s="35" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="G59" s="48" t="inlineStr">
+      <c r="G59" s="43" t="inlineStr">
         <is>
           <t>-10 signed · -10.1 pp</t>
         </is>
@@ -3393,38 +3390,38 @@
       </c>
     </row>
     <row r="71" ht="24" customHeight="1">
-      <c r="A71" s="43" t="n">
+      <c r="A71" s="32" t="n">
         <v>46213</v>
       </c>
-      <c r="B71" s="44" t="inlineStr">
+      <c r="B71" s="33" t="inlineStr">
         <is>
           <t>Astrea @Eco Radiance</t>
         </is>
       </c>
-      <c r="C71" s="44" t="inlineStr">
+      <c r="C71" s="33" t="inlineStr">
         <is>
           <t>No group details</t>
         </is>
       </c>
-      <c r="D71" s="45" t="inlineStr">
-        <is>
-          <t>Unclassified</t>
-        </is>
-      </c>
-      <c r="E71" s="45" t="inlineStr">
+      <c r="D71" s="34" t="inlineStr">
+        <is>
+          <t>Yet to launch</t>
+        </is>
+      </c>
+      <c r="E71" s="34" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F71" s="46" t="n"/>
-      <c r="G71" s="47" t="inlineStr">
+      <c r="F71" s="35" t="n"/>
+      <c r="G71" s="36" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="H71" s="44" t="inlineStr">
-        <is>
-          <t>No parseable group-level values: Yet to Launch; Blank/unclassified status; verify source</t>
+      <c r="H71" s="33" t="inlineStr">
+        <is>
+          <t>Yet to Launch; Non-signed status retained for audit; excluded from signed trend</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3533,7 @@
           <t>+0 signed · +0.0 pp</t>
         </is>
       </c>
-      <c r="H74" s="51" t="inlineStr">
+      <c r="H74" s="50" t="inlineStr">
         <is>
           <t>62% Signed (70/113 units); 32-day gap; not daily movement; Under revised scope since 08 Jun 2026 (99 → 113); review</t>
         </is>
@@ -4075,38 +4072,38 @@
       </c>
     </row>
     <row r="89" ht="24" customHeight="1">
-      <c r="A89" s="43" t="n">
+      <c r="A89" s="32" t="n">
         <v>46213</v>
       </c>
-      <c r="B89" s="44" t="inlineStr">
+      <c r="B89" s="33" t="inlineStr">
         <is>
           <t>Majestic Flora</t>
         </is>
       </c>
-      <c r="C89" s="44" t="inlineStr">
+      <c r="C89" s="33" t="inlineStr">
         <is>
           <t>No group details</t>
         </is>
       </c>
-      <c r="D89" s="45" t="inlineStr">
-        <is>
-          <t>Unclassified</t>
-        </is>
-      </c>
-      <c r="E89" s="45" t="inlineStr">
+      <c r="D89" s="34" t="inlineStr">
+        <is>
+          <t>Yet to sign</t>
+        </is>
+      </c>
+      <c r="E89" s="34" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F89" s="46" t="n"/>
-      <c r="G89" s="47" t="inlineStr">
+      <c r="F89" s="35" t="n"/>
+      <c r="G89" s="36" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="H89" s="44" t="inlineStr">
-        <is>
-          <t>No parseable group-level values: Yet to Sign; Blank/unclassified status; verify source</t>
+      <c r="H89" s="33" t="inlineStr">
+        <is>
+          <t>Yet to Sign; Non-signed status retained for audit; excluded from signed trend</t>
         </is>
       </c>
     </row>
@@ -4301,38 +4298,38 @@
       </c>
     </row>
     <row r="95" ht="24" customHeight="1">
-      <c r="A95" s="43" t="n">
+      <c r="A95" s="37" t="n">
         <v>46308</v>
       </c>
-      <c r="B95" s="44" t="inlineStr">
+      <c r="B95" s="38" t="inlineStr">
         <is>
           <t>Astrea @Eco Radiance</t>
         </is>
       </c>
-      <c r="C95" s="44" t="inlineStr">
+      <c r="C95" s="38" t="inlineStr">
         <is>
           <t>No group details</t>
         </is>
       </c>
-      <c r="D95" s="45" t="inlineStr">
-        <is>
-          <t>Unclassified</t>
-        </is>
-      </c>
-      <c r="E95" s="45" t="inlineStr">
+      <c r="D95" s="39" t="inlineStr">
+        <is>
+          <t>Yet to launch</t>
+        </is>
+      </c>
+      <c r="E95" s="39" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F95" s="46" t="n"/>
-      <c r="G95" s="47" t="inlineStr">
+      <c r="F95" s="40" t="n"/>
+      <c r="G95" s="41" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="H95" s="44" t="inlineStr">
-        <is>
-          <t>No parseable group-level values: Yet to Launch; Blank/unclassified status; verify source</t>
+      <c r="H95" s="38" t="inlineStr">
+        <is>
+          <t>Yet to Launch; Non-signed status retained for audit; excluded from signed trend</t>
         </is>
       </c>
     </row>
@@ -4444,7 +4441,7 @@
           <t>+1 signed · +0.9 pp</t>
         </is>
       </c>
-      <c r="H98" s="51" t="inlineStr">
+      <c r="H98" s="50" t="inlineStr">
         <is>
           <t>63% Signed (71/113 units); 95-day gap; not daily movement; Under revised scope since 08 Jun 2026 (99 → 113); review</t>
         </is>
@@ -4983,38 +4980,38 @@
       </c>
     </row>
     <row r="113" ht="24" customHeight="1">
-      <c r="A113" s="43" t="n">
+      <c r="A113" s="37" t="n">
         <v>46308</v>
       </c>
-      <c r="B113" s="44" t="inlineStr">
+      <c r="B113" s="38" t="inlineStr">
         <is>
           <t>Majestic Flora</t>
         </is>
       </c>
-      <c r="C113" s="44" t="inlineStr">
+      <c r="C113" s="38" t="inlineStr">
         <is>
           <t>No group details</t>
         </is>
       </c>
-      <c r="D113" s="45" t="inlineStr">
-        <is>
-          <t>Unclassified</t>
-        </is>
-      </c>
-      <c r="E113" s="45" t="inlineStr">
+      <c r="D113" s="39" t="inlineStr">
+        <is>
+          <t>Yet to sign</t>
+        </is>
+      </c>
+      <c r="E113" s="39" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F113" s="46" t="n"/>
-      <c r="G113" s="47" t="inlineStr">
+      <c r="F113" s="40" t="n"/>
+      <c r="G113" s="41" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="H113" s="44" t="inlineStr">
-        <is>
-          <t>No parseable group-level values: Yet to Sign; Blank/unclassified status; verify source</t>
+      <c r="H113" s="38" t="inlineStr">
+        <is>
+          <t>Yet to Sign; Non-signed status retained for audit; excluded from signed trend</t>
         </is>
       </c>
     </row>
@@ -5095,38 +5092,38 @@
       </c>
     </row>
     <row r="116" ht="30" customHeight="1">
-      <c r="A116" s="43" t="n">
+      <c r="A116" s="44" t="n">
         <v>46308</v>
       </c>
-      <c r="B116" s="44" t="inlineStr">
+      <c r="B116" s="45" t="inlineStr">
         <is>
           <t>Springvale Sempurna Heights</t>
         </is>
       </c>
-      <c r="C116" s="44" t="inlineStr">
+      <c r="C116" s="45" t="inlineStr">
         <is>
           <t>Group B · rear-kitchen layout</t>
         </is>
       </c>
-      <c r="D116" s="45" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E116" s="45" t="inlineStr">
+      <c r="D116" s="46" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E116" s="46" t="inlineStr">
         <is>
           <t>160 / 308</t>
         </is>
       </c>
-      <c r="F116" s="46" t="n">
+      <c r="F116" s="47" t="n">
         <v>0.5194805194805194</v>
       </c>
-      <c r="G116" s="52" t="inlineStr">
+      <c r="G116" s="51" t="inlineStr">
         <is>
           <t>+6 signed · -29.5 pp</t>
         </is>
       </c>
-      <c r="H116" s="50" t="inlineStr">
+      <c r="H116" s="49" t="inlineStr">
         <is>
           <t>52% Signed (160/308 units); TOTAL CHANGED: 189 → 308 (+119); percentage recalculated; 95-day gap; not daily movement</t>
         </is>
@@ -5316,7 +5313,7 @@
           <t>+0 signed · +0.0 pp</t>
         </is>
       </c>
-      <c r="H121" s="51" t="inlineStr">
+      <c r="H121" s="50" t="inlineStr">
         <is>
           <t>71/113 signed; 2-day gap; not daily movement; Under revised scope since 08 Jun 2026 (99 → 113); review</t>
         </is>
@@ -5962,7 +5959,7 @@
           <t>+1 signed · +0.3 pp</t>
         </is>
       </c>
-      <c r="H138" s="51" t="inlineStr">
+      <c r="H138" s="50" t="inlineStr">
         <is>
           <t>161/308 signed; 2-day gap; not daily movement; Under revised scope since 13 Oct 2026 (189 → 308); review</t>
         </is>
@@ -6152,7 +6149,7 @@
           <t>+0 signed · +0.0 pp</t>
         </is>
       </c>
-      <c r="H143" s="51" t="inlineStr">
+      <c r="H143" s="50" t="inlineStr">
         <is>
           <t>71/113 signed; Under revised scope since 08 Jun 2026 (99 → 113); review</t>
         </is>
@@ -6798,7 +6795,7 @@
           <t>+0 signed · +0.0 pp</t>
         </is>
       </c>
-      <c r="H160" s="51" t="inlineStr">
+      <c r="H160" s="50" t="inlineStr">
         <is>
           <t>161/308 signed; Under revised scope since 13 Oct 2026 (189 → 308); review</t>
         </is>
@@ -6988,7 +6985,7 @@
           <t>+0 signed · +0.0 pp</t>
         </is>
       </c>
-      <c r="H165" s="51" t="inlineStr">
+      <c r="H165" s="50" t="inlineStr">
         <is>
           <t>71/113 signed; Under revised scope since 08 Jun 2026 (99 → 113); review</t>
         </is>
@@ -7634,7 +7631,7 @@
           <t>+0 signed · +0.0 pp</t>
         </is>
       </c>
-      <c r="H182" s="51" t="inlineStr">
+      <c r="H182" s="50" t="inlineStr">
         <is>
           <t>161/308 signed; Under revised scope since 13 Oct 2026 (189 → 308); review</t>
         </is>
@@ -7824,7 +7821,7 @@
           <t>+0 signed · +0.0 pp</t>
         </is>
       </c>
-      <c r="H187" s="51" t="inlineStr">
+      <c r="H187" s="50" t="inlineStr">
         <is>
           <t>71/113 signed; Under revised scope since 08 Jun 2026 (99 → 113); review</t>
         </is>
@@ -8470,7 +8467,7 @@
           <t>+0 signed · +0.0 pp</t>
         </is>
       </c>
-      <c r="H204" s="51" t="inlineStr">
+      <c r="H204" s="50" t="inlineStr">
         <is>
           <t>161/308 signed; Under revised scope since 13 Oct 2026 (189 → 308); review</t>
         </is>
@@ -8660,7 +8657,7 @@
           <t>+0 signed · +0.0 pp</t>
         </is>
       </c>
-      <c r="H209" s="51" t="inlineStr">
+      <c r="H209" s="50" t="inlineStr">
         <is>
           <t>71/113 signed; Under revised scope since 08 Jun 2026 (99 → 113); review</t>
         </is>
@@ -9306,7 +9303,7 @@
           <t>+0 signed · +0.0 pp</t>
         </is>
       </c>
-      <c r="H226" s="51" t="inlineStr">
+      <c r="H226" s="50" t="inlineStr">
         <is>
           <t>161/308 signed; Under revised scope since 13 Oct 2026 (189 → 308); review</t>
         </is>
@@ -9496,7 +9493,7 @@
           <t>+0 signed · +0.0 pp</t>
         </is>
       </c>
-      <c r="H231" s="51" t="inlineStr">
+      <c r="H231" s="50" t="inlineStr">
         <is>
           <t>71/113 signed; Under revised scope since 08 Jun 2026 (99 → 113); review</t>
         </is>
@@ -10142,7 +10139,7 @@
           <t>+0 signed · +0.0 pp</t>
         </is>
       </c>
-      <c r="H248" s="51" t="inlineStr">
+      <c r="H248" s="50" t="inlineStr">
         <is>
           <t>161/308 signed; Under revised scope since 13 Oct 2026 (189 → 308); review</t>
         </is>
@@ -10268,9 +10265,9 @@
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="G2" s="53" t="n"/>
-      <c r="H2" s="53" t="n"/>
-      <c r="I2" s="54" t="n"/>
+      <c r="G2" s="52" t="n"/>
+      <c r="H2" s="52" t="n"/>
+      <c r="I2" s="53" t="n"/>
       <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Chorus @Setia Ecohill 2</t>
@@ -10281,22 +10278,22 @@
           <t>M Legasi Phase 1</t>
         </is>
       </c>
-      <c r="L2" s="53" t="n"/>
-      <c r="M2" s="54" t="n"/>
+      <c r="L2" s="52" t="n"/>
+      <c r="M2" s="53" t="n"/>
       <c r="N2" s="4" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="O2" s="53" t="n"/>
-      <c r="P2" s="54" t="n"/>
+      <c r="O2" s="52" t="n"/>
+      <c r="P2" s="53" t="n"/>
       <c r="Q2" s="4" t="inlineStr">
         <is>
           <t>M Legasi Phase 3</t>
         </is>
       </c>
-      <c r="R2" s="53" t="n"/>
-      <c r="S2" s="54" t="n"/>
+      <c r="R2" s="52" t="n"/>
+      <c r="S2" s="53" t="n"/>
       <c r="T2" s="3" t="inlineStr">
         <is>
           <t>Sapphire Residence @Diamond City</t>
@@ -10307,7 +10304,7 @@
           <t>Springvale Sempurna Heights</t>
         </is>
       </c>
-      <c r="V2" s="54" t="n"/>
+      <c r="V2" s="53" t="n"/>
       <c r="W2" s="3" t="inlineStr">
         <is>
           <t>Zinnia Residences</t>
@@ -10432,12 +10429,12 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="55" t="inlineStr">
+      <c r="A4" s="54" t="inlineStr">
         <is>
           <t>WEEK · 28 Sep 2026 – 4 Oct 2026</t>
         </is>
       </c>
-      <c r="W4" s="56" t="n"/>
+      <c r="W4" s="55" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
@@ -10674,12 +10671,12 @@
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="55" t="inlineStr">
+      <c r="A7" s="54" t="inlineStr">
         <is>
           <t>WEEK · 5 Oct 2026 – 11 Oct 2026</t>
         </is>
       </c>
-      <c r="W7" s="56" t="n"/>
+      <c r="W7" s="55" t="n"/>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
@@ -10916,12 +10913,12 @@
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="55" t="inlineStr">
+      <c r="A10" s="54" t="inlineStr">
         <is>
           <t>WEEK · 12 Oct 2026 – 18 Oct 2026</t>
         </is>
       </c>
-      <c r="W10" s="56" t="n"/>
+      <c r="W10" s="55" t="n"/>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="14" t="inlineStr">
@@ -11158,12 +11155,12 @@
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="55" t="inlineStr">
+      <c r="A13" s="54" t="inlineStr">
         <is>
           <t>WEEK · 19 Oct 2026 – 25 Oct 2026</t>
         </is>
       </c>
-      <c r="W13" s="56" t="n"/>
+      <c r="W13" s="55" t="n"/>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="14" t="inlineStr">
@@ -11400,12 +11397,12 @@
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="55" t="inlineStr">
+      <c r="A16" s="54" t="inlineStr">
         <is>
           <t>WEEK · 26 Oct 2026 – 1 Nov 2026</t>
         </is>
       </c>
-      <c r="W16" s="56" t="n"/>
+      <c r="W16" s="55" t="n"/>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="14" t="inlineStr">

--- a/Broga_Weekly_Tracking.xlsx
+++ b/Broga_Weekly_Tracking.xlsx
@@ -4,11 +4,12 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Snapshot History" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Oct 2026" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TEDUH Search Reference" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Snapshot History'!$A$3:$A$249</definedName>
@@ -21,12 +22,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="dd mmm yyyy"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="dd mmm yyyy"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,6 +79,12 @@
       <b val="1"/>
       <color rgb="00B54708"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="001769AA"/>
+      <sz val="9"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="13">
@@ -291,7 +297,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -380,7 +386,7 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -389,13 +395,13 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -404,7 +410,7 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -416,7 +422,7 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -425,7 +431,7 @@
     <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -446,6 +452,36 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -874,7 +910,7 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="32" t="n">
+      <c r="A4" s="56" t="n">
         <v>45505</v>
       </c>
       <c r="B4" s="33" t="inlineStr">
@@ -897,7 +933,7 @@
           <t>— / 113</t>
         </is>
       </c>
-      <c r="F4" s="35" t="n"/>
+      <c r="F4" s="57" t="n"/>
       <c r="G4" s="36" t="inlineStr">
         <is>
           <t>Not applicable</t>
@@ -910,7 +946,7 @@
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="37" t="n">
+      <c r="A5" s="58" t="n">
         <v>45582</v>
       </c>
       <c r="B5" s="38" t="inlineStr">
@@ -933,7 +969,7 @@
           <t>— / 113</t>
         </is>
       </c>
-      <c r="F5" s="40" t="n"/>
+      <c r="F5" s="59" t="n"/>
       <c r="G5" s="41" t="inlineStr">
         <is>
           <t>Not applicable</t>
@@ -946,7 +982,7 @@
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="37" t="n">
+      <c r="A6" s="58" t="n">
         <v>45582</v>
       </c>
       <c r="B6" s="38" t="inlineStr">
@@ -969,7 +1005,7 @@
           <t>— / 48</t>
         </is>
       </c>
-      <c r="F6" s="40" t="n"/>
+      <c r="F6" s="59" t="n"/>
       <c r="G6" s="41" t="inlineStr">
         <is>
           <t>Not applicable</t>
@@ -982,7 +1018,7 @@
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="32" t="n">
+      <c r="A7" s="56" t="n">
         <v>45625</v>
       </c>
       <c r="B7" s="33" t="inlineStr">
@@ -1005,7 +1041,7 @@
           <t>— / 113</t>
         </is>
       </c>
-      <c r="F7" s="35" t="n"/>
+      <c r="F7" s="57" t="n"/>
       <c r="G7" s="36" t="inlineStr">
         <is>
           <t>Not applicable</t>
@@ -1018,7 +1054,7 @@
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="32" t="n">
+      <c r="A8" s="56" t="n">
         <v>45625</v>
       </c>
       <c r="B8" s="33" t="inlineStr">
@@ -1041,7 +1077,7 @@
           <t>— / 48</t>
         </is>
       </c>
-      <c r="F8" s="35" t="n"/>
+      <c r="F8" s="57" t="n"/>
       <c r="G8" s="36" t="inlineStr">
         <is>
           <t>Not applicable</t>
@@ -1054,7 +1090,7 @@
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="32" t="n">
+      <c r="A9" s="56" t="n">
         <v>45733</v>
       </c>
       <c r="B9" s="33" t="inlineStr">
@@ -1077,7 +1113,7 @@
           <t>— / 81</t>
         </is>
       </c>
-      <c r="F9" s="35" t="n"/>
+      <c r="F9" s="57" t="n"/>
       <c r="G9" s="36" t="inlineStr">
         <is>
           <t>Not applicable</t>
@@ -1090,7 +1126,7 @@
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="37" t="n">
+      <c r="A10" s="58" t="n">
         <v>45733</v>
       </c>
       <c r="B10" s="38" t="inlineStr">
@@ -1113,7 +1149,7 @@
           <t>— / 113</t>
         </is>
       </c>
-      <c r="F10" s="40" t="n"/>
+      <c r="F10" s="59" t="n"/>
       <c r="G10" s="41" t="inlineStr">
         <is>
           <t>Not applicable</t>
@@ -1126,7 +1162,7 @@
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="37" t="n">
+      <c r="A11" s="58" t="n">
         <v>45733</v>
       </c>
       <c r="B11" s="38" t="inlineStr">
@@ -1149,7 +1185,7 @@
           <t>— / 48</t>
         </is>
       </c>
-      <c r="F11" s="40" t="n"/>
+      <c r="F11" s="59" t="n"/>
       <c r="G11" s="41" t="inlineStr">
         <is>
           <t>Not applicable</t>
@@ -1162,7 +1198,7 @@
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="32" t="n">
+      <c r="A12" s="56" t="n">
         <v>45733</v>
       </c>
       <c r="B12" s="33" t="inlineStr">
@@ -1185,7 +1221,7 @@
           <t>9 / 149</t>
         </is>
       </c>
-      <c r="F12" s="35" t="n">
+      <c r="F12" s="57" t="n">
         <v>0.06040268456375839</v>
       </c>
       <c r="G12" s="36" t="inlineStr">
@@ -1200,7 +1236,7 @@
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="32" t="n">
+      <c r="A13" s="56" t="n">
         <v>45889</v>
       </c>
       <c r="B13" s="33" t="inlineStr">
@@ -1223,7 +1259,7 @@
           <t>34 / 113</t>
         </is>
       </c>
-      <c r="F13" s="35" t="n">
+      <c r="F13" s="57" t="n">
         <v>0.3008849557522124</v>
       </c>
       <c r="G13" s="36" t="inlineStr">
@@ -1238,7 +1274,7 @@
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="32" t="n">
+      <c r="A14" s="56" t="n">
         <v>45889</v>
       </c>
       <c r="B14" s="33" t="inlineStr">
@@ -1261,7 +1297,7 @@
           <t>— / 48</t>
         </is>
       </c>
-      <c r="F14" s="35" t="n"/>
+      <c r="F14" s="57" t="n"/>
       <c r="G14" s="36" t="inlineStr">
         <is>
           <t>Not applicable</t>
@@ -1274,7 +1310,7 @@
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="37" t="n">
+      <c r="A15" s="58" t="n">
         <v>45889</v>
       </c>
       <c r="B15" s="38" t="inlineStr">
@@ -1297,7 +1333,7 @@
           <t>21 / 149</t>
         </is>
       </c>
-      <c r="F15" s="40" t="n">
+      <c r="F15" s="59" t="n">
         <v>0.1409395973154362</v>
       </c>
       <c r="G15" s="42" t="inlineStr">
@@ -1312,7 +1348,7 @@
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="37" t="n">
+      <c r="A16" s="58" t="n">
         <v>45894</v>
       </c>
       <c r="B16" s="38" t="inlineStr">
@@ -1335,7 +1371,7 @@
           <t>57 / 111</t>
         </is>
       </c>
-      <c r="F16" s="40" t="n">
+      <c r="F16" s="59" t="n">
         <v>0.5135135135135135</v>
       </c>
       <c r="G16" s="41" t="inlineStr">
@@ -1350,7 +1386,7 @@
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="32" t="n">
+      <c r="A17" s="56" t="n">
         <v>45894</v>
       </c>
       <c r="B17" s="33" t="inlineStr">
@@ -1373,7 +1409,7 @@
           <t>93 / 138</t>
         </is>
       </c>
-      <c r="F17" s="35" t="n">
+      <c r="F17" s="57" t="n">
         <v>0.6739130434782609</v>
       </c>
       <c r="G17" s="36" t="inlineStr">
@@ -1388,7 +1424,7 @@
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="37" t="n">
+      <c r="A18" s="58" t="n">
         <v>45894</v>
       </c>
       <c r="B18" s="38" t="inlineStr">
@@ -1411,7 +1447,7 @@
           <t>44 / 81</t>
         </is>
       </c>
-      <c r="F18" s="40" t="n">
+      <c r="F18" s="59" t="n">
         <v>0.5432098765432098</v>
       </c>
       <c r="G18" s="41" t="inlineStr">
@@ -1426,7 +1462,7 @@
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="37" t="n">
+      <c r="A19" s="58" t="n">
         <v>45894</v>
       </c>
       <c r="B19" s="38" t="inlineStr">
@@ -1449,7 +1485,7 @@
           <t>1 / 27</t>
         </is>
       </c>
-      <c r="F19" s="40" t="n">
+      <c r="F19" s="59" t="n">
         <v>0.03703703703703703</v>
       </c>
       <c r="G19" s="41" t="inlineStr">
@@ -1464,7 +1500,7 @@
       </c>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="32" t="n">
+      <c r="A20" s="56" t="n">
         <v>45894</v>
       </c>
       <c r="B20" s="33" t="inlineStr">
@@ -1487,7 +1523,7 @@
           <t>81 / 189</t>
         </is>
       </c>
-      <c r="F20" s="35" t="n">
+      <c r="F20" s="57" t="n">
         <v>0.4285714285714285</v>
       </c>
       <c r="G20" s="36" t="inlineStr">
@@ -1502,7 +1538,7 @@
       </c>
     </row>
     <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="37" t="n">
+      <c r="A21" s="58" t="n">
         <v>45911</v>
       </c>
       <c r="B21" s="38" t="inlineStr">
@@ -1525,7 +1561,7 @@
           <t>37 / 113</t>
         </is>
       </c>
-      <c r="F21" s="40" t="n">
+      <c r="F21" s="59" t="n">
         <v>0.3274336283185841</v>
       </c>
       <c r="G21" s="42" t="inlineStr">
@@ -1540,7 +1576,7 @@
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="37" t="n">
+      <c r="A22" s="58" t="n">
         <v>45911</v>
       </c>
       <c r="B22" s="38" t="inlineStr">
@@ -1563,7 +1599,7 @@
           <t>— / 48</t>
         </is>
       </c>
-      <c r="F22" s="40" t="n"/>
+      <c r="F22" s="59" t="n"/>
       <c r="G22" s="41" t="inlineStr">
         <is>
           <t>Not applicable</t>
@@ -1576,7 +1612,7 @@
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="37" t="n">
+      <c r="A23" s="58" t="n">
         <v>45936</v>
       </c>
       <c r="B23" s="38" t="inlineStr">
@@ -1599,7 +1635,7 @@
           <t>— / 81</t>
         </is>
       </c>
-      <c r="F23" s="40" t="n"/>
+      <c r="F23" s="59" t="n"/>
       <c r="G23" s="41" t="inlineStr">
         <is>
           <t>Not applicable</t>
@@ -1612,7 +1648,7 @@
       </c>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="32" t="n">
+      <c r="A24" s="56" t="n">
         <v>45936</v>
       </c>
       <c r="B24" s="33" t="inlineStr">
@@ -1635,7 +1671,7 @@
           <t>37 / 113</t>
         </is>
       </c>
-      <c r="F24" s="35" t="n">
+      <c r="F24" s="57" t="n">
         <v>0.3274336283185841</v>
       </c>
       <c r="G24" s="41" t="inlineStr">
@@ -1650,7 +1686,7 @@
       </c>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="32" t="n">
+      <c r="A25" s="56" t="n">
         <v>45936</v>
       </c>
       <c r="B25" s="33" t="inlineStr">
@@ -1673,7 +1709,7 @@
           <t>— / 48</t>
         </is>
       </c>
-      <c r="F25" s="35" t="n"/>
+      <c r="F25" s="57" t="n"/>
       <c r="G25" s="36" t="inlineStr">
         <is>
           <t>Not applicable</t>
@@ -1686,7 +1722,7 @@
       </c>
     </row>
     <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="37" t="n">
+      <c r="A26" s="58" t="n">
         <v>45936</v>
       </c>
       <c r="B26" s="38" t="inlineStr">
@@ -1709,7 +1745,7 @@
           <t>83 / 99</t>
         </is>
       </c>
-      <c r="F26" s="40" t="n">
+      <c r="F26" s="59" t="n">
         <v>0.8383838383838383</v>
       </c>
       <c r="G26" s="41" t="inlineStr">
@@ -1724,7 +1760,7 @@
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="37" t="n">
+      <c r="A27" s="58" t="n">
         <v>45936</v>
       </c>
       <c r="B27" s="38" t="inlineStr">
@@ -1747,7 +1783,7 @@
           <t>45 / 46</t>
         </is>
       </c>
-      <c r="F27" s="40" t="n">
+      <c r="F27" s="59" t="n">
         <v>0.9782608695652174</v>
       </c>
       <c r="G27" s="41" t="inlineStr">
@@ -1762,7 +1798,7 @@
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="32" t="n">
+      <c r="A28" s="56" t="n">
         <v>45936</v>
       </c>
       <c r="B28" s="33" t="inlineStr">
@@ -1785,7 +1821,7 @@
           <t>47 / 56</t>
         </is>
       </c>
-      <c r="F28" s="35" t="n">
+      <c r="F28" s="57" t="n">
         <v>0.8392857142857143</v>
       </c>
       <c r="G28" s="36" t="inlineStr">
@@ -1800,7 +1836,7 @@
       </c>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="37" t="n">
+      <c r="A29" s="58" t="n">
         <v>45936</v>
       </c>
       <c r="B29" s="38" t="inlineStr">
@@ -1823,7 +1859,7 @@
           <t>13 / 25</t>
         </is>
       </c>
-      <c r="F29" s="40" t="n">
+      <c r="F29" s="59" t="n">
         <v>0.52</v>
       </c>
       <c r="G29" s="41" t="inlineStr">
@@ -1838,7 +1874,7 @@
       </c>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="32" t="n">
+      <c r="A30" s="56" t="n">
         <v>45936</v>
       </c>
       <c r="B30" s="33" t="inlineStr">
@@ -1861,7 +1897,7 @@
           <t>3 / 25</t>
         </is>
       </c>
-      <c r="F30" s="35" t="n">
+      <c r="F30" s="57" t="n">
         <v>0.12</v>
       </c>
       <c r="G30" s="36" t="inlineStr">
@@ -1876,7 +1912,7 @@
       </c>
     </row>
     <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="37" t="n">
+      <c r="A31" s="58" t="n">
         <v>45936</v>
       </c>
       <c r="B31" s="38" t="inlineStr">
@@ -1899,7 +1935,7 @@
           <t>87 / 99</t>
         </is>
       </c>
-      <c r="F31" s="40" t="n">
+      <c r="F31" s="59" t="n">
         <v>0.8787878787878788</v>
       </c>
       <c r="G31" s="41" t="inlineStr">
@@ -1914,7 +1950,7 @@
       </c>
     </row>
     <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="32" t="n">
+      <c r="A32" s="56" t="n">
         <v>45936</v>
       </c>
       <c r="B32" s="33" t="inlineStr">
@@ -1937,7 +1973,7 @@
           <t>62 / 111</t>
         </is>
       </c>
-      <c r="F32" s="35" t="n">
+      <c r="F32" s="57" t="n">
         <v>0.5585585585585585</v>
       </c>
       <c r="G32" s="42" t="inlineStr">
@@ -1952,7 +1988,7 @@
       </c>
     </row>
     <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="37" t="n">
+      <c r="A33" s="58" t="n">
         <v>45936</v>
       </c>
       <c r="B33" s="38" t="inlineStr">
@@ -1975,7 +2011,7 @@
           <t>98 / 138</t>
         </is>
       </c>
-      <c r="F33" s="40" t="n">
+      <c r="F33" s="59" t="n">
         <v>0.7101449275362319</v>
       </c>
       <c r="G33" s="42" t="inlineStr">
@@ -1990,7 +2026,7 @@
       </c>
     </row>
     <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="32" t="n">
+      <c r="A34" s="56" t="n">
         <v>45936</v>
       </c>
       <c r="B34" s="33" t="inlineStr">
@@ -2013,7 +2049,7 @@
           <t>52 / 81</t>
         </is>
       </c>
-      <c r="F34" s="35" t="n">
+      <c r="F34" s="57" t="n">
         <v>0.6419753086419753</v>
       </c>
       <c r="G34" s="42" t="inlineStr">
@@ -2028,7 +2064,7 @@
       </c>
     </row>
     <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="37" t="n">
+      <c r="A35" s="58" t="n">
         <v>45936</v>
       </c>
       <c r="B35" s="38" t="inlineStr">
@@ -2051,7 +2087,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F35" s="40" t="n"/>
+      <c r="F35" s="59" t="n"/>
       <c r="G35" s="41" t="inlineStr">
         <is>
           <t>Not applicable</t>
@@ -2064,7 +2100,7 @@
       </c>
     </row>
     <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="32" t="n">
+      <c r="A36" s="56" t="n">
         <v>45936</v>
       </c>
       <c r="B36" s="33" t="inlineStr">
@@ -2087,7 +2123,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F36" s="35" t="n"/>
+      <c r="F36" s="57" t="n"/>
       <c r="G36" s="36" t="inlineStr">
         <is>
           <t>Not applicable</t>
@@ -2100,7 +2136,7 @@
       </c>
     </row>
     <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="37" t="n">
+      <c r="A37" s="58" t="n">
         <v>45936</v>
       </c>
       <c r="B37" s="38" t="inlineStr">
@@ -2123,7 +2159,7 @@
           <t>0 / 27</t>
         </is>
       </c>
-      <c r="F37" s="40" t="n">
+      <c r="F37" s="59" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="43" t="inlineStr">
@@ -2138,7 +2174,7 @@
       </c>
     </row>
     <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="32" t="n">
+      <c r="A38" s="56" t="n">
         <v>45936</v>
       </c>
       <c r="B38" s="33" t="inlineStr">
@@ -2161,7 +2197,7 @@
           <t>84 / 189</t>
         </is>
       </c>
-      <c r="F38" s="35" t="n">
+      <c r="F38" s="57" t="n">
         <v>0.4444444444444444</v>
       </c>
       <c r="G38" s="42" t="inlineStr">
@@ -2176,7 +2212,7 @@
       </c>
     </row>
     <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="32" t="n">
+      <c r="A39" s="56" t="n">
         <v>45936</v>
       </c>
       <c r="B39" s="33" t="inlineStr">
@@ -2199,7 +2235,7 @@
           <t>23 / 149</t>
         </is>
       </c>
-      <c r="F39" s="35" t="n">
+      <c r="F39" s="57" t="n">
         <v>0.1543624161073825</v>
       </c>
       <c r="G39" s="42" t="inlineStr">
@@ -2214,7 +2250,7 @@
       </c>
     </row>
     <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="37" t="n">
+      <c r="A40" s="58" t="n">
         <v>46080</v>
       </c>
       <c r="B40" s="38" t="inlineStr">
@@ -2237,7 +2273,7 @@
           <t>54 / 113</t>
         </is>
       </c>
-      <c r="F40" s="40" t="n">
+      <c r="F40" s="59" t="n">
         <v>0.4778761061946903</v>
       </c>
       <c r="G40" s="42" t="inlineStr">
@@ -2252,7 +2288,7 @@
       </c>
     </row>
     <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="37" t="n">
+      <c r="A41" s="58" t="n">
         <v>46080</v>
       </c>
       <c r="B41" s="38" t="inlineStr">
@@ -2275,7 +2311,7 @@
           <t>15 / 48</t>
         </is>
       </c>
-      <c r="F41" s="40" t="n">
+      <c r="F41" s="59" t="n">
         <v>0.3125</v>
       </c>
       <c r="G41" s="41" t="inlineStr">
@@ -2290,7 +2326,7 @@
       </c>
     </row>
     <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="37" t="n">
+      <c r="A42" s="58" t="n">
         <v>46080</v>
       </c>
       <c r="B42" s="38" t="inlineStr">
@@ -2313,7 +2349,7 @@
           <t>101 / 111</t>
         </is>
       </c>
-      <c r="F42" s="40" t="n">
+      <c r="F42" s="59" t="n">
         <v>0.9099099099099099</v>
       </c>
       <c r="G42" s="42" t="inlineStr">
@@ -2328,7 +2364,7 @@
       </c>
     </row>
     <row r="43" ht="24" customHeight="1">
-      <c r="A43" s="32" t="n">
+      <c r="A43" s="56" t="n">
         <v>46080</v>
       </c>
       <c r="B43" s="33" t="inlineStr">
@@ -2351,7 +2387,7 @@
           <t>131 / 138</t>
         </is>
       </c>
-      <c r="F43" s="35" t="n">
+      <c r="F43" s="57" t="n">
         <v>0.9492753623188406</v>
       </c>
       <c r="G43" s="42" t="inlineStr">
@@ -2366,7 +2402,7 @@
       </c>
     </row>
     <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="37" t="n">
+      <c r="A44" s="58" t="n">
         <v>46080</v>
       </c>
       <c r="B44" s="38" t="inlineStr">
@@ -2389,7 +2425,7 @@
           <t>78 / 81</t>
         </is>
       </c>
-      <c r="F44" s="40" t="n">
+      <c r="F44" s="59" t="n">
         <v>0.9629629629629629</v>
       </c>
       <c r="G44" s="42" t="inlineStr">
@@ -2404,7 +2440,7 @@
       </c>
     </row>
     <row r="45" ht="24" customHeight="1">
-      <c r="A45" s="32" t="n">
+      <c r="A45" s="56" t="n">
         <v>46080</v>
       </c>
       <c r="B45" s="33" t="inlineStr">
@@ -2427,7 +2463,7 @@
           <t>3 / 26</t>
         </is>
       </c>
-      <c r="F45" s="35" t="n">
+      <c r="F45" s="57" t="n">
         <v>0.1153846153846154</v>
       </c>
       <c r="G45" s="36" t="inlineStr">
@@ -2442,7 +2478,7 @@
       </c>
     </row>
     <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="37" t="n">
+      <c r="A46" s="58" t="n">
         <v>46080</v>
       </c>
       <c r="B46" s="38" t="inlineStr">
@@ -2465,7 +2501,7 @@
           <t>77 / 126</t>
         </is>
       </c>
-      <c r="F46" s="40" t="n">
+      <c r="F46" s="59" t="n">
         <v>0.6111111111111112</v>
       </c>
       <c r="G46" s="41" t="inlineStr">
@@ -2480,7 +2516,7 @@
       </c>
     </row>
     <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="32" t="n">
+      <c r="A47" s="56" t="n">
         <v>46080</v>
       </c>
       <c r="B47" s="33" t="inlineStr">
@@ -2503,7 +2539,7 @@
           <t>17 / 104</t>
         </is>
       </c>
-      <c r="F47" s="35" t="n">
+      <c r="F47" s="57" t="n">
         <v>0.1634615384615385</v>
       </c>
       <c r="G47" s="36" t="inlineStr">
@@ -2518,7 +2554,7 @@
       </c>
     </row>
     <row r="48" ht="24" customHeight="1">
-      <c r="A48" s="37" t="n">
+      <c r="A48" s="58" t="n">
         <v>46080</v>
       </c>
       <c r="B48" s="38" t="inlineStr">
@@ -2541,7 +2577,7 @@
           <t>0 / 27</t>
         </is>
       </c>
-      <c r="F48" s="40" t="n">
+      <c r="F48" s="59" t="n">
         <v>0</v>
       </c>
       <c r="G48" s="41" t="inlineStr">
@@ -2556,7 +2592,7 @@
       </c>
     </row>
     <row r="49" ht="24" customHeight="1">
-      <c r="A49" s="32" t="n">
+      <c r="A49" s="56" t="n">
         <v>46080</v>
       </c>
       <c r="B49" s="33" t="inlineStr">
@@ -2579,7 +2615,7 @@
           <t>124 / 189</t>
         </is>
       </c>
-      <c r="F49" s="35" t="n">
+      <c r="F49" s="57" t="n">
         <v>0.656084656084656</v>
       </c>
       <c r="G49" s="42" t="inlineStr">
@@ -2594,7 +2630,7 @@
       </c>
     </row>
     <row r="50" ht="24" customHeight="1">
-      <c r="A50" s="32" t="n">
+      <c r="A50" s="56" t="n">
         <v>46181</v>
       </c>
       <c r="B50" s="33" t="inlineStr">
@@ -2617,7 +2653,7 @@
           <t>48 / 81</t>
         </is>
       </c>
-      <c r="F50" s="35" t="n">
+      <c r="F50" s="57" t="n">
         <v>0.5925925925925926</v>
       </c>
       <c r="G50" s="36" t="inlineStr">
@@ -2632,7 +2668,7 @@
       </c>
     </row>
     <row r="51" ht="24" customHeight="1">
-      <c r="A51" s="37" t="n">
+      <c r="A51" s="58" t="n">
         <v>46181</v>
       </c>
       <c r="B51" s="38" t="inlineStr">
@@ -2655,7 +2691,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F51" s="40" t="n"/>
+      <c r="F51" s="59" t="n"/>
       <c r="G51" s="41" t="inlineStr">
         <is>
           <t>Not applicable</t>
@@ -2668,7 +2704,7 @@
       </c>
     </row>
     <row r="52" ht="24" customHeight="1">
-      <c r="A52" s="32" t="n">
+      <c r="A52" s="56" t="n">
         <v>46181</v>
       </c>
       <c r="B52" s="33" t="inlineStr">
@@ -2691,7 +2727,7 @@
           <t>63 / 113</t>
         </is>
       </c>
-      <c r="F52" s="35" t="n">
+      <c r="F52" s="57" t="n">
         <v>0.5575221238938053</v>
       </c>
       <c r="G52" s="42" t="inlineStr">
@@ -2706,7 +2742,7 @@
       </c>
     </row>
     <row r="53" ht="24" customHeight="1">
-      <c r="A53" s="32" t="n">
+      <c r="A53" s="56" t="n">
         <v>46181</v>
       </c>
       <c r="B53" s="33" t="inlineStr">
@@ -2729,7 +2765,7 @@
           <t>19 / 48</t>
         </is>
       </c>
-      <c r="F53" s="35" t="n">
+      <c r="F53" s="57" t="n">
         <v>0.3958333333333333</v>
       </c>
       <c r="G53" s="42" t="inlineStr">
@@ -2744,7 +2780,7 @@
       </c>
     </row>
     <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="44" t="n">
+      <c r="A54" s="60" t="n">
         <v>46181</v>
       </c>
       <c r="B54" s="45" t="inlineStr">
@@ -2767,7 +2803,7 @@
           <t>70 / 113</t>
         </is>
       </c>
-      <c r="F54" s="47" t="n">
+      <c r="F54" s="61" t="n">
         <v>0.6194690265486725</v>
       </c>
       <c r="G54" s="48" t="inlineStr">
@@ -2782,7 +2818,7 @@
       </c>
     </row>
     <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="37" t="n">
+      <c r="A55" s="58" t="n">
         <v>46181</v>
       </c>
       <c r="B55" s="38" t="inlineStr">
@@ -2805,7 +2841,7 @@
           <t>46 / 46</t>
         </is>
       </c>
-      <c r="F55" s="40" t="n">
+      <c r="F55" s="59" t="n">
         <v>1</v>
       </c>
       <c r="G55" s="42" t="inlineStr">
@@ -2820,7 +2856,7 @@
       </c>
     </row>
     <row r="56" ht="24" customHeight="1">
-      <c r="A56" s="32" t="n">
+      <c r="A56" s="56" t="n">
         <v>46181</v>
       </c>
       <c r="B56" s="33" t="inlineStr">
@@ -2843,7 +2879,7 @@
           <t>56 / 56</t>
         </is>
       </c>
-      <c r="F56" s="35" t="n">
+      <c r="F56" s="57" t="n">
         <v>1</v>
       </c>
       <c r="G56" s="42" t="inlineStr">
@@ -2858,7 +2894,7 @@
       </c>
     </row>
     <row r="57" ht="24" customHeight="1">
-      <c r="A57" s="37" t="n">
+      <c r="A57" s="58" t="n">
         <v>46181</v>
       </c>
       <c r="B57" s="38" t="inlineStr">
@@ -2881,7 +2917,7 @@
           <t>24 / 25</t>
         </is>
       </c>
-      <c r="F57" s="40" t="n">
+      <c r="F57" s="59" t="n">
         <v>0.96</v>
       </c>
       <c r="G57" s="42" t="inlineStr">
@@ -2896,7 +2932,7 @@
       </c>
     </row>
     <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="32" t="n">
+      <c r="A58" s="56" t="n">
         <v>46181</v>
       </c>
       <c r="B58" s="33" t="inlineStr">
@@ -2919,7 +2955,7 @@
           <t>7 / 25</t>
         </is>
       </c>
-      <c r="F58" s="35" t="n">
+      <c r="F58" s="57" t="n">
         <v>0.28</v>
       </c>
       <c r="G58" s="42" t="inlineStr">
@@ -2934,7 +2970,7 @@
       </c>
     </row>
     <row r="59" ht="24" customHeight="1">
-      <c r="A59" s="32" t="n">
+      <c r="A59" s="56" t="n">
         <v>46181</v>
       </c>
       <c r="B59" s="33" t="inlineStr">
@@ -2957,7 +2993,7 @@
           <t>77 / 99</t>
         </is>
       </c>
-      <c r="F59" s="35" t="n">
+      <c r="F59" s="57" t="n">
         <v>0.7777777777777778</v>
       </c>
       <c r="G59" s="43" t="inlineStr">
@@ -2972,7 +3008,7 @@
       </c>
     </row>
     <row r="60" ht="24" customHeight="1">
-      <c r="A60" s="32" t="n">
+      <c r="A60" s="56" t="n">
         <v>46181</v>
       </c>
       <c r="B60" s="33" t="inlineStr">
@@ -2995,7 +3031,7 @@
           <t>102 / 111</t>
         </is>
       </c>
-      <c r="F60" s="35" t="n">
+      <c r="F60" s="57" t="n">
         <v>0.918918918918919</v>
       </c>
       <c r="G60" s="42" t="inlineStr">
@@ -3010,7 +3046,7 @@
       </c>
     </row>
     <row r="61" ht="24" customHeight="1">
-      <c r="A61" s="37" t="n">
+      <c r="A61" s="58" t="n">
         <v>46181</v>
       </c>
       <c r="B61" s="38" t="inlineStr">
@@ -3033,7 +3069,7 @@
           <t>131 / 138</t>
         </is>
       </c>
-      <c r="F61" s="40" t="n">
+      <c r="F61" s="59" t="n">
         <v>0.9492753623188406</v>
       </c>
       <c r="G61" s="41" t="inlineStr">
@@ -3048,7 +3084,7 @@
       </c>
     </row>
     <row r="62" ht="24" customHeight="1">
-      <c r="A62" s="32" t="n">
+      <c r="A62" s="56" t="n">
         <v>46181</v>
       </c>
       <c r="B62" s="33" t="inlineStr">
@@ -3071,7 +3107,7 @@
           <t>78 / 81</t>
         </is>
       </c>
-      <c r="F62" s="35" t="n">
+      <c r="F62" s="57" t="n">
         <v>0.9629629629629629</v>
       </c>
       <c r="G62" s="41" t="inlineStr">
@@ -3086,7 +3122,7 @@
       </c>
     </row>
     <row r="63" ht="24" customHeight="1">
-      <c r="A63" s="37" t="n">
+      <c r="A63" s="58" t="n">
         <v>46181</v>
       </c>
       <c r="B63" s="38" t="inlineStr">
@@ -3109,7 +3145,7 @@
           <t>17 / 26</t>
         </is>
       </c>
-      <c r="F63" s="40" t="n">
+      <c r="F63" s="59" t="n">
         <v>0.6538461538461539</v>
       </c>
       <c r="G63" s="42" t="inlineStr">
@@ -3124,7 +3160,7 @@
       </c>
     </row>
     <row r="64" ht="24" customHeight="1">
-      <c r="A64" s="32" t="n">
+      <c r="A64" s="56" t="n">
         <v>46181</v>
       </c>
       <c r="B64" s="33" t="inlineStr">
@@ -3147,7 +3183,7 @@
           <t>111 / 126</t>
         </is>
       </c>
-      <c r="F64" s="35" t="n">
+      <c r="F64" s="57" t="n">
         <v>0.8809523809523809</v>
       </c>
       <c r="G64" s="42" t="inlineStr">
@@ -3162,7 +3198,7 @@
       </c>
     </row>
     <row r="65" ht="24" customHeight="1">
-      <c r="A65" s="37" t="n">
+      <c r="A65" s="58" t="n">
         <v>46181</v>
       </c>
       <c r="B65" s="38" t="inlineStr">
@@ -3185,7 +3221,7 @@
           <t>71 / 104</t>
         </is>
       </c>
-      <c r="F65" s="40" t="n">
+      <c r="F65" s="59" t="n">
         <v>0.6826923076923077</v>
       </c>
       <c r="G65" s="42" t="inlineStr">
@@ -3200,7 +3236,7 @@
       </c>
     </row>
     <row r="66" ht="24" customHeight="1">
-      <c r="A66" s="37" t="n">
+      <c r="A66" s="58" t="n">
         <v>46181</v>
       </c>
       <c r="B66" s="38" t="inlineStr">
@@ -3223,7 +3259,7 @@
           <t>24 / 136</t>
         </is>
       </c>
-      <c r="F66" s="40" t="n">
+      <c r="F66" s="59" t="n">
         <v>0.1764705882352941</v>
       </c>
       <c r="G66" s="41" t="inlineStr">
@@ -3238,7 +3274,7 @@
       </c>
     </row>
     <row r="67" ht="24" customHeight="1">
-      <c r="A67" s="37" t="n">
+      <c r="A67" s="58" t="n">
         <v>46181</v>
       </c>
       <c r="B67" s="38" t="inlineStr">
@@ -3261,7 +3297,7 @@
           <t>1 / 27</t>
         </is>
       </c>
-      <c r="F67" s="40" t="n">
+      <c r="F67" s="59" t="n">
         <v>0.03703703703703703</v>
       </c>
       <c r="G67" s="42" t="inlineStr">
@@ -3276,7 +3312,7 @@
       </c>
     </row>
     <row r="68" ht="24" customHeight="1">
-      <c r="A68" s="32" t="n">
+      <c r="A68" s="56" t="n">
         <v>46181</v>
       </c>
       <c r="B68" s="33" t="inlineStr">
@@ -3299,7 +3335,7 @@
           <t>148 / 189</t>
         </is>
       </c>
-      <c r="F68" s="35" t="n">
+      <c r="F68" s="57" t="n">
         <v>0.783068783068783</v>
       </c>
       <c r="G68" s="42" t="inlineStr">
@@ -3314,7 +3350,7 @@
       </c>
     </row>
     <row r="69" ht="24" customHeight="1">
-      <c r="A69" s="37" t="n">
+      <c r="A69" s="58" t="n">
         <v>46181</v>
       </c>
       <c r="B69" s="38" t="inlineStr">
@@ -3337,7 +3373,7 @@
           <t>31 / 149</t>
         </is>
       </c>
-      <c r="F69" s="40" t="n">
+      <c r="F69" s="59" t="n">
         <v>0.2080536912751678</v>
       </c>
       <c r="G69" s="42" t="inlineStr">
@@ -3352,7 +3388,7 @@
       </c>
     </row>
     <row r="70" ht="24" customHeight="1">
-      <c r="A70" s="37" t="n">
+      <c r="A70" s="58" t="n">
         <v>46213</v>
       </c>
       <c r="B70" s="38" t="inlineStr">
@@ -3375,7 +3411,7 @@
           <t>53 / 81</t>
         </is>
       </c>
-      <c r="F70" s="40" t="n">
+      <c r="F70" s="59" t="n">
         <v>0.654320987654321</v>
       </c>
       <c r="G70" s="42" t="inlineStr">
@@ -3390,7 +3426,7 @@
       </c>
     </row>
     <row r="71" ht="24" customHeight="1">
-      <c r="A71" s="32" t="n">
+      <c r="A71" s="56" t="n">
         <v>46213</v>
       </c>
       <c r="B71" s="33" t="inlineStr">
@@ -3413,7 +3449,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F71" s="35" t="n"/>
+      <c r="F71" s="57" t="n"/>
       <c r="G71" s="36" t="inlineStr">
         <is>
           <t>Not applicable</t>
@@ -3426,7 +3462,7 @@
       </c>
     </row>
     <row r="72" ht="24" customHeight="1">
-      <c r="A72" s="37" t="n">
+      <c r="A72" s="58" t="n">
         <v>46213</v>
       </c>
       <c r="B72" s="38" t="inlineStr">
@@ -3449,7 +3485,7 @@
           <t>68 / 113</t>
         </is>
       </c>
-      <c r="F72" s="40" t="n">
+      <c r="F72" s="59" t="n">
         <v>0.6017699115044248</v>
       </c>
       <c r="G72" s="42" t="inlineStr">
@@ -3464,7 +3500,7 @@
       </c>
     </row>
     <row r="73" ht="24" customHeight="1">
-      <c r="A73" s="37" t="n">
+      <c r="A73" s="58" t="n">
         <v>46213</v>
       </c>
       <c r="B73" s="38" t="inlineStr">
@@ -3487,7 +3523,7 @@
           <t>19 / 48</t>
         </is>
       </c>
-      <c r="F73" s="40" t="n">
+      <c r="F73" s="59" t="n">
         <v>0.3958333333333333</v>
       </c>
       <c r="G73" s="41" t="inlineStr">
@@ -3502,7 +3538,7 @@
       </c>
     </row>
     <row r="74" ht="24" customHeight="1">
-      <c r="A74" s="37" t="n">
+      <c r="A74" s="58" t="n">
         <v>46213</v>
       </c>
       <c r="B74" s="38" t="inlineStr">
@@ -3525,7 +3561,7 @@
           <t>70 / 113</t>
         </is>
       </c>
-      <c r="F74" s="40" t="n">
+      <c r="F74" s="59" t="n">
         <v>0.6194690265486725</v>
       </c>
       <c r="G74" s="41" t="inlineStr">
@@ -3540,7 +3576,7 @@
       </c>
     </row>
     <row r="75" ht="24" customHeight="1">
-      <c r="A75" s="37" t="n">
+      <c r="A75" s="58" t="n">
         <v>46213</v>
       </c>
       <c r="B75" s="38" t="inlineStr">
@@ -3563,7 +3599,7 @@
           <t>46 / 46</t>
         </is>
       </c>
-      <c r="F75" s="40" t="n">
+      <c r="F75" s="59" t="n">
         <v>1</v>
       </c>
       <c r="G75" s="41" t="inlineStr">
@@ -3578,7 +3614,7 @@
       </c>
     </row>
     <row r="76" ht="24" customHeight="1">
-      <c r="A76" s="32" t="n">
+      <c r="A76" s="56" t="n">
         <v>46213</v>
       </c>
       <c r="B76" s="33" t="inlineStr">
@@ -3601,7 +3637,7 @@
           <t>56 / 56</t>
         </is>
       </c>
-      <c r="F76" s="35" t="n">
+      <c r="F76" s="57" t="n">
         <v>1</v>
       </c>
       <c r="G76" s="41" t="inlineStr">
@@ -3616,7 +3652,7 @@
       </c>
     </row>
     <row r="77" ht="24" customHeight="1">
-      <c r="A77" s="37" t="n">
+      <c r="A77" s="58" t="n">
         <v>46213</v>
       </c>
       <c r="B77" s="38" t="inlineStr">
@@ -3639,7 +3675,7 @@
           <t>24 / 25</t>
         </is>
       </c>
-      <c r="F77" s="40" t="n">
+      <c r="F77" s="59" t="n">
         <v>0.96</v>
       </c>
       <c r="G77" s="41" t="inlineStr">
@@ -3654,7 +3690,7 @@
       </c>
     </row>
     <row r="78" ht="24" customHeight="1">
-      <c r="A78" s="32" t="n">
+      <c r="A78" s="56" t="n">
         <v>46213</v>
       </c>
       <c r="B78" s="33" t="inlineStr">
@@ -3677,7 +3713,7 @@
           <t>8 / 25</t>
         </is>
       </c>
-      <c r="F78" s="35" t="n">
+      <c r="F78" s="57" t="n">
         <v>0.32</v>
       </c>
       <c r="G78" s="42" t="inlineStr">
@@ -3692,7 +3728,7 @@
       </c>
     </row>
     <row r="79" ht="24" customHeight="1">
-      <c r="A79" s="37" t="n">
+      <c r="A79" s="58" t="n">
         <v>46213</v>
       </c>
       <c r="B79" s="38" t="inlineStr">
@@ -3715,7 +3751,7 @@
           <t>77 / 99</t>
         </is>
       </c>
-      <c r="F79" s="40" t="n">
+      <c r="F79" s="59" t="n">
         <v>0.7777777777777778</v>
       </c>
       <c r="G79" s="41" t="inlineStr">
@@ -3730,7 +3766,7 @@
       </c>
     </row>
     <row r="80" ht="24" customHeight="1">
-      <c r="A80" s="37" t="n">
+      <c r="A80" s="58" t="n">
         <v>46213</v>
       </c>
       <c r="B80" s="38" t="inlineStr">
@@ -3753,7 +3789,7 @@
           <t>102 / 111</t>
         </is>
       </c>
-      <c r="F80" s="40" t="n">
+      <c r="F80" s="59" t="n">
         <v>0.918918918918919</v>
       </c>
       <c r="G80" s="41" t="inlineStr">
@@ -3768,7 +3804,7 @@
       </c>
     </row>
     <row r="81" ht="24" customHeight="1">
-      <c r="A81" s="32" t="n">
+      <c r="A81" s="56" t="n">
         <v>46213</v>
       </c>
       <c r="B81" s="33" t="inlineStr">
@@ -3791,7 +3827,7 @@
           <t>131 / 138</t>
         </is>
       </c>
-      <c r="F81" s="35" t="n">
+      <c r="F81" s="57" t="n">
         <v>0.9492753623188406</v>
       </c>
       <c r="G81" s="41" t="inlineStr">
@@ -3806,7 +3842,7 @@
       </c>
     </row>
     <row r="82" ht="24" customHeight="1">
-      <c r="A82" s="37" t="n">
+      <c r="A82" s="58" t="n">
         <v>46213</v>
       </c>
       <c r="B82" s="38" t="inlineStr">
@@ -3829,7 +3865,7 @@
           <t>78 / 81</t>
         </is>
       </c>
-      <c r="F82" s="40" t="n">
+      <c r="F82" s="59" t="n">
         <v>0.9629629629629629</v>
       </c>
       <c r="G82" s="41" t="inlineStr">
@@ -3844,7 +3880,7 @@
       </c>
     </row>
     <row r="83" ht="24" customHeight="1">
-      <c r="A83" s="32" t="n">
+      <c r="A83" s="56" t="n">
         <v>46213</v>
       </c>
       <c r="B83" s="33" t="inlineStr">
@@ -3867,7 +3903,7 @@
           <t>17 / 26</t>
         </is>
       </c>
-      <c r="F83" s="35" t="n">
+      <c r="F83" s="57" t="n">
         <v>0.6538461538461539</v>
       </c>
       <c r="G83" s="41" t="inlineStr">
@@ -3882,7 +3918,7 @@
       </c>
     </row>
     <row r="84" ht="24" customHeight="1">
-      <c r="A84" s="37" t="n">
+      <c r="A84" s="58" t="n">
         <v>46213</v>
       </c>
       <c r="B84" s="38" t="inlineStr">
@@ -3905,7 +3941,7 @@
           <t>116 / 126</t>
         </is>
       </c>
-      <c r="F84" s="40" t="n">
+      <c r="F84" s="59" t="n">
         <v>0.9206349206349206</v>
       </c>
       <c r="G84" s="42" t="inlineStr">
@@ -3920,7 +3956,7 @@
       </c>
     </row>
     <row r="85" ht="24" customHeight="1">
-      <c r="A85" s="32" t="n">
+      <c r="A85" s="56" t="n">
         <v>46213</v>
       </c>
       <c r="B85" s="33" t="inlineStr">
@@ -3943,7 +3979,7 @@
           <t>89 / 104</t>
         </is>
       </c>
-      <c r="F85" s="35" t="n">
+      <c r="F85" s="57" t="n">
         <v>0.8557692307692307</v>
       </c>
       <c r="G85" s="42" t="inlineStr">
@@ -3958,7 +3994,7 @@
       </c>
     </row>
     <row r="86" ht="24" customHeight="1">
-      <c r="A86" s="32" t="n">
+      <c r="A86" s="56" t="n">
         <v>46213</v>
       </c>
       <c r="B86" s="33" t="inlineStr">
@@ -3981,7 +4017,7 @@
           <t>16 / 44</t>
         </is>
       </c>
-      <c r="F86" s="35" t="n">
+      <c r="F86" s="57" t="n">
         <v>0.3636363636363636</v>
       </c>
       <c r="G86" s="36" t="inlineStr">
@@ -3996,7 +4032,7 @@
       </c>
     </row>
     <row r="87" ht="24" customHeight="1">
-      <c r="A87" s="37" t="n">
+      <c r="A87" s="58" t="n">
         <v>46213</v>
       </c>
       <c r="B87" s="38" t="inlineStr">
@@ -4019,7 +4055,7 @@
           <t>39 / 85</t>
         </is>
       </c>
-      <c r="F87" s="40" t="n">
+      <c r="F87" s="59" t="n">
         <v>0.4588235294117647</v>
       </c>
       <c r="G87" s="41" t="inlineStr">
@@ -4034,7 +4070,7 @@
       </c>
     </row>
     <row r="88" ht="24" customHeight="1">
-      <c r="A88" s="32" t="n">
+      <c r="A88" s="56" t="n">
         <v>46213</v>
       </c>
       <c r="B88" s="33" t="inlineStr">
@@ -4057,7 +4093,7 @@
           <t>11 / 102</t>
         </is>
       </c>
-      <c r="F88" s="35" t="n">
+      <c r="F88" s="57" t="n">
         <v>0.107843137254902</v>
       </c>
       <c r="G88" s="36" t="inlineStr">
@@ -4072,7 +4108,7 @@
       </c>
     </row>
     <row r="89" ht="24" customHeight="1">
-      <c r="A89" s="32" t="n">
+      <c r="A89" s="56" t="n">
         <v>46213</v>
       </c>
       <c r="B89" s="33" t="inlineStr">
@@ -4095,7 +4131,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F89" s="35" t="n"/>
+      <c r="F89" s="57" t="n"/>
       <c r="G89" s="36" t="inlineStr">
         <is>
           <t>Not applicable</t>
@@ -4108,7 +4144,7 @@
       </c>
     </row>
     <row r="90" ht="24" customHeight="1">
-      <c r="A90" s="32" t="n">
+      <c r="A90" s="56" t="n">
         <v>46213</v>
       </c>
       <c r="B90" s="33" t="inlineStr">
@@ -4131,7 +4167,7 @@
           <t>30 / 136</t>
         </is>
       </c>
-      <c r="F90" s="35" t="n">
+      <c r="F90" s="57" t="n">
         <v>0.2205882352941176</v>
       </c>
       <c r="G90" s="42" t="inlineStr">
@@ -4146,7 +4182,7 @@
       </c>
     </row>
     <row r="91" ht="24" customHeight="1">
-      <c r="A91" s="37" t="n">
+      <c r="A91" s="58" t="n">
         <v>46213</v>
       </c>
       <c r="B91" s="38" t="inlineStr">
@@ -4169,7 +4205,7 @@
           <t>1 / 27</t>
         </is>
       </c>
-      <c r="F91" s="40" t="n">
+      <c r="F91" s="59" t="n">
         <v>0.03703703703703703</v>
       </c>
       <c r="G91" s="41" t="inlineStr">
@@ -4184,7 +4220,7 @@
       </c>
     </row>
     <row r="92" ht="24" customHeight="1">
-      <c r="A92" s="32" t="n">
+      <c r="A92" s="56" t="n">
         <v>46213</v>
       </c>
       <c r="B92" s="33" t="inlineStr">
@@ -4207,7 +4243,7 @@
           <t>154 / 189</t>
         </is>
       </c>
-      <c r="F92" s="35" t="n">
+      <c r="F92" s="57" t="n">
         <v>0.8148148148148148</v>
       </c>
       <c r="G92" s="42" t="inlineStr">
@@ -4222,7 +4258,7 @@
       </c>
     </row>
     <row r="93" ht="24" customHeight="1">
-      <c r="A93" s="32" t="n">
+      <c r="A93" s="56" t="n">
         <v>46213</v>
       </c>
       <c r="B93" s="33" t="inlineStr">
@@ -4245,7 +4281,7 @@
           <t>34 / 149</t>
         </is>
       </c>
-      <c r="F93" s="35" t="n">
+      <c r="F93" s="57" t="n">
         <v>0.2281879194630873</v>
       </c>
       <c r="G93" s="42" t="inlineStr">
@@ -4260,7 +4296,7 @@
       </c>
     </row>
     <row r="94" ht="24" customHeight="1">
-      <c r="A94" s="32" t="n">
+      <c r="A94" s="56" t="n">
         <v>46308</v>
       </c>
       <c r="B94" s="33" t="inlineStr">
@@ -4283,7 +4319,7 @@
           <t>72 / 81</t>
         </is>
       </c>
-      <c r="F94" s="35" t="n">
+      <c r="F94" s="57" t="n">
         <v>0.8888888888888888</v>
       </c>
       <c r="G94" s="42" t="inlineStr">
@@ -4298,7 +4334,7 @@
       </c>
     </row>
     <row r="95" ht="24" customHeight="1">
-      <c r="A95" s="37" t="n">
+      <c r="A95" s="58" t="n">
         <v>46308</v>
       </c>
       <c r="B95" s="38" t="inlineStr">
@@ -4321,7 +4357,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F95" s="40" t="n"/>
+      <c r="F95" s="59" t="n"/>
       <c r="G95" s="41" t="inlineStr">
         <is>
           <t>Not applicable</t>
@@ -4334,7 +4370,7 @@
       </c>
     </row>
     <row r="96" ht="24" customHeight="1">
-      <c r="A96" s="32" t="n">
+      <c r="A96" s="56" t="n">
         <v>46308</v>
       </c>
       <c r="B96" s="33" t="inlineStr">
@@ -4357,7 +4393,7 @@
           <t>68 / 113</t>
         </is>
       </c>
-      <c r="F96" s="35" t="n">
+      <c r="F96" s="57" t="n">
         <v>0.6017699115044248</v>
       </c>
       <c r="G96" s="41" t="inlineStr">
@@ -4372,7 +4408,7 @@
       </c>
     </row>
     <row r="97" ht="24" customHeight="1">
-      <c r="A97" s="32" t="n">
+      <c r="A97" s="56" t="n">
         <v>46308</v>
       </c>
       <c r="B97" s="33" t="inlineStr">
@@ -4395,7 +4431,7 @@
           <t>21 / 48</t>
         </is>
       </c>
-      <c r="F97" s="35" t="n">
+      <c r="F97" s="57" t="n">
         <v>0.4375</v>
       </c>
       <c r="G97" s="42" t="inlineStr">
@@ -4410,7 +4446,7 @@
       </c>
     </row>
     <row r="98" ht="24" customHeight="1">
-      <c r="A98" s="32" t="n">
+      <c r="A98" s="56" t="n">
         <v>46308</v>
       </c>
       <c r="B98" s="33" t="inlineStr">
@@ -4433,7 +4469,7 @@
           <t>71 / 113</t>
         </is>
       </c>
-      <c r="F98" s="35" t="n">
+      <c r="F98" s="57" t="n">
         <v>0.6283185840707964</v>
       </c>
       <c r="G98" s="42" t="inlineStr">
@@ -4448,7 +4484,7 @@
       </c>
     </row>
     <row r="99" ht="24" customHeight="1">
-      <c r="A99" s="37" t="n">
+      <c r="A99" s="58" t="n">
         <v>46308</v>
       </c>
       <c r="B99" s="38" t="inlineStr">
@@ -4471,7 +4507,7 @@
           <t>46 / 46</t>
         </is>
       </c>
-      <c r="F99" s="40" t="n">
+      <c r="F99" s="59" t="n">
         <v>1</v>
       </c>
       <c r="G99" s="41" t="inlineStr">
@@ -4486,7 +4522,7 @@
       </c>
     </row>
     <row r="100" ht="24" customHeight="1">
-      <c r="A100" s="32" t="n">
+      <c r="A100" s="56" t="n">
         <v>46308</v>
       </c>
       <c r="B100" s="33" t="inlineStr">
@@ -4509,7 +4545,7 @@
           <t>56 / 56</t>
         </is>
       </c>
-      <c r="F100" s="35" t="n">
+      <c r="F100" s="57" t="n">
         <v>1</v>
       </c>
       <c r="G100" s="41" t="inlineStr">
@@ -4524,7 +4560,7 @@
       </c>
     </row>
     <row r="101" ht="24" customHeight="1">
-      <c r="A101" s="37" t="n">
+      <c r="A101" s="58" t="n">
         <v>46308</v>
       </c>
       <c r="B101" s="38" t="inlineStr">
@@ -4547,7 +4583,7 @@
           <t>24 / 25</t>
         </is>
       </c>
-      <c r="F101" s="40" t="n">
+      <c r="F101" s="59" t="n">
         <v>0.96</v>
       </c>
       <c r="G101" s="41" t="inlineStr">
@@ -4562,7 +4598,7 @@
       </c>
     </row>
     <row r="102" ht="24" customHeight="1">
-      <c r="A102" s="32" t="n">
+      <c r="A102" s="56" t="n">
         <v>46308</v>
       </c>
       <c r="B102" s="33" t="inlineStr">
@@ -4585,7 +4621,7 @@
           <t>10 / 25</t>
         </is>
       </c>
-      <c r="F102" s="35" t="n">
+      <c r="F102" s="57" t="n">
         <v>0.4</v>
       </c>
       <c r="G102" s="42" t="inlineStr">
@@ -4600,7 +4636,7 @@
       </c>
     </row>
     <row r="103" ht="24" customHeight="1">
-      <c r="A103" s="32" t="n">
+      <c r="A103" s="56" t="n">
         <v>46308</v>
       </c>
       <c r="B103" s="33" t="inlineStr">
@@ -4623,7 +4659,7 @@
           <t>77 / 99</t>
         </is>
       </c>
-      <c r="F103" s="35" t="n">
+      <c r="F103" s="57" t="n">
         <v>0.7777777777777778</v>
       </c>
       <c r="G103" s="41" t="inlineStr">
@@ -4638,7 +4674,7 @@
       </c>
     </row>
     <row r="104" ht="24" customHeight="1">
-      <c r="A104" s="32" t="n">
+      <c r="A104" s="56" t="n">
         <v>46308</v>
       </c>
       <c r="B104" s="33" t="inlineStr">
@@ -4661,7 +4697,7 @@
           <t>111 / 111</t>
         </is>
       </c>
-      <c r="F104" s="35" t="n">
+      <c r="F104" s="57" t="n">
         <v>1</v>
       </c>
       <c r="G104" s="42" t="inlineStr">
@@ -4676,7 +4712,7 @@
       </c>
     </row>
     <row r="105" ht="24" customHeight="1">
-      <c r="A105" s="37" t="n">
+      <c r="A105" s="58" t="n">
         <v>46308</v>
       </c>
       <c r="B105" s="38" t="inlineStr">
@@ -4699,7 +4735,7 @@
           <t>134 / 138</t>
         </is>
       </c>
-      <c r="F105" s="40" t="n">
+      <c r="F105" s="59" t="n">
         <v>0.9710144927536232</v>
       </c>
       <c r="G105" s="42" t="inlineStr">
@@ -4714,7 +4750,7 @@
       </c>
     </row>
     <row r="106" ht="24" customHeight="1">
-      <c r="A106" s="32" t="n">
+      <c r="A106" s="56" t="n">
         <v>46308</v>
       </c>
       <c r="B106" s="33" t="inlineStr">
@@ -4737,7 +4773,7 @@
           <t>79 / 81</t>
         </is>
       </c>
-      <c r="F106" s="35" t="n">
+      <c r="F106" s="57" t="n">
         <v>0.9753086419753086</v>
       </c>
       <c r="G106" s="42" t="inlineStr">
@@ -4752,7 +4788,7 @@
       </c>
     </row>
     <row r="107" ht="24" customHeight="1">
-      <c r="A107" s="37" t="n">
+      <c r="A107" s="58" t="n">
         <v>46308</v>
       </c>
       <c r="B107" s="38" t="inlineStr">
@@ -4775,7 +4811,7 @@
           <t>23 / 26</t>
         </is>
       </c>
-      <c r="F107" s="40" t="n">
+      <c r="F107" s="59" t="n">
         <v>0.8846153846153846</v>
       </c>
       <c r="G107" s="42" t="inlineStr">
@@ -4790,7 +4826,7 @@
       </c>
     </row>
     <row r="108" ht="24" customHeight="1">
-      <c r="A108" s="32" t="n">
+      <c r="A108" s="56" t="n">
         <v>46308</v>
       </c>
       <c r="B108" s="33" t="inlineStr">
@@ -4813,7 +4849,7 @@
           <t>124 / 126</t>
         </is>
       </c>
-      <c r="F108" s="35" t="n">
+      <c r="F108" s="57" t="n">
         <v>0.9841269841269841</v>
       </c>
       <c r="G108" s="42" t="inlineStr">
@@ -4828,7 +4864,7 @@
       </c>
     </row>
     <row r="109" ht="24" customHeight="1">
-      <c r="A109" s="37" t="n">
+      <c r="A109" s="58" t="n">
         <v>46308</v>
       </c>
       <c r="B109" s="38" t="inlineStr">
@@ -4851,7 +4887,7 @@
           <t>98 / 104</t>
         </is>
       </c>
-      <c r="F109" s="40" t="n">
+      <c r="F109" s="59" t="n">
         <v>0.9423076923076923</v>
       </c>
       <c r="G109" s="42" t="inlineStr">
@@ -4866,7 +4902,7 @@
       </c>
     </row>
     <row r="110" ht="24" customHeight="1">
-      <c r="A110" s="37" t="n">
+      <c r="A110" s="58" t="n">
         <v>46308</v>
       </c>
       <c r="B110" s="38" t="inlineStr">
@@ -4889,7 +4925,7 @@
           <t>29 / 44</t>
         </is>
       </c>
-      <c r="F110" s="40" t="n">
+      <c r="F110" s="59" t="n">
         <v>0.6590909090909091</v>
       </c>
       <c r="G110" s="42" t="inlineStr">
@@ -4904,7 +4940,7 @@
       </c>
     </row>
     <row r="111" ht="24" customHeight="1">
-      <c r="A111" s="32" t="n">
+      <c r="A111" s="56" t="n">
         <v>46308</v>
       </c>
       <c r="B111" s="33" t="inlineStr">
@@ -4927,7 +4963,7 @@
           <t>63 / 85</t>
         </is>
       </c>
-      <c r="F111" s="35" t="n">
+      <c r="F111" s="57" t="n">
         <v>0.7411764705882353</v>
       </c>
       <c r="G111" s="42" t="inlineStr">
@@ -4942,7 +4978,7 @@
       </c>
     </row>
     <row r="112" ht="24" customHeight="1">
-      <c r="A112" s="37" t="n">
+      <c r="A112" s="58" t="n">
         <v>46308</v>
       </c>
       <c r="B112" s="38" t="inlineStr">
@@ -4965,7 +5001,7 @@
           <t>22 / 102</t>
         </is>
       </c>
-      <c r="F112" s="40" t="n">
+      <c r="F112" s="59" t="n">
         <v>0.2156862745098039</v>
       </c>
       <c r="G112" s="42" t="inlineStr">
@@ -4980,7 +5016,7 @@
       </c>
     </row>
     <row r="113" ht="24" customHeight="1">
-      <c r="A113" s="37" t="n">
+      <c r="A113" s="58" t="n">
         <v>46308</v>
       </c>
       <c r="B113" s="38" t="inlineStr">
@@ -5003,7 +5039,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F113" s="40" t="n"/>
+      <c r="F113" s="59" t="n"/>
       <c r="G113" s="41" t="inlineStr">
         <is>
           <t>Not applicable</t>
@@ -5016,7 +5052,7 @@
       </c>
     </row>
     <row r="114" ht="24" customHeight="1">
-      <c r="A114" s="37" t="n">
+      <c r="A114" s="58" t="n">
         <v>46308</v>
       </c>
       <c r="B114" s="38" t="inlineStr">
@@ -5039,7 +5075,7 @@
           <t>45 / 136</t>
         </is>
       </c>
-      <c r="F114" s="40" t="n">
+      <c r="F114" s="59" t="n">
         <v>0.3308823529411765</v>
       </c>
       <c r="G114" s="42" t="inlineStr">
@@ -5054,7 +5090,7 @@
       </c>
     </row>
     <row r="115" ht="24" customHeight="1">
-      <c r="A115" s="37" t="n">
+      <c r="A115" s="58" t="n">
         <v>46308</v>
       </c>
       <c r="B115" s="38" t="inlineStr">
@@ -5077,7 +5113,7 @@
           <t>1 / 27</t>
         </is>
       </c>
-      <c r="F115" s="40" t="n">
+      <c r="F115" s="59" t="n">
         <v>0.03703703703703703</v>
       </c>
       <c r="G115" s="41" t="inlineStr">
@@ -5092,7 +5128,7 @@
       </c>
     </row>
     <row r="116" ht="30" customHeight="1">
-      <c r="A116" s="44" t="n">
+      <c r="A116" s="60" t="n">
         <v>46308</v>
       </c>
       <c r="B116" s="45" t="inlineStr">
@@ -5115,7 +5151,7 @@
           <t>160 / 308</t>
         </is>
       </c>
-      <c r="F116" s="47" t="n">
+      <c r="F116" s="61" t="n">
         <v>0.5194805194805194</v>
       </c>
       <c r="G116" s="51" t="inlineStr">
@@ -5130,7 +5166,7 @@
       </c>
     </row>
     <row r="117" ht="24" customHeight="1">
-      <c r="A117" s="37" t="n">
+      <c r="A117" s="58" t="n">
         <v>46308</v>
       </c>
       <c r="B117" s="38" t="inlineStr">
@@ -5153,7 +5189,7 @@
           <t>34 / 149</t>
         </is>
       </c>
-      <c r="F117" s="40" t="n">
+      <c r="F117" s="59" t="n">
         <v>0.2281879194630873</v>
       </c>
       <c r="G117" s="41" t="inlineStr">
@@ -5168,7 +5204,7 @@
       </c>
     </row>
     <row r="118" ht="24" customHeight="1">
-      <c r="A118" s="37" t="n">
+      <c r="A118" s="58" t="n">
         <v>46310</v>
       </c>
       <c r="B118" s="38" t="inlineStr">
@@ -5191,7 +5227,7 @@
           <t>74 / 81</t>
         </is>
       </c>
-      <c r="F118" s="40" t="n">
+      <c r="F118" s="59" t="n">
         <v>0.9135802469135802</v>
       </c>
       <c r="G118" s="42" t="inlineStr">
@@ -5206,7 +5242,7 @@
       </c>
     </row>
     <row r="119" ht="24" customHeight="1">
-      <c r="A119" s="37" t="n">
+      <c r="A119" s="58" t="n">
         <v>46310</v>
       </c>
       <c r="B119" s="38" t="inlineStr">
@@ -5229,7 +5265,7 @@
           <t>68 / 113</t>
         </is>
       </c>
-      <c r="F119" s="40" t="n">
+      <c r="F119" s="59" t="n">
         <v>0.6017699115044248</v>
       </c>
       <c r="G119" s="41" t="inlineStr">
@@ -5244,7 +5280,7 @@
       </c>
     </row>
     <row r="120" ht="24" customHeight="1">
-      <c r="A120" s="37" t="n">
+      <c r="A120" s="58" t="n">
         <v>46310</v>
       </c>
       <c r="B120" s="38" t="inlineStr">
@@ -5267,7 +5303,7 @@
           <t>21 / 48</t>
         </is>
       </c>
-      <c r="F120" s="40" t="n">
+      <c r="F120" s="59" t="n">
         <v>0.4375</v>
       </c>
       <c r="G120" s="41" t="inlineStr">
@@ -5282,7 +5318,7 @@
       </c>
     </row>
     <row r="121" ht="24" customHeight="1">
-      <c r="A121" s="37" t="n">
+      <c r="A121" s="58" t="n">
         <v>46310</v>
       </c>
       <c r="B121" s="38" t="inlineStr">
@@ -5305,7 +5341,7 @@
           <t>71 / 113</t>
         </is>
       </c>
-      <c r="F121" s="40" t="n">
+      <c r="F121" s="59" t="n">
         <v>0.6283185840707964</v>
       </c>
       <c r="G121" s="41" t="inlineStr">
@@ -5320,7 +5356,7 @@
       </c>
     </row>
     <row r="122" ht="24" customHeight="1">
-      <c r="A122" s="37" t="n">
+      <c r="A122" s="58" t="n">
         <v>46310</v>
       </c>
       <c r="B122" s="38" t="inlineStr">
@@ -5343,7 +5379,7 @@
           <t>46 / 46</t>
         </is>
       </c>
-      <c r="F122" s="40" t="n">
+      <c r="F122" s="59" t="n">
         <v>1</v>
       </c>
       <c r="G122" s="41" t="inlineStr">
@@ -5358,7 +5394,7 @@
       </c>
     </row>
     <row r="123" ht="24" customHeight="1">
-      <c r="A123" s="32" t="n">
+      <c r="A123" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="B123" s="33" t="inlineStr">
@@ -5381,7 +5417,7 @@
           <t>56 / 56</t>
         </is>
       </c>
-      <c r="F123" s="35" t="n">
+      <c r="F123" s="57" t="n">
         <v>1</v>
       </c>
       <c r="G123" s="41" t="inlineStr">
@@ -5396,7 +5432,7 @@
       </c>
     </row>
     <row r="124" ht="24" customHeight="1">
-      <c r="A124" s="37" t="n">
+      <c r="A124" s="58" t="n">
         <v>46310</v>
       </c>
       <c r="B124" s="38" t="inlineStr">
@@ -5419,7 +5455,7 @@
           <t>24 / 25</t>
         </is>
       </c>
-      <c r="F124" s="40" t="n">
+      <c r="F124" s="59" t="n">
         <v>0.96</v>
       </c>
       <c r="G124" s="41" t="inlineStr">
@@ -5434,7 +5470,7 @@
       </c>
     </row>
     <row r="125" ht="24" customHeight="1">
-      <c r="A125" s="32" t="n">
+      <c r="A125" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="B125" s="33" t="inlineStr">
@@ -5457,7 +5493,7 @@
           <t>10 / 25</t>
         </is>
       </c>
-      <c r="F125" s="35" t="n">
+      <c r="F125" s="57" t="n">
         <v>0.4</v>
       </c>
       <c r="G125" s="41" t="inlineStr">
@@ -5472,7 +5508,7 @@
       </c>
     </row>
     <row r="126" ht="24" customHeight="1">
-      <c r="A126" s="37" t="n">
+      <c r="A126" s="58" t="n">
         <v>46310</v>
       </c>
       <c r="B126" s="38" t="inlineStr">
@@ -5495,7 +5531,7 @@
           <t>77 / 99</t>
         </is>
       </c>
-      <c r="F126" s="40" t="n">
+      <c r="F126" s="59" t="n">
         <v>0.7777777777777778</v>
       </c>
       <c r="G126" s="41" t="inlineStr">
@@ -5510,7 +5546,7 @@
       </c>
     </row>
     <row r="127" ht="24" customHeight="1">
-      <c r="A127" s="37" t="n">
+      <c r="A127" s="58" t="n">
         <v>46310</v>
       </c>
       <c r="B127" s="38" t="inlineStr">
@@ -5533,7 +5569,7 @@
           <t>111 / 111</t>
         </is>
       </c>
-      <c r="F127" s="40" t="n">
+      <c r="F127" s="59" t="n">
         <v>1</v>
       </c>
       <c r="G127" s="41" t="inlineStr">
@@ -5548,7 +5584,7 @@
       </c>
     </row>
     <row r="128" ht="24" customHeight="1">
-      <c r="A128" s="32" t="n">
+      <c r="A128" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="B128" s="33" t="inlineStr">
@@ -5571,7 +5607,7 @@
           <t>134 / 138</t>
         </is>
       </c>
-      <c r="F128" s="35" t="n">
+      <c r="F128" s="57" t="n">
         <v>0.9710144927536232</v>
       </c>
       <c r="G128" s="41" t="inlineStr">
@@ -5586,7 +5622,7 @@
       </c>
     </row>
     <row r="129" ht="24" customHeight="1">
-      <c r="A129" s="37" t="n">
+      <c r="A129" s="58" t="n">
         <v>46310</v>
       </c>
       <c r="B129" s="38" t="inlineStr">
@@ -5609,7 +5645,7 @@
           <t>79 / 81</t>
         </is>
       </c>
-      <c r="F129" s="40" t="n">
+      <c r="F129" s="59" t="n">
         <v>0.9753086419753086</v>
       </c>
       <c r="G129" s="41" t="inlineStr">
@@ -5624,7 +5660,7 @@
       </c>
     </row>
     <row r="130" ht="24" customHeight="1">
-      <c r="A130" s="32" t="n">
+      <c r="A130" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="B130" s="33" t="inlineStr">
@@ -5647,7 +5683,7 @@
           <t>23 / 26</t>
         </is>
       </c>
-      <c r="F130" s="35" t="n">
+      <c r="F130" s="57" t="n">
         <v>0.8846153846153846</v>
       </c>
       <c r="G130" s="41" t="inlineStr">
@@ -5662,7 +5698,7 @@
       </c>
     </row>
     <row r="131" ht="24" customHeight="1">
-      <c r="A131" s="37" t="n">
+      <c r="A131" s="58" t="n">
         <v>46310</v>
       </c>
       <c r="B131" s="38" t="inlineStr">
@@ -5685,7 +5721,7 @@
           <t>124 / 126</t>
         </is>
       </c>
-      <c r="F131" s="40" t="n">
+      <c r="F131" s="59" t="n">
         <v>0.9841269841269841</v>
       </c>
       <c r="G131" s="41" t="inlineStr">
@@ -5700,7 +5736,7 @@
       </c>
     </row>
     <row r="132" ht="24" customHeight="1">
-      <c r="A132" s="32" t="n">
+      <c r="A132" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="B132" s="33" t="inlineStr">
@@ -5723,7 +5759,7 @@
           <t>98 / 104</t>
         </is>
       </c>
-      <c r="F132" s="35" t="n">
+      <c r="F132" s="57" t="n">
         <v>0.9423076923076923</v>
       </c>
       <c r="G132" s="41" t="inlineStr">
@@ -5738,7 +5774,7 @@
       </c>
     </row>
     <row r="133" ht="24" customHeight="1">
-      <c r="A133" s="32" t="n">
+      <c r="A133" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="B133" s="33" t="inlineStr">
@@ -5761,7 +5797,7 @@
           <t>29 / 44</t>
         </is>
       </c>
-      <c r="F133" s="35" t="n">
+      <c r="F133" s="57" t="n">
         <v>0.6590909090909091</v>
       </c>
       <c r="G133" s="41" t="inlineStr">
@@ -5776,7 +5812,7 @@
       </c>
     </row>
     <row r="134" ht="24" customHeight="1">
-      <c r="A134" s="37" t="n">
+      <c r="A134" s="58" t="n">
         <v>46310</v>
       </c>
       <c r="B134" s="38" t="inlineStr">
@@ -5799,7 +5835,7 @@
           <t>63 / 85</t>
         </is>
       </c>
-      <c r="F134" s="40" t="n">
+      <c r="F134" s="59" t="n">
         <v>0.7411764705882353</v>
       </c>
       <c r="G134" s="41" t="inlineStr">
@@ -5814,7 +5850,7 @@
       </c>
     </row>
     <row r="135" ht="24" customHeight="1">
-      <c r="A135" s="32" t="n">
+      <c r="A135" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="B135" s="33" t="inlineStr">
@@ -5837,7 +5873,7 @@
           <t>23 / 102</t>
         </is>
       </c>
-      <c r="F135" s="35" t="n">
+      <c r="F135" s="57" t="n">
         <v>0.2254901960784314</v>
       </c>
       <c r="G135" s="42" t="inlineStr">
@@ -5852,7 +5888,7 @@
       </c>
     </row>
     <row r="136" ht="24" customHeight="1">
-      <c r="A136" s="32" t="n">
+      <c r="A136" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="B136" s="33" t="inlineStr">
@@ -5875,7 +5911,7 @@
           <t>45 / 136</t>
         </is>
       </c>
-      <c r="F136" s="35" t="n">
+      <c r="F136" s="57" t="n">
         <v>0.3308823529411765</v>
       </c>
       <c r="G136" s="41" t="inlineStr">
@@ -5890,7 +5926,7 @@
       </c>
     </row>
     <row r="137" ht="24" customHeight="1">
-      <c r="A137" s="32" t="n">
+      <c r="A137" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="B137" s="33" t="inlineStr">
@@ -5913,7 +5949,7 @@
           <t>1 / 27</t>
         </is>
       </c>
-      <c r="F137" s="35" t="n">
+      <c r="F137" s="57" t="n">
         <v>0.03703703703703703</v>
       </c>
       <c r="G137" s="41" t="inlineStr">
@@ -5928,7 +5964,7 @@
       </c>
     </row>
     <row r="138" ht="24" customHeight="1">
-      <c r="A138" s="37" t="n">
+      <c r="A138" s="58" t="n">
         <v>46310</v>
       </c>
       <c r="B138" s="38" t="inlineStr">
@@ -5951,7 +5987,7 @@
           <t>161 / 308</t>
         </is>
       </c>
-      <c r="F138" s="40" t="n">
+      <c r="F138" s="59" t="n">
         <v>0.5227272727272727</v>
       </c>
       <c r="G138" s="42" t="inlineStr">
@@ -5966,7 +6002,7 @@
       </c>
     </row>
     <row r="139" ht="24" customHeight="1">
-      <c r="A139" s="32" t="n">
+      <c r="A139" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="B139" s="33" t="inlineStr">
@@ -5989,7 +6025,7 @@
           <t>34 / 149</t>
         </is>
       </c>
-      <c r="F139" s="35" t="n">
+      <c r="F139" s="57" t="n">
         <v>0.2281879194630873</v>
       </c>
       <c r="G139" s="41" t="inlineStr">
@@ -6004,7 +6040,7 @@
       </c>
     </row>
     <row r="140" ht="24" customHeight="1">
-      <c r="A140" s="32" t="n">
+      <c r="A140" s="56" t="n">
         <v>46311</v>
       </c>
       <c r="B140" s="33" t="inlineStr">
@@ -6027,7 +6063,7 @@
           <t>74 / 81</t>
         </is>
       </c>
-      <c r="F140" s="35" t="n">
+      <c r="F140" s="57" t="n">
         <v>0.9135802469135802</v>
       </c>
       <c r="G140" s="41" t="inlineStr">
@@ -6042,7 +6078,7 @@
       </c>
     </row>
     <row r="141" ht="24" customHeight="1">
-      <c r="A141" s="32" t="n">
+      <c r="A141" s="56" t="n">
         <v>46311</v>
       </c>
       <c r="B141" s="33" t="inlineStr">
@@ -6065,7 +6101,7 @@
           <t>68 / 113</t>
         </is>
       </c>
-      <c r="F141" s="35" t="n">
+      <c r="F141" s="57" t="n">
         <v>0.6017699115044248</v>
       </c>
       <c r="G141" s="41" t="inlineStr">
@@ -6080,7 +6116,7 @@
       </c>
     </row>
     <row r="142" ht="24" customHeight="1">
-      <c r="A142" s="32" t="n">
+      <c r="A142" s="56" t="n">
         <v>46311</v>
       </c>
       <c r="B142" s="33" t="inlineStr">
@@ -6103,7 +6139,7 @@
           <t>21 / 48</t>
         </is>
       </c>
-      <c r="F142" s="35" t="n">
+      <c r="F142" s="57" t="n">
         <v>0.4375</v>
       </c>
       <c r="G142" s="41" t="inlineStr">
@@ -6118,7 +6154,7 @@
       </c>
     </row>
     <row r="143" ht="24" customHeight="1">
-      <c r="A143" s="32" t="n">
+      <c r="A143" s="56" t="n">
         <v>46311</v>
       </c>
       <c r="B143" s="33" t="inlineStr">
@@ -6141,7 +6177,7 @@
           <t>71 / 113</t>
         </is>
       </c>
-      <c r="F143" s="35" t="n">
+      <c r="F143" s="57" t="n">
         <v>0.6283185840707964</v>
       </c>
       <c r="G143" s="41" t="inlineStr">
@@ -6156,7 +6192,7 @@
       </c>
     </row>
     <row r="144" ht="24" customHeight="1">
-      <c r="A144" s="37" t="n">
+      <c r="A144" s="58" t="n">
         <v>46311</v>
       </c>
       <c r="B144" s="38" t="inlineStr">
@@ -6179,7 +6215,7 @@
           <t>46 / 46</t>
         </is>
       </c>
-      <c r="F144" s="40" t="n">
+      <c r="F144" s="59" t="n">
         <v>1</v>
       </c>
       <c r="G144" s="41" t="inlineStr">
@@ -6194,7 +6230,7 @@
       </c>
     </row>
     <row r="145" ht="24" customHeight="1">
-      <c r="A145" s="32" t="n">
+      <c r="A145" s="56" t="n">
         <v>46311</v>
       </c>
       <c r="B145" s="33" t="inlineStr">
@@ -6217,7 +6253,7 @@
           <t>56 / 56</t>
         </is>
       </c>
-      <c r="F145" s="35" t="n">
+      <c r="F145" s="57" t="n">
         <v>1</v>
       </c>
       <c r="G145" s="41" t="inlineStr">
@@ -6232,7 +6268,7 @@
       </c>
     </row>
     <row r="146" ht="24" customHeight="1">
-      <c r="A146" s="37" t="n">
+      <c r="A146" s="58" t="n">
         <v>46311</v>
       </c>
       <c r="B146" s="38" t="inlineStr">
@@ -6255,7 +6291,7 @@
           <t>24 / 25</t>
         </is>
       </c>
-      <c r="F146" s="40" t="n">
+      <c r="F146" s="59" t="n">
         <v>0.96</v>
       </c>
       <c r="G146" s="41" t="inlineStr">
@@ -6270,7 +6306,7 @@
       </c>
     </row>
     <row r="147" ht="24" customHeight="1">
-      <c r="A147" s="32" t="n">
+      <c r="A147" s="56" t="n">
         <v>46311</v>
       </c>
       <c r="B147" s="33" t="inlineStr">
@@ -6293,7 +6329,7 @@
           <t>10 / 25</t>
         </is>
       </c>
-      <c r="F147" s="35" t="n">
+      <c r="F147" s="57" t="n">
         <v>0.4</v>
       </c>
       <c r="G147" s="41" t="inlineStr">
@@ -6308,7 +6344,7 @@
       </c>
     </row>
     <row r="148" ht="24" customHeight="1">
-      <c r="A148" s="32" t="n">
+      <c r="A148" s="56" t="n">
         <v>46311</v>
       </c>
       <c r="B148" s="33" t="inlineStr">
@@ -6331,7 +6367,7 @@
           <t>77 / 99</t>
         </is>
       </c>
-      <c r="F148" s="35" t="n">
+      <c r="F148" s="57" t="n">
         <v>0.7777777777777778</v>
       </c>
       <c r="G148" s="41" t="inlineStr">
@@ -6346,7 +6382,7 @@
       </c>
     </row>
     <row r="149" ht="24" customHeight="1">
-      <c r="A149" s="32" t="n">
+      <c r="A149" s="56" t="n">
         <v>46311</v>
       </c>
       <c r="B149" s="33" t="inlineStr">
@@ -6369,7 +6405,7 @@
           <t>111 / 111</t>
         </is>
       </c>
-      <c r="F149" s="35" t="n">
+      <c r="F149" s="57" t="n">
         <v>1</v>
       </c>
       <c r="G149" s="41" t="inlineStr">
@@ -6384,7 +6420,7 @@
       </c>
     </row>
     <row r="150" ht="24" customHeight="1">
-      <c r="A150" s="37" t="n">
+      <c r="A150" s="58" t="n">
         <v>46311</v>
       </c>
       <c r="B150" s="38" t="inlineStr">
@@ -6407,7 +6443,7 @@
           <t>134 / 138</t>
         </is>
       </c>
-      <c r="F150" s="40" t="n">
+      <c r="F150" s="59" t="n">
         <v>0.9710144927536232</v>
       </c>
       <c r="G150" s="41" t="inlineStr">
@@ -6422,7 +6458,7 @@
       </c>
     </row>
     <row r="151" ht="24" customHeight="1">
-      <c r="A151" s="32" t="n">
+      <c r="A151" s="56" t="n">
         <v>46311</v>
       </c>
       <c r="B151" s="33" t="inlineStr">
@@ -6445,7 +6481,7 @@
           <t>79 / 81</t>
         </is>
       </c>
-      <c r="F151" s="35" t="n">
+      <c r="F151" s="57" t="n">
         <v>0.9753086419753086</v>
       </c>
       <c r="G151" s="41" t="inlineStr">
@@ -6460,7 +6496,7 @@
       </c>
     </row>
     <row r="152" ht="24" customHeight="1">
-      <c r="A152" s="37" t="n">
+      <c r="A152" s="58" t="n">
         <v>46311</v>
       </c>
       <c r="B152" s="38" t="inlineStr">
@@ -6483,7 +6519,7 @@
           <t>23 / 26</t>
         </is>
       </c>
-      <c r="F152" s="40" t="n">
+      <c r="F152" s="59" t="n">
         <v>0.8846153846153846</v>
       </c>
       <c r="G152" s="41" t="inlineStr">
@@ -6498,7 +6534,7 @@
       </c>
     </row>
     <row r="153" ht="24" customHeight="1">
-      <c r="A153" s="32" t="n">
+      <c r="A153" s="56" t="n">
         <v>46311</v>
       </c>
       <c r="B153" s="33" t="inlineStr">
@@ -6521,7 +6557,7 @@
           <t>124 / 126</t>
         </is>
       </c>
-      <c r="F153" s="35" t="n">
+      <c r="F153" s="57" t="n">
         <v>0.9841269841269841</v>
       </c>
       <c r="G153" s="41" t="inlineStr">
@@ -6536,7 +6572,7 @@
       </c>
     </row>
     <row r="154" ht="24" customHeight="1">
-      <c r="A154" s="37" t="n">
+      <c r="A154" s="58" t="n">
         <v>46311</v>
       </c>
       <c r="B154" s="38" t="inlineStr">
@@ -6559,7 +6595,7 @@
           <t>98 / 104</t>
         </is>
       </c>
-      <c r="F154" s="40" t="n">
+      <c r="F154" s="59" t="n">
         <v>0.9423076923076923</v>
       </c>
       <c r="G154" s="41" t="inlineStr">
@@ -6574,7 +6610,7 @@
       </c>
     </row>
     <row r="155" ht="24" customHeight="1">
-      <c r="A155" s="37" t="n">
+      <c r="A155" s="58" t="n">
         <v>46311</v>
       </c>
       <c r="B155" s="38" t="inlineStr">
@@ -6597,7 +6633,7 @@
           <t>29 / 44</t>
         </is>
       </c>
-      <c r="F155" s="40" t="n">
+      <c r="F155" s="59" t="n">
         <v>0.6590909090909091</v>
       </c>
       <c r="G155" s="41" t="inlineStr">
@@ -6612,7 +6648,7 @@
       </c>
     </row>
     <row r="156" ht="24" customHeight="1">
-      <c r="A156" s="32" t="n">
+      <c r="A156" s="56" t="n">
         <v>46311</v>
       </c>
       <c r="B156" s="33" t="inlineStr">
@@ -6635,7 +6671,7 @@
           <t>63 / 85</t>
         </is>
       </c>
-      <c r="F156" s="35" t="n">
+      <c r="F156" s="57" t="n">
         <v>0.7411764705882353</v>
       </c>
       <c r="G156" s="41" t="inlineStr">
@@ -6650,7 +6686,7 @@
       </c>
     </row>
     <row r="157" ht="24" customHeight="1">
-      <c r="A157" s="37" t="n">
+      <c r="A157" s="58" t="n">
         <v>46311</v>
       </c>
       <c r="B157" s="38" t="inlineStr">
@@ -6673,7 +6709,7 @@
           <t>23 / 102</t>
         </is>
       </c>
-      <c r="F157" s="40" t="n">
+      <c r="F157" s="59" t="n">
         <v>0.2254901960784314</v>
       </c>
       <c r="G157" s="41" t="inlineStr">
@@ -6688,7 +6724,7 @@
       </c>
     </row>
     <row r="158" ht="24" customHeight="1">
-      <c r="A158" s="37" t="n">
+      <c r="A158" s="58" t="n">
         <v>46311</v>
       </c>
       <c r="B158" s="38" t="inlineStr">
@@ -6711,7 +6747,7 @@
           <t>45 / 136</t>
         </is>
       </c>
-      <c r="F158" s="40" t="n">
+      <c r="F158" s="59" t="n">
         <v>0.3308823529411765</v>
       </c>
       <c r="G158" s="41" t="inlineStr">
@@ -6726,7 +6762,7 @@
       </c>
     </row>
     <row r="159" ht="24" customHeight="1">
-      <c r="A159" s="32" t="n">
+      <c r="A159" s="56" t="n">
         <v>46311</v>
       </c>
       <c r="B159" s="33" t="inlineStr">
@@ -6749,7 +6785,7 @@
           <t>1 / 27</t>
         </is>
       </c>
-      <c r="F159" s="35" t="n">
+      <c r="F159" s="57" t="n">
         <v>0.03703703703703703</v>
       </c>
       <c r="G159" s="41" t="inlineStr">
@@ -6764,7 +6800,7 @@
       </c>
     </row>
     <row r="160" ht="24" customHeight="1">
-      <c r="A160" s="37" t="n">
+      <c r="A160" s="58" t="n">
         <v>46311</v>
       </c>
       <c r="B160" s="38" t="inlineStr">
@@ -6787,7 +6823,7 @@
           <t>161 / 308</t>
         </is>
       </c>
-      <c r="F160" s="40" t="n">
+      <c r="F160" s="59" t="n">
         <v>0.5227272727272727</v>
       </c>
       <c r="G160" s="41" t="inlineStr">
@@ -6802,7 +6838,7 @@
       </c>
     </row>
     <row r="161" ht="24" customHeight="1">
-      <c r="A161" s="37" t="n">
+      <c r="A161" s="58" t="n">
         <v>46311</v>
       </c>
       <c r="B161" s="38" t="inlineStr">
@@ -6825,7 +6861,7 @@
           <t>34 / 149</t>
         </is>
       </c>
-      <c r="F161" s="40" t="n">
+      <c r="F161" s="59" t="n">
         <v>0.2281879194630873</v>
       </c>
       <c r="G161" s="41" t="inlineStr">
@@ -6840,7 +6876,7 @@
       </c>
     </row>
     <row r="162" ht="24" customHeight="1">
-      <c r="A162" s="37" t="n">
+      <c r="A162" s="58" t="n">
         <v>46312</v>
       </c>
       <c r="B162" s="38" t="inlineStr">
@@ -6863,7 +6899,7 @@
           <t>74 / 81</t>
         </is>
       </c>
-      <c r="F162" s="40" t="n">
+      <c r="F162" s="59" t="n">
         <v>0.9135802469135802</v>
       </c>
       <c r="G162" s="41" t="inlineStr">
@@ -6878,7 +6914,7 @@
       </c>
     </row>
     <row r="163" ht="24" customHeight="1">
-      <c r="A163" s="37" t="n">
+      <c r="A163" s="58" t="n">
         <v>46312</v>
       </c>
       <c r="B163" s="38" t="inlineStr">
@@ -6901,7 +6937,7 @@
           <t>69 / 113</t>
         </is>
       </c>
-      <c r="F163" s="40" t="n">
+      <c r="F163" s="59" t="n">
         <v>0.6106194690265486</v>
       </c>
       <c r="G163" s="42" t="inlineStr">
@@ -6916,7 +6952,7 @@
       </c>
     </row>
     <row r="164" ht="24" customHeight="1">
-      <c r="A164" s="37" t="n">
+      <c r="A164" s="58" t="n">
         <v>46312</v>
       </c>
       <c r="B164" s="38" t="inlineStr">
@@ -6939,7 +6975,7 @@
           <t>21 / 48</t>
         </is>
       </c>
-      <c r="F164" s="40" t="n">
+      <c r="F164" s="59" t="n">
         <v>0.4375</v>
       </c>
       <c r="G164" s="41" t="inlineStr">
@@ -6954,7 +6990,7 @@
       </c>
     </row>
     <row r="165" ht="24" customHeight="1">
-      <c r="A165" s="37" t="n">
+      <c r="A165" s="58" t="n">
         <v>46312</v>
       </c>
       <c r="B165" s="38" t="inlineStr">
@@ -6977,7 +7013,7 @@
           <t>71 / 113</t>
         </is>
       </c>
-      <c r="F165" s="40" t="n">
+      <c r="F165" s="59" t="n">
         <v>0.6283185840707964</v>
       </c>
       <c r="G165" s="41" t="inlineStr">
@@ -6992,7 +7028,7 @@
       </c>
     </row>
     <row r="166" ht="24" customHeight="1">
-      <c r="A166" s="37" t="n">
+      <c r="A166" s="58" t="n">
         <v>46312</v>
       </c>
       <c r="B166" s="38" t="inlineStr">
@@ -7015,7 +7051,7 @@
           <t>46 / 46</t>
         </is>
       </c>
-      <c r="F166" s="40" t="n">
+      <c r="F166" s="59" t="n">
         <v>1</v>
       </c>
       <c r="G166" s="41" t="inlineStr">
@@ -7030,7 +7066,7 @@
       </c>
     </row>
     <row r="167" ht="24" customHeight="1">
-      <c r="A167" s="32" t="n">
+      <c r="A167" s="56" t="n">
         <v>46312</v>
       </c>
       <c r="B167" s="33" t="inlineStr">
@@ -7053,7 +7089,7 @@
           <t>56 / 56</t>
         </is>
       </c>
-      <c r="F167" s="35" t="n">
+      <c r="F167" s="57" t="n">
         <v>1</v>
       </c>
       <c r="G167" s="41" t="inlineStr">
@@ -7068,7 +7104,7 @@
       </c>
     </row>
     <row r="168" ht="24" customHeight="1">
-      <c r="A168" s="37" t="n">
+      <c r="A168" s="58" t="n">
         <v>46312</v>
       </c>
       <c r="B168" s="38" t="inlineStr">
@@ -7091,7 +7127,7 @@
           <t>24 / 25</t>
         </is>
       </c>
-      <c r="F168" s="40" t="n">
+      <c r="F168" s="59" t="n">
         <v>0.96</v>
       </c>
       <c r="G168" s="41" t="inlineStr">
@@ -7106,7 +7142,7 @@
       </c>
     </row>
     <row r="169" ht="24" customHeight="1">
-      <c r="A169" s="32" t="n">
+      <c r="A169" s="56" t="n">
         <v>46312</v>
       </c>
       <c r="B169" s="33" t="inlineStr">
@@ -7129,7 +7165,7 @@
           <t>10 / 25</t>
         </is>
       </c>
-      <c r="F169" s="35" t="n">
+      <c r="F169" s="57" t="n">
         <v>0.4</v>
       </c>
       <c r="G169" s="41" t="inlineStr">
@@ -7144,7 +7180,7 @@
       </c>
     </row>
     <row r="170" ht="24" customHeight="1">
-      <c r="A170" s="37" t="n">
+      <c r="A170" s="58" t="n">
         <v>46312</v>
       </c>
       <c r="B170" s="38" t="inlineStr">
@@ -7167,7 +7203,7 @@
           <t>77 / 99</t>
         </is>
       </c>
-      <c r="F170" s="40" t="n">
+      <c r="F170" s="59" t="n">
         <v>0.7777777777777778</v>
       </c>
       <c r="G170" s="41" t="inlineStr">
@@ -7182,7 +7218,7 @@
       </c>
     </row>
     <row r="171" ht="24" customHeight="1">
-      <c r="A171" s="37" t="n">
+      <c r="A171" s="58" t="n">
         <v>46312</v>
       </c>
       <c r="B171" s="38" t="inlineStr">
@@ -7205,7 +7241,7 @@
           <t>111 / 111</t>
         </is>
       </c>
-      <c r="F171" s="40" t="n">
+      <c r="F171" s="59" t="n">
         <v>1</v>
       </c>
       <c r="G171" s="41" t="inlineStr">
@@ -7220,7 +7256,7 @@
       </c>
     </row>
     <row r="172" ht="24" customHeight="1">
-      <c r="A172" s="32" t="n">
+      <c r="A172" s="56" t="n">
         <v>46312</v>
       </c>
       <c r="B172" s="33" t="inlineStr">
@@ -7243,7 +7279,7 @@
           <t>134 / 138</t>
         </is>
       </c>
-      <c r="F172" s="35" t="n">
+      <c r="F172" s="57" t="n">
         <v>0.9710144927536232</v>
       </c>
       <c r="G172" s="41" t="inlineStr">
@@ -7258,7 +7294,7 @@
       </c>
     </row>
     <row r="173" ht="24" customHeight="1">
-      <c r="A173" s="37" t="n">
+      <c r="A173" s="58" t="n">
         <v>46312</v>
       </c>
       <c r="B173" s="38" t="inlineStr">
@@ -7281,7 +7317,7 @@
           <t>79 / 81</t>
         </is>
       </c>
-      <c r="F173" s="40" t="n">
+      <c r="F173" s="59" t="n">
         <v>0.9753086419753086</v>
       </c>
       <c r="G173" s="41" t="inlineStr">
@@ -7296,7 +7332,7 @@
       </c>
     </row>
     <row r="174" ht="24" customHeight="1">
-      <c r="A174" s="32" t="n">
+      <c r="A174" s="56" t="n">
         <v>46312</v>
       </c>
       <c r="B174" s="33" t="inlineStr">
@@ -7319,7 +7355,7 @@
           <t>23 / 26</t>
         </is>
       </c>
-      <c r="F174" s="35" t="n">
+      <c r="F174" s="57" t="n">
         <v>0.8846153846153846</v>
       </c>
       <c r="G174" s="41" t="inlineStr">
@@ -7334,7 +7370,7 @@
       </c>
     </row>
     <row r="175" ht="24" customHeight="1">
-      <c r="A175" s="37" t="n">
+      <c r="A175" s="58" t="n">
         <v>46312</v>
       </c>
       <c r="B175" s="38" t="inlineStr">
@@ -7357,7 +7393,7 @@
           <t>124 / 126</t>
         </is>
       </c>
-      <c r="F175" s="40" t="n">
+      <c r="F175" s="59" t="n">
         <v>0.9841269841269841</v>
       </c>
       <c r="G175" s="41" t="inlineStr">
@@ -7372,7 +7408,7 @@
       </c>
     </row>
     <row r="176" ht="24" customHeight="1">
-      <c r="A176" s="32" t="n">
+      <c r="A176" s="56" t="n">
         <v>46312</v>
       </c>
       <c r="B176" s="33" t="inlineStr">
@@ -7395,7 +7431,7 @@
           <t>98 / 104</t>
         </is>
       </c>
-      <c r="F176" s="35" t="n">
+      <c r="F176" s="57" t="n">
         <v>0.9423076923076923</v>
       </c>
       <c r="G176" s="41" t="inlineStr">
@@ -7410,7 +7446,7 @@
       </c>
     </row>
     <row r="177" ht="24" customHeight="1">
-      <c r="A177" s="32" t="n">
+      <c r="A177" s="56" t="n">
         <v>46312</v>
       </c>
       <c r="B177" s="33" t="inlineStr">
@@ -7433,7 +7469,7 @@
           <t>29 / 44</t>
         </is>
       </c>
-      <c r="F177" s="35" t="n">
+      <c r="F177" s="57" t="n">
         <v>0.6590909090909091</v>
       </c>
       <c r="G177" s="41" t="inlineStr">
@@ -7448,7 +7484,7 @@
       </c>
     </row>
     <row r="178" ht="24" customHeight="1">
-      <c r="A178" s="37" t="n">
+      <c r="A178" s="58" t="n">
         <v>46312</v>
       </c>
       <c r="B178" s="38" t="inlineStr">
@@ -7471,7 +7507,7 @@
           <t>65 / 85</t>
         </is>
       </c>
-      <c r="F178" s="40" t="n">
+      <c r="F178" s="59" t="n">
         <v>0.7647058823529411</v>
       </c>
       <c r="G178" s="42" t="inlineStr">
@@ -7486,7 +7522,7 @@
       </c>
     </row>
     <row r="179" ht="24" customHeight="1">
-      <c r="A179" s="32" t="n">
+      <c r="A179" s="56" t="n">
         <v>46312</v>
       </c>
       <c r="B179" s="33" t="inlineStr">
@@ -7509,7 +7545,7 @@
           <t>24 / 102</t>
         </is>
       </c>
-      <c r="F179" s="35" t="n">
+      <c r="F179" s="57" t="n">
         <v>0.2352941176470588</v>
       </c>
       <c r="G179" s="42" t="inlineStr">
@@ -7524,7 +7560,7 @@
       </c>
     </row>
     <row r="180" ht="24" customHeight="1">
-      <c r="A180" s="32" t="n">
+      <c r="A180" s="56" t="n">
         <v>46312</v>
       </c>
       <c r="B180" s="33" t="inlineStr">
@@ -7547,7 +7583,7 @@
           <t>45 / 136</t>
         </is>
       </c>
-      <c r="F180" s="35" t="n">
+      <c r="F180" s="57" t="n">
         <v>0.3308823529411765</v>
       </c>
       <c r="G180" s="41" t="inlineStr">
@@ -7562,7 +7598,7 @@
       </c>
     </row>
     <row r="181" ht="24" customHeight="1">
-      <c r="A181" s="32" t="n">
+      <c r="A181" s="56" t="n">
         <v>46312</v>
       </c>
       <c r="B181" s="33" t="inlineStr">
@@ -7585,7 +7621,7 @@
           <t>1 / 27</t>
         </is>
       </c>
-      <c r="F181" s="35" t="n">
+      <c r="F181" s="57" t="n">
         <v>0.03703703703703703</v>
       </c>
       <c r="G181" s="41" t="inlineStr">
@@ -7600,7 +7636,7 @@
       </c>
     </row>
     <row r="182" ht="24" customHeight="1">
-      <c r="A182" s="37" t="n">
+      <c r="A182" s="58" t="n">
         <v>46312</v>
       </c>
       <c r="B182" s="38" t="inlineStr">
@@ -7623,7 +7659,7 @@
           <t>161 / 308</t>
         </is>
       </c>
-      <c r="F182" s="40" t="n">
+      <c r="F182" s="59" t="n">
         <v>0.5227272727272727</v>
       </c>
       <c r="G182" s="41" t="inlineStr">
@@ -7638,7 +7674,7 @@
       </c>
     </row>
     <row r="183" ht="24" customHeight="1">
-      <c r="A183" s="32" t="n">
+      <c r="A183" s="56" t="n">
         <v>46312</v>
       </c>
       <c r="B183" s="33" t="inlineStr">
@@ -7661,7 +7697,7 @@
           <t>34 / 149</t>
         </is>
       </c>
-      <c r="F183" s="35" t="n">
+      <c r="F183" s="57" t="n">
         <v>0.2281879194630873</v>
       </c>
       <c r="G183" s="41" t="inlineStr">
@@ -7676,7 +7712,7 @@
       </c>
     </row>
     <row r="184" ht="24" customHeight="1">
-      <c r="A184" s="32" t="n">
+      <c r="A184" s="56" t="n">
         <v>46313</v>
       </c>
       <c r="B184" s="33" t="inlineStr">
@@ -7699,7 +7735,7 @@
           <t>74 / 81</t>
         </is>
       </c>
-      <c r="F184" s="35" t="n">
+      <c r="F184" s="57" t="n">
         <v>0.9135802469135802</v>
       </c>
       <c r="G184" s="41" t="inlineStr">
@@ -7714,7 +7750,7 @@
       </c>
     </row>
     <row r="185" ht="24" customHeight="1">
-      <c r="A185" s="32" t="n">
+      <c r="A185" s="56" t="n">
         <v>46313</v>
       </c>
       <c r="B185" s="33" t="inlineStr">
@@ -7737,7 +7773,7 @@
           <t>69 / 113</t>
         </is>
       </c>
-      <c r="F185" s="35" t="n">
+      <c r="F185" s="57" t="n">
         <v>0.6106194690265486</v>
       </c>
       <c r="G185" s="41" t="inlineStr">
@@ -7752,7 +7788,7 @@
       </c>
     </row>
     <row r="186" ht="24" customHeight="1">
-      <c r="A186" s="32" t="n">
+      <c r="A186" s="56" t="n">
         <v>46313</v>
       </c>
       <c r="B186" s="33" t="inlineStr">
@@ -7775,7 +7811,7 @@
           <t>21 / 48</t>
         </is>
       </c>
-      <c r="F186" s="35" t="n">
+      <c r="F186" s="57" t="n">
         <v>0.4375</v>
       </c>
       <c r="G186" s="41" t="inlineStr">
@@ -7790,7 +7826,7 @@
       </c>
     </row>
     <row r="187" ht="24" customHeight="1">
-      <c r="A187" s="32" t="n">
+      <c r="A187" s="56" t="n">
         <v>46313</v>
       </c>
       <c r="B187" s="33" t="inlineStr">
@@ -7813,7 +7849,7 @@
           <t>71 / 113</t>
         </is>
       </c>
-      <c r="F187" s="35" t="n">
+      <c r="F187" s="57" t="n">
         <v>0.6283185840707964</v>
       </c>
       <c r="G187" s="41" t="inlineStr">
@@ -7828,7 +7864,7 @@
       </c>
     </row>
     <row r="188" ht="24" customHeight="1">
-      <c r="A188" s="37" t="n">
+      <c r="A188" s="58" t="n">
         <v>46313</v>
       </c>
       <c r="B188" s="38" t="inlineStr">
@@ -7851,7 +7887,7 @@
           <t>46 / 46</t>
         </is>
       </c>
-      <c r="F188" s="40" t="n">
+      <c r="F188" s="59" t="n">
         <v>1</v>
       </c>
       <c r="G188" s="41" t="inlineStr">
@@ -7866,7 +7902,7 @@
       </c>
     </row>
     <row r="189" ht="24" customHeight="1">
-      <c r="A189" s="32" t="n">
+      <c r="A189" s="56" t="n">
         <v>46313</v>
       </c>
       <c r="B189" s="33" t="inlineStr">
@@ -7889,7 +7925,7 @@
           <t>56 / 56</t>
         </is>
       </c>
-      <c r="F189" s="35" t="n">
+      <c r="F189" s="57" t="n">
         <v>1</v>
       </c>
       <c r="G189" s="41" t="inlineStr">
@@ -7904,7 +7940,7 @@
       </c>
     </row>
     <row r="190" ht="24" customHeight="1">
-      <c r="A190" s="37" t="n">
+      <c r="A190" s="58" t="n">
         <v>46313</v>
       </c>
       <c r="B190" s="38" t="inlineStr">
@@ -7927,7 +7963,7 @@
           <t>24 / 25</t>
         </is>
       </c>
-      <c r="F190" s="40" t="n">
+      <c r="F190" s="59" t="n">
         <v>0.96</v>
       </c>
       <c r="G190" s="41" t="inlineStr">
@@ -7942,7 +7978,7 @@
       </c>
     </row>
     <row r="191" ht="24" customHeight="1">
-      <c r="A191" s="32" t="n">
+      <c r="A191" s="56" t="n">
         <v>46313</v>
       </c>
       <c r="B191" s="33" t="inlineStr">
@@ -7965,7 +8001,7 @@
           <t>10 / 25</t>
         </is>
       </c>
-      <c r="F191" s="35" t="n">
+      <c r="F191" s="57" t="n">
         <v>0.4</v>
       </c>
       <c r="G191" s="41" t="inlineStr">
@@ -7980,7 +8016,7 @@
       </c>
     </row>
     <row r="192" ht="24" customHeight="1">
-      <c r="A192" s="32" t="n">
+      <c r="A192" s="56" t="n">
         <v>46313</v>
       </c>
       <c r="B192" s="33" t="inlineStr">
@@ -8003,7 +8039,7 @@
           <t>77 / 99</t>
         </is>
       </c>
-      <c r="F192" s="35" t="n">
+      <c r="F192" s="57" t="n">
         <v>0.7777777777777778</v>
       </c>
       <c r="G192" s="41" t="inlineStr">
@@ -8018,7 +8054,7 @@
       </c>
     </row>
     <row r="193" ht="24" customHeight="1">
-      <c r="A193" s="32" t="n">
+      <c r="A193" s="56" t="n">
         <v>46313</v>
       </c>
       <c r="B193" s="33" t="inlineStr">
@@ -8041,7 +8077,7 @@
           <t>111 / 111</t>
         </is>
       </c>
-      <c r="F193" s="35" t="n">
+      <c r="F193" s="57" t="n">
         <v>1</v>
       </c>
       <c r="G193" s="41" t="inlineStr">
@@ -8056,7 +8092,7 @@
       </c>
     </row>
     <row r="194" ht="24" customHeight="1">
-      <c r="A194" s="37" t="n">
+      <c r="A194" s="58" t="n">
         <v>46313</v>
       </c>
       <c r="B194" s="38" t="inlineStr">
@@ -8079,7 +8115,7 @@
           <t>134 / 138</t>
         </is>
       </c>
-      <c r="F194" s="40" t="n">
+      <c r="F194" s="59" t="n">
         <v>0.9710144927536232</v>
       </c>
       <c r="G194" s="41" t="inlineStr">
@@ -8094,7 +8130,7 @@
       </c>
     </row>
     <row r="195" ht="24" customHeight="1">
-      <c r="A195" s="32" t="n">
+      <c r="A195" s="56" t="n">
         <v>46313</v>
       </c>
       <c r="B195" s="33" t="inlineStr">
@@ -8117,7 +8153,7 @@
           <t>79 / 81</t>
         </is>
       </c>
-      <c r="F195" s="35" t="n">
+      <c r="F195" s="57" t="n">
         <v>0.9753086419753086</v>
       </c>
       <c r="G195" s="41" t="inlineStr">
@@ -8132,7 +8168,7 @@
       </c>
     </row>
     <row r="196" ht="24" customHeight="1">
-      <c r="A196" s="37" t="n">
+      <c r="A196" s="58" t="n">
         <v>46313</v>
       </c>
       <c r="B196" s="38" t="inlineStr">
@@ -8155,7 +8191,7 @@
           <t>23 / 26</t>
         </is>
       </c>
-      <c r="F196" s="40" t="n">
+      <c r="F196" s="59" t="n">
         <v>0.8846153846153846</v>
       </c>
       <c r="G196" s="41" t="inlineStr">
@@ -8170,7 +8206,7 @@
       </c>
     </row>
     <row r="197" ht="24" customHeight="1">
-      <c r="A197" s="32" t="n">
+      <c r="A197" s="56" t="n">
         <v>46313</v>
       </c>
       <c r="B197" s="33" t="inlineStr">
@@ -8193,7 +8229,7 @@
           <t>124 / 126</t>
         </is>
       </c>
-      <c r="F197" s="35" t="n">
+      <c r="F197" s="57" t="n">
         <v>0.9841269841269841</v>
       </c>
       <c r="G197" s="41" t="inlineStr">
@@ -8208,7 +8244,7 @@
       </c>
     </row>
     <row r="198" ht="24" customHeight="1">
-      <c r="A198" s="37" t="n">
+      <c r="A198" s="58" t="n">
         <v>46313</v>
       </c>
       <c r="B198" s="38" t="inlineStr">
@@ -8231,7 +8267,7 @@
           <t>98 / 104</t>
         </is>
       </c>
-      <c r="F198" s="40" t="n">
+      <c r="F198" s="59" t="n">
         <v>0.9423076923076923</v>
       </c>
       <c r="G198" s="41" t="inlineStr">
@@ -8246,7 +8282,7 @@
       </c>
     </row>
     <row r="199" ht="24" customHeight="1">
-      <c r="A199" s="37" t="n">
+      <c r="A199" s="58" t="n">
         <v>46313</v>
       </c>
       <c r="B199" s="38" t="inlineStr">
@@ -8269,7 +8305,7 @@
           <t>29 / 44</t>
         </is>
       </c>
-      <c r="F199" s="40" t="n">
+      <c r="F199" s="59" t="n">
         <v>0.6590909090909091</v>
       </c>
       <c r="G199" s="41" t="inlineStr">
@@ -8284,7 +8320,7 @@
       </c>
     </row>
     <row r="200" ht="24" customHeight="1">
-      <c r="A200" s="32" t="n">
+      <c r="A200" s="56" t="n">
         <v>46313</v>
       </c>
       <c r="B200" s="33" t="inlineStr">
@@ -8307,7 +8343,7 @@
           <t>65 / 85</t>
         </is>
       </c>
-      <c r="F200" s="35" t="n">
+      <c r="F200" s="57" t="n">
         <v>0.7647058823529411</v>
       </c>
       <c r="G200" s="41" t="inlineStr">
@@ -8322,7 +8358,7 @@
       </c>
     </row>
     <row r="201" ht="24" customHeight="1">
-      <c r="A201" s="37" t="n">
+      <c r="A201" s="58" t="n">
         <v>46313</v>
       </c>
       <c r="B201" s="38" t="inlineStr">
@@ -8345,7 +8381,7 @@
           <t>24 / 102</t>
         </is>
       </c>
-      <c r="F201" s="40" t="n">
+      <c r="F201" s="59" t="n">
         <v>0.2352941176470588</v>
       </c>
       <c r="G201" s="41" t="inlineStr">
@@ -8360,7 +8396,7 @@
       </c>
     </row>
     <row r="202" ht="24" customHeight="1">
-      <c r="A202" s="37" t="n">
+      <c r="A202" s="58" t="n">
         <v>46313</v>
       </c>
       <c r="B202" s="38" t="inlineStr">
@@ -8383,7 +8419,7 @@
           <t>45 / 136</t>
         </is>
       </c>
-      <c r="F202" s="40" t="n">
+      <c r="F202" s="59" t="n">
         <v>0.3308823529411765</v>
       </c>
       <c r="G202" s="41" t="inlineStr">
@@ -8398,7 +8434,7 @@
       </c>
     </row>
     <row r="203" ht="24" customHeight="1">
-      <c r="A203" s="32" t="n">
+      <c r="A203" s="56" t="n">
         <v>46313</v>
       </c>
       <c r="B203" s="33" t="inlineStr">
@@ -8421,7 +8457,7 @@
           <t>1 / 27</t>
         </is>
       </c>
-      <c r="F203" s="35" t="n">
+      <c r="F203" s="57" t="n">
         <v>0.03703703703703703</v>
       </c>
       <c r="G203" s="41" t="inlineStr">
@@ -8436,7 +8472,7 @@
       </c>
     </row>
     <row r="204" ht="24" customHeight="1">
-      <c r="A204" s="37" t="n">
+      <c r="A204" s="58" t="n">
         <v>46313</v>
       </c>
       <c r="B204" s="38" t="inlineStr">
@@ -8459,7 +8495,7 @@
           <t>161 / 308</t>
         </is>
       </c>
-      <c r="F204" s="40" t="n">
+      <c r="F204" s="59" t="n">
         <v>0.5227272727272727</v>
       </c>
       <c r="G204" s="41" t="inlineStr">
@@ -8474,7 +8510,7 @@
       </c>
     </row>
     <row r="205" ht="24" customHeight="1">
-      <c r="A205" s="37" t="n">
+      <c r="A205" s="58" t="n">
         <v>46313</v>
       </c>
       <c r="B205" s="38" t="inlineStr">
@@ -8497,7 +8533,7 @@
           <t>34 / 149</t>
         </is>
       </c>
-      <c r="F205" s="40" t="n">
+      <c r="F205" s="59" t="n">
         <v>0.2281879194630873</v>
       </c>
       <c r="G205" s="41" t="inlineStr">
@@ -8512,7 +8548,7 @@
       </c>
     </row>
     <row r="206" ht="24" customHeight="1">
-      <c r="A206" s="37" t="n">
+      <c r="A206" s="58" t="n">
         <v>46314</v>
       </c>
       <c r="B206" s="38" t="inlineStr">
@@ -8535,7 +8571,7 @@
           <t>74 / 81</t>
         </is>
       </c>
-      <c r="F206" s="40" t="n">
+      <c r="F206" s="59" t="n">
         <v>0.9135802469135802</v>
       </c>
       <c r="G206" s="41" t="inlineStr">
@@ -8550,7 +8586,7 @@
       </c>
     </row>
     <row r="207" ht="24" customHeight="1">
-      <c r="A207" s="37" t="n">
+      <c r="A207" s="58" t="n">
         <v>46314</v>
       </c>
       <c r="B207" s="38" t="inlineStr">
@@ -8573,7 +8609,7 @@
           <t>69 / 113</t>
         </is>
       </c>
-      <c r="F207" s="40" t="n">
+      <c r="F207" s="59" t="n">
         <v>0.6106194690265486</v>
       </c>
       <c r="G207" s="41" t="inlineStr">
@@ -8588,7 +8624,7 @@
       </c>
     </row>
     <row r="208" ht="24" customHeight="1">
-      <c r="A208" s="37" t="n">
+      <c r="A208" s="58" t="n">
         <v>46314</v>
       </c>
       <c r="B208" s="38" t="inlineStr">
@@ -8611,7 +8647,7 @@
           <t>21 / 48</t>
         </is>
       </c>
-      <c r="F208" s="40" t="n">
+      <c r="F208" s="59" t="n">
         <v>0.4375</v>
       </c>
       <c r="G208" s="41" t="inlineStr">
@@ -8626,7 +8662,7 @@
       </c>
     </row>
     <row r="209" ht="24" customHeight="1">
-      <c r="A209" s="37" t="n">
+      <c r="A209" s="58" t="n">
         <v>46314</v>
       </c>
       <c r="B209" s="38" t="inlineStr">
@@ -8649,7 +8685,7 @@
           <t>71 / 113</t>
         </is>
       </c>
-      <c r="F209" s="40" t="n">
+      <c r="F209" s="59" t="n">
         <v>0.6283185840707964</v>
       </c>
       <c r="G209" s="41" t="inlineStr">
@@ -8664,7 +8700,7 @@
       </c>
     </row>
     <row r="210" ht="24" customHeight="1">
-      <c r="A210" s="37" t="n">
+      <c r="A210" s="58" t="n">
         <v>46314</v>
       </c>
       <c r="B210" s="38" t="inlineStr">
@@ -8687,7 +8723,7 @@
           <t>46 / 46</t>
         </is>
       </c>
-      <c r="F210" s="40" t="n">
+      <c r="F210" s="59" t="n">
         <v>1</v>
       </c>
       <c r="G210" s="41" t="inlineStr">
@@ -8702,7 +8738,7 @@
       </c>
     </row>
     <row r="211" ht="24" customHeight="1">
-      <c r="A211" s="32" t="n">
+      <c r="A211" s="56" t="n">
         <v>46314</v>
       </c>
       <c r="B211" s="33" t="inlineStr">
@@ -8725,7 +8761,7 @@
           <t>56 / 56</t>
         </is>
       </c>
-      <c r="F211" s="35" t="n">
+      <c r="F211" s="57" t="n">
         <v>1</v>
       </c>
       <c r="G211" s="41" t="inlineStr">
@@ -8740,7 +8776,7 @@
       </c>
     </row>
     <row r="212" ht="24" customHeight="1">
-      <c r="A212" s="37" t="n">
+      <c r="A212" s="58" t="n">
         <v>46314</v>
       </c>
       <c r="B212" s="38" t="inlineStr">
@@ -8763,7 +8799,7 @@
           <t>24 / 25</t>
         </is>
       </c>
-      <c r="F212" s="40" t="n">
+      <c r="F212" s="59" t="n">
         <v>0.96</v>
       </c>
       <c r="G212" s="41" t="inlineStr">
@@ -8778,7 +8814,7 @@
       </c>
     </row>
     <row r="213" ht="24" customHeight="1">
-      <c r="A213" s="32" t="n">
+      <c r="A213" s="56" t="n">
         <v>46314</v>
       </c>
       <c r="B213" s="33" t="inlineStr">
@@ -8801,7 +8837,7 @@
           <t>10 / 25</t>
         </is>
       </c>
-      <c r="F213" s="35" t="n">
+      <c r="F213" s="57" t="n">
         <v>0.4</v>
       </c>
       <c r="G213" s="41" t="inlineStr">
@@ -8816,7 +8852,7 @@
       </c>
     </row>
     <row r="214" ht="24" customHeight="1">
-      <c r="A214" s="37" t="n">
+      <c r="A214" s="58" t="n">
         <v>46314</v>
       </c>
       <c r="B214" s="38" t="inlineStr">
@@ -8839,7 +8875,7 @@
           <t>77 / 99</t>
         </is>
       </c>
-      <c r="F214" s="40" t="n">
+      <c r="F214" s="59" t="n">
         <v>0.7777777777777778</v>
       </c>
       <c r="G214" s="41" t="inlineStr">
@@ -8854,7 +8890,7 @@
       </c>
     </row>
     <row r="215" ht="24" customHeight="1">
-      <c r="A215" s="37" t="n">
+      <c r="A215" s="58" t="n">
         <v>46314</v>
       </c>
       <c r="B215" s="38" t="inlineStr">
@@ -8877,7 +8913,7 @@
           <t>111 / 111</t>
         </is>
       </c>
-      <c r="F215" s="40" t="n">
+      <c r="F215" s="59" t="n">
         <v>1</v>
       </c>
       <c r="G215" s="41" t="inlineStr">
@@ -8892,7 +8928,7 @@
       </c>
     </row>
     <row r="216" ht="24" customHeight="1">
-      <c r="A216" s="32" t="n">
+      <c r="A216" s="56" t="n">
         <v>46314</v>
       </c>
       <c r="B216" s="33" t="inlineStr">
@@ -8915,7 +8951,7 @@
           <t>134 / 138</t>
         </is>
       </c>
-      <c r="F216" s="35" t="n">
+      <c r="F216" s="57" t="n">
         <v>0.9710144927536232</v>
       </c>
       <c r="G216" s="41" t="inlineStr">
@@ -8930,7 +8966,7 @@
       </c>
     </row>
     <row r="217" ht="24" customHeight="1">
-      <c r="A217" s="37" t="n">
+      <c r="A217" s="58" t="n">
         <v>46314</v>
       </c>
       <c r="B217" s="38" t="inlineStr">
@@ -8953,7 +8989,7 @@
           <t>79 / 81</t>
         </is>
       </c>
-      <c r="F217" s="40" t="n">
+      <c r="F217" s="59" t="n">
         <v>0.9753086419753086</v>
       </c>
       <c r="G217" s="41" t="inlineStr">
@@ -8968,7 +9004,7 @@
       </c>
     </row>
     <row r="218" ht="24" customHeight="1">
-      <c r="A218" s="32" t="n">
+      <c r="A218" s="56" t="n">
         <v>46314</v>
       </c>
       <c r="B218" s="33" t="inlineStr">
@@ -8991,7 +9027,7 @@
           <t>23 / 26</t>
         </is>
       </c>
-      <c r="F218" s="35" t="n">
+      <c r="F218" s="57" t="n">
         <v>0.8846153846153846</v>
       </c>
       <c r="G218" s="41" t="inlineStr">
@@ -9006,7 +9042,7 @@
       </c>
     </row>
     <row r="219" ht="24" customHeight="1">
-      <c r="A219" s="37" t="n">
+      <c r="A219" s="58" t="n">
         <v>46314</v>
       </c>
       <c r="B219" s="38" t="inlineStr">
@@ -9029,7 +9065,7 @@
           <t>124 / 126</t>
         </is>
       </c>
-      <c r="F219" s="40" t="n">
+      <c r="F219" s="59" t="n">
         <v>0.9841269841269841</v>
       </c>
       <c r="G219" s="41" t="inlineStr">
@@ -9044,7 +9080,7 @@
       </c>
     </row>
     <row r="220" ht="24" customHeight="1">
-      <c r="A220" s="32" t="n">
+      <c r="A220" s="56" t="n">
         <v>46314</v>
       </c>
       <c r="B220" s="33" t="inlineStr">
@@ -9067,7 +9103,7 @@
           <t>98 / 104</t>
         </is>
       </c>
-      <c r="F220" s="35" t="n">
+      <c r="F220" s="57" t="n">
         <v>0.9423076923076923</v>
       </c>
       <c r="G220" s="41" t="inlineStr">
@@ -9082,7 +9118,7 @@
       </c>
     </row>
     <row r="221" ht="24" customHeight="1">
-      <c r="A221" s="32" t="n">
+      <c r="A221" s="56" t="n">
         <v>46314</v>
       </c>
       <c r="B221" s="33" t="inlineStr">
@@ -9105,7 +9141,7 @@
           <t>29 / 44</t>
         </is>
       </c>
-      <c r="F221" s="35" t="n">
+      <c r="F221" s="57" t="n">
         <v>0.6590909090909091</v>
       </c>
       <c r="G221" s="41" t="inlineStr">
@@ -9120,7 +9156,7 @@
       </c>
     </row>
     <row r="222" ht="24" customHeight="1">
-      <c r="A222" s="37" t="n">
+      <c r="A222" s="58" t="n">
         <v>46314</v>
       </c>
       <c r="B222" s="38" t="inlineStr">
@@ -9143,7 +9179,7 @@
           <t>65 / 85</t>
         </is>
       </c>
-      <c r="F222" s="40" t="n">
+      <c r="F222" s="59" t="n">
         <v>0.7647058823529411</v>
       </c>
       <c r="G222" s="41" t="inlineStr">
@@ -9158,7 +9194,7 @@
       </c>
     </row>
     <row r="223" ht="24" customHeight="1">
-      <c r="A223" s="32" t="n">
+      <c r="A223" s="56" t="n">
         <v>46314</v>
       </c>
       <c r="B223" s="33" t="inlineStr">
@@ -9181,7 +9217,7 @@
           <t>24 / 102</t>
         </is>
       </c>
-      <c r="F223" s="35" t="n">
+      <c r="F223" s="57" t="n">
         <v>0.2352941176470588</v>
       </c>
       <c r="G223" s="41" t="inlineStr">
@@ -9196,7 +9232,7 @@
       </c>
     </row>
     <row r="224" ht="24" customHeight="1">
-      <c r="A224" s="32" t="n">
+      <c r="A224" s="56" t="n">
         <v>46314</v>
       </c>
       <c r="B224" s="33" t="inlineStr">
@@ -9219,7 +9255,7 @@
           <t>45 / 136</t>
         </is>
       </c>
-      <c r="F224" s="35" t="n">
+      <c r="F224" s="57" t="n">
         <v>0.3308823529411765</v>
       </c>
       <c r="G224" s="41" t="inlineStr">
@@ -9234,7 +9270,7 @@
       </c>
     </row>
     <row r="225" ht="24" customHeight="1">
-      <c r="A225" s="32" t="n">
+      <c r="A225" s="56" t="n">
         <v>46314</v>
       </c>
       <c r="B225" s="33" t="inlineStr">
@@ -9257,7 +9293,7 @@
           <t>1 / 27</t>
         </is>
       </c>
-      <c r="F225" s="35" t="n">
+      <c r="F225" s="57" t="n">
         <v>0.03703703703703703</v>
       </c>
       <c r="G225" s="41" t="inlineStr">
@@ -9272,7 +9308,7 @@
       </c>
     </row>
     <row r="226" ht="24" customHeight="1">
-      <c r="A226" s="37" t="n">
+      <c r="A226" s="58" t="n">
         <v>46314</v>
       </c>
       <c r="B226" s="38" t="inlineStr">
@@ -9295,7 +9331,7 @@
           <t>161 / 308</t>
         </is>
       </c>
-      <c r="F226" s="40" t="n">
+      <c r="F226" s="59" t="n">
         <v>0.5227272727272727</v>
       </c>
       <c r="G226" s="41" t="inlineStr">
@@ -9310,7 +9346,7 @@
       </c>
     </row>
     <row r="227" ht="24" customHeight="1">
-      <c r="A227" s="32" t="n">
+      <c r="A227" s="56" t="n">
         <v>46314</v>
       </c>
       <c r="B227" s="33" t="inlineStr">
@@ -9333,7 +9369,7 @@
           <t>34 / 149</t>
         </is>
       </c>
-      <c r="F227" s="35" t="n">
+      <c r="F227" s="57" t="n">
         <v>0.2281879194630873</v>
       </c>
       <c r="G227" s="41" t="inlineStr">
@@ -9348,7 +9384,7 @@
       </c>
     </row>
     <row r="228" ht="24" customHeight="1">
-      <c r="A228" s="32" t="n">
+      <c r="A228" s="56" t="n">
         <v>46315</v>
       </c>
       <c r="B228" s="33" t="inlineStr">
@@ -9371,7 +9407,7 @@
           <t>74 / 81</t>
         </is>
       </c>
-      <c r="F228" s="35" t="n">
+      <c r="F228" s="57" t="n">
         <v>0.9135802469135802</v>
       </c>
       <c r="G228" s="41" t="inlineStr">
@@ -9386,7 +9422,7 @@
       </c>
     </row>
     <row r="229" ht="24" customHeight="1">
-      <c r="A229" s="32" t="n">
+      <c r="A229" s="56" t="n">
         <v>46315</v>
       </c>
       <c r="B229" s="33" t="inlineStr">
@@ -9409,7 +9445,7 @@
           <t>69 / 113</t>
         </is>
       </c>
-      <c r="F229" s="35" t="n">
+      <c r="F229" s="57" t="n">
         <v>0.6106194690265486</v>
       </c>
       <c r="G229" s="41" t="inlineStr">
@@ -9424,7 +9460,7 @@
       </c>
     </row>
     <row r="230" ht="24" customHeight="1">
-      <c r="A230" s="32" t="n">
+      <c r="A230" s="56" t="n">
         <v>46315</v>
       </c>
       <c r="B230" s="33" t="inlineStr">
@@ -9447,7 +9483,7 @@
           <t>21 / 48</t>
         </is>
       </c>
-      <c r="F230" s="35" t="n">
+      <c r="F230" s="57" t="n">
         <v>0.4375</v>
       </c>
       <c r="G230" s="41" t="inlineStr">
@@ -9462,7 +9498,7 @@
       </c>
     </row>
     <row r="231" ht="24" customHeight="1">
-      <c r="A231" s="32" t="n">
+      <c r="A231" s="56" t="n">
         <v>46315</v>
       </c>
       <c r="B231" s="33" t="inlineStr">
@@ -9485,7 +9521,7 @@
           <t>71 / 113</t>
         </is>
       </c>
-      <c r="F231" s="35" t="n">
+      <c r="F231" s="57" t="n">
         <v>0.6283185840707964</v>
       </c>
       <c r="G231" s="41" t="inlineStr">
@@ -9500,7 +9536,7 @@
       </c>
     </row>
     <row r="232" ht="24" customHeight="1">
-      <c r="A232" s="37" t="n">
+      <c r="A232" s="58" t="n">
         <v>46315</v>
       </c>
       <c r="B232" s="38" t="inlineStr">
@@ -9523,7 +9559,7 @@
           <t>46 / 46</t>
         </is>
       </c>
-      <c r="F232" s="40" t="n">
+      <c r="F232" s="59" t="n">
         <v>1</v>
       </c>
       <c r="G232" s="41" t="inlineStr">
@@ -9538,7 +9574,7 @@
       </c>
     </row>
     <row r="233" ht="24" customHeight="1">
-      <c r="A233" s="32" t="n">
+      <c r="A233" s="56" t="n">
         <v>46315</v>
       </c>
       <c r="B233" s="33" t="inlineStr">
@@ -9561,7 +9597,7 @@
           <t>56 / 56</t>
         </is>
       </c>
-      <c r="F233" s="35" t="n">
+      <c r="F233" s="57" t="n">
         <v>1</v>
       </c>
       <c r="G233" s="41" t="inlineStr">
@@ -9576,7 +9612,7 @@
       </c>
     </row>
     <row r="234" ht="24" customHeight="1">
-      <c r="A234" s="37" t="n">
+      <c r="A234" s="58" t="n">
         <v>46315</v>
       </c>
       <c r="B234" s="38" t="inlineStr">
@@ -9599,7 +9635,7 @@
           <t>24 / 25</t>
         </is>
       </c>
-      <c r="F234" s="40" t="n">
+      <c r="F234" s="59" t="n">
         <v>0.96</v>
       </c>
       <c r="G234" s="41" t="inlineStr">
@@ -9614,7 +9650,7 @@
       </c>
     </row>
     <row r="235" ht="24" customHeight="1">
-      <c r="A235" s="32" t="n">
+      <c r="A235" s="56" t="n">
         <v>46315</v>
       </c>
       <c r="B235" s="33" t="inlineStr">
@@ -9637,7 +9673,7 @@
           <t>10 / 25</t>
         </is>
       </c>
-      <c r="F235" s="35" t="n">
+      <c r="F235" s="57" t="n">
         <v>0.4</v>
       </c>
       <c r="G235" s="41" t="inlineStr">
@@ -9652,7 +9688,7 @@
       </c>
     </row>
     <row r="236" ht="24" customHeight="1">
-      <c r="A236" s="32" t="n">
+      <c r="A236" s="56" t="n">
         <v>46315</v>
       </c>
       <c r="B236" s="33" t="inlineStr">
@@ -9675,7 +9711,7 @@
           <t>77 / 99</t>
         </is>
       </c>
-      <c r="F236" s="35" t="n">
+      <c r="F236" s="57" t="n">
         <v>0.7777777777777778</v>
       </c>
       <c r="G236" s="41" t="inlineStr">
@@ -9690,7 +9726,7 @@
       </c>
     </row>
     <row r="237" ht="24" customHeight="1">
-      <c r="A237" s="32" t="n">
+      <c r="A237" s="56" t="n">
         <v>46315</v>
       </c>
       <c r="B237" s="33" t="inlineStr">
@@ -9713,7 +9749,7 @@
           <t>111 / 111</t>
         </is>
       </c>
-      <c r="F237" s="35" t="n">
+      <c r="F237" s="57" t="n">
         <v>1</v>
       </c>
       <c r="G237" s="41" t="inlineStr">
@@ -9728,7 +9764,7 @@
       </c>
     </row>
     <row r="238" ht="24" customHeight="1">
-      <c r="A238" s="37" t="n">
+      <c r="A238" s="58" t="n">
         <v>46315</v>
       </c>
       <c r="B238" s="38" t="inlineStr">
@@ -9751,7 +9787,7 @@
           <t>134 / 138</t>
         </is>
       </c>
-      <c r="F238" s="40" t="n">
+      <c r="F238" s="59" t="n">
         <v>0.9710144927536232</v>
       </c>
       <c r="G238" s="41" t="inlineStr">
@@ -9766,7 +9802,7 @@
       </c>
     </row>
     <row r="239" ht="24" customHeight="1">
-      <c r="A239" s="32" t="n">
+      <c r="A239" s="56" t="n">
         <v>46315</v>
       </c>
       <c r="B239" s="33" t="inlineStr">
@@ -9789,7 +9825,7 @@
           <t>79 / 81</t>
         </is>
       </c>
-      <c r="F239" s="35" t="n">
+      <c r="F239" s="57" t="n">
         <v>0.9753086419753086</v>
       </c>
       <c r="G239" s="41" t="inlineStr">
@@ -9804,7 +9840,7 @@
       </c>
     </row>
     <row r="240" ht="24" customHeight="1">
-      <c r="A240" s="37" t="n">
+      <c r="A240" s="58" t="n">
         <v>46315</v>
       </c>
       <c r="B240" s="38" t="inlineStr">
@@ -9827,7 +9863,7 @@
           <t>23 / 26</t>
         </is>
       </c>
-      <c r="F240" s="40" t="n">
+      <c r="F240" s="59" t="n">
         <v>0.8846153846153846</v>
       </c>
       <c r="G240" s="41" t="inlineStr">
@@ -9842,7 +9878,7 @@
       </c>
     </row>
     <row r="241" ht="24" customHeight="1">
-      <c r="A241" s="32" t="n">
+      <c r="A241" s="56" t="n">
         <v>46315</v>
       </c>
       <c r="B241" s="33" t="inlineStr">
@@ -9865,7 +9901,7 @@
           <t>124 / 126</t>
         </is>
       </c>
-      <c r="F241" s="35" t="n">
+      <c r="F241" s="57" t="n">
         <v>0.9841269841269841</v>
       </c>
       <c r="G241" s="41" t="inlineStr">
@@ -9880,7 +9916,7 @@
       </c>
     </row>
     <row r="242" ht="24" customHeight="1">
-      <c r="A242" s="37" t="n">
+      <c r="A242" s="58" t="n">
         <v>46315</v>
       </c>
       <c r="B242" s="38" t="inlineStr">
@@ -9903,7 +9939,7 @@
           <t>98 / 104</t>
         </is>
       </c>
-      <c r="F242" s="40" t="n">
+      <c r="F242" s="59" t="n">
         <v>0.9423076923076923</v>
       </c>
       <c r="G242" s="41" t="inlineStr">
@@ -9918,7 +9954,7 @@
       </c>
     </row>
     <row r="243" ht="24" customHeight="1">
-      <c r="A243" s="37" t="n">
+      <c r="A243" s="58" t="n">
         <v>46315</v>
       </c>
       <c r="B243" s="38" t="inlineStr">
@@ -9941,7 +9977,7 @@
           <t>29 / 44</t>
         </is>
       </c>
-      <c r="F243" s="40" t="n">
+      <c r="F243" s="59" t="n">
         <v>0.6590909090909091</v>
       </c>
       <c r="G243" s="41" t="inlineStr">
@@ -9956,7 +9992,7 @@
       </c>
     </row>
     <row r="244" ht="24" customHeight="1">
-      <c r="A244" s="32" t="n">
+      <c r="A244" s="56" t="n">
         <v>46315</v>
       </c>
       <c r="B244" s="33" t="inlineStr">
@@ -9979,7 +10015,7 @@
           <t>65 / 85</t>
         </is>
       </c>
-      <c r="F244" s="35" t="n">
+      <c r="F244" s="57" t="n">
         <v>0.7647058823529411</v>
       </c>
       <c r="G244" s="41" t="inlineStr">
@@ -9994,7 +10030,7 @@
       </c>
     </row>
     <row r="245" ht="24" customHeight="1">
-      <c r="A245" s="37" t="n">
+      <c r="A245" s="58" t="n">
         <v>46315</v>
       </c>
       <c r="B245" s="38" t="inlineStr">
@@ -10017,7 +10053,7 @@
           <t>24 / 102</t>
         </is>
       </c>
-      <c r="F245" s="40" t="n">
+      <c r="F245" s="59" t="n">
         <v>0.2352941176470588</v>
       </c>
       <c r="G245" s="41" t="inlineStr">
@@ -10032,7 +10068,7 @@
       </c>
     </row>
     <row r="246" ht="24" customHeight="1">
-      <c r="A246" s="37" t="n">
+      <c r="A246" s="58" t="n">
         <v>46315</v>
       </c>
       <c r="B246" s="38" t="inlineStr">
@@ -10055,7 +10091,7 @@
           <t>45 / 136</t>
         </is>
       </c>
-      <c r="F246" s="40" t="n">
+      <c r="F246" s="59" t="n">
         <v>0.3308823529411765</v>
       </c>
       <c r="G246" s="41" t="inlineStr">
@@ -10070,7 +10106,7 @@
       </c>
     </row>
     <row r="247" ht="24" customHeight="1">
-      <c r="A247" s="32" t="n">
+      <c r="A247" s="56" t="n">
         <v>46315</v>
       </c>
       <c r="B247" s="33" t="inlineStr">
@@ -10093,7 +10129,7 @@
           <t>1 / 27</t>
         </is>
       </c>
-      <c r="F247" s="35" t="n">
+      <c r="F247" s="57" t="n">
         <v>0.03703703703703703</v>
       </c>
       <c r="G247" s="41" t="inlineStr">
@@ -10108,7 +10144,7 @@
       </c>
     </row>
     <row r="248" ht="24" customHeight="1">
-      <c r="A248" s="37" t="n">
+      <c r="A248" s="58" t="n">
         <v>46315</v>
       </c>
       <c r="B248" s="38" t="inlineStr">
@@ -10131,7 +10167,7 @@
           <t>161 / 308</t>
         </is>
       </c>
-      <c r="F248" s="40" t="n">
+      <c r="F248" s="59" t="n">
         <v>0.5227272727272727</v>
       </c>
       <c r="G248" s="41" t="inlineStr">
@@ -10146,7 +10182,7 @@
       </c>
     </row>
     <row r="249" ht="24" customHeight="1">
-      <c r="A249" s="37" t="n">
+      <c r="A249" s="58" t="n">
         <v>46315</v>
       </c>
       <c r="B249" s="38" t="inlineStr">
@@ -10169,7 +10205,7 @@
           <t>34 / 149</t>
         </is>
       </c>
-      <c r="F249" s="40" t="n">
+      <c r="F249" s="59" t="n">
         <v>0.2281879194630873</v>
       </c>
       <c r="G249" s="41" t="inlineStr">
@@ -11655,4 +11691,383 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BROGA COMPETITOR SALES ANALYSIS | TEDUH SEARCH REFERENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>BROGA Developer</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Search Keyword</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Project Code and Name</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>TEDUH Data Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="62" t="inlineStr">
+        <is>
+          <t>Balau Homes 2A</t>
+        </is>
+      </c>
+      <c r="B4" s="33" t="inlineStr">
+        <is>
+          <t>Pemaju: Boustead</t>
+        </is>
+      </c>
+      <c r="C4" s="33" t="inlineStr">
+        <is>
+          <t>20094-4
+MUTIARA HILLS</t>
+        </is>
+      </c>
+      <c r="D4" s="63" t="inlineStr">
+        <is>
+          <t>Open 20094-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="64" t="inlineStr">
+        <is>
+          <t>Balau Homes 2C</t>
+        </is>
+      </c>
+      <c r="B5" s="38" t="inlineStr">
+        <is>
+          <t>Pemaju: Boustead</t>
+        </is>
+      </c>
+      <c r="C5" s="38" t="inlineStr">
+        <is>
+          <t>20094-5
+MUTIARA HILLS, SEMENYIH</t>
+        </is>
+      </c>
+      <c r="D5" s="65" t="inlineStr">
+        <is>
+          <t>Open 20094-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="62" t="inlineStr">
+        <is>
+          <t>Springvale Sempurna Heights</t>
+        </is>
+      </c>
+      <c r="B6" s="33" t="inlineStr">
+        <is>
+          <t>springvale</t>
+        </is>
+      </c>
+      <c r="C6" s="33" t="inlineStr">
+        <is>
+          <t>19321-4
+SPRINGVALE SEMPURNA HEIGHT</t>
+        </is>
+      </c>
+      <c r="D6" s="63" t="inlineStr">
+        <is>
+          <t>Open 19321-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="64" t="inlineStr">
+        <is>
+          <t>Zinnia Residences</t>
+        </is>
+      </c>
+      <c r="B7" s="38" t="inlineStr">
+        <is>
+          <t>Pemaju: crimson villa</t>
+        </is>
+      </c>
+      <c r="C7" s="38" t="inlineStr">
+        <is>
+          <t>19959-3
+TAMAN AKASIA</t>
+        </is>
+      </c>
+      <c r="D7" s="65" t="inlineStr">
+        <is>
+          <t>Open 19959-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="62" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="B8" s="33" t="inlineStr">
+        <is>
+          <t>m legasi</t>
+        </is>
+      </c>
+      <c r="C8" s="33" t="inlineStr">
+        <is>
+          <t>30897-1
+M LEGASI</t>
+        </is>
+      </c>
+      <c r="D8" s="63" t="inlineStr">
+        <is>
+          <t>Open 30897-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="64" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="B9" s="38" t="inlineStr">
+        <is>
+          <t>m legasi</t>
+        </is>
+      </c>
+      <c r="C9" s="38" t="inlineStr">
+        <is>
+          <t>30897-2
+M LEGASI</t>
+        </is>
+      </c>
+      <c r="D9" s="65" t="inlineStr">
+        <is>
+          <t>Open 30897-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="62" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 3</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>m legasi</t>
+        </is>
+      </c>
+      <c r="C10" s="33" t="inlineStr">
+        <is>
+          <t>30897-3
+M LEGASI</t>
+        </is>
+      </c>
+      <c r="D10" s="63" t="inlineStr">
+        <is>
+          <t>Open 30897-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="64" t="inlineStr">
+        <is>
+          <t>Sapphire Residence @Diamond City</t>
+        </is>
+      </c>
+      <c r="B11" s="38" t="inlineStr">
+        <is>
+          <t>sapphire</t>
+        </is>
+      </c>
+      <c r="C11" s="38" t="inlineStr">
+        <is>
+          <t>13170-7
+SAPPHIRE RESIDENCE</t>
+        </is>
+      </c>
+      <c r="D11" s="65" t="inlineStr">
+        <is>
+          <t>Open 13170-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="62" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>birchpark</t>
+        </is>
+      </c>
+      <c r="C12" s="33" t="inlineStr">
+        <is>
+          <t>19150-17
+BIRCHPARK</t>
+        </is>
+      </c>
+      <c r="D12" s="63" t="inlineStr">
+        <is>
+          <t>Open 19150-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="64" t="inlineStr">
+        <is>
+          <t>Chorus @Setia Ecohill 2</t>
+        </is>
+      </c>
+      <c r="B13" s="38" t="inlineStr">
+        <is>
+          <t>ecohill</t>
+        </is>
+      </c>
+      <c r="C13" s="38" t="inlineStr">
+        <is>
+          <t>14421-21
+SETIA ECOHILL 2</t>
+        </is>
+      </c>
+      <c r="D13" s="65" t="inlineStr">
+        <is>
+          <t>Open 14421-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="62" t="inlineStr">
+        <is>
+          <t>Banyan @Setia Ecohill 2</t>
+        </is>
+      </c>
+      <c r="B14" s="33" t="inlineStr">
+        <is>
+          <t>ecohill</t>
+        </is>
+      </c>
+      <c r="C14" s="33" t="inlineStr">
+        <is>
+          <t>14421-22
+SETIA ECOHILL 2</t>
+        </is>
+      </c>
+      <c r="D14" s="63" t="inlineStr">
+        <is>
+          <t>Open 14421-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="64" t="inlineStr">
+        <is>
+          <t>Amani Gallery Homes</t>
+        </is>
+      </c>
+      <c r="B15" s="38" t="inlineStr">
+        <is>
+          <t>amani</t>
+        </is>
+      </c>
+      <c r="C15" s="38" t="inlineStr">
+        <is>
+          <t>6868-20
+GALLERY HOMES - AMANI</t>
+        </is>
+      </c>
+      <c r="D15" s="65" t="inlineStr">
+        <is>
+          <t>Open 6868-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="62" t="inlineStr">
+        <is>
+          <t>Majestic Flora</t>
+        </is>
+      </c>
+      <c r="B16" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C16" s="33" t="inlineStr">
+        <is>
+          <t>Not yet on TEDUH</t>
+        </is>
+      </c>
+      <c r="D16" s="33" t="inlineStr"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="64" t="inlineStr">
+        <is>
+          <t>Astrea @Eco Radiance</t>
+        </is>
+      </c>
+      <c r="B17" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" s="38" t="inlineStr">
+        <is>
+          <t>Not yet on TEDUH</t>
+        </is>
+      </c>
+      <c r="D17" s="38" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId12"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/Broga_Weekly_Tracking.xlsx
+++ b/Broga_Weekly_Tracking.xlsx
@@ -12026,7 +12026,7 @@
       </c>
       <c r="C16" s="33" t="inlineStr">
         <is>
-          <t>Not yet on TEDUH</t>
+          <t>No TEDUH code recorded</t>
         </is>
       </c>
       <c r="D16" s="33" t="inlineStr"/>
@@ -12044,7 +12044,7 @@
       </c>
       <c r="C17" s="38" t="inlineStr">
         <is>
-          <t>Not yet on TEDUH</t>
+          <t>No TEDUH code recorded</t>
         </is>
       </c>
       <c r="D17" s="38" t="inlineStr"/>

--- a/Broga_Weekly_Tracking.xlsx
+++ b/Broga_Weekly_Tracking.xlsx
@@ -12,7 +12,7 @@
     <sheet name="TEDUH Search Reference" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Snapshot History'!$A$3:$A$271</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Snapshot History'!$A$3:$A$293</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Snapshot History'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Oct 2026'!$1:$3</definedName>
   </definedNames>
@@ -126,12 +126,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F7F8F4"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00F7F8F4"/>
       </patternFill>
     </fill>
     <fill>
@@ -473,16 +473,16 @@
     <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -850,7 +850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H271"/>
+  <dimension ref="A1:H293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -985,36 +985,36 @@
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="57" t="n">
+      <c r="A6" s="59" t="n">
         <v>45582</v>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="39" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C6" s="34" t="inlineStr">
+      <c r="C6" s="39" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D6" s="35" t="inlineStr">
+      <c r="D6" s="40" t="inlineStr">
         <is>
           <t>Booked</t>
         </is>
       </c>
-      <c r="E6" s="35" t="inlineStr">
+      <c r="E6" s="40" t="inlineStr">
         <is>
           <t>— / 48</t>
         </is>
       </c>
-      <c r="F6" s="58" t="n"/>
-      <c r="G6" s="37" t="inlineStr">
+      <c r="F6" s="60" t="n"/>
+      <c r="G6" s="42" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="H6" s="34" t="inlineStr">
+      <c r="H6" s="39" t="inlineStr">
         <is>
           <t>8% Booked (4/48 units); Non-signed status retained for audit; excluded from signed trend</t>
         </is>
@@ -1057,72 +1057,72 @@
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="59" t="n">
+      <c r="A8" s="57" t="n">
         <v>45625</v>
       </c>
-      <c r="B8" s="39" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C8" s="39" t="inlineStr">
+      <c r="C8" s="34" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D8" s="40" t="inlineStr">
+      <c r="D8" s="35" t="inlineStr">
         <is>
           <t>Booked</t>
         </is>
       </c>
-      <c r="E8" s="40" t="inlineStr">
+      <c r="E8" s="35" t="inlineStr">
         <is>
           <t>— / 48</t>
         </is>
       </c>
-      <c r="F8" s="60" t="n"/>
-      <c r="G8" s="42" t="inlineStr">
+      <c r="F8" s="58" t="n"/>
+      <c r="G8" s="37" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="H8" s="39" t="inlineStr">
+      <c r="H8" s="34" t="inlineStr">
         <is>
           <t>15% Booked (7/48 units); Non-signed status retained for audit; excluded from signed trend</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="59" t="n">
+      <c r="A9" s="57" t="n">
         <v>45733</v>
       </c>
-      <c r="B9" s="39" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>Amani Gallery Homes</t>
         </is>
       </c>
-      <c r="C9" s="39" t="inlineStr">
+      <c r="C9" s="34" t="inlineStr">
         <is>
           <t>20' x 70' / 20' x 72'</t>
         </is>
       </c>
-      <c r="D9" s="40" t="inlineStr">
+      <c r="D9" s="35" t="inlineStr">
         <is>
           <t>Booked</t>
         </is>
       </c>
-      <c r="E9" s="40" t="inlineStr">
+      <c r="E9" s="35" t="inlineStr">
         <is>
           <t>— / 81</t>
         </is>
       </c>
-      <c r="F9" s="60" t="n"/>
-      <c r="G9" s="42" t="inlineStr">
+      <c r="F9" s="58" t="n"/>
+      <c r="G9" s="37" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="H9" s="39" t="inlineStr">
+      <c r="H9" s="34" t="inlineStr">
         <is>
           <t>11% Booked (9/81 units); Non-signed status retained for audit; excluded from signed trend</t>
         </is>
@@ -1165,36 +1165,36 @@
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="57" t="n">
+      <c r="A11" s="59" t="n">
         <v>45733</v>
       </c>
-      <c r="B11" s="34" t="inlineStr">
+      <c r="B11" s="39" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C11" s="34" t="inlineStr">
+      <c r="C11" s="39" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D11" s="35" t="inlineStr">
+      <c r="D11" s="40" t="inlineStr">
         <is>
           <t>Booked</t>
         </is>
       </c>
-      <c r="E11" s="35" t="inlineStr">
+      <c r="E11" s="40" t="inlineStr">
         <is>
           <t>— / 48</t>
         </is>
       </c>
-      <c r="F11" s="58" t="n"/>
-      <c r="G11" s="37" t="inlineStr">
+      <c r="F11" s="60" t="n"/>
+      <c r="G11" s="42" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="H11" s="34" t="inlineStr">
+      <c r="H11" s="39" t="inlineStr">
         <is>
           <t>15% Booked (7/48 units); Non-signed status retained for audit; excluded from signed trend</t>
         </is>
@@ -1277,36 +1277,36 @@
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="59" t="n">
+      <c r="A14" s="57" t="n">
         <v>45889</v>
       </c>
-      <c r="B14" s="39" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C14" s="39" t="inlineStr">
+      <c r="C14" s="34" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D14" s="40" t="inlineStr">
+      <c r="D14" s="35" t="inlineStr">
         <is>
           <t>Booked</t>
         </is>
       </c>
-      <c r="E14" s="40" t="inlineStr">
+      <c r="E14" s="35" t="inlineStr">
         <is>
           <t>— / 48</t>
         </is>
       </c>
-      <c r="F14" s="60" t="n"/>
-      <c r="G14" s="42" t="inlineStr">
+      <c r="F14" s="58" t="n"/>
+      <c r="G14" s="37" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="H14" s="39" t="inlineStr">
+      <c r="H14" s="34" t="inlineStr">
         <is>
           <t>50% Booked (24/48 units); Non-signed status retained for audit; excluded from signed trend</t>
         </is>
@@ -1579,72 +1579,72 @@
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="57" t="n">
+      <c r="A22" s="59" t="n">
         <v>45911</v>
       </c>
-      <c r="B22" s="34" t="inlineStr">
+      <c r="B22" s="39" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C22" s="34" t="inlineStr">
+      <c r="C22" s="39" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D22" s="35" t="inlineStr">
+      <c r="D22" s="40" t="inlineStr">
         <is>
           <t>Booked</t>
         </is>
       </c>
-      <c r="E22" s="35" t="inlineStr">
+      <c r="E22" s="40" t="inlineStr">
         <is>
           <t>— / 48</t>
         </is>
       </c>
-      <c r="F22" s="58" t="n"/>
-      <c r="G22" s="37" t="inlineStr">
+      <c r="F22" s="60" t="n"/>
+      <c r="G22" s="42" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="H22" s="34" t="inlineStr">
+      <c r="H22" s="39" t="inlineStr">
         <is>
           <t>52% Booked (25/48 units); Non-signed status retained for audit; excluded from signed trend</t>
         </is>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="57" t="n">
+      <c r="A23" s="59" t="n">
         <v>45936</v>
       </c>
-      <c r="B23" s="34" t="inlineStr">
+      <c r="B23" s="39" t="inlineStr">
         <is>
           <t>Amani Gallery Homes</t>
         </is>
       </c>
-      <c r="C23" s="34" t="inlineStr">
+      <c r="C23" s="39" t="inlineStr">
         <is>
           <t>20' x 70' / 20' x 72'</t>
         </is>
       </c>
-      <c r="D23" s="35" t="inlineStr">
+      <c r="D23" s="40" t="inlineStr">
         <is>
           <t>Booked</t>
         </is>
       </c>
-      <c r="E23" s="35" t="inlineStr">
+      <c r="E23" s="40" t="inlineStr">
         <is>
           <t>— / 81</t>
         </is>
       </c>
-      <c r="F23" s="58" t="n"/>
-      <c r="G23" s="37" t="inlineStr">
+      <c r="F23" s="60" t="n"/>
+      <c r="G23" s="42" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="H23" s="34" t="inlineStr">
+      <c r="H23" s="39" t="inlineStr">
         <is>
           <t>35% Booked (28/81 units); Non-signed status retained for audit; excluded from signed trend</t>
         </is>
@@ -1677,7 +1677,7 @@
       <c r="F24" s="58" t="n">
         <v>0.3274336283185841</v>
       </c>
-      <c r="G24" s="37" t="inlineStr">
+      <c r="G24" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -1689,36 +1689,36 @@
       </c>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="59" t="n">
+      <c r="A25" s="57" t="n">
         <v>45936</v>
       </c>
-      <c r="B25" s="39" t="inlineStr">
+      <c r="B25" s="34" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C25" s="39" t="inlineStr">
+      <c r="C25" s="34" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D25" s="40" t="inlineStr">
+      <c r="D25" s="35" t="inlineStr">
         <is>
           <t>Booked</t>
         </is>
       </c>
-      <c r="E25" s="40" t="inlineStr">
+      <c r="E25" s="35" t="inlineStr">
         <is>
           <t>— / 48</t>
         </is>
       </c>
-      <c r="F25" s="60" t="n"/>
-      <c r="G25" s="42" t="inlineStr">
+      <c r="F25" s="58" t="n"/>
+      <c r="G25" s="37" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="H25" s="39" t="inlineStr">
+      <c r="H25" s="34" t="inlineStr">
         <is>
           <t>52% Booked (25/48 units); Non-signed status retained for audit; excluded from signed trend</t>
         </is>
@@ -1763,190 +1763,190 @@
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="57" t="n">
+      <c r="A27" s="59" t="n">
         <v>45936</v>
       </c>
-      <c r="B27" s="34" t="inlineStr">
+      <c r="B27" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C27" s="34" t="inlineStr">
+      <c r="C27" s="39" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D27" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E27" s="35" t="inlineStr">
+      <c r="D27" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E27" s="40" t="inlineStr">
         <is>
           <t>45 / 46</t>
         </is>
       </c>
-      <c r="F27" s="58" t="n">
+      <c r="F27" s="60" t="n">
         <v>0.9782608695652174</v>
       </c>
-      <c r="G27" s="37" t="inlineStr">
+      <c r="G27" s="42" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="H27" s="34" t="inlineStr">
+      <c r="H27" s="39" t="inlineStr">
         <is>
           <t>98% Signed (45/46 units); No earlier valid signed observation</t>
         </is>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="59" t="n">
+      <c r="A28" s="57" t="n">
         <v>45936</v>
       </c>
-      <c r="B28" s="39" t="inlineStr">
+      <c r="B28" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C28" s="39" t="inlineStr">
+      <c r="C28" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D28" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E28" s="40" t="inlineStr">
+      <c r="D28" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E28" s="35" t="inlineStr">
         <is>
           <t>47 / 56</t>
         </is>
       </c>
-      <c r="F28" s="60" t="n">
+      <c r="F28" s="58" t="n">
         <v>0.8392857142857143</v>
       </c>
-      <c r="G28" s="42" t="inlineStr">
+      <c r="G28" s="37" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="H28" s="39" t="inlineStr">
+      <c r="H28" s="34" t="inlineStr">
         <is>
           <t>84% Signed (47/56 units); No earlier valid signed observation</t>
         </is>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="57" t="n">
+      <c r="A29" s="59" t="n">
         <v>45936</v>
       </c>
-      <c r="B29" s="34" t="inlineStr">
+      <c r="B29" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C29" s="34" t="inlineStr">
+      <c r="C29" s="39" t="inlineStr">
         <is>
           <t>20' x 75'</t>
         </is>
       </c>
-      <c r="D29" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E29" s="35" t="inlineStr">
+      <c r="D29" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E29" s="40" t="inlineStr">
         <is>
           <t>13 / 25</t>
         </is>
       </c>
-      <c r="F29" s="58" t="n">
+      <c r="F29" s="60" t="n">
         <v>0.52</v>
       </c>
-      <c r="G29" s="37" t="inlineStr">
+      <c r="G29" s="42" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="H29" s="34" t="inlineStr">
+      <c r="H29" s="39" t="inlineStr">
         <is>
           <t>52% Signed (13/25 units); No earlier valid signed observation</t>
         </is>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="59" t="n">
+      <c r="A30" s="57" t="n">
         <v>45936</v>
       </c>
-      <c r="B30" s="39" t="inlineStr">
+      <c r="B30" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C30" s="39" t="inlineStr">
+      <c r="C30" s="34" t="inlineStr">
         <is>
           <t>20' x 80'</t>
         </is>
       </c>
-      <c r="D30" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E30" s="40" t="inlineStr">
+      <c r="D30" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E30" s="35" t="inlineStr">
         <is>
           <t>3 / 25</t>
         </is>
       </c>
-      <c r="F30" s="60" t="n">
+      <c r="F30" s="58" t="n">
         <v>0.12</v>
       </c>
-      <c r="G30" s="42" t="inlineStr">
+      <c r="G30" s="37" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="H30" s="39" t="inlineStr">
+      <c r="H30" s="34" t="inlineStr">
         <is>
           <t>12% Signed (3/25 units); No earlier valid signed observation</t>
         </is>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="57" t="n">
+      <c r="A31" s="59" t="n">
         <v>45936</v>
       </c>
-      <c r="B31" s="34" t="inlineStr">
+      <c r="B31" s="39" t="inlineStr">
         <is>
           <t>Chorus @Setia Ecohill 2</t>
         </is>
       </c>
-      <c r="C31" s="34" t="inlineStr">
+      <c r="C31" s="39" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D31" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E31" s="35" t="inlineStr">
+      <c r="D31" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E31" s="40" t="inlineStr">
         <is>
           <t>87 / 99</t>
         </is>
       </c>
-      <c r="F31" s="58" t="n">
+      <c r="F31" s="60" t="n">
         <v>0.8787878787878788</v>
       </c>
-      <c r="G31" s="37" t="inlineStr">
+      <c r="G31" s="42" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="H31" s="34" t="inlineStr">
+      <c r="H31" s="39" t="inlineStr">
         <is>
           <t>88% Signed (87/99 units); No earlier valid signed observation</t>
         </is>
@@ -2067,72 +2067,72 @@
       </c>
     </row>
     <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="57" t="n">
+      <c r="A35" s="59" t="n">
         <v>45936</v>
       </c>
-      <c r="B35" s="34" t="inlineStr">
+      <c r="B35" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C35" s="34" t="inlineStr">
+      <c r="C35" s="39" t="inlineStr">
         <is>
           <t>No group details</t>
         </is>
       </c>
-      <c r="D35" s="35" t="inlineStr">
+      <c r="D35" s="40" t="inlineStr">
         <is>
           <t>Yet to sign</t>
         </is>
       </c>
-      <c r="E35" s="35" t="inlineStr">
+      <c r="E35" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F35" s="58" t="n"/>
-      <c r="G35" s="37" t="inlineStr">
+      <c r="F35" s="60" t="n"/>
+      <c r="G35" s="42" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="H35" s="34" t="inlineStr">
+      <c r="H35" s="39" t="inlineStr">
         <is>
           <t>Yet to sign; Non-signed status retained for audit; excluded from signed trend</t>
         </is>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="59" t="n">
+      <c r="A36" s="57" t="n">
         <v>45936</v>
       </c>
-      <c r="B36" s="39" t="inlineStr">
+      <c r="B36" s="34" t="inlineStr">
         <is>
           <t>Sapphire Residence @Diamond City</t>
         </is>
       </c>
-      <c r="C36" s="39" t="inlineStr">
+      <c r="C36" s="34" t="inlineStr">
         <is>
           <t>No group details</t>
         </is>
       </c>
-      <c r="D36" s="40" t="inlineStr">
+      <c r="D36" s="35" t="inlineStr">
         <is>
           <t>Yet to sign</t>
         </is>
       </c>
-      <c r="E36" s="40" t="inlineStr">
+      <c r="E36" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F36" s="60" t="n"/>
-      <c r="G36" s="42" t="inlineStr">
+      <c r="F36" s="58" t="n"/>
+      <c r="G36" s="37" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="H36" s="39" t="inlineStr">
+      <c r="H36" s="34" t="inlineStr">
         <is>
           <t>Yet to sign; Non-signed status retained for audit; excluded from signed trend</t>
         </is>
@@ -2291,38 +2291,38 @@
       </c>
     </row>
     <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="57" t="n">
+      <c r="A41" s="59" t="n">
         <v>46080</v>
       </c>
-      <c r="B41" s="34" t="inlineStr">
+      <c r="B41" s="39" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C41" s="34" t="inlineStr">
+      <c r="C41" s="39" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D41" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E41" s="35" t="inlineStr">
+      <c r="D41" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E41" s="40" t="inlineStr">
         <is>
           <t>15 / 48</t>
         </is>
       </c>
-      <c r="F41" s="58" t="n">
+      <c r="F41" s="60" t="n">
         <v>0.3125</v>
       </c>
-      <c r="G41" s="37" t="inlineStr">
+      <c r="G41" s="42" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="H41" s="34" t="inlineStr">
+      <c r="H41" s="39" t="inlineStr">
         <is>
           <t>31% Signed (15/48 units); No earlier valid signed observation</t>
         </is>
@@ -2443,114 +2443,114 @@
       </c>
     </row>
     <row r="45" ht="24" customHeight="1">
-      <c r="A45" s="59" t="n">
+      <c r="A45" s="57" t="n">
         <v>46080</v>
       </c>
-      <c r="B45" s="39" t="inlineStr">
+      <c r="B45" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C45" s="39" t="inlineStr">
+      <c r="C45" s="34" t="inlineStr">
         <is>
           <t>20' x 60'</t>
         </is>
       </c>
-      <c r="D45" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E45" s="40" t="inlineStr">
+      <c r="D45" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E45" s="35" t="inlineStr">
         <is>
           <t>3 / 26</t>
         </is>
       </c>
-      <c r="F45" s="60" t="n">
+      <c r="F45" s="58" t="n">
         <v>0.1153846153846154</v>
       </c>
-      <c r="G45" s="42" t="inlineStr">
+      <c r="G45" s="37" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="H45" s="39" t="inlineStr">
+      <c r="H45" s="34" t="inlineStr">
         <is>
           <t>12% Signed (3/26 units); No earlier valid signed observation</t>
         </is>
       </c>
     </row>
     <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="57" t="n">
+      <c r="A46" s="59" t="n">
         <v>46080</v>
       </c>
-      <c r="B46" s="34" t="inlineStr">
+      <c r="B46" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C46" s="34" t="inlineStr">
+      <c r="C46" s="39" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D46" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E46" s="35" t="inlineStr">
+      <c r="D46" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E46" s="40" t="inlineStr">
         <is>
           <t>77 / 126</t>
         </is>
       </c>
-      <c r="F46" s="58" t="n">
+      <c r="F46" s="60" t="n">
         <v>0.6111111111111112</v>
       </c>
-      <c r="G46" s="37" t="inlineStr">
+      <c r="G46" s="42" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="H46" s="34" t="inlineStr">
+      <c r="H46" s="39" t="inlineStr">
         <is>
           <t>61% Signed (77/126 units); No earlier valid signed observation</t>
         </is>
       </c>
     </row>
     <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="59" t="n">
+      <c r="A47" s="57" t="n">
         <v>46080</v>
       </c>
-      <c r="B47" s="39" t="inlineStr">
+      <c r="B47" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C47" s="39" t="inlineStr">
+      <c r="C47" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D47" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E47" s="40" t="inlineStr">
+      <c r="D47" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E47" s="35" t="inlineStr">
         <is>
           <t>17 / 104</t>
         </is>
       </c>
-      <c r="F47" s="60" t="n">
+      <c r="F47" s="58" t="n">
         <v>0.1634615384615385</v>
       </c>
-      <c r="G47" s="42" t="inlineStr">
+      <c r="G47" s="37" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="H47" s="39" t="inlineStr">
+      <c r="H47" s="34" t="inlineStr">
         <is>
           <t>16% Signed (17/104 units); No earlier valid signed observation</t>
         </is>
@@ -2583,7 +2583,7 @@
       <c r="F48" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="G48" s="37" t="inlineStr">
+      <c r="G48" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -2633,38 +2633,38 @@
       </c>
     </row>
     <row r="50" ht="24" customHeight="1">
-      <c r="A50" s="59" t="n">
+      <c r="A50" s="57" t="n">
         <v>46181</v>
       </c>
-      <c r="B50" s="39" t="inlineStr">
+      <c r="B50" s="34" t="inlineStr">
         <is>
           <t>Amani Gallery Homes</t>
         </is>
       </c>
-      <c r="C50" s="39" t="inlineStr">
+      <c r="C50" s="34" t="inlineStr">
         <is>
           <t>20' x 70' / 20' x 72'</t>
         </is>
       </c>
-      <c r="D50" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E50" s="40" t="inlineStr">
+      <c r="D50" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E50" s="35" t="inlineStr">
         <is>
           <t>48 / 81</t>
         </is>
       </c>
-      <c r="F50" s="60" t="n">
+      <c r="F50" s="58" t="n">
         <v>0.5925925925925926</v>
       </c>
-      <c r="G50" s="42" t="inlineStr">
+      <c r="G50" s="37" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="H50" s="39" t="inlineStr">
+      <c r="H50" s="34" t="inlineStr">
         <is>
           <t>59% Signed (48/81 units); No earlier valid signed observation</t>
         </is>
@@ -2745,30 +2745,30 @@
       </c>
     </row>
     <row r="53" ht="24" customHeight="1">
-      <c r="A53" s="59" t="n">
+      <c r="A53" s="57" t="n">
         <v>46181</v>
       </c>
-      <c r="B53" s="39" t="inlineStr">
+      <c r="B53" s="34" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C53" s="39" t="inlineStr">
+      <c r="C53" s="34" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D53" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E53" s="40" t="inlineStr">
+      <c r="D53" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E53" s="35" t="inlineStr">
         <is>
           <t>19 / 48</t>
         </is>
       </c>
-      <c r="F53" s="60" t="n">
+      <c r="F53" s="58" t="n">
         <v>0.3958333333333333</v>
       </c>
       <c r="G53" s="43" t="inlineStr">
@@ -2776,7 +2776,7 @@
           <t>+4 signed · +8.3 pp</t>
         </is>
       </c>
-      <c r="H53" s="39" t="inlineStr">
+      <c r="H53" s="34" t="inlineStr">
         <is>
           <t>40% Signed (19/48 units); 101-day gap; not daily movement</t>
         </is>
@@ -2821,30 +2821,30 @@
       </c>
     </row>
     <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="57" t="n">
+      <c r="A55" s="59" t="n">
         <v>46181</v>
       </c>
-      <c r="B55" s="34" t="inlineStr">
+      <c r="B55" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C55" s="34" t="inlineStr">
+      <c r="C55" s="39" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D55" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E55" s="35" t="inlineStr">
+      <c r="D55" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E55" s="40" t="inlineStr">
         <is>
           <t>46 / 46</t>
         </is>
       </c>
-      <c r="F55" s="58" t="n">
+      <c r="F55" s="60" t="n">
         <v>1</v>
       </c>
       <c r="G55" s="43" t="inlineStr">
@@ -2852,37 +2852,37 @@
           <t>+1 signed · +2.2 pp</t>
         </is>
       </c>
-      <c r="H55" s="34" t="inlineStr">
+      <c r="H55" s="39" t="inlineStr">
         <is>
           <t>100% Signed (46/46 units); 245-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="56" ht="24" customHeight="1">
-      <c r="A56" s="59" t="n">
+      <c r="A56" s="57" t="n">
         <v>46181</v>
       </c>
-      <c r="B56" s="39" t="inlineStr">
+      <c r="B56" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C56" s="39" t="inlineStr">
+      <c r="C56" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D56" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E56" s="40" t="inlineStr">
+      <c r="D56" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E56" s="35" t="inlineStr">
         <is>
           <t>56 / 56</t>
         </is>
       </c>
-      <c r="F56" s="60" t="n">
+      <c r="F56" s="58" t="n">
         <v>1</v>
       </c>
       <c r="G56" s="43" t="inlineStr">
@@ -2890,37 +2890,37 @@
           <t>+9 signed · +16.1 pp</t>
         </is>
       </c>
-      <c r="H56" s="39" t="inlineStr">
+      <c r="H56" s="34" t="inlineStr">
         <is>
           <t>100% Signed (56/56 units); 245-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="57" ht="24" customHeight="1">
-      <c r="A57" s="57" t="n">
+      <c r="A57" s="59" t="n">
         <v>46181</v>
       </c>
-      <c r="B57" s="34" t="inlineStr">
+      <c r="B57" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C57" s="34" t="inlineStr">
+      <c r="C57" s="39" t="inlineStr">
         <is>
           <t>20' x 75'</t>
         </is>
       </c>
-      <c r="D57" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E57" s="35" t="inlineStr">
+      <c r="D57" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E57" s="40" t="inlineStr">
         <is>
           <t>24 / 25</t>
         </is>
       </c>
-      <c r="F57" s="58" t="n">
+      <c r="F57" s="60" t="n">
         <v>0.96</v>
       </c>
       <c r="G57" s="43" t="inlineStr">
@@ -2928,37 +2928,37 @@
           <t>+11 signed · +44.0 pp</t>
         </is>
       </c>
-      <c r="H57" s="34" t="inlineStr">
+      <c r="H57" s="39" t="inlineStr">
         <is>
           <t>96% Signed (24/25 units); 245-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="59" t="n">
+      <c r="A58" s="57" t="n">
         <v>46181</v>
       </c>
-      <c r="B58" s="39" t="inlineStr">
+      <c r="B58" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C58" s="39" t="inlineStr">
+      <c r="C58" s="34" t="inlineStr">
         <is>
           <t>20' x 80'</t>
         </is>
       </c>
-      <c r="D58" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E58" s="40" t="inlineStr">
+      <c r="D58" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E58" s="35" t="inlineStr">
         <is>
           <t>7 / 25</t>
         </is>
       </c>
-      <c r="F58" s="60" t="n">
+      <c r="F58" s="58" t="n">
         <v>0.28</v>
       </c>
       <c r="G58" s="43" t="inlineStr">
@@ -2966,37 +2966,37 @@
           <t>+4 signed · +16.0 pp</t>
         </is>
       </c>
-      <c r="H58" s="39" t="inlineStr">
+      <c r="H58" s="34" t="inlineStr">
         <is>
           <t>28% Signed (7/25 units); 245-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="59" ht="24" customHeight="1">
-      <c r="A59" s="59" t="n">
+      <c r="A59" s="57" t="n">
         <v>46181</v>
       </c>
-      <c r="B59" s="39" t="inlineStr">
+      <c r="B59" s="34" t="inlineStr">
         <is>
           <t>Chorus @Setia Ecohill 2</t>
         </is>
       </c>
-      <c r="C59" s="39" t="inlineStr">
+      <c r="C59" s="34" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D59" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E59" s="40" t="inlineStr">
+      <c r="D59" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E59" s="35" t="inlineStr">
         <is>
           <t>77 / 99</t>
         </is>
       </c>
-      <c r="F59" s="60" t="n">
+      <c r="F59" s="58" t="n">
         <v>0.7777777777777778</v>
       </c>
       <c r="G59" s="44" t="inlineStr">
@@ -3004,7 +3004,7 @@
           <t>-10 signed · -10.1 pp</t>
         </is>
       </c>
-      <c r="H59" s="39" t="inlineStr">
+      <c r="H59" s="34" t="inlineStr">
         <is>
           <t>78% Signed (77/99 units); 245-day gap; not daily movement; Signed count decreased; verify source/status correction</t>
         </is>
@@ -3075,7 +3075,7 @@
       <c r="F61" s="60" t="n">
         <v>0.9492753623188406</v>
       </c>
-      <c r="G61" s="37" t="inlineStr">
+      <c r="G61" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -3113,7 +3113,7 @@
       <c r="F62" s="58" t="n">
         <v>0.9629629629629629</v>
       </c>
-      <c r="G62" s="37" t="inlineStr">
+      <c r="G62" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -3125,30 +3125,30 @@
       </c>
     </row>
     <row r="63" ht="24" customHeight="1">
-      <c r="A63" s="57" t="n">
+      <c r="A63" s="59" t="n">
         <v>46181</v>
       </c>
-      <c r="B63" s="34" t="inlineStr">
+      <c r="B63" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C63" s="34" t="inlineStr">
+      <c r="C63" s="39" t="inlineStr">
         <is>
           <t>20' x 60'</t>
         </is>
       </c>
-      <c r="D63" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E63" s="35" t="inlineStr">
+      <c r="D63" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E63" s="40" t="inlineStr">
         <is>
           <t>17 / 26</t>
         </is>
       </c>
-      <c r="F63" s="58" t="n">
+      <c r="F63" s="60" t="n">
         <v>0.6538461538461539</v>
       </c>
       <c r="G63" s="43" t="inlineStr">
@@ -3156,37 +3156,37 @@
           <t>+14 signed · +53.8 pp</t>
         </is>
       </c>
-      <c r="H63" s="34" t="inlineStr">
+      <c r="H63" s="39" t="inlineStr">
         <is>
           <t>65% Signed (17/26 units); 101-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="64" ht="24" customHeight="1">
-      <c r="A64" s="59" t="n">
+      <c r="A64" s="57" t="n">
         <v>46181</v>
       </c>
-      <c r="B64" s="39" t="inlineStr">
+      <c r="B64" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C64" s="39" t="inlineStr">
+      <c r="C64" s="34" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D64" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E64" s="40" t="inlineStr">
+      <c r="D64" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E64" s="35" t="inlineStr">
         <is>
           <t>111 / 126</t>
         </is>
       </c>
-      <c r="F64" s="60" t="n">
+      <c r="F64" s="58" t="n">
         <v>0.8809523809523809</v>
       </c>
       <c r="G64" s="43" t="inlineStr">
@@ -3194,37 +3194,37 @@
           <t>+34 signed · +27.0 pp</t>
         </is>
       </c>
-      <c r="H64" s="39" t="inlineStr">
+      <c r="H64" s="34" t="inlineStr">
         <is>
           <t>88% Signed  (111/126 units); 101-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="65" ht="24" customHeight="1">
-      <c r="A65" s="57" t="n">
+      <c r="A65" s="59" t="n">
         <v>46181</v>
       </c>
-      <c r="B65" s="34" t="inlineStr">
+      <c r="B65" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C65" s="34" t="inlineStr">
+      <c r="C65" s="39" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D65" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E65" s="35" t="inlineStr">
+      <c r="D65" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E65" s="40" t="inlineStr">
         <is>
           <t>71 / 104</t>
         </is>
       </c>
-      <c r="F65" s="58" t="n">
+      <c r="F65" s="60" t="n">
         <v>0.6826923076923077</v>
       </c>
       <c r="G65" s="43" t="inlineStr">
@@ -3232,45 +3232,45 @@
           <t>+54 signed · +51.9 pp</t>
         </is>
       </c>
-      <c r="H65" s="34" t="inlineStr">
+      <c r="H65" s="39" t="inlineStr">
         <is>
           <t>68% Signed (71/104 units); 101-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="66" ht="24" customHeight="1">
-      <c r="A66" s="57" t="n">
+      <c r="A66" s="59" t="n">
         <v>46181</v>
       </c>
-      <c r="B66" s="34" t="inlineStr">
+      <c r="B66" s="39" t="inlineStr">
         <is>
           <t>Sapphire Residence @Diamond City</t>
         </is>
       </c>
-      <c r="C66" s="34" t="inlineStr">
+      <c r="C66" s="39" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D66" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E66" s="35" t="inlineStr">
+      <c r="D66" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E66" s="40" t="inlineStr">
         <is>
           <t>24 / 136</t>
         </is>
       </c>
-      <c r="F66" s="58" t="n">
+      <c r="F66" s="60" t="n">
         <v>0.1764705882352941</v>
       </c>
-      <c r="G66" s="37" t="inlineStr">
+      <c r="G66" s="42" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="H66" s="34" t="inlineStr">
+      <c r="H66" s="39" t="inlineStr">
         <is>
           <t>18% Signed (24/136 units); No earlier valid signed observation</t>
         </is>
@@ -3391,30 +3391,30 @@
       </c>
     </row>
     <row r="70" ht="24" customHeight="1">
-      <c r="A70" s="57" t="n">
+      <c r="A70" s="59" t="n">
         <v>46213</v>
       </c>
-      <c r="B70" s="34" t="inlineStr">
+      <c r="B70" s="39" t="inlineStr">
         <is>
           <t>Amani Gallery Homes</t>
         </is>
       </c>
-      <c r="C70" s="34" t="inlineStr">
+      <c r="C70" s="39" t="inlineStr">
         <is>
           <t>20' x 70' / 20' x 72'</t>
         </is>
       </c>
-      <c r="D70" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E70" s="35" t="inlineStr">
+      <c r="D70" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E70" s="40" t="inlineStr">
         <is>
           <t>53 / 81</t>
         </is>
       </c>
-      <c r="F70" s="58" t="n">
+      <c r="F70" s="60" t="n">
         <v>0.654320987654321</v>
       </c>
       <c r="G70" s="43" t="inlineStr">
@@ -3422,7 +3422,7 @@
           <t>+5 signed · +6.2 pp</t>
         </is>
       </c>
-      <c r="H70" s="34" t="inlineStr">
+      <c r="H70" s="39" t="inlineStr">
         <is>
           <t>65% Signed (53/81 units); 32-day gap; not daily movement</t>
         </is>
@@ -3503,38 +3503,38 @@
       </c>
     </row>
     <row r="73" ht="24" customHeight="1">
-      <c r="A73" s="57" t="n">
+      <c r="A73" s="59" t="n">
         <v>46213</v>
       </c>
-      <c r="B73" s="34" t="inlineStr">
+      <c r="B73" s="39" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C73" s="34" t="inlineStr">
+      <c r="C73" s="39" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D73" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E73" s="35" t="inlineStr">
+      <c r="D73" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E73" s="40" t="inlineStr">
         <is>
           <t>19 / 48</t>
         </is>
       </c>
-      <c r="F73" s="58" t="n">
+      <c r="F73" s="60" t="n">
         <v>0.3958333333333333</v>
       </c>
-      <c r="G73" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H73" s="34" t="inlineStr">
+      <c r="G73" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H73" s="39" t="inlineStr">
         <is>
           <t>40% Signed (19/48 units); 32-day gap; not daily movement</t>
         </is>
@@ -3567,7 +3567,7 @@
       <c r="F74" s="60" t="n">
         <v>0.6194690265486725</v>
       </c>
-      <c r="G74" s="37" t="inlineStr">
+      <c r="G74" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -3579,144 +3579,144 @@
       </c>
     </row>
     <row r="75" ht="24" customHeight="1">
-      <c r="A75" s="57" t="n">
+      <c r="A75" s="59" t="n">
         <v>46213</v>
       </c>
-      <c r="B75" s="34" t="inlineStr">
+      <c r="B75" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C75" s="34" t="inlineStr">
+      <c r="C75" s="39" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D75" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E75" s="35" t="inlineStr">
+      <c r="D75" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E75" s="40" t="inlineStr">
         <is>
           <t>46 / 46</t>
         </is>
       </c>
-      <c r="F75" s="58" t="n">
+      <c r="F75" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="G75" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H75" s="34" t="inlineStr">
+      <c r="G75" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H75" s="39" t="inlineStr">
         <is>
           <t>100% Signed (46/46 units); 32-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="76" ht="24" customHeight="1">
-      <c r="A76" s="59" t="n">
+      <c r="A76" s="57" t="n">
         <v>46213</v>
       </c>
-      <c r="B76" s="39" t="inlineStr">
+      <c r="B76" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C76" s="39" t="inlineStr">
+      <c r="C76" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D76" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E76" s="40" t="inlineStr">
+      <c r="D76" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E76" s="35" t="inlineStr">
         <is>
           <t>56 / 56</t>
         </is>
       </c>
-      <c r="F76" s="60" t="n">
+      <c r="F76" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="G76" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H76" s="39" t="inlineStr">
+      <c r="G76" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H76" s="34" t="inlineStr">
         <is>
           <t>100% Signed (56/56 units); 32-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="77" ht="24" customHeight="1">
-      <c r="A77" s="57" t="n">
+      <c r="A77" s="59" t="n">
         <v>46213</v>
       </c>
-      <c r="B77" s="34" t="inlineStr">
+      <c r="B77" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C77" s="34" t="inlineStr">
+      <c r="C77" s="39" t="inlineStr">
         <is>
           <t>20' x 75'</t>
         </is>
       </c>
-      <c r="D77" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E77" s="35" t="inlineStr">
+      <c r="D77" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E77" s="40" t="inlineStr">
         <is>
           <t>24 / 25</t>
         </is>
       </c>
-      <c r="F77" s="58" t="n">
+      <c r="F77" s="60" t="n">
         <v>0.96</v>
       </c>
-      <c r="G77" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H77" s="34" t="inlineStr">
+      <c r="G77" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H77" s="39" t="inlineStr">
         <is>
           <t>96% Signed (24/25 units); 32-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="78" ht="24" customHeight="1">
-      <c r="A78" s="59" t="n">
+      <c r="A78" s="57" t="n">
         <v>46213</v>
       </c>
-      <c r="B78" s="39" t="inlineStr">
+      <c r="B78" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C78" s="39" t="inlineStr">
+      <c r="C78" s="34" t="inlineStr">
         <is>
           <t>20' x 80'</t>
         </is>
       </c>
-      <c r="D78" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E78" s="40" t="inlineStr">
+      <c r="D78" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E78" s="35" t="inlineStr">
         <is>
           <t>8 / 25</t>
         </is>
       </c>
-      <c r="F78" s="60" t="n">
+      <c r="F78" s="58" t="n">
         <v>0.32</v>
       </c>
       <c r="G78" s="43" t="inlineStr">
@@ -3724,45 +3724,45 @@
           <t>+1 signed · +4.0 pp</t>
         </is>
       </c>
-      <c r="H78" s="39" t="inlineStr">
+      <c r="H78" s="34" t="inlineStr">
         <is>
           <t>32% Signed (8/25 units); 32-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="79" ht="24" customHeight="1">
-      <c r="A79" s="57" t="n">
+      <c r="A79" s="59" t="n">
         <v>46213</v>
       </c>
-      <c r="B79" s="34" t="inlineStr">
+      <c r="B79" s="39" t="inlineStr">
         <is>
           <t>Chorus @Setia Ecohill 2</t>
         </is>
       </c>
-      <c r="C79" s="34" t="inlineStr">
+      <c r="C79" s="39" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D79" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E79" s="35" t="inlineStr">
+      <c r="D79" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E79" s="40" t="inlineStr">
         <is>
           <t>77 / 99</t>
         </is>
       </c>
-      <c r="F79" s="58" t="n">
+      <c r="F79" s="60" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="G79" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H79" s="34" t="inlineStr">
+      <c r="G79" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H79" s="39" t="inlineStr">
         <is>
           <t>78% Signed (77/99 units); 32-day gap; not daily movement</t>
         </is>
@@ -3795,7 +3795,7 @@
       <c r="F80" s="60" t="n">
         <v>0.918918918918919</v>
       </c>
-      <c r="G80" s="37" t="inlineStr">
+      <c r="G80" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -3833,7 +3833,7 @@
       <c r="F81" s="58" t="n">
         <v>0.9492753623188406</v>
       </c>
-      <c r="G81" s="37" t="inlineStr">
+      <c r="G81" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -3871,7 +3871,7 @@
       <c r="F82" s="60" t="n">
         <v>0.9629629629629629</v>
       </c>
-      <c r="G82" s="37" t="inlineStr">
+      <c r="G82" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -3883,68 +3883,68 @@
       </c>
     </row>
     <row r="83" ht="24" customHeight="1">
-      <c r="A83" s="59" t="n">
+      <c r="A83" s="57" t="n">
         <v>46213</v>
       </c>
-      <c r="B83" s="39" t="inlineStr">
+      <c r="B83" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C83" s="39" t="inlineStr">
+      <c r="C83" s="34" t="inlineStr">
         <is>
           <t>20' x 60'</t>
         </is>
       </c>
-      <c r="D83" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E83" s="40" t="inlineStr">
+      <c r="D83" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E83" s="35" t="inlineStr">
         <is>
           <t>17 / 26</t>
         </is>
       </c>
-      <c r="F83" s="60" t="n">
+      <c r="F83" s="58" t="n">
         <v>0.6538461538461539</v>
       </c>
-      <c r="G83" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H83" s="39" t="inlineStr">
+      <c r="G83" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H83" s="34" t="inlineStr">
         <is>
           <t>65% Signed (17/26 units); 32-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="84" ht="24" customHeight="1">
-      <c r="A84" s="57" t="n">
+      <c r="A84" s="59" t="n">
         <v>46213</v>
       </c>
-      <c r="B84" s="34" t="inlineStr">
+      <c r="B84" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C84" s="34" t="inlineStr">
+      <c r="C84" s="39" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D84" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E84" s="35" t="inlineStr">
+      <c r="D84" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E84" s="40" t="inlineStr">
         <is>
           <t>116 / 126</t>
         </is>
       </c>
-      <c r="F84" s="58" t="n">
+      <c r="F84" s="60" t="n">
         <v>0.9206349206349206</v>
       </c>
       <c r="G84" s="43" t="inlineStr">
@@ -3952,37 +3952,37 @@
           <t>+5 signed · +4.0 pp</t>
         </is>
       </c>
-      <c r="H84" s="34" t="inlineStr">
+      <c r="H84" s="39" t="inlineStr">
         <is>
           <t>92% Signed  (116/126 units); 32-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="85" ht="24" customHeight="1">
-      <c r="A85" s="59" t="n">
+      <c r="A85" s="57" t="n">
         <v>46213</v>
       </c>
-      <c r="B85" s="39" t="inlineStr">
+      <c r="B85" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C85" s="39" t="inlineStr">
+      <c r="C85" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D85" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E85" s="40" t="inlineStr">
+      <c r="D85" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E85" s="35" t="inlineStr">
         <is>
           <t>89 / 104</t>
         </is>
       </c>
-      <c r="F85" s="60" t="n">
+      <c r="F85" s="58" t="n">
         <v>0.8557692307692307</v>
       </c>
       <c r="G85" s="43" t="inlineStr">
@@ -3990,7 +3990,7 @@
           <t>+18 signed · +17.3 pp</t>
         </is>
       </c>
-      <c r="H85" s="39" t="inlineStr">
+      <c r="H85" s="34" t="inlineStr">
         <is>
           <t>86% Signed (89/104 units); 32-day gap; not daily movement</t>
         </is>
@@ -4111,66 +4111,66 @@
       </c>
     </row>
     <row r="89" ht="24" customHeight="1">
-      <c r="A89" s="59" t="n">
+      <c r="A89" s="57" t="n">
         <v>46213</v>
       </c>
-      <c r="B89" s="39" t="inlineStr">
+      <c r="B89" s="34" t="inlineStr">
         <is>
           <t>Majestic Flora</t>
         </is>
       </c>
-      <c r="C89" s="39" t="inlineStr">
+      <c r="C89" s="34" t="inlineStr">
         <is>
           <t>No group details</t>
         </is>
       </c>
-      <c r="D89" s="40" t="inlineStr">
+      <c r="D89" s="35" t="inlineStr">
         <is>
           <t>Yet to sign</t>
         </is>
       </c>
-      <c r="E89" s="40" t="inlineStr">
+      <c r="E89" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F89" s="60" t="n"/>
-      <c r="G89" s="42" t="inlineStr">
+      <c r="F89" s="58" t="n"/>
+      <c r="G89" s="37" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="H89" s="39" t="inlineStr">
+      <c r="H89" s="34" t="inlineStr">
         <is>
           <t>Yet to Sign; Non-signed status retained for audit; excluded from signed trend</t>
         </is>
       </c>
     </row>
     <row r="90" ht="24" customHeight="1">
-      <c r="A90" s="59" t="n">
+      <c r="A90" s="57" t="n">
         <v>46213</v>
       </c>
-      <c r="B90" s="39" t="inlineStr">
+      <c r="B90" s="34" t="inlineStr">
         <is>
           <t>Sapphire Residence @Diamond City</t>
         </is>
       </c>
-      <c r="C90" s="39" t="inlineStr">
+      <c r="C90" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D90" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E90" s="40" t="inlineStr">
+      <c r="D90" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E90" s="35" t="inlineStr">
         <is>
           <t>30 / 136</t>
         </is>
       </c>
-      <c r="F90" s="60" t="n">
+      <c r="F90" s="58" t="n">
         <v>0.2205882352941176</v>
       </c>
       <c r="G90" s="43" t="inlineStr">
@@ -4178,7 +4178,7 @@
           <t>+6 signed · +4.4 pp</t>
         </is>
       </c>
-      <c r="H90" s="39" t="inlineStr">
+      <c r="H90" s="34" t="inlineStr">
         <is>
           <t>22% Signed (30/136 units); 32-day gap; not daily movement</t>
         </is>
@@ -4211,7 +4211,7 @@
       <c r="F91" s="60" t="n">
         <v>0.03703703703703703</v>
       </c>
-      <c r="G91" s="37" t="inlineStr">
+      <c r="G91" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -4299,30 +4299,30 @@
       </c>
     </row>
     <row r="94" ht="24" customHeight="1">
-      <c r="A94" s="59" t="n">
+      <c r="A94" s="57" t="n">
         <v>46308</v>
       </c>
-      <c r="B94" s="39" t="inlineStr">
+      <c r="B94" s="34" t="inlineStr">
         <is>
           <t>Amani Gallery Homes</t>
         </is>
       </c>
-      <c r="C94" s="39" t="inlineStr">
+      <c r="C94" s="34" t="inlineStr">
         <is>
           <t>20' x 70' / 20' x 72'</t>
         </is>
       </c>
-      <c r="D94" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E94" s="40" t="inlineStr">
+      <c r="D94" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E94" s="35" t="inlineStr">
         <is>
           <t>72 / 81</t>
         </is>
       </c>
-      <c r="F94" s="60" t="n">
+      <c r="F94" s="58" t="n">
         <v>0.8888888888888888</v>
       </c>
       <c r="G94" s="43" t="inlineStr">
@@ -4330,7 +4330,7 @@
           <t>+19 signed · +23.5 pp</t>
         </is>
       </c>
-      <c r="H94" s="39" t="inlineStr">
+      <c r="H94" s="34" t="inlineStr">
         <is>
           <t>88% Signed (72/81 units); 95-day gap; not daily movement</t>
         </is>
@@ -4399,7 +4399,7 @@
       <c r="F96" s="58" t="n">
         <v>0.6017699115044248</v>
       </c>
-      <c r="G96" s="37" t="inlineStr">
+      <c r="G96" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -4411,30 +4411,30 @@
       </c>
     </row>
     <row r="97" ht="24" customHeight="1">
-      <c r="A97" s="59" t="n">
+      <c r="A97" s="57" t="n">
         <v>46308</v>
       </c>
-      <c r="B97" s="39" t="inlineStr">
+      <c r="B97" s="34" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C97" s="39" t="inlineStr">
+      <c r="C97" s="34" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D97" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E97" s="40" t="inlineStr">
+      <c r="D97" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E97" s="35" t="inlineStr">
         <is>
           <t>21 / 48</t>
         </is>
       </c>
-      <c r="F97" s="60" t="n">
+      <c r="F97" s="58" t="n">
         <v>0.4375</v>
       </c>
       <c r="G97" s="43" t="inlineStr">
@@ -4442,7 +4442,7 @@
           <t>+2 signed · +4.2 pp</t>
         </is>
       </c>
-      <c r="H97" s="39" t="inlineStr">
+      <c r="H97" s="34" t="inlineStr">
         <is>
           <t>44% Signed (21/48 units); 95-day gap; not daily movement</t>
         </is>
@@ -4487,144 +4487,144 @@
       </c>
     </row>
     <row r="99" ht="24" customHeight="1">
-      <c r="A99" s="57" t="n">
+      <c r="A99" s="59" t="n">
         <v>46308</v>
       </c>
-      <c r="B99" s="34" t="inlineStr">
+      <c r="B99" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C99" s="34" t="inlineStr">
+      <c r="C99" s="39" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D99" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E99" s="35" t="inlineStr">
+      <c r="D99" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E99" s="40" t="inlineStr">
         <is>
           <t>46 / 46</t>
         </is>
       </c>
-      <c r="F99" s="58" t="n">
+      <c r="F99" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="G99" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H99" s="34" t="inlineStr">
+      <c r="G99" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H99" s="39" t="inlineStr">
         <is>
           <t>100% Signed (46/46 units); 95-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="100" ht="24" customHeight="1">
-      <c r="A100" s="59" t="n">
+      <c r="A100" s="57" t="n">
         <v>46308</v>
       </c>
-      <c r="B100" s="39" t="inlineStr">
+      <c r="B100" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C100" s="39" t="inlineStr">
+      <c r="C100" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D100" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E100" s="40" t="inlineStr">
+      <c r="D100" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E100" s="35" t="inlineStr">
         <is>
           <t>56 / 56</t>
         </is>
       </c>
-      <c r="F100" s="60" t="n">
+      <c r="F100" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="G100" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H100" s="39" t="inlineStr">
+      <c r="G100" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H100" s="34" t="inlineStr">
         <is>
           <t>100% Signed (56/56 units); 95-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="101" ht="24" customHeight="1">
-      <c r="A101" s="57" t="n">
+      <c r="A101" s="59" t="n">
         <v>46308</v>
       </c>
-      <c r="B101" s="34" t="inlineStr">
+      <c r="B101" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C101" s="34" t="inlineStr">
+      <c r="C101" s="39" t="inlineStr">
         <is>
           <t>20' x 75'</t>
         </is>
       </c>
-      <c r="D101" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E101" s="35" t="inlineStr">
+      <c r="D101" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E101" s="40" t="inlineStr">
         <is>
           <t>24 / 25</t>
         </is>
       </c>
-      <c r="F101" s="58" t="n">
+      <c r="F101" s="60" t="n">
         <v>0.96</v>
       </c>
-      <c r="G101" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H101" s="34" t="inlineStr">
+      <c r="G101" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H101" s="39" t="inlineStr">
         <is>
           <t>96% Signed (24/25 units); 95-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="102" ht="24" customHeight="1">
-      <c r="A102" s="59" t="n">
+      <c r="A102" s="57" t="n">
         <v>46308</v>
       </c>
-      <c r="B102" s="39" t="inlineStr">
+      <c r="B102" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C102" s="39" t="inlineStr">
+      <c r="C102" s="34" t="inlineStr">
         <is>
           <t>20' x 80'</t>
         </is>
       </c>
-      <c r="D102" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E102" s="40" t="inlineStr">
+      <c r="D102" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E102" s="35" t="inlineStr">
         <is>
           <t>10 / 25</t>
         </is>
       </c>
-      <c r="F102" s="60" t="n">
+      <c r="F102" s="58" t="n">
         <v>0.4</v>
       </c>
       <c r="G102" s="43" t="inlineStr">
@@ -4632,45 +4632,45 @@
           <t>+2 signed · +8.0 pp</t>
         </is>
       </c>
-      <c r="H102" s="39" t="inlineStr">
+      <c r="H102" s="34" t="inlineStr">
         <is>
           <t>40% Signed (10/25 units); 95-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="103" ht="24" customHeight="1">
-      <c r="A103" s="59" t="n">
+      <c r="A103" s="57" t="n">
         <v>46308</v>
       </c>
-      <c r="B103" s="39" t="inlineStr">
+      <c r="B103" s="34" t="inlineStr">
         <is>
           <t>Chorus @Setia Ecohill 2</t>
         </is>
       </c>
-      <c r="C103" s="39" t="inlineStr">
+      <c r="C103" s="34" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D103" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E103" s="40" t="inlineStr">
+      <c r="D103" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E103" s="35" t="inlineStr">
         <is>
           <t>77 / 99</t>
         </is>
       </c>
-      <c r="F103" s="60" t="n">
+      <c r="F103" s="58" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="G103" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H103" s="39" t="inlineStr">
+      <c r="G103" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H103" s="34" t="inlineStr">
         <is>
           <t>78% Signed (77/99 units); 95-day gap; not daily movement</t>
         </is>
@@ -4791,30 +4791,30 @@
       </c>
     </row>
     <row r="107" ht="24" customHeight="1">
-      <c r="A107" s="57" t="n">
+      <c r="A107" s="59" t="n">
         <v>46308</v>
       </c>
-      <c r="B107" s="34" t="inlineStr">
+      <c r="B107" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C107" s="34" t="inlineStr">
+      <c r="C107" s="39" t="inlineStr">
         <is>
           <t>20' x 60'</t>
         </is>
       </c>
-      <c r="D107" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E107" s="35" t="inlineStr">
+      <c r="D107" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E107" s="40" t="inlineStr">
         <is>
           <t>23 / 26</t>
         </is>
       </c>
-      <c r="F107" s="58" t="n">
+      <c r="F107" s="60" t="n">
         <v>0.8846153846153846</v>
       </c>
       <c r="G107" s="43" t="inlineStr">
@@ -4822,37 +4822,37 @@
           <t>+6 signed · +23.1 pp</t>
         </is>
       </c>
-      <c r="H107" s="34" t="inlineStr">
+      <c r="H107" s="39" t="inlineStr">
         <is>
           <t>88% Signed (23/26 units); 95-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="108" ht="24" customHeight="1">
-      <c r="A108" s="59" t="n">
+      <c r="A108" s="57" t="n">
         <v>46308</v>
       </c>
-      <c r="B108" s="39" t="inlineStr">
+      <c r="B108" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C108" s="39" t="inlineStr">
+      <c r="C108" s="34" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D108" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E108" s="40" t="inlineStr">
+      <c r="D108" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E108" s="35" t="inlineStr">
         <is>
           <t>124 / 126</t>
         </is>
       </c>
-      <c r="F108" s="60" t="n">
+      <c r="F108" s="58" t="n">
         <v>0.9841269841269841</v>
       </c>
       <c r="G108" s="43" t="inlineStr">
@@ -4860,37 +4860,37 @@
           <t>+8 signed · +6.3 pp</t>
         </is>
       </c>
-      <c r="H108" s="39" t="inlineStr">
+      <c r="H108" s="34" t="inlineStr">
         <is>
           <t>98% Signed  (124/126 units); 95-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="109" ht="24" customHeight="1">
-      <c r="A109" s="57" t="n">
+      <c r="A109" s="59" t="n">
         <v>46308</v>
       </c>
-      <c r="B109" s="34" t="inlineStr">
+      <c r="B109" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C109" s="34" t="inlineStr">
+      <c r="C109" s="39" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D109" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E109" s="35" t="inlineStr">
+      <c r="D109" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E109" s="40" t="inlineStr">
         <is>
           <t>98 / 104</t>
         </is>
       </c>
-      <c r="F109" s="58" t="n">
+      <c r="F109" s="60" t="n">
         <v>0.9423076923076923</v>
       </c>
       <c r="G109" s="43" t="inlineStr">
@@ -4898,7 +4898,7 @@
           <t>+9 signed · +8.7 pp</t>
         </is>
       </c>
-      <c r="H109" s="34" t="inlineStr">
+      <c r="H109" s="39" t="inlineStr">
         <is>
           <t>94% Signed (98/104 units); 95-day gap; not daily movement</t>
         </is>
@@ -5019,66 +5019,66 @@
       </c>
     </row>
     <row r="113" ht="24" customHeight="1">
-      <c r="A113" s="57" t="n">
+      <c r="A113" s="59" t="n">
         <v>46308</v>
       </c>
-      <c r="B113" s="34" t="inlineStr">
+      <c r="B113" s="39" t="inlineStr">
         <is>
           <t>Majestic Flora</t>
         </is>
       </c>
-      <c r="C113" s="34" t="inlineStr">
+      <c r="C113" s="39" t="inlineStr">
         <is>
           <t>No group details</t>
         </is>
       </c>
-      <c r="D113" s="35" t="inlineStr">
+      <c r="D113" s="40" t="inlineStr">
         <is>
           <t>Yet to sign</t>
         </is>
       </c>
-      <c r="E113" s="35" t="inlineStr">
+      <c r="E113" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F113" s="58" t="n"/>
-      <c r="G113" s="37" t="inlineStr">
+      <c r="F113" s="60" t="n"/>
+      <c r="G113" s="42" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="H113" s="34" t="inlineStr">
+      <c r="H113" s="39" t="inlineStr">
         <is>
           <t>Yet to Sign; Non-signed status retained for audit; excluded from signed trend</t>
         </is>
       </c>
     </row>
     <row r="114" ht="24" customHeight="1">
-      <c r="A114" s="57" t="n">
+      <c r="A114" s="59" t="n">
         <v>46308</v>
       </c>
-      <c r="B114" s="34" t="inlineStr">
+      <c r="B114" s="39" t="inlineStr">
         <is>
           <t>Sapphire Residence @Diamond City</t>
         </is>
       </c>
-      <c r="C114" s="34" t="inlineStr">
+      <c r="C114" s="39" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D114" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E114" s="35" t="inlineStr">
+      <c r="D114" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E114" s="40" t="inlineStr">
         <is>
           <t>45 / 136</t>
         </is>
       </c>
-      <c r="F114" s="58" t="n">
+      <c r="F114" s="60" t="n">
         <v>0.3308823529411765</v>
       </c>
       <c r="G114" s="43" t="inlineStr">
@@ -5086,7 +5086,7 @@
           <t>+15 signed · +11.0 pp</t>
         </is>
       </c>
-      <c r="H114" s="34" t="inlineStr">
+      <c r="H114" s="39" t="inlineStr">
         <is>
           <t>33% Signed (45/136 units); 95-day gap; not daily movement</t>
         </is>
@@ -5119,7 +5119,7 @@
       <c r="F115" s="60" t="n">
         <v>0.03703703703703703</v>
       </c>
-      <c r="G115" s="37" t="inlineStr">
+      <c r="G115" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -5195,7 +5195,7 @@
       <c r="F117" s="60" t="n">
         <v>0.2281879194630873</v>
       </c>
-      <c r="G117" s="37" t="inlineStr">
+      <c r="G117" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -5207,30 +5207,30 @@
       </c>
     </row>
     <row r="118" ht="24" customHeight="1">
-      <c r="A118" s="57" t="n">
+      <c r="A118" s="59" t="n">
         <v>46310</v>
       </c>
-      <c r="B118" s="34" t="inlineStr">
+      <c r="B118" s="39" t="inlineStr">
         <is>
           <t>Amani Gallery Homes</t>
         </is>
       </c>
-      <c r="C118" s="34" t="inlineStr">
+      <c r="C118" s="39" t="inlineStr">
         <is>
           <t>20' x 70' / 20' x 72'</t>
         </is>
       </c>
-      <c r="D118" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E118" s="35" t="inlineStr">
+      <c r="D118" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E118" s="40" t="inlineStr">
         <is>
           <t>74 / 81</t>
         </is>
       </c>
-      <c r="F118" s="58" t="n">
+      <c r="F118" s="60" t="n">
         <v>0.9135802469135802</v>
       </c>
       <c r="G118" s="43" t="inlineStr">
@@ -5238,7 +5238,7 @@
           <t>+2 signed · +2.5 pp</t>
         </is>
       </c>
-      <c r="H118" s="34" t="inlineStr">
+      <c r="H118" s="39" t="inlineStr">
         <is>
           <t>74/81 signed; 2-day gap; not daily movement</t>
         </is>
@@ -5271,7 +5271,7 @@
       <c r="F119" s="60" t="n">
         <v>0.6017699115044248</v>
       </c>
-      <c r="G119" s="37" t="inlineStr">
+      <c r="G119" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -5283,38 +5283,38 @@
       </c>
     </row>
     <row r="120" ht="24" customHeight="1">
-      <c r="A120" s="57" t="n">
+      <c r="A120" s="59" t="n">
         <v>46310</v>
       </c>
-      <c r="B120" s="34" t="inlineStr">
+      <c r="B120" s="39" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C120" s="34" t="inlineStr">
+      <c r="C120" s="39" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D120" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E120" s="35" t="inlineStr">
+      <c r="D120" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E120" s="40" t="inlineStr">
         <is>
           <t>21 / 48</t>
         </is>
       </c>
-      <c r="F120" s="58" t="n">
+      <c r="F120" s="60" t="n">
         <v>0.4375</v>
       </c>
-      <c r="G120" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H120" s="34" t="inlineStr">
+      <c r="G120" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H120" s="39" t="inlineStr">
         <is>
           <t>21/48 signed; 2-day gap; not daily movement</t>
         </is>
@@ -5347,7 +5347,7 @@
       <c r="F121" s="60" t="n">
         <v>0.6283185840707964</v>
       </c>
-      <c r="G121" s="37" t="inlineStr">
+      <c r="G121" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -5359,190 +5359,190 @@
       </c>
     </row>
     <row r="122" ht="24" customHeight="1">
-      <c r="A122" s="57" t="n">
+      <c r="A122" s="59" t="n">
         <v>46310</v>
       </c>
-      <c r="B122" s="34" t="inlineStr">
+      <c r="B122" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C122" s="34" t="inlineStr">
+      <c r="C122" s="39" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D122" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E122" s="35" t="inlineStr">
+      <c r="D122" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E122" s="40" t="inlineStr">
         <is>
           <t>46 / 46</t>
         </is>
       </c>
-      <c r="F122" s="58" t="n">
+      <c r="F122" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="G122" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H122" s="34" t="inlineStr">
+      <c r="G122" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H122" s="39" t="inlineStr">
         <is>
           <t>46/46 signed; 2-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="123" ht="24" customHeight="1">
-      <c r="A123" s="59" t="n">
+      <c r="A123" s="57" t="n">
         <v>46310</v>
       </c>
-      <c r="B123" s="39" t="inlineStr">
+      <c r="B123" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C123" s="39" t="inlineStr">
+      <c r="C123" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D123" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E123" s="40" t="inlineStr">
+      <c r="D123" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E123" s="35" t="inlineStr">
         <is>
           <t>56 / 56</t>
         </is>
       </c>
-      <c r="F123" s="60" t="n">
+      <c r="F123" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="G123" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H123" s="39" t="inlineStr">
+      <c r="G123" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H123" s="34" t="inlineStr">
         <is>
           <t>56/56 signed; 2-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="124" ht="24" customHeight="1">
-      <c r="A124" s="57" t="n">
+      <c r="A124" s="59" t="n">
         <v>46310</v>
       </c>
-      <c r="B124" s="34" t="inlineStr">
+      <c r="B124" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C124" s="34" t="inlineStr">
+      <c r="C124" s="39" t="inlineStr">
         <is>
           <t>20' x 75'</t>
         </is>
       </c>
-      <c r="D124" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E124" s="35" t="inlineStr">
+      <c r="D124" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E124" s="40" t="inlineStr">
         <is>
           <t>24 / 25</t>
         </is>
       </c>
-      <c r="F124" s="58" t="n">
+      <c r="F124" s="60" t="n">
         <v>0.96</v>
       </c>
-      <c r="G124" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H124" s="34" t="inlineStr">
+      <c r="G124" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H124" s="39" t="inlineStr">
         <is>
           <t>24/25 signed; 2-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="125" ht="24" customHeight="1">
-      <c r="A125" s="59" t="n">
+      <c r="A125" s="57" t="n">
         <v>46310</v>
       </c>
-      <c r="B125" s="39" t="inlineStr">
+      <c r="B125" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C125" s="39" t="inlineStr">
+      <c r="C125" s="34" t="inlineStr">
         <is>
           <t>20' x 80'</t>
         </is>
       </c>
-      <c r="D125" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E125" s="40" t="inlineStr">
+      <c r="D125" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E125" s="35" t="inlineStr">
         <is>
           <t>10 / 25</t>
         </is>
       </c>
-      <c r="F125" s="60" t="n">
+      <c r="F125" s="58" t="n">
         <v>0.4</v>
       </c>
-      <c r="G125" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H125" s="39" t="inlineStr">
+      <c r="G125" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H125" s="34" t="inlineStr">
         <is>
           <t>10/25 signed; 2-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="126" ht="24" customHeight="1">
-      <c r="A126" s="57" t="n">
+      <c r="A126" s="59" t="n">
         <v>46310</v>
       </c>
-      <c r="B126" s="34" t="inlineStr">
+      <c r="B126" s="39" t="inlineStr">
         <is>
           <t>Chorus @Setia Ecohill 2</t>
         </is>
       </c>
-      <c r="C126" s="34" t="inlineStr">
+      <c r="C126" s="39" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D126" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E126" s="35" t="inlineStr">
+      <c r="D126" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E126" s="40" t="inlineStr">
         <is>
           <t>77 / 99</t>
         </is>
       </c>
-      <c r="F126" s="58" t="n">
+      <c r="F126" s="60" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="G126" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H126" s="34" t="inlineStr">
+      <c r="G126" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H126" s="39" t="inlineStr">
         <is>
           <t>77/99 signed; 2-day gap; not daily movement</t>
         </is>
@@ -5575,7 +5575,7 @@
       <c r="F127" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="G127" s="37" t="inlineStr">
+      <c r="G127" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -5613,7 +5613,7 @@
       <c r="F128" s="58" t="n">
         <v>0.9710144927536232</v>
       </c>
-      <c r="G128" s="37" t="inlineStr">
+      <c r="G128" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -5651,7 +5651,7 @@
       <c r="F129" s="60" t="n">
         <v>0.9753086419753086</v>
       </c>
-      <c r="G129" s="37" t="inlineStr">
+      <c r="G129" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -5663,114 +5663,114 @@
       </c>
     </row>
     <row r="130" ht="24" customHeight="1">
-      <c r="A130" s="59" t="n">
+      <c r="A130" s="57" t="n">
         <v>46310</v>
       </c>
-      <c r="B130" s="39" t="inlineStr">
+      <c r="B130" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C130" s="39" t="inlineStr">
+      <c r="C130" s="34" t="inlineStr">
         <is>
           <t>20' x 60'</t>
         </is>
       </c>
-      <c r="D130" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E130" s="40" t="inlineStr">
+      <c r="D130" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E130" s="35" t="inlineStr">
         <is>
           <t>23 / 26</t>
         </is>
       </c>
-      <c r="F130" s="60" t="n">
+      <c r="F130" s="58" t="n">
         <v>0.8846153846153846</v>
       </c>
-      <c r="G130" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H130" s="39" t="inlineStr">
+      <c r="G130" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H130" s="34" t="inlineStr">
         <is>
           <t>23/26 signed; 2-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="131" ht="24" customHeight="1">
-      <c r="A131" s="57" t="n">
+      <c r="A131" s="59" t="n">
         <v>46310</v>
       </c>
-      <c r="B131" s="34" t="inlineStr">
+      <c r="B131" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C131" s="34" t="inlineStr">
+      <c r="C131" s="39" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D131" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E131" s="35" t="inlineStr">
+      <c r="D131" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E131" s="40" t="inlineStr">
         <is>
           <t>124 / 126</t>
         </is>
       </c>
-      <c r="F131" s="58" t="n">
+      <c r="F131" s="60" t="n">
         <v>0.9841269841269841</v>
       </c>
-      <c r="G131" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H131" s="34" t="inlineStr">
+      <c r="G131" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H131" s="39" t="inlineStr">
         <is>
           <t>124/126 signed; 2-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="132" ht="24" customHeight="1">
-      <c r="A132" s="59" t="n">
+      <c r="A132" s="57" t="n">
         <v>46310</v>
       </c>
-      <c r="B132" s="39" t="inlineStr">
+      <c r="B132" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C132" s="39" t="inlineStr">
+      <c r="C132" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D132" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E132" s="40" t="inlineStr">
+      <c r="D132" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E132" s="35" t="inlineStr">
         <is>
           <t>98 / 104</t>
         </is>
       </c>
-      <c r="F132" s="60" t="n">
+      <c r="F132" s="58" t="n">
         <v>0.9423076923076923</v>
       </c>
-      <c r="G132" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H132" s="39" t="inlineStr">
+      <c r="G132" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H132" s="34" t="inlineStr">
         <is>
           <t>98/104 signed; 2-day gap; not daily movement</t>
         </is>
@@ -5803,7 +5803,7 @@
       <c r="F133" s="58" t="n">
         <v>0.6590909090909091</v>
       </c>
-      <c r="G133" s="37" t="inlineStr">
+      <c r="G133" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -5841,7 +5841,7 @@
       <c r="F134" s="60" t="n">
         <v>0.7411764705882353</v>
       </c>
-      <c r="G134" s="37" t="inlineStr">
+      <c r="G134" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -5891,38 +5891,38 @@
       </c>
     </row>
     <row r="136" ht="24" customHeight="1">
-      <c r="A136" s="59" t="n">
+      <c r="A136" s="57" t="n">
         <v>46310</v>
       </c>
-      <c r="B136" s="39" t="inlineStr">
+      <c r="B136" s="34" t="inlineStr">
         <is>
           <t>Sapphire Residence @Diamond City</t>
         </is>
       </c>
-      <c r="C136" s="39" t="inlineStr">
+      <c r="C136" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D136" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E136" s="40" t="inlineStr">
+      <c r="D136" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E136" s="35" t="inlineStr">
         <is>
           <t>45 / 136</t>
         </is>
       </c>
-      <c r="F136" s="60" t="n">
+      <c r="F136" s="58" t="n">
         <v>0.3308823529411765</v>
       </c>
-      <c r="G136" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H136" s="39" t="inlineStr">
+      <c r="G136" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H136" s="34" t="inlineStr">
         <is>
           <t>45/136 signed; 2-day gap; not daily movement</t>
         </is>
@@ -5955,7 +5955,7 @@
       <c r="F137" s="58" t="n">
         <v>0.03703703703703703</v>
       </c>
-      <c r="G137" s="37" t="inlineStr">
+      <c r="G137" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -6031,7 +6031,7 @@
       <c r="F139" s="58" t="n">
         <v>0.2281879194630873</v>
       </c>
-      <c r="G139" s="37" t="inlineStr">
+      <c r="G139" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -6043,38 +6043,38 @@
       </c>
     </row>
     <row r="140" ht="24" customHeight="1">
-      <c r="A140" s="59" t="n">
+      <c r="A140" s="57" t="n">
         <v>46311</v>
       </c>
-      <c r="B140" s="39" t="inlineStr">
+      <c r="B140" s="34" t="inlineStr">
         <is>
           <t>Amani Gallery Homes</t>
         </is>
       </c>
-      <c r="C140" s="39" t="inlineStr">
+      <c r="C140" s="34" t="inlineStr">
         <is>
           <t>20' x 70' / 20' x 72'</t>
         </is>
       </c>
-      <c r="D140" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E140" s="40" t="inlineStr">
+      <c r="D140" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E140" s="35" t="inlineStr">
         <is>
           <t>74 / 81</t>
         </is>
       </c>
-      <c r="F140" s="60" t="n">
+      <c r="F140" s="58" t="n">
         <v>0.9135802469135802</v>
       </c>
-      <c r="G140" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H140" s="39" t="inlineStr">
+      <c r="G140" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H140" s="34" t="inlineStr">
         <is>
           <t>74/81 signed; No scope change detected</t>
         </is>
@@ -6107,7 +6107,7 @@
       <c r="F141" s="58" t="n">
         <v>0.6017699115044248</v>
       </c>
-      <c r="G141" s="37" t="inlineStr">
+      <c r="G141" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -6119,38 +6119,38 @@
       </c>
     </row>
     <row r="142" ht="24" customHeight="1">
-      <c r="A142" s="59" t="n">
+      <c r="A142" s="57" t="n">
         <v>46311</v>
       </c>
-      <c r="B142" s="39" t="inlineStr">
+      <c r="B142" s="34" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C142" s="39" t="inlineStr">
+      <c r="C142" s="34" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D142" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E142" s="40" t="inlineStr">
+      <c r="D142" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E142" s="35" t="inlineStr">
         <is>
           <t>21 / 48</t>
         </is>
       </c>
-      <c r="F142" s="60" t="n">
+      <c r="F142" s="58" t="n">
         <v>0.4375</v>
       </c>
-      <c r="G142" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H142" s="39" t="inlineStr">
+      <c r="G142" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H142" s="34" t="inlineStr">
         <is>
           <t>21/48 signed; No scope change detected</t>
         </is>
@@ -6183,7 +6183,7 @@
       <c r="F143" s="58" t="n">
         <v>0.6283185840707964</v>
       </c>
-      <c r="G143" s="37" t="inlineStr">
+      <c r="G143" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -6195,190 +6195,190 @@
       </c>
     </row>
     <row r="144" ht="24" customHeight="1">
-      <c r="A144" s="57" t="n">
+      <c r="A144" s="59" t="n">
         <v>46311</v>
       </c>
-      <c r="B144" s="34" t="inlineStr">
+      <c r="B144" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C144" s="34" t="inlineStr">
+      <c r="C144" s="39" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D144" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E144" s="35" t="inlineStr">
+      <c r="D144" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E144" s="40" t="inlineStr">
         <is>
           <t>46 / 46</t>
         </is>
       </c>
-      <c r="F144" s="58" t="n">
+      <c r="F144" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="G144" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H144" s="34" t="inlineStr">
+      <c r="G144" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H144" s="39" t="inlineStr">
         <is>
           <t>46/46 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="145" ht="24" customHeight="1">
-      <c r="A145" s="59" t="n">
+      <c r="A145" s="57" t="n">
         <v>46311</v>
       </c>
-      <c r="B145" s="39" t="inlineStr">
+      <c r="B145" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C145" s="39" t="inlineStr">
+      <c r="C145" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D145" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E145" s="40" t="inlineStr">
+      <c r="D145" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E145" s="35" t="inlineStr">
         <is>
           <t>56 / 56</t>
         </is>
       </c>
-      <c r="F145" s="60" t="n">
+      <c r="F145" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="G145" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H145" s="39" t="inlineStr">
+      <c r="G145" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H145" s="34" t="inlineStr">
         <is>
           <t>56/56 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="146" ht="24" customHeight="1">
-      <c r="A146" s="57" t="n">
+      <c r="A146" s="59" t="n">
         <v>46311</v>
       </c>
-      <c r="B146" s="34" t="inlineStr">
+      <c r="B146" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C146" s="34" t="inlineStr">
+      <c r="C146" s="39" t="inlineStr">
         <is>
           <t>20' x 75'</t>
         </is>
       </c>
-      <c r="D146" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E146" s="35" t="inlineStr">
+      <c r="D146" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E146" s="40" t="inlineStr">
         <is>
           <t>24 / 25</t>
         </is>
       </c>
-      <c r="F146" s="58" t="n">
+      <c r="F146" s="60" t="n">
         <v>0.96</v>
       </c>
-      <c r="G146" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H146" s="34" t="inlineStr">
+      <c r="G146" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H146" s="39" t="inlineStr">
         <is>
           <t>24/25 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="147" ht="24" customHeight="1">
-      <c r="A147" s="59" t="n">
+      <c r="A147" s="57" t="n">
         <v>46311</v>
       </c>
-      <c r="B147" s="39" t="inlineStr">
+      <c r="B147" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C147" s="39" t="inlineStr">
+      <c r="C147" s="34" t="inlineStr">
         <is>
           <t>20' x 80'</t>
         </is>
       </c>
-      <c r="D147" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E147" s="40" t="inlineStr">
+      <c r="D147" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E147" s="35" t="inlineStr">
         <is>
           <t>10 / 25</t>
         </is>
       </c>
-      <c r="F147" s="60" t="n">
+      <c r="F147" s="58" t="n">
         <v>0.4</v>
       </c>
-      <c r="G147" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H147" s="39" t="inlineStr">
+      <c r="G147" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H147" s="34" t="inlineStr">
         <is>
           <t>10/25 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="148" ht="24" customHeight="1">
-      <c r="A148" s="59" t="n">
+      <c r="A148" s="57" t="n">
         <v>46311</v>
       </c>
-      <c r="B148" s="39" t="inlineStr">
+      <c r="B148" s="34" t="inlineStr">
         <is>
           <t>Chorus @Setia Ecohill 2</t>
         </is>
       </c>
-      <c r="C148" s="39" t="inlineStr">
+      <c r="C148" s="34" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D148" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E148" s="40" t="inlineStr">
+      <c r="D148" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E148" s="35" t="inlineStr">
         <is>
           <t>77 / 99</t>
         </is>
       </c>
-      <c r="F148" s="60" t="n">
+      <c r="F148" s="58" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="G148" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H148" s="39" t="inlineStr">
+      <c r="G148" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H148" s="34" t="inlineStr">
         <is>
           <t>77/99 signed; No scope change detected</t>
         </is>
@@ -6411,7 +6411,7 @@
       <c r="F149" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="G149" s="37" t="inlineStr">
+      <c r="G149" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -6449,7 +6449,7 @@
       <c r="F150" s="60" t="n">
         <v>0.9710144927536232</v>
       </c>
-      <c r="G150" s="37" t="inlineStr">
+      <c r="G150" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -6487,7 +6487,7 @@
       <c r="F151" s="58" t="n">
         <v>0.9753086419753086</v>
       </c>
-      <c r="G151" s="37" t="inlineStr">
+      <c r="G151" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -6499,114 +6499,114 @@
       </c>
     </row>
     <row r="152" ht="24" customHeight="1">
-      <c r="A152" s="57" t="n">
+      <c r="A152" s="59" t="n">
         <v>46311</v>
       </c>
-      <c r="B152" s="34" t="inlineStr">
+      <c r="B152" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C152" s="34" t="inlineStr">
+      <c r="C152" s="39" t="inlineStr">
         <is>
           <t>20' x 60'</t>
         </is>
       </c>
-      <c r="D152" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E152" s="35" t="inlineStr">
+      <c r="D152" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E152" s="40" t="inlineStr">
         <is>
           <t>23 / 26</t>
         </is>
       </c>
-      <c r="F152" s="58" t="n">
+      <c r="F152" s="60" t="n">
         <v>0.8846153846153846</v>
       </c>
-      <c r="G152" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H152" s="34" t="inlineStr">
+      <c r="G152" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H152" s="39" t="inlineStr">
         <is>
           <t>23/26 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="153" ht="24" customHeight="1">
-      <c r="A153" s="59" t="n">
+      <c r="A153" s="57" t="n">
         <v>46311</v>
       </c>
-      <c r="B153" s="39" t="inlineStr">
+      <c r="B153" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C153" s="39" t="inlineStr">
+      <c r="C153" s="34" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D153" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E153" s="40" t="inlineStr">
+      <c r="D153" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E153" s="35" t="inlineStr">
         <is>
           <t>124 / 126</t>
         </is>
       </c>
-      <c r="F153" s="60" t="n">
+      <c r="F153" s="58" t="n">
         <v>0.9841269841269841</v>
       </c>
-      <c r="G153" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H153" s="39" t="inlineStr">
+      <c r="G153" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H153" s="34" t="inlineStr">
         <is>
           <t>124/126 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="154" ht="24" customHeight="1">
-      <c r="A154" s="57" t="n">
+      <c r="A154" s="59" t="n">
         <v>46311</v>
       </c>
-      <c r="B154" s="34" t="inlineStr">
+      <c r="B154" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C154" s="34" t="inlineStr">
+      <c r="C154" s="39" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D154" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E154" s="35" t="inlineStr">
+      <c r="D154" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E154" s="40" t="inlineStr">
         <is>
           <t>98 / 104</t>
         </is>
       </c>
-      <c r="F154" s="58" t="n">
+      <c r="F154" s="60" t="n">
         <v>0.9423076923076923</v>
       </c>
-      <c r="G154" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H154" s="34" t="inlineStr">
+      <c r="G154" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H154" s="39" t="inlineStr">
         <is>
           <t>98/104 signed; No scope change detected</t>
         </is>
@@ -6639,7 +6639,7 @@
       <c r="F155" s="60" t="n">
         <v>0.6590909090909091</v>
       </c>
-      <c r="G155" s="37" t="inlineStr">
+      <c r="G155" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -6677,7 +6677,7 @@
       <c r="F156" s="58" t="n">
         <v>0.7411764705882353</v>
       </c>
-      <c r="G156" s="37" t="inlineStr">
+      <c r="G156" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -6715,7 +6715,7 @@
       <c r="F157" s="60" t="n">
         <v>0.2254901960784314</v>
       </c>
-      <c r="G157" s="37" t="inlineStr">
+      <c r="G157" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -6727,38 +6727,38 @@
       </c>
     </row>
     <row r="158" ht="24" customHeight="1">
-      <c r="A158" s="57" t="n">
+      <c r="A158" s="59" t="n">
         <v>46311</v>
       </c>
-      <c r="B158" s="34" t="inlineStr">
+      <c r="B158" s="39" t="inlineStr">
         <is>
           <t>Sapphire Residence @Diamond City</t>
         </is>
       </c>
-      <c r="C158" s="34" t="inlineStr">
+      <c r="C158" s="39" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D158" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E158" s="35" t="inlineStr">
+      <c r="D158" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E158" s="40" t="inlineStr">
         <is>
           <t>45 / 136</t>
         </is>
       </c>
-      <c r="F158" s="58" t="n">
+      <c r="F158" s="60" t="n">
         <v>0.3308823529411765</v>
       </c>
-      <c r="G158" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H158" s="34" t="inlineStr">
+      <c r="G158" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H158" s="39" t="inlineStr">
         <is>
           <t>45/136 signed; No scope change detected</t>
         </is>
@@ -6791,7 +6791,7 @@
       <c r="F159" s="58" t="n">
         <v>0.03703703703703703</v>
       </c>
-      <c r="G159" s="37" t="inlineStr">
+      <c r="G159" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -6829,7 +6829,7 @@
       <c r="F160" s="60" t="n">
         <v>0.5227272727272727</v>
       </c>
-      <c r="G160" s="37" t="inlineStr">
+      <c r="G160" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -6867,7 +6867,7 @@
       <c r="F161" s="60" t="n">
         <v>0.2281879194630873</v>
       </c>
-      <c r="G161" s="37" t="inlineStr">
+      <c r="G161" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -6879,38 +6879,38 @@
       </c>
     </row>
     <row r="162" ht="24" customHeight="1">
-      <c r="A162" s="57" t="n">
+      <c r="A162" s="59" t="n">
         <v>46312</v>
       </c>
-      <c r="B162" s="34" t="inlineStr">
+      <c r="B162" s="39" t="inlineStr">
         <is>
           <t>Amani Gallery Homes</t>
         </is>
       </c>
-      <c r="C162" s="34" t="inlineStr">
+      <c r="C162" s="39" t="inlineStr">
         <is>
           <t>20' x 70' / 20' x 72'</t>
         </is>
       </c>
-      <c r="D162" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E162" s="35" t="inlineStr">
+      <c r="D162" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E162" s="40" t="inlineStr">
         <is>
           <t>74 / 81</t>
         </is>
       </c>
-      <c r="F162" s="58" t="n">
+      <c r="F162" s="60" t="n">
         <v>0.9135802469135802</v>
       </c>
-      <c r="G162" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H162" s="34" t="inlineStr">
+      <c r="G162" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H162" s="39" t="inlineStr">
         <is>
           <t>74/81 signed; No scope change detected</t>
         </is>
@@ -6955,38 +6955,38 @@
       </c>
     </row>
     <row r="164" ht="24" customHeight="1">
-      <c r="A164" s="57" t="n">
+      <c r="A164" s="59" t="n">
         <v>46312</v>
       </c>
-      <c r="B164" s="34" t="inlineStr">
+      <c r="B164" s="39" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C164" s="34" t="inlineStr">
+      <c r="C164" s="39" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D164" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E164" s="35" t="inlineStr">
+      <c r="D164" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E164" s="40" t="inlineStr">
         <is>
           <t>21 / 48</t>
         </is>
       </c>
-      <c r="F164" s="58" t="n">
+      <c r="F164" s="60" t="n">
         <v>0.4375</v>
       </c>
-      <c r="G164" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H164" s="34" t="inlineStr">
+      <c r="G164" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H164" s="39" t="inlineStr">
         <is>
           <t>21/48 signed; No scope change detected</t>
         </is>
@@ -7019,7 +7019,7 @@
       <c r="F165" s="60" t="n">
         <v>0.6283185840707964</v>
       </c>
-      <c r="G165" s="37" t="inlineStr">
+      <c r="G165" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -7031,190 +7031,190 @@
       </c>
     </row>
     <row r="166" ht="24" customHeight="1">
-      <c r="A166" s="57" t="n">
+      <c r="A166" s="59" t="n">
         <v>46312</v>
       </c>
-      <c r="B166" s="34" t="inlineStr">
+      <c r="B166" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C166" s="34" t="inlineStr">
+      <c r="C166" s="39" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D166" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E166" s="35" t="inlineStr">
+      <c r="D166" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E166" s="40" t="inlineStr">
         <is>
           <t>46 / 46</t>
         </is>
       </c>
-      <c r="F166" s="58" t="n">
+      <c r="F166" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="G166" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H166" s="34" t="inlineStr">
+      <c r="G166" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H166" s="39" t="inlineStr">
         <is>
           <t>46/46 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="167" ht="24" customHeight="1">
-      <c r="A167" s="59" t="n">
+      <c r="A167" s="57" t="n">
         <v>46312</v>
       </c>
-      <c r="B167" s="39" t="inlineStr">
+      <c r="B167" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C167" s="39" t="inlineStr">
+      <c r="C167" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D167" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E167" s="40" t="inlineStr">
+      <c r="D167" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E167" s="35" t="inlineStr">
         <is>
           <t>56 / 56</t>
         </is>
       </c>
-      <c r="F167" s="60" t="n">
+      <c r="F167" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="G167" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H167" s="39" t="inlineStr">
+      <c r="G167" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H167" s="34" t="inlineStr">
         <is>
           <t>56/56 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="168" ht="24" customHeight="1">
-      <c r="A168" s="57" t="n">
+      <c r="A168" s="59" t="n">
         <v>46312</v>
       </c>
-      <c r="B168" s="34" t="inlineStr">
+      <c r="B168" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C168" s="34" t="inlineStr">
+      <c r="C168" s="39" t="inlineStr">
         <is>
           <t>20' x 75'</t>
         </is>
       </c>
-      <c r="D168" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E168" s="35" t="inlineStr">
+      <c r="D168" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E168" s="40" t="inlineStr">
         <is>
           <t>24 / 25</t>
         </is>
       </c>
-      <c r="F168" s="58" t="n">
+      <c r="F168" s="60" t="n">
         <v>0.96</v>
       </c>
-      <c r="G168" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H168" s="34" t="inlineStr">
+      <c r="G168" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H168" s="39" t="inlineStr">
         <is>
           <t>24/25 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="169" ht="24" customHeight="1">
-      <c r="A169" s="59" t="n">
+      <c r="A169" s="57" t="n">
         <v>46312</v>
       </c>
-      <c r="B169" s="39" t="inlineStr">
+      <c r="B169" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C169" s="39" t="inlineStr">
+      <c r="C169" s="34" t="inlineStr">
         <is>
           <t>20' x 80'</t>
         </is>
       </c>
-      <c r="D169" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E169" s="40" t="inlineStr">
+      <c r="D169" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E169" s="35" t="inlineStr">
         <is>
           <t>10 / 25</t>
         </is>
       </c>
-      <c r="F169" s="60" t="n">
+      <c r="F169" s="58" t="n">
         <v>0.4</v>
       </c>
-      <c r="G169" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H169" s="39" t="inlineStr">
+      <c r="G169" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H169" s="34" t="inlineStr">
         <is>
           <t>10/25 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="170" ht="24" customHeight="1">
-      <c r="A170" s="57" t="n">
+      <c r="A170" s="59" t="n">
         <v>46312</v>
       </c>
-      <c r="B170" s="34" t="inlineStr">
+      <c r="B170" s="39" t="inlineStr">
         <is>
           <t>Chorus @Setia Ecohill 2</t>
         </is>
       </c>
-      <c r="C170" s="34" t="inlineStr">
+      <c r="C170" s="39" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D170" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E170" s="35" t="inlineStr">
+      <c r="D170" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E170" s="40" t="inlineStr">
         <is>
           <t>77 / 99</t>
         </is>
       </c>
-      <c r="F170" s="58" t="n">
+      <c r="F170" s="60" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="G170" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H170" s="34" t="inlineStr">
+      <c r="G170" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H170" s="39" t="inlineStr">
         <is>
           <t>77/99 signed; No scope change detected</t>
         </is>
@@ -7247,7 +7247,7 @@
       <c r="F171" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="G171" s="37" t="inlineStr">
+      <c r="G171" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -7285,7 +7285,7 @@
       <c r="F172" s="58" t="n">
         <v>0.9710144927536232</v>
       </c>
-      <c r="G172" s="37" t="inlineStr">
+      <c r="G172" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -7323,7 +7323,7 @@
       <c r="F173" s="60" t="n">
         <v>0.9753086419753086</v>
       </c>
-      <c r="G173" s="37" t="inlineStr">
+      <c r="G173" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -7335,114 +7335,114 @@
       </c>
     </row>
     <row r="174" ht="24" customHeight="1">
-      <c r="A174" s="59" t="n">
+      <c r="A174" s="57" t="n">
         <v>46312</v>
       </c>
-      <c r="B174" s="39" t="inlineStr">
+      <c r="B174" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C174" s="39" t="inlineStr">
+      <c r="C174" s="34" t="inlineStr">
         <is>
           <t>20' x 60'</t>
         </is>
       </c>
-      <c r="D174" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E174" s="40" t="inlineStr">
+      <c r="D174" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E174" s="35" t="inlineStr">
         <is>
           <t>23 / 26</t>
         </is>
       </c>
-      <c r="F174" s="60" t="n">
+      <c r="F174" s="58" t="n">
         <v>0.8846153846153846</v>
       </c>
-      <c r="G174" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H174" s="39" t="inlineStr">
+      <c r="G174" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H174" s="34" t="inlineStr">
         <is>
           <t>23/26 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="175" ht="24" customHeight="1">
-      <c r="A175" s="57" t="n">
+      <c r="A175" s="59" t="n">
         <v>46312</v>
       </c>
-      <c r="B175" s="34" t="inlineStr">
+      <c r="B175" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C175" s="34" t="inlineStr">
+      <c r="C175" s="39" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D175" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E175" s="35" t="inlineStr">
+      <c r="D175" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E175" s="40" t="inlineStr">
         <is>
           <t>124 / 126</t>
         </is>
       </c>
-      <c r="F175" s="58" t="n">
+      <c r="F175" s="60" t="n">
         <v>0.9841269841269841</v>
       </c>
-      <c r="G175" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H175" s="34" t="inlineStr">
+      <c r="G175" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H175" s="39" t="inlineStr">
         <is>
           <t>124/126 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="176" ht="24" customHeight="1">
-      <c r="A176" s="59" t="n">
+      <c r="A176" s="57" t="n">
         <v>46312</v>
       </c>
-      <c r="B176" s="39" t="inlineStr">
+      <c r="B176" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C176" s="39" t="inlineStr">
+      <c r="C176" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D176" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E176" s="40" t="inlineStr">
+      <c r="D176" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E176" s="35" t="inlineStr">
         <is>
           <t>98 / 104</t>
         </is>
       </c>
-      <c r="F176" s="60" t="n">
+      <c r="F176" s="58" t="n">
         <v>0.9423076923076923</v>
       </c>
-      <c r="G176" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H176" s="39" t="inlineStr">
+      <c r="G176" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H176" s="34" t="inlineStr">
         <is>
           <t>98/104 signed; No scope change detected</t>
         </is>
@@ -7475,7 +7475,7 @@
       <c r="F177" s="58" t="n">
         <v>0.6590909090909091</v>
       </c>
-      <c r="G177" s="37" t="inlineStr">
+      <c r="G177" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -7563,38 +7563,38 @@
       </c>
     </row>
     <row r="180" ht="24" customHeight="1">
-      <c r="A180" s="59" t="n">
+      <c r="A180" s="57" t="n">
         <v>46312</v>
       </c>
-      <c r="B180" s="39" t="inlineStr">
+      <c r="B180" s="34" t="inlineStr">
         <is>
           <t>Sapphire Residence @Diamond City</t>
         </is>
       </c>
-      <c r="C180" s="39" t="inlineStr">
+      <c r="C180" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D180" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E180" s="40" t="inlineStr">
+      <c r="D180" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E180" s="35" t="inlineStr">
         <is>
           <t>45 / 136</t>
         </is>
       </c>
-      <c r="F180" s="60" t="n">
+      <c r="F180" s="58" t="n">
         <v>0.3308823529411765</v>
       </c>
-      <c r="G180" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H180" s="39" t="inlineStr">
+      <c r="G180" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H180" s="34" t="inlineStr">
         <is>
           <t>45/136 signed; No scope change detected</t>
         </is>
@@ -7627,7 +7627,7 @@
       <c r="F181" s="58" t="n">
         <v>0.03703703703703703</v>
       </c>
-      <c r="G181" s="37" t="inlineStr">
+      <c r="G181" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -7665,7 +7665,7 @@
       <c r="F182" s="60" t="n">
         <v>0.5227272727272727</v>
       </c>
-      <c r="G182" s="37" t="inlineStr">
+      <c r="G182" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -7703,7 +7703,7 @@
       <c r="F183" s="58" t="n">
         <v>0.2281879194630873</v>
       </c>
-      <c r="G183" s="37" t="inlineStr">
+      <c r="G183" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -7715,38 +7715,38 @@
       </c>
     </row>
     <row r="184" ht="24" customHeight="1">
-      <c r="A184" s="59" t="n">
+      <c r="A184" s="57" t="n">
         <v>46313</v>
       </c>
-      <c r="B184" s="39" t="inlineStr">
+      <c r="B184" s="34" t="inlineStr">
         <is>
           <t>Amani Gallery Homes</t>
         </is>
       </c>
-      <c r="C184" s="39" t="inlineStr">
+      <c r="C184" s="34" t="inlineStr">
         <is>
           <t>20' x 70' / 20' x 72'</t>
         </is>
       </c>
-      <c r="D184" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E184" s="40" t="inlineStr">
+      <c r="D184" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E184" s="35" t="inlineStr">
         <is>
           <t>74 / 81</t>
         </is>
       </c>
-      <c r="F184" s="60" t="n">
+      <c r="F184" s="58" t="n">
         <v>0.9135802469135802</v>
       </c>
-      <c r="G184" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H184" s="39" t="inlineStr">
+      <c r="G184" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H184" s="34" t="inlineStr">
         <is>
           <t>74/81 signed; No scope change detected</t>
         </is>
@@ -7779,7 +7779,7 @@
       <c r="F185" s="58" t="n">
         <v>0.6106194690265486</v>
       </c>
-      <c r="G185" s="37" t="inlineStr">
+      <c r="G185" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -7791,38 +7791,38 @@
       </c>
     </row>
     <row r="186" ht="24" customHeight="1">
-      <c r="A186" s="59" t="n">
+      <c r="A186" s="57" t="n">
         <v>46313</v>
       </c>
-      <c r="B186" s="39" t="inlineStr">
+      <c r="B186" s="34" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C186" s="39" t="inlineStr">
+      <c r="C186" s="34" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D186" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E186" s="40" t="inlineStr">
+      <c r="D186" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E186" s="35" t="inlineStr">
         <is>
           <t>21 / 48</t>
         </is>
       </c>
-      <c r="F186" s="60" t="n">
+      <c r="F186" s="58" t="n">
         <v>0.4375</v>
       </c>
-      <c r="G186" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H186" s="39" t="inlineStr">
+      <c r="G186" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H186" s="34" t="inlineStr">
         <is>
           <t>21/48 signed; No scope change detected</t>
         </is>
@@ -7855,7 +7855,7 @@
       <c r="F187" s="58" t="n">
         <v>0.6283185840707964</v>
       </c>
-      <c r="G187" s="37" t="inlineStr">
+      <c r="G187" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -7867,190 +7867,190 @@
       </c>
     </row>
     <row r="188" ht="24" customHeight="1">
-      <c r="A188" s="57" t="n">
+      <c r="A188" s="59" t="n">
         <v>46313</v>
       </c>
-      <c r="B188" s="34" t="inlineStr">
+      <c r="B188" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C188" s="34" t="inlineStr">
+      <c r="C188" s="39" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D188" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E188" s="35" t="inlineStr">
+      <c r="D188" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E188" s="40" t="inlineStr">
         <is>
           <t>46 / 46</t>
         </is>
       </c>
-      <c r="F188" s="58" t="n">
+      <c r="F188" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="G188" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H188" s="34" t="inlineStr">
+      <c r="G188" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H188" s="39" t="inlineStr">
         <is>
           <t>46/46 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="189" ht="24" customHeight="1">
-      <c r="A189" s="59" t="n">
+      <c r="A189" s="57" t="n">
         <v>46313</v>
       </c>
-      <c r="B189" s="39" t="inlineStr">
+      <c r="B189" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C189" s="39" t="inlineStr">
+      <c r="C189" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D189" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E189" s="40" t="inlineStr">
+      <c r="D189" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E189" s="35" t="inlineStr">
         <is>
           <t>56 / 56</t>
         </is>
       </c>
-      <c r="F189" s="60" t="n">
+      <c r="F189" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="G189" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H189" s="39" t="inlineStr">
+      <c r="G189" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H189" s="34" t="inlineStr">
         <is>
           <t>56/56 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="190" ht="24" customHeight="1">
-      <c r="A190" s="57" t="n">
+      <c r="A190" s="59" t="n">
         <v>46313</v>
       </c>
-      <c r="B190" s="34" t="inlineStr">
+      <c r="B190" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C190" s="34" t="inlineStr">
+      <c r="C190" s="39" t="inlineStr">
         <is>
           <t>20' x 75'</t>
         </is>
       </c>
-      <c r="D190" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E190" s="35" t="inlineStr">
+      <c r="D190" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E190" s="40" t="inlineStr">
         <is>
           <t>24 / 25</t>
         </is>
       </c>
-      <c r="F190" s="58" t="n">
+      <c r="F190" s="60" t="n">
         <v>0.96</v>
       </c>
-      <c r="G190" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H190" s="34" t="inlineStr">
+      <c r="G190" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H190" s="39" t="inlineStr">
         <is>
           <t>24/25 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="191" ht="24" customHeight="1">
-      <c r="A191" s="59" t="n">
+      <c r="A191" s="57" t="n">
         <v>46313</v>
       </c>
-      <c r="B191" s="39" t="inlineStr">
+      <c r="B191" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C191" s="39" t="inlineStr">
+      <c r="C191" s="34" t="inlineStr">
         <is>
           <t>20' x 80'</t>
         </is>
       </c>
-      <c r="D191" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E191" s="40" t="inlineStr">
+      <c r="D191" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E191" s="35" t="inlineStr">
         <is>
           <t>10 / 25</t>
         </is>
       </c>
-      <c r="F191" s="60" t="n">
+      <c r="F191" s="58" t="n">
         <v>0.4</v>
       </c>
-      <c r="G191" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H191" s="39" t="inlineStr">
+      <c r="G191" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H191" s="34" t="inlineStr">
         <is>
           <t>10/25 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="192" ht="24" customHeight="1">
-      <c r="A192" s="59" t="n">
+      <c r="A192" s="57" t="n">
         <v>46313</v>
       </c>
-      <c r="B192" s="39" t="inlineStr">
+      <c r="B192" s="34" t="inlineStr">
         <is>
           <t>Chorus @Setia Ecohill 2</t>
         </is>
       </c>
-      <c r="C192" s="39" t="inlineStr">
+      <c r="C192" s="34" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D192" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E192" s="40" t="inlineStr">
+      <c r="D192" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E192" s="35" t="inlineStr">
         <is>
           <t>77 / 99</t>
         </is>
       </c>
-      <c r="F192" s="60" t="n">
+      <c r="F192" s="58" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="G192" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H192" s="39" t="inlineStr">
+      <c r="G192" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H192" s="34" t="inlineStr">
         <is>
           <t>77/99 signed; No scope change detected</t>
         </is>
@@ -8083,7 +8083,7 @@
       <c r="F193" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="G193" s="37" t="inlineStr">
+      <c r="G193" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -8121,7 +8121,7 @@
       <c r="F194" s="60" t="n">
         <v>0.9710144927536232</v>
       </c>
-      <c r="G194" s="37" t="inlineStr">
+      <c r="G194" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -8159,7 +8159,7 @@
       <c r="F195" s="58" t="n">
         <v>0.9753086419753086</v>
       </c>
-      <c r="G195" s="37" t="inlineStr">
+      <c r="G195" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -8171,114 +8171,114 @@
       </c>
     </row>
     <row r="196" ht="24" customHeight="1">
-      <c r="A196" s="57" t="n">
+      <c r="A196" s="59" t="n">
         <v>46313</v>
       </c>
-      <c r="B196" s="34" t="inlineStr">
+      <c r="B196" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C196" s="34" t="inlineStr">
+      <c r="C196" s="39" t="inlineStr">
         <is>
           <t>20' x 60'</t>
         </is>
       </c>
-      <c r="D196" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E196" s="35" t="inlineStr">
+      <c r="D196" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E196" s="40" t="inlineStr">
         <is>
           <t>23 / 26</t>
         </is>
       </c>
-      <c r="F196" s="58" t="n">
+      <c r="F196" s="60" t="n">
         <v>0.8846153846153846</v>
       </c>
-      <c r="G196" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H196" s="34" t="inlineStr">
+      <c r="G196" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H196" s="39" t="inlineStr">
         <is>
           <t>23/26 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="197" ht="24" customHeight="1">
-      <c r="A197" s="59" t="n">
+      <c r="A197" s="57" t="n">
         <v>46313</v>
       </c>
-      <c r="B197" s="39" t="inlineStr">
+      <c r="B197" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C197" s="39" t="inlineStr">
+      <c r="C197" s="34" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D197" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E197" s="40" t="inlineStr">
+      <c r="D197" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E197" s="35" t="inlineStr">
         <is>
           <t>124 / 126</t>
         </is>
       </c>
-      <c r="F197" s="60" t="n">
+      <c r="F197" s="58" t="n">
         <v>0.9841269841269841</v>
       </c>
-      <c r="G197" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H197" s="39" t="inlineStr">
+      <c r="G197" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H197" s="34" t="inlineStr">
         <is>
           <t>124/126 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="198" ht="24" customHeight="1">
-      <c r="A198" s="57" t="n">
+      <c r="A198" s="59" t="n">
         <v>46313</v>
       </c>
-      <c r="B198" s="34" t="inlineStr">
+      <c r="B198" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C198" s="34" t="inlineStr">
+      <c r="C198" s="39" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D198" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E198" s="35" t="inlineStr">
+      <c r="D198" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E198" s="40" t="inlineStr">
         <is>
           <t>98 / 104</t>
         </is>
       </c>
-      <c r="F198" s="58" t="n">
+      <c r="F198" s="60" t="n">
         <v>0.9423076923076923</v>
       </c>
-      <c r="G198" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H198" s="34" t="inlineStr">
+      <c r="G198" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H198" s="39" t="inlineStr">
         <is>
           <t>98/104 signed; No scope change detected</t>
         </is>
@@ -8311,7 +8311,7 @@
       <c r="F199" s="60" t="n">
         <v>0.6590909090909091</v>
       </c>
-      <c r="G199" s="37" t="inlineStr">
+      <c r="G199" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -8349,7 +8349,7 @@
       <c r="F200" s="58" t="n">
         <v>0.7647058823529411</v>
       </c>
-      <c r="G200" s="37" t="inlineStr">
+      <c r="G200" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -8387,7 +8387,7 @@
       <c r="F201" s="60" t="n">
         <v>0.2352941176470588</v>
       </c>
-      <c r="G201" s="37" t="inlineStr">
+      <c r="G201" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -8399,38 +8399,38 @@
       </c>
     </row>
     <row r="202" ht="24" customHeight="1">
-      <c r="A202" s="57" t="n">
+      <c r="A202" s="59" t="n">
         <v>46313</v>
       </c>
-      <c r="B202" s="34" t="inlineStr">
+      <c r="B202" s="39" t="inlineStr">
         <is>
           <t>Sapphire Residence @Diamond City</t>
         </is>
       </c>
-      <c r="C202" s="34" t="inlineStr">
+      <c r="C202" s="39" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D202" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E202" s="35" t="inlineStr">
+      <c r="D202" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E202" s="40" t="inlineStr">
         <is>
           <t>45 / 136</t>
         </is>
       </c>
-      <c r="F202" s="58" t="n">
+      <c r="F202" s="60" t="n">
         <v>0.3308823529411765</v>
       </c>
-      <c r="G202" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H202" s="34" t="inlineStr">
+      <c r="G202" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H202" s="39" t="inlineStr">
         <is>
           <t>45/136 signed; No scope change detected</t>
         </is>
@@ -8463,7 +8463,7 @@
       <c r="F203" s="58" t="n">
         <v>0.03703703703703703</v>
       </c>
-      <c r="G203" s="37" t="inlineStr">
+      <c r="G203" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -8501,7 +8501,7 @@
       <c r="F204" s="60" t="n">
         <v>0.5227272727272727</v>
       </c>
-      <c r="G204" s="37" t="inlineStr">
+      <c r="G204" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -8539,7 +8539,7 @@
       <c r="F205" s="60" t="n">
         <v>0.2281879194630873</v>
       </c>
-      <c r="G205" s="37" t="inlineStr">
+      <c r="G205" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -8551,38 +8551,38 @@
       </c>
     </row>
     <row r="206" ht="24" customHeight="1">
-      <c r="A206" s="57" t="n">
+      <c r="A206" s="59" t="n">
         <v>46314</v>
       </c>
-      <c r="B206" s="34" t="inlineStr">
+      <c r="B206" s="39" t="inlineStr">
         <is>
           <t>Amani Gallery Homes</t>
         </is>
       </c>
-      <c r="C206" s="34" t="inlineStr">
+      <c r="C206" s="39" t="inlineStr">
         <is>
           <t>20' x 70' / 20' x 72'</t>
         </is>
       </c>
-      <c r="D206" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E206" s="35" t="inlineStr">
+      <c r="D206" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E206" s="40" t="inlineStr">
         <is>
           <t>74 / 81</t>
         </is>
       </c>
-      <c r="F206" s="58" t="n">
+      <c r="F206" s="60" t="n">
         <v>0.9135802469135802</v>
       </c>
-      <c r="G206" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H206" s="34" t="inlineStr">
+      <c r="G206" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H206" s="39" t="inlineStr">
         <is>
           <t>74/81 signed; No scope change detected</t>
         </is>
@@ -8615,7 +8615,7 @@
       <c r="F207" s="60" t="n">
         <v>0.6106194690265486</v>
       </c>
-      <c r="G207" s="37" t="inlineStr">
+      <c r="G207" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -8627,38 +8627,38 @@
       </c>
     </row>
     <row r="208" ht="24" customHeight="1">
-      <c r="A208" s="57" t="n">
+      <c r="A208" s="59" t="n">
         <v>46314</v>
       </c>
-      <c r="B208" s="34" t="inlineStr">
+      <c r="B208" s="39" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C208" s="34" t="inlineStr">
+      <c r="C208" s="39" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D208" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E208" s="35" t="inlineStr">
+      <c r="D208" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E208" s="40" t="inlineStr">
         <is>
           <t>21 / 48</t>
         </is>
       </c>
-      <c r="F208" s="58" t="n">
+      <c r="F208" s="60" t="n">
         <v>0.4375</v>
       </c>
-      <c r="G208" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H208" s="34" t="inlineStr">
+      <c r="G208" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H208" s="39" t="inlineStr">
         <is>
           <t>21/48 signed; No scope change detected</t>
         </is>
@@ -8691,7 +8691,7 @@
       <c r="F209" s="60" t="n">
         <v>0.6283185840707964</v>
       </c>
-      <c r="G209" s="37" t="inlineStr">
+      <c r="G209" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -8703,190 +8703,190 @@
       </c>
     </row>
     <row r="210" ht="24" customHeight="1">
-      <c r="A210" s="57" t="n">
+      <c r="A210" s="59" t="n">
         <v>46314</v>
       </c>
-      <c r="B210" s="34" t="inlineStr">
+      <c r="B210" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C210" s="34" t="inlineStr">
+      <c r="C210" s="39" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D210" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E210" s="35" t="inlineStr">
+      <c r="D210" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E210" s="40" t="inlineStr">
         <is>
           <t>46 / 46</t>
         </is>
       </c>
-      <c r="F210" s="58" t="n">
+      <c r="F210" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="G210" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H210" s="34" t="inlineStr">
+      <c r="G210" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H210" s="39" t="inlineStr">
         <is>
           <t>46/46 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="211" ht="24" customHeight="1">
-      <c r="A211" s="59" t="n">
+      <c r="A211" s="57" t="n">
         <v>46314</v>
       </c>
-      <c r="B211" s="39" t="inlineStr">
+      <c r="B211" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C211" s="39" t="inlineStr">
+      <c r="C211" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D211" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E211" s="40" t="inlineStr">
+      <c r="D211" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E211" s="35" t="inlineStr">
         <is>
           <t>56 / 56</t>
         </is>
       </c>
-      <c r="F211" s="60" t="n">
+      <c r="F211" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="G211" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H211" s="39" t="inlineStr">
+      <c r="G211" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H211" s="34" t="inlineStr">
         <is>
           <t>56/56 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="212" ht="24" customHeight="1">
-      <c r="A212" s="57" t="n">
+      <c r="A212" s="59" t="n">
         <v>46314</v>
       </c>
-      <c r="B212" s="34" t="inlineStr">
+      <c r="B212" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C212" s="34" t="inlineStr">
+      <c r="C212" s="39" t="inlineStr">
         <is>
           <t>20' x 75'</t>
         </is>
       </c>
-      <c r="D212" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E212" s="35" t="inlineStr">
+      <c r="D212" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E212" s="40" t="inlineStr">
         <is>
           <t>24 / 25</t>
         </is>
       </c>
-      <c r="F212" s="58" t="n">
+      <c r="F212" s="60" t="n">
         <v>0.96</v>
       </c>
-      <c r="G212" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H212" s="34" t="inlineStr">
+      <c r="G212" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H212" s="39" t="inlineStr">
         <is>
           <t>24/25 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="213" ht="24" customHeight="1">
-      <c r="A213" s="59" t="n">
+      <c r="A213" s="57" t="n">
         <v>46314</v>
       </c>
-      <c r="B213" s="39" t="inlineStr">
+      <c r="B213" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C213" s="39" t="inlineStr">
+      <c r="C213" s="34" t="inlineStr">
         <is>
           <t>20' x 80'</t>
         </is>
       </c>
-      <c r="D213" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E213" s="40" t="inlineStr">
+      <c r="D213" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E213" s="35" t="inlineStr">
         <is>
           <t>10 / 25</t>
         </is>
       </c>
-      <c r="F213" s="60" t="n">
+      <c r="F213" s="58" t="n">
         <v>0.4</v>
       </c>
-      <c r="G213" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H213" s="39" t="inlineStr">
+      <c r="G213" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H213" s="34" t="inlineStr">
         <is>
           <t>10/25 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="214" ht="24" customHeight="1">
-      <c r="A214" s="57" t="n">
+      <c r="A214" s="59" t="n">
         <v>46314</v>
       </c>
-      <c r="B214" s="34" t="inlineStr">
+      <c r="B214" s="39" t="inlineStr">
         <is>
           <t>Chorus @Setia Ecohill 2</t>
         </is>
       </c>
-      <c r="C214" s="34" t="inlineStr">
+      <c r="C214" s="39" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D214" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E214" s="35" t="inlineStr">
+      <c r="D214" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E214" s="40" t="inlineStr">
         <is>
           <t>77 / 99</t>
         </is>
       </c>
-      <c r="F214" s="58" t="n">
+      <c r="F214" s="60" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="G214" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H214" s="34" t="inlineStr">
+      <c r="G214" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H214" s="39" t="inlineStr">
         <is>
           <t>77/99 signed; No scope change detected</t>
         </is>
@@ -8919,7 +8919,7 @@
       <c r="F215" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="G215" s="37" t="inlineStr">
+      <c r="G215" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -8957,7 +8957,7 @@
       <c r="F216" s="58" t="n">
         <v>0.9710144927536232</v>
       </c>
-      <c r="G216" s="37" t="inlineStr">
+      <c r="G216" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -8995,7 +8995,7 @@
       <c r="F217" s="60" t="n">
         <v>0.9753086419753086</v>
       </c>
-      <c r="G217" s="37" t="inlineStr">
+      <c r="G217" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -9007,114 +9007,114 @@
       </c>
     </row>
     <row r="218" ht="24" customHeight="1">
-      <c r="A218" s="59" t="n">
+      <c r="A218" s="57" t="n">
         <v>46314</v>
       </c>
-      <c r="B218" s="39" t="inlineStr">
+      <c r="B218" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C218" s="39" t="inlineStr">
+      <c r="C218" s="34" t="inlineStr">
         <is>
           <t>20' x 60'</t>
         </is>
       </c>
-      <c r="D218" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E218" s="40" t="inlineStr">
+      <c r="D218" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E218" s="35" t="inlineStr">
         <is>
           <t>23 / 26</t>
         </is>
       </c>
-      <c r="F218" s="60" t="n">
+      <c r="F218" s="58" t="n">
         <v>0.8846153846153846</v>
       </c>
-      <c r="G218" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H218" s="39" t="inlineStr">
+      <c r="G218" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H218" s="34" t="inlineStr">
         <is>
           <t>23/26 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="219" ht="24" customHeight="1">
-      <c r="A219" s="57" t="n">
+      <c r="A219" s="59" t="n">
         <v>46314</v>
       </c>
-      <c r="B219" s="34" t="inlineStr">
+      <c r="B219" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C219" s="34" t="inlineStr">
+      <c r="C219" s="39" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D219" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E219" s="35" t="inlineStr">
+      <c r="D219" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E219" s="40" t="inlineStr">
         <is>
           <t>124 / 126</t>
         </is>
       </c>
-      <c r="F219" s="58" t="n">
+      <c r="F219" s="60" t="n">
         <v>0.9841269841269841</v>
       </c>
-      <c r="G219" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H219" s="34" t="inlineStr">
+      <c r="G219" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H219" s="39" t="inlineStr">
         <is>
           <t>124/126 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="220" ht="24" customHeight="1">
-      <c r="A220" s="59" t="n">
+      <c r="A220" s="57" t="n">
         <v>46314</v>
       </c>
-      <c r="B220" s="39" t="inlineStr">
+      <c r="B220" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C220" s="39" t="inlineStr">
+      <c r="C220" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D220" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E220" s="40" t="inlineStr">
+      <c r="D220" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E220" s="35" t="inlineStr">
         <is>
           <t>98 / 104</t>
         </is>
       </c>
-      <c r="F220" s="60" t="n">
+      <c r="F220" s="58" t="n">
         <v>0.9423076923076923</v>
       </c>
-      <c r="G220" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H220" s="39" t="inlineStr">
+      <c r="G220" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H220" s="34" t="inlineStr">
         <is>
           <t>98/104 signed; No scope change detected</t>
         </is>
@@ -9147,7 +9147,7 @@
       <c r="F221" s="58" t="n">
         <v>0.6590909090909091</v>
       </c>
-      <c r="G221" s="37" t="inlineStr">
+      <c r="G221" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -9185,7 +9185,7 @@
       <c r="F222" s="60" t="n">
         <v>0.7647058823529411</v>
       </c>
-      <c r="G222" s="37" t="inlineStr">
+      <c r="G222" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -9223,7 +9223,7 @@
       <c r="F223" s="58" t="n">
         <v>0.2352941176470588</v>
       </c>
-      <c r="G223" s="37" t="inlineStr">
+      <c r="G223" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -9235,38 +9235,38 @@
       </c>
     </row>
     <row r="224" ht="24" customHeight="1">
-      <c r="A224" s="59" t="n">
+      <c r="A224" s="57" t="n">
         <v>46314</v>
       </c>
-      <c r="B224" s="39" t="inlineStr">
+      <c r="B224" s="34" t="inlineStr">
         <is>
           <t>Sapphire Residence @Diamond City</t>
         </is>
       </c>
-      <c r="C224" s="39" t="inlineStr">
+      <c r="C224" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D224" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E224" s="40" t="inlineStr">
+      <c r="D224" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E224" s="35" t="inlineStr">
         <is>
           <t>45 / 136</t>
         </is>
       </c>
-      <c r="F224" s="60" t="n">
+      <c r="F224" s="58" t="n">
         <v>0.3308823529411765</v>
       </c>
-      <c r="G224" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H224" s="39" t="inlineStr">
+      <c r="G224" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H224" s="34" t="inlineStr">
         <is>
           <t>45/136 signed; No scope change detected</t>
         </is>
@@ -9299,7 +9299,7 @@
       <c r="F225" s="58" t="n">
         <v>0.03703703703703703</v>
       </c>
-      <c r="G225" s="37" t="inlineStr">
+      <c r="G225" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -9337,7 +9337,7 @@
       <c r="F226" s="60" t="n">
         <v>0.5227272727272727</v>
       </c>
-      <c r="G226" s="37" t="inlineStr">
+      <c r="G226" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -9375,7 +9375,7 @@
       <c r="F227" s="58" t="n">
         <v>0.2281879194630873</v>
       </c>
-      <c r="G227" s="37" t="inlineStr">
+      <c r="G227" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -9387,38 +9387,38 @@
       </c>
     </row>
     <row r="228" ht="24" customHeight="1">
-      <c r="A228" s="59" t="n">
+      <c r="A228" s="57" t="n">
         <v>46315</v>
       </c>
-      <c r="B228" s="39" t="inlineStr">
+      <c r="B228" s="34" t="inlineStr">
         <is>
           <t>Amani Gallery Homes</t>
         </is>
       </c>
-      <c r="C228" s="39" t="inlineStr">
+      <c r="C228" s="34" t="inlineStr">
         <is>
           <t>20' x 70' / 20' x 72'</t>
         </is>
       </c>
-      <c r="D228" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E228" s="40" t="inlineStr">
+      <c r="D228" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E228" s="35" t="inlineStr">
         <is>
           <t>74 / 81</t>
         </is>
       </c>
-      <c r="F228" s="60" t="n">
+      <c r="F228" s="58" t="n">
         <v>0.9135802469135802</v>
       </c>
-      <c r="G228" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H228" s="39" t="inlineStr">
+      <c r="G228" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H228" s="34" t="inlineStr">
         <is>
           <t>74/81 signed; No scope change detected</t>
         </is>
@@ -9451,7 +9451,7 @@
       <c r="F229" s="58" t="n">
         <v>0.6106194690265486</v>
       </c>
-      <c r="G229" s="37" t="inlineStr">
+      <c r="G229" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -9463,38 +9463,38 @@
       </c>
     </row>
     <row r="230" ht="24" customHeight="1">
-      <c r="A230" s="59" t="n">
+      <c r="A230" s="57" t="n">
         <v>46315</v>
       </c>
-      <c r="B230" s="39" t="inlineStr">
+      <c r="B230" s="34" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C230" s="39" t="inlineStr">
+      <c r="C230" s="34" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D230" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E230" s="40" t="inlineStr">
+      <c r="D230" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E230" s="35" t="inlineStr">
         <is>
           <t>21 / 48</t>
         </is>
       </c>
-      <c r="F230" s="60" t="n">
+      <c r="F230" s="58" t="n">
         <v>0.4375</v>
       </c>
-      <c r="G230" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H230" s="39" t="inlineStr">
+      <c r="G230" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H230" s="34" t="inlineStr">
         <is>
           <t>21/48 signed; No scope change detected</t>
         </is>
@@ -9527,7 +9527,7 @@
       <c r="F231" s="58" t="n">
         <v>0.6283185840707964</v>
       </c>
-      <c r="G231" s="37" t="inlineStr">
+      <c r="G231" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -9539,190 +9539,190 @@
       </c>
     </row>
     <row r="232" ht="24" customHeight="1">
-      <c r="A232" s="57" t="n">
+      <c r="A232" s="59" t="n">
         <v>46315</v>
       </c>
-      <c r="B232" s="34" t="inlineStr">
+      <c r="B232" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C232" s="34" t="inlineStr">
+      <c r="C232" s="39" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D232" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E232" s="35" t="inlineStr">
+      <c r="D232" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E232" s="40" t="inlineStr">
         <is>
           <t>46 / 46</t>
         </is>
       </c>
-      <c r="F232" s="58" t="n">
+      <c r="F232" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="G232" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H232" s="34" t="inlineStr">
+      <c r="G232" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H232" s="39" t="inlineStr">
         <is>
           <t>46/46 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="233" ht="24" customHeight="1">
-      <c r="A233" s="59" t="n">
+      <c r="A233" s="57" t="n">
         <v>46315</v>
       </c>
-      <c r="B233" s="39" t="inlineStr">
+      <c r="B233" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C233" s="39" t="inlineStr">
+      <c r="C233" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D233" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E233" s="40" t="inlineStr">
+      <c r="D233" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E233" s="35" t="inlineStr">
         <is>
           <t>56 / 56</t>
         </is>
       </c>
-      <c r="F233" s="60" t="n">
+      <c r="F233" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="G233" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H233" s="39" t="inlineStr">
+      <c r="G233" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H233" s="34" t="inlineStr">
         <is>
           <t>56/56 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="234" ht="24" customHeight="1">
-      <c r="A234" s="57" t="n">
+      <c r="A234" s="59" t="n">
         <v>46315</v>
       </c>
-      <c r="B234" s="34" t="inlineStr">
+      <c r="B234" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C234" s="34" t="inlineStr">
+      <c r="C234" s="39" t="inlineStr">
         <is>
           <t>20' x 75'</t>
         </is>
       </c>
-      <c r="D234" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E234" s="35" t="inlineStr">
+      <c r="D234" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E234" s="40" t="inlineStr">
         <is>
           <t>24 / 25</t>
         </is>
       </c>
-      <c r="F234" s="58" t="n">
+      <c r="F234" s="60" t="n">
         <v>0.96</v>
       </c>
-      <c r="G234" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H234" s="34" t="inlineStr">
+      <c r="G234" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H234" s="39" t="inlineStr">
         <is>
           <t>24/25 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="235" ht="24" customHeight="1">
-      <c r="A235" s="59" t="n">
+      <c r="A235" s="57" t="n">
         <v>46315</v>
       </c>
-      <c r="B235" s="39" t="inlineStr">
+      <c r="B235" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C235" s="39" t="inlineStr">
+      <c r="C235" s="34" t="inlineStr">
         <is>
           <t>20' x 80'</t>
         </is>
       </c>
-      <c r="D235" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E235" s="40" t="inlineStr">
+      <c r="D235" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E235" s="35" t="inlineStr">
         <is>
           <t>10 / 25</t>
         </is>
       </c>
-      <c r="F235" s="60" t="n">
+      <c r="F235" s="58" t="n">
         <v>0.4</v>
       </c>
-      <c r="G235" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H235" s="39" t="inlineStr">
+      <c r="G235" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H235" s="34" t="inlineStr">
         <is>
           <t>10/25 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="236" ht="24" customHeight="1">
-      <c r="A236" s="59" t="n">
+      <c r="A236" s="57" t="n">
         <v>46315</v>
       </c>
-      <c r="B236" s="39" t="inlineStr">
+      <c r="B236" s="34" t="inlineStr">
         <is>
           <t>Chorus @Setia Ecohill 2</t>
         </is>
       </c>
-      <c r="C236" s="39" t="inlineStr">
+      <c r="C236" s="34" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D236" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E236" s="40" t="inlineStr">
+      <c r="D236" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E236" s="35" t="inlineStr">
         <is>
           <t>77 / 99</t>
         </is>
       </c>
-      <c r="F236" s="60" t="n">
+      <c r="F236" s="58" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="G236" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H236" s="39" t="inlineStr">
+      <c r="G236" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H236" s="34" t="inlineStr">
         <is>
           <t>77/99 signed; No scope change detected</t>
         </is>
@@ -9755,7 +9755,7 @@
       <c r="F237" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="G237" s="37" t="inlineStr">
+      <c r="G237" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -9793,7 +9793,7 @@
       <c r="F238" s="60" t="n">
         <v>0.9710144927536232</v>
       </c>
-      <c r="G238" s="37" t="inlineStr">
+      <c r="G238" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -9831,7 +9831,7 @@
       <c r="F239" s="58" t="n">
         <v>0.9753086419753086</v>
       </c>
-      <c r="G239" s="37" t="inlineStr">
+      <c r="G239" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -9843,114 +9843,114 @@
       </c>
     </row>
     <row r="240" ht="24" customHeight="1">
-      <c r="A240" s="57" t="n">
+      <c r="A240" s="59" t="n">
         <v>46315</v>
       </c>
-      <c r="B240" s="34" t="inlineStr">
+      <c r="B240" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C240" s="34" t="inlineStr">
+      <c r="C240" s="39" t="inlineStr">
         <is>
           <t>20' x 60'</t>
         </is>
       </c>
-      <c r="D240" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E240" s="35" t="inlineStr">
+      <c r="D240" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E240" s="40" t="inlineStr">
         <is>
           <t>23 / 26</t>
         </is>
       </c>
-      <c r="F240" s="58" t="n">
+      <c r="F240" s="60" t="n">
         <v>0.8846153846153846</v>
       </c>
-      <c r="G240" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H240" s="34" t="inlineStr">
+      <c r="G240" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H240" s="39" t="inlineStr">
         <is>
           <t>23/26 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="241" ht="24" customHeight="1">
-      <c r="A241" s="59" t="n">
+      <c r="A241" s="57" t="n">
         <v>46315</v>
       </c>
-      <c r="B241" s="39" t="inlineStr">
+      <c r="B241" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C241" s="39" t="inlineStr">
+      <c r="C241" s="34" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D241" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E241" s="40" t="inlineStr">
+      <c r="D241" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E241" s="35" t="inlineStr">
         <is>
           <t>124 / 126</t>
         </is>
       </c>
-      <c r="F241" s="60" t="n">
+      <c r="F241" s="58" t="n">
         <v>0.9841269841269841</v>
       </c>
-      <c r="G241" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H241" s="39" t="inlineStr">
+      <c r="G241" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H241" s="34" t="inlineStr">
         <is>
           <t>124/126 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="242" ht="24" customHeight="1">
-      <c r="A242" s="57" t="n">
+      <c r="A242" s="59" t="n">
         <v>46315</v>
       </c>
-      <c r="B242" s="34" t="inlineStr">
+      <c r="B242" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C242" s="34" t="inlineStr">
+      <c r="C242" s="39" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D242" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E242" s="35" t="inlineStr">
+      <c r="D242" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E242" s="40" t="inlineStr">
         <is>
           <t>98 / 104</t>
         </is>
       </c>
-      <c r="F242" s="58" t="n">
+      <c r="F242" s="60" t="n">
         <v>0.9423076923076923</v>
       </c>
-      <c r="G242" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H242" s="34" t="inlineStr">
+      <c r="G242" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H242" s="39" t="inlineStr">
         <is>
           <t>98/104 signed; No scope change detected</t>
         </is>
@@ -9983,7 +9983,7 @@
       <c r="F243" s="60" t="n">
         <v>0.6590909090909091</v>
       </c>
-      <c r="G243" s="37" t="inlineStr">
+      <c r="G243" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -10021,7 +10021,7 @@
       <c r="F244" s="58" t="n">
         <v>0.7647058823529411</v>
       </c>
-      <c r="G244" s="37" t="inlineStr">
+      <c r="G244" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -10059,7 +10059,7 @@
       <c r="F245" s="60" t="n">
         <v>0.2352941176470588</v>
       </c>
-      <c r="G245" s="37" t="inlineStr">
+      <c r="G245" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -10071,38 +10071,38 @@
       </c>
     </row>
     <row r="246" ht="24" customHeight="1">
-      <c r="A246" s="57" t="n">
+      <c r="A246" s="59" t="n">
         <v>46315</v>
       </c>
-      <c r="B246" s="34" t="inlineStr">
+      <c r="B246" s="39" t="inlineStr">
         <is>
           <t>Sapphire Residence @Diamond City</t>
         </is>
       </c>
-      <c r="C246" s="34" t="inlineStr">
+      <c r="C246" s="39" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D246" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E246" s="35" t="inlineStr">
+      <c r="D246" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E246" s="40" t="inlineStr">
         <is>
           <t>45 / 136</t>
         </is>
       </c>
-      <c r="F246" s="58" t="n">
+      <c r="F246" s="60" t="n">
         <v>0.3308823529411765</v>
       </c>
-      <c r="G246" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H246" s="34" t="inlineStr">
+      <c r="G246" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H246" s="39" t="inlineStr">
         <is>
           <t>45/136 signed; No scope change detected</t>
         </is>
@@ -10135,7 +10135,7 @@
       <c r="F247" s="58" t="n">
         <v>0.03703703703703703</v>
       </c>
-      <c r="G247" s="37" t="inlineStr">
+      <c r="G247" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -10173,7 +10173,7 @@
       <c r="F248" s="60" t="n">
         <v>0.5227272727272727</v>
       </c>
-      <c r="G248" s="37" t="inlineStr">
+      <c r="G248" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -10211,7 +10211,7 @@
       <c r="F249" s="60" t="n">
         <v>0.2281879194630873</v>
       </c>
-      <c r="G249" s="37" t="inlineStr">
+      <c r="G249" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -10223,38 +10223,38 @@
       </c>
     </row>
     <row r="250" ht="24" customHeight="1">
-      <c r="A250" s="57" t="n">
+      <c r="A250" s="59" t="n">
         <v>46316</v>
       </c>
-      <c r="B250" s="34" t="inlineStr">
+      <c r="B250" s="39" t="inlineStr">
         <is>
           <t>Amani Gallery Homes</t>
         </is>
       </c>
-      <c r="C250" s="34" t="inlineStr">
+      <c r="C250" s="39" t="inlineStr">
         <is>
           <t>20' x 70' / 20' x 72'</t>
         </is>
       </c>
-      <c r="D250" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E250" s="35" t="inlineStr">
+      <c r="D250" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E250" s="40" t="inlineStr">
         <is>
           <t>74 / 81</t>
         </is>
       </c>
-      <c r="F250" s="58" t="n">
+      <c r="F250" s="60" t="n">
         <v>0.9135802469135802</v>
       </c>
-      <c r="G250" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H250" s="34" t="inlineStr">
+      <c r="G250" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H250" s="39" t="inlineStr">
         <is>
           <t>74/81 signed; No scope change detected</t>
         </is>
@@ -10287,7 +10287,7 @@
       <c r="F251" s="60" t="n">
         <v>0.6106194690265486</v>
       </c>
-      <c r="G251" s="37" t="inlineStr">
+      <c r="G251" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -10299,30 +10299,30 @@
       </c>
     </row>
     <row r="252" ht="24" customHeight="1">
-      <c r="A252" s="57" t="n">
+      <c r="A252" s="59" t="n">
         <v>46316</v>
       </c>
-      <c r="B252" s="34" t="inlineStr">
+      <c r="B252" s="39" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C252" s="34" t="inlineStr">
+      <c r="C252" s="39" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D252" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E252" s="35" t="inlineStr">
+      <c r="D252" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E252" s="40" t="inlineStr">
         <is>
           <t>22 / 48</t>
         </is>
       </c>
-      <c r="F252" s="58" t="n">
+      <c r="F252" s="60" t="n">
         <v>0.4583333333333333</v>
       </c>
       <c r="G252" s="43" t="inlineStr">
@@ -10330,7 +10330,7 @@
           <t>+1 signed · +2.1 pp</t>
         </is>
       </c>
-      <c r="H252" s="34" t="inlineStr">
+      <c r="H252" s="39" t="inlineStr">
         <is>
           <t>22/48 signed; No scope change detected</t>
         </is>
@@ -10363,7 +10363,7 @@
       <c r="F253" s="60" t="n">
         <v>0.6283185840707964</v>
       </c>
-      <c r="G253" s="37" t="inlineStr">
+      <c r="G253" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -10375,106 +10375,106 @@
       </c>
     </row>
     <row r="254" ht="24" customHeight="1">
-      <c r="A254" s="57" t="n">
+      <c r="A254" s="59" t="n">
         <v>46316</v>
       </c>
-      <c r="B254" s="34" t="inlineStr">
+      <c r="B254" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C254" s="34" t="inlineStr">
+      <c r="C254" s="39" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D254" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E254" s="35" t="inlineStr">
+      <c r="D254" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E254" s="40" t="inlineStr">
         <is>
           <t>46 / 46</t>
         </is>
       </c>
-      <c r="F254" s="58" t="n">
+      <c r="F254" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="G254" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H254" s="34" t="inlineStr">
+      <c r="G254" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H254" s="39" t="inlineStr">
         <is>
           <t>46/46 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="255" ht="24" customHeight="1">
-      <c r="A255" s="59" t="n">
+      <c r="A255" s="57" t="n">
         <v>46316</v>
       </c>
-      <c r="B255" s="39" t="inlineStr">
+      <c r="B255" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C255" s="39" t="inlineStr">
+      <c r="C255" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D255" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E255" s="40" t="inlineStr">
+      <c r="D255" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E255" s="35" t="inlineStr">
         <is>
           <t>56 / 56</t>
         </is>
       </c>
-      <c r="F255" s="60" t="n">
+      <c r="F255" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="G255" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H255" s="39" t="inlineStr">
+      <c r="G255" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H255" s="34" t="inlineStr">
         <is>
           <t>56/56 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="256" ht="24" customHeight="1">
-      <c r="A256" s="57" t="n">
+      <c r="A256" s="59" t="n">
         <v>46316</v>
       </c>
-      <c r="B256" s="34" t="inlineStr">
+      <c r="B256" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C256" s="34" t="inlineStr">
+      <c r="C256" s="39" t="inlineStr">
         <is>
           <t>20' x 75'</t>
         </is>
       </c>
-      <c r="D256" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E256" s="35" t="inlineStr">
+      <c r="D256" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E256" s="40" t="inlineStr">
         <is>
           <t>25 / 25</t>
         </is>
       </c>
-      <c r="F256" s="58" t="n">
+      <c r="F256" s="60" t="n">
         <v>1</v>
       </c>
       <c r="G256" s="43" t="inlineStr">
@@ -10482,83 +10482,83 @@
           <t>+1 signed · +4.0 pp</t>
         </is>
       </c>
-      <c r="H256" s="34" t="inlineStr">
+      <c r="H256" s="39" t="inlineStr">
         <is>
           <t>25/25 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="257" ht="24" customHeight="1">
-      <c r="A257" s="59" t="n">
+      <c r="A257" s="57" t="n">
         <v>46316</v>
       </c>
-      <c r="B257" s="39" t="inlineStr">
+      <c r="B257" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C257" s="39" t="inlineStr">
+      <c r="C257" s="34" t="inlineStr">
         <is>
           <t>20' x 80'</t>
         </is>
       </c>
-      <c r="D257" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E257" s="40" t="inlineStr">
+      <c r="D257" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E257" s="35" t="inlineStr">
         <is>
           <t>10 / 25</t>
         </is>
       </c>
-      <c r="F257" s="60" t="n">
+      <c r="F257" s="58" t="n">
         <v>0.4</v>
       </c>
-      <c r="G257" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H257" s="39" t="inlineStr">
+      <c r="G257" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H257" s="34" t="inlineStr">
         <is>
           <t>10/25 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="258" ht="24" customHeight="1">
-      <c r="A258" s="57" t="n">
+      <c r="A258" s="59" t="n">
         <v>46316</v>
       </c>
-      <c r="B258" s="34" t="inlineStr">
+      <c r="B258" s="39" t="inlineStr">
         <is>
           <t>Chorus @Setia Ecohill 2</t>
         </is>
       </c>
-      <c r="C258" s="34" t="inlineStr">
+      <c r="C258" s="39" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D258" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E258" s="35" t="inlineStr">
+      <c r="D258" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E258" s="40" t="inlineStr">
         <is>
           <t>77 / 99</t>
         </is>
       </c>
-      <c r="F258" s="58" t="n">
+      <c r="F258" s="60" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="G258" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H258" s="34" t="inlineStr">
+      <c r="G258" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H258" s="39" t="inlineStr">
         <is>
           <t>77/99 signed; No scope change detected</t>
         </is>
@@ -10591,7 +10591,7 @@
       <c r="F259" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="G259" s="37" t="inlineStr">
+      <c r="G259" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -10629,7 +10629,7 @@
       <c r="F260" s="58" t="n">
         <v>0.9710144927536232</v>
       </c>
-      <c r="G260" s="37" t="inlineStr">
+      <c r="G260" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -10667,7 +10667,7 @@
       <c r="F261" s="60" t="n">
         <v>0.9753086419753086</v>
       </c>
-      <c r="G261" s="37" t="inlineStr">
+      <c r="G261" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -10679,114 +10679,114 @@
       </c>
     </row>
     <row r="262" ht="24" customHeight="1">
-      <c r="A262" s="59" t="n">
+      <c r="A262" s="57" t="n">
         <v>46316</v>
       </c>
-      <c r="B262" s="39" t="inlineStr">
+      <c r="B262" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C262" s="39" t="inlineStr">
+      <c r="C262" s="34" t="inlineStr">
         <is>
           <t>20' x 60'</t>
         </is>
       </c>
-      <c r="D262" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E262" s="40" t="inlineStr">
+      <c r="D262" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E262" s="35" t="inlineStr">
         <is>
           <t>23 / 26</t>
         </is>
       </c>
-      <c r="F262" s="60" t="n">
+      <c r="F262" s="58" t="n">
         <v>0.8846153846153846</v>
       </c>
-      <c r="G262" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H262" s="39" t="inlineStr">
+      <c r="G262" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H262" s="34" t="inlineStr">
         <is>
           <t>23/26 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="263" ht="24" customHeight="1">
-      <c r="A263" s="57" t="n">
+      <c r="A263" s="59" t="n">
         <v>46316</v>
       </c>
-      <c r="B263" s="34" t="inlineStr">
+      <c r="B263" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C263" s="34" t="inlineStr">
+      <c r="C263" s="39" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D263" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E263" s="35" t="inlineStr">
+      <c r="D263" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E263" s="40" t="inlineStr">
         <is>
           <t>124 / 126</t>
         </is>
       </c>
-      <c r="F263" s="58" t="n">
+      <c r="F263" s="60" t="n">
         <v>0.9841269841269841</v>
       </c>
-      <c r="G263" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H263" s="34" t="inlineStr">
+      <c r="G263" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H263" s="39" t="inlineStr">
         <is>
           <t>124/126 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="264" ht="24" customHeight="1">
-      <c r="A264" s="59" t="n">
+      <c r="A264" s="57" t="n">
         <v>46316</v>
       </c>
-      <c r="B264" s="39" t="inlineStr">
+      <c r="B264" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C264" s="39" t="inlineStr">
+      <c r="C264" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D264" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E264" s="40" t="inlineStr">
+      <c r="D264" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E264" s="35" t="inlineStr">
         <is>
           <t>98 / 104</t>
         </is>
       </c>
-      <c r="F264" s="60" t="n">
+      <c r="F264" s="58" t="n">
         <v>0.9423076923076923</v>
       </c>
-      <c r="G264" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H264" s="39" t="inlineStr">
+      <c r="G264" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H264" s="34" t="inlineStr">
         <is>
           <t>98/104 signed; No scope change detected</t>
         </is>
@@ -10819,7 +10819,7 @@
       <c r="F265" s="58" t="n">
         <v>0.6590909090909091</v>
       </c>
-      <c r="G265" s="37" t="inlineStr">
+      <c r="G265" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -10857,7 +10857,7 @@
       <c r="F266" s="60" t="n">
         <v>0.7647058823529411</v>
       </c>
-      <c r="G266" s="37" t="inlineStr">
+      <c r="G266" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -10907,38 +10907,38 @@
       </c>
     </row>
     <row r="268" ht="24" customHeight="1">
-      <c r="A268" s="59" t="n">
+      <c r="A268" s="57" t="n">
         <v>46316</v>
       </c>
-      <c r="B268" s="39" t="inlineStr">
+      <c r="B268" s="34" t="inlineStr">
         <is>
           <t>Sapphire Residence @Diamond City</t>
         </is>
       </c>
-      <c r="C268" s="39" t="inlineStr">
+      <c r="C268" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D268" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E268" s="40" t="inlineStr">
+      <c r="D268" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E268" s="35" t="inlineStr">
         <is>
           <t>45 / 136</t>
         </is>
       </c>
-      <c r="F268" s="60" t="n">
+      <c r="F268" s="58" t="n">
         <v>0.3308823529411765</v>
       </c>
-      <c r="G268" s="37" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H268" s="39" t="inlineStr">
+      <c r="G268" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H268" s="34" t="inlineStr">
         <is>
           <t>45/136 signed; No scope change detected</t>
         </is>
@@ -10971,7 +10971,7 @@
       <c r="F269" s="58" t="n">
         <v>0.03703703703703703</v>
       </c>
-      <c r="G269" s="37" t="inlineStr">
+      <c r="G269" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -11047,7 +11047,7 @@
       <c r="F271" s="58" t="n">
         <v>0.2281879194630873</v>
       </c>
-      <c r="G271" s="37" t="inlineStr">
+      <c r="G271" s="42" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -11058,8 +11058,844 @@
         </is>
       </c>
     </row>
+    <row r="272" ht="24" customHeight="1">
+      <c r="A272" s="57" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B272" s="34" t="inlineStr">
+        <is>
+          <t>Amani Gallery Homes</t>
+        </is>
+      </c>
+      <c r="C272" s="34" t="inlineStr">
+        <is>
+          <t>20' x 70' / 20' x 72'</t>
+        </is>
+      </c>
+      <c r="D272" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E272" s="35" t="inlineStr">
+        <is>
+          <t>74 / 81</t>
+        </is>
+      </c>
+      <c r="F272" s="58" t="n">
+        <v>0.9135802469135802</v>
+      </c>
+      <c r="G272" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H272" s="34" t="inlineStr">
+        <is>
+          <t>74/81 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="24" customHeight="1">
+      <c r="A273" s="57" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B273" s="34" t="inlineStr">
+        <is>
+          <t>Balau Homes 2A</t>
+        </is>
+      </c>
+      <c r="C273" s="34" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D273" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E273" s="35" t="inlineStr">
+        <is>
+          <t>69 / 113</t>
+        </is>
+      </c>
+      <c r="F273" s="58" t="n">
+        <v>0.6106194690265486</v>
+      </c>
+      <c r="G273" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H273" s="34" t="inlineStr">
+        <is>
+          <t>69/113 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="24" customHeight="1">
+      <c r="A274" s="57" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B274" s="34" t="inlineStr">
+        <is>
+          <t>Balau Homes 2C</t>
+        </is>
+      </c>
+      <c r="C274" s="34" t="inlineStr">
+        <is>
+          <t>22' x 70'</t>
+        </is>
+      </c>
+      <c r="D274" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E274" s="35" t="inlineStr">
+        <is>
+          <t>22 / 48</t>
+        </is>
+      </c>
+      <c r="F274" s="58" t="n">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="G274" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H274" s="34" t="inlineStr">
+        <is>
+          <t>22/48 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="24" customHeight="1">
+      <c r="A275" s="57" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B275" s="34" t="inlineStr">
+        <is>
+          <t>Banyan @Setia Ecohill 2</t>
+        </is>
+      </c>
+      <c r="C275" s="34" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D275" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E275" s="35" t="inlineStr">
+        <is>
+          <t>71 / 113</t>
+        </is>
+      </c>
+      <c r="F275" s="58" t="n">
+        <v>0.6283185840707964</v>
+      </c>
+      <c r="G275" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H275" s="51" t="inlineStr">
+        <is>
+          <t>71/113 signed; Under revised scope since 08 Jun 2026 (99 → 113); review</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="24" customHeight="1">
+      <c r="A276" s="59" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B276" s="39" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C276" s="39" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D276" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E276" s="40" t="inlineStr">
+        <is>
+          <t>46 / 46</t>
+        </is>
+      </c>
+      <c r="F276" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G276" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H276" s="39" t="inlineStr">
+        <is>
+          <t>46/46 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="24" customHeight="1">
+      <c r="A277" s="57" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B277" s="34" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C277" s="34" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D277" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E277" s="35" t="inlineStr">
+        <is>
+          <t>56 / 56</t>
+        </is>
+      </c>
+      <c r="F277" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G277" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H277" s="34" t="inlineStr">
+        <is>
+          <t>56/56 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="24" customHeight="1">
+      <c r="A278" s="59" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B278" s="39" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C278" s="39" t="inlineStr">
+        <is>
+          <t>20' x 75'</t>
+        </is>
+      </c>
+      <c r="D278" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E278" s="40" t="inlineStr">
+        <is>
+          <t>25 / 25</t>
+        </is>
+      </c>
+      <c r="F278" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G278" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H278" s="39" t="inlineStr">
+        <is>
+          <t>25/25 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="24" customHeight="1">
+      <c r="A279" s="57" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B279" s="34" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C279" s="34" t="inlineStr">
+        <is>
+          <t>20' x 80'</t>
+        </is>
+      </c>
+      <c r="D279" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E279" s="35" t="inlineStr">
+        <is>
+          <t>10 / 25</t>
+        </is>
+      </c>
+      <c r="F279" s="58" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G279" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H279" s="34" t="inlineStr">
+        <is>
+          <t>10/25 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="24" customHeight="1">
+      <c r="A280" s="57" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B280" s="34" t="inlineStr">
+        <is>
+          <t>Chorus @Setia Ecohill 2</t>
+        </is>
+      </c>
+      <c r="C280" s="34" t="inlineStr">
+        <is>
+          <t>22' x 70'</t>
+        </is>
+      </c>
+      <c r="D280" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E280" s="35" t="inlineStr">
+        <is>
+          <t>77 / 99</t>
+        </is>
+      </c>
+      <c r="F280" s="58" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="G280" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H280" s="34" t="inlineStr">
+        <is>
+          <t>77/99 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="24" customHeight="1">
+      <c r="A281" s="57" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B281" s="34" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C281" s="34" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D281" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E281" s="35" t="inlineStr">
+        <is>
+          <t>111 / 111</t>
+        </is>
+      </c>
+      <c r="F281" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G281" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H281" s="34" t="inlineStr">
+        <is>
+          <t>111/111 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="24" customHeight="1">
+      <c r="A282" s="59" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B282" s="39" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C282" s="39" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D282" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E282" s="40" t="inlineStr">
+        <is>
+          <t>134 / 138</t>
+        </is>
+      </c>
+      <c r="F282" s="60" t="n">
+        <v>0.9710144927536232</v>
+      </c>
+      <c r="G282" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H282" s="39" t="inlineStr">
+        <is>
+          <t>134/138 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="24" customHeight="1">
+      <c r="A283" s="57" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B283" s="34" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C283" s="34" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D283" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E283" s="35" t="inlineStr">
+        <is>
+          <t>79 / 81</t>
+        </is>
+      </c>
+      <c r="F283" s="58" t="n">
+        <v>0.9753086419753086</v>
+      </c>
+      <c r="G283" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H283" s="34" t="inlineStr">
+        <is>
+          <t>79/81 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="24" customHeight="1">
+      <c r="A284" s="59" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B284" s="39" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="C284" s="39" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D284" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E284" s="40" t="inlineStr">
+        <is>
+          <t>23 / 26</t>
+        </is>
+      </c>
+      <c r="F284" s="60" t="n">
+        <v>0.8846153846153846</v>
+      </c>
+      <c r="G284" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H284" s="39" t="inlineStr">
+        <is>
+          <t>23/26 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="24" customHeight="1">
+      <c r="A285" s="57" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B285" s="34" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="C285" s="34" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D285" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E285" s="35" t="inlineStr">
+        <is>
+          <t>124 / 126</t>
+        </is>
+      </c>
+      <c r="F285" s="58" t="n">
+        <v>0.9841269841269841</v>
+      </c>
+      <c r="G285" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H285" s="34" t="inlineStr">
+        <is>
+          <t>124/126 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="24" customHeight="1">
+      <c r="A286" s="59" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B286" s="39" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="C286" s="39" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D286" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E286" s="40" t="inlineStr">
+        <is>
+          <t>98 / 104</t>
+        </is>
+      </c>
+      <c r="F286" s="60" t="n">
+        <v>0.9423076923076923</v>
+      </c>
+      <c r="G286" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H286" s="39" t="inlineStr">
+        <is>
+          <t>98/104 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="24" customHeight="1">
+      <c r="A287" s="59" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B287" s="39" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 3</t>
+        </is>
+      </c>
+      <c r="C287" s="39" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D287" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E287" s="40" t="inlineStr">
+        <is>
+          <t>29 / 44</t>
+        </is>
+      </c>
+      <c r="F287" s="60" t="n">
+        <v>0.6590909090909091</v>
+      </c>
+      <c r="G287" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H287" s="39" t="inlineStr">
+        <is>
+          <t>29/44 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="24" customHeight="1">
+      <c r="A288" s="57" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B288" s="34" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 3</t>
+        </is>
+      </c>
+      <c r="C288" s="34" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D288" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E288" s="35" t="inlineStr">
+        <is>
+          <t>66 / 85</t>
+        </is>
+      </c>
+      <c r="F288" s="58" t="n">
+        <v>0.7764705882352941</v>
+      </c>
+      <c r="G288" s="43" t="inlineStr">
+        <is>
+          <t>+1 signed · +1.2 pp</t>
+        </is>
+      </c>
+      <c r="H288" s="34" t="inlineStr">
+        <is>
+          <t>66/85 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="24" customHeight="1">
+      <c r="A289" s="59" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B289" s="39" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 3</t>
+        </is>
+      </c>
+      <c r="C289" s="39" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D289" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E289" s="40" t="inlineStr">
+        <is>
+          <t>25 / 102</t>
+        </is>
+      </c>
+      <c r="F289" s="60" t="n">
+        <v>0.2450980392156863</v>
+      </c>
+      <c r="G289" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H289" s="39" t="inlineStr">
+        <is>
+          <t>25/102 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="24" customHeight="1">
+      <c r="A290" s="59" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B290" s="39" t="inlineStr">
+        <is>
+          <t>Sapphire Residence @Diamond City</t>
+        </is>
+      </c>
+      <c r="C290" s="39" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D290" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E290" s="40" t="inlineStr">
+        <is>
+          <t>45 / 136</t>
+        </is>
+      </c>
+      <c r="F290" s="60" t="n">
+        <v>0.3308823529411765</v>
+      </c>
+      <c r="G290" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H290" s="39" t="inlineStr">
+        <is>
+          <t>45/136 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="24" customHeight="1">
+      <c r="A291" s="57" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B291" s="34" t="inlineStr">
+        <is>
+          <t>Springvale Sempurna Heights</t>
+        </is>
+      </c>
+      <c r="C291" s="34" t="inlineStr">
+        <is>
+          <t>Group A · front-kitchen layout</t>
+        </is>
+      </c>
+      <c r="D291" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E291" s="35" t="inlineStr">
+        <is>
+          <t>1 / 27</t>
+        </is>
+      </c>
+      <c r="F291" s="58" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="G291" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H291" s="34" t="inlineStr">
+        <is>
+          <t>1/27 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="24" customHeight="1">
+      <c r="A292" s="59" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B292" s="39" t="inlineStr">
+        <is>
+          <t>Springvale Sempurna Heights</t>
+        </is>
+      </c>
+      <c r="C292" s="39" t="inlineStr">
+        <is>
+          <t>Group B · rear-kitchen layout</t>
+        </is>
+      </c>
+      <c r="D292" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E292" s="40" t="inlineStr">
+        <is>
+          <t>161 / 346</t>
+        </is>
+      </c>
+      <c r="F292" s="60" t="n">
+        <v>0.4653179190751445</v>
+      </c>
+      <c r="G292" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H292" s="51" t="inlineStr">
+        <is>
+          <t>161/346 signed; Under revised scope since 21 Oct 2026 (308 → 346); review</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="24" customHeight="1">
+      <c r="A293" s="59" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B293" s="39" t="inlineStr">
+        <is>
+          <t>Zinnia Residences</t>
+        </is>
+      </c>
+      <c r="C293" s="39" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D293" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E293" s="40" t="inlineStr">
+        <is>
+          <t>34 / 149</t>
+        </is>
+      </c>
+      <c r="F293" s="60" t="n">
+        <v>0.2281879194630873</v>
+      </c>
+      <c r="G293" s="42" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H293" s="39" t="inlineStr">
+        <is>
+          <t>34/149 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:A271"/>
+  <autoFilter ref="A3:A293"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
@@ -12125,7 +12961,7 @@
       </c>
       <c r="R14" s="26" t="inlineStr">
         <is>
-          <t>76% Signed (65/85 units)</t>
+          <t>78% Signed (66/85 units)</t>
         </is>
       </c>
       <c r="S14" s="27" t="inlineStr">
@@ -12162,112 +12998,112 @@
       </c>
       <c r="B15" s="28" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 21 Oct; over 3 day(s))</t>
+          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
         </is>
       </c>
       <c r="C15" s="28" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 21 Oct; over 3 day(s))</t>
+          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
         </is>
       </c>
       <c r="D15" s="28" t="inlineStr">
         <is>
-          <t>+1 signed (18 Oct → 21 Oct; over 3 day(s))</t>
+          <t>+1 signed (18 Oct → 22 Oct; over 4 day(s))</t>
         </is>
       </c>
       <c r="E15" s="28" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 21 Oct; over 3 day(s))</t>
+          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
         </is>
       </c>
       <c r="F15" s="29" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 21 Oct; over 3 day(s))</t>
+          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
         </is>
       </c>
       <c r="G15" s="30" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 21 Oct; over 3 day(s))</t>
+          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
         </is>
       </c>
       <c r="H15" s="30" t="inlineStr">
         <is>
-          <t>+1 signed (18 Oct → 21 Oct; over 3 day(s))</t>
+          <t>+1 signed (18 Oct → 22 Oct; over 4 day(s))</t>
         </is>
       </c>
       <c r="I15" s="31" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 21 Oct; over 3 day(s))</t>
+          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
         </is>
       </c>
       <c r="J15" s="28" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 21 Oct; over 3 day(s))</t>
+          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
         </is>
       </c>
       <c r="K15" s="29" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 21 Oct; over 3 day(s))</t>
+          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
         </is>
       </c>
       <c r="L15" s="30" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 21 Oct; over 3 day(s))</t>
+          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
         </is>
       </c>
       <c r="M15" s="31" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 21 Oct; over 3 day(s))</t>
+          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
         </is>
       </c>
       <c r="N15" s="29" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 21 Oct; over 3 day(s))</t>
+          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
         </is>
       </c>
       <c r="O15" s="30" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 21 Oct; over 3 day(s))</t>
+          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
         </is>
       </c>
       <c r="P15" s="31" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 21 Oct; over 3 day(s))</t>
+          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
         </is>
       </c>
       <c r="Q15" s="29" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 21 Oct; over 3 day(s))</t>
+          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
         </is>
       </c>
       <c r="R15" s="30" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 21 Oct; over 3 day(s))</t>
+          <t>+1 signed (18 Oct → 22 Oct; over 4 day(s))</t>
         </is>
       </c>
       <c r="S15" s="31" t="inlineStr">
         <is>
-          <t>+1 signed (18 Oct → 21 Oct; over 3 day(s))</t>
+          <t>+1 signed (18 Oct → 22 Oct; over 4 day(s))</t>
         </is>
       </c>
       <c r="T15" s="28" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 21 Oct; over 3 day(s))</t>
+          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
         </is>
       </c>
       <c r="U15" s="29" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 21 Oct; over 3 day(s))</t>
+          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
         </is>
       </c>
       <c r="V15" s="32" t="inlineStr">
         <is>
-          <t>⚠ Scope changed (308 → 346); 0 signed change; -5.7 pp (18 Oct → 21 Oct; over 3 day(s))</t>
+          <t>⚠ Scope changed (308 → 346); 0 signed change; -5.7 pp (18 Oct → 22 Oct; over 4 day(s))</t>
         </is>
       </c>
       <c r="W15" s="28" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 21 Oct; over 3 day(s))</t>
+          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
         </is>
       </c>
     </row>
@@ -12582,12 +13418,12 @@
           <t>Balau Homes 2A</t>
         </is>
       </c>
-      <c r="B4" s="39" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>Pemaju: Boustead</t>
         </is>
       </c>
-      <c r="C4" s="39" t="inlineStr">
+      <c r="C4" s="34" t="inlineStr">
         <is>
           <t>20094-4
 MUTIARA HILLS</t>
@@ -12605,12 +13441,12 @@
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="B5" s="34" t="inlineStr">
+      <c r="B5" s="39" t="inlineStr">
         <is>
           <t>Pemaju: Boustead</t>
         </is>
       </c>
-      <c r="C5" s="34" t="inlineStr">
+      <c r="C5" s="39" t="inlineStr">
         <is>
           <t>20094-5
 MUTIARA HILLS, SEMENYIH</t>
@@ -12628,12 +13464,12 @@
           <t>Springvale Sempurna Heights</t>
         </is>
       </c>
-      <c r="B6" s="39" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>springvale</t>
         </is>
       </c>
-      <c r="C6" s="39" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>19321-4
 SPRINGVALE SEMPURNA HEIGHT</t>
@@ -12651,12 +13487,12 @@
           <t>Zinnia Residences</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>Pemaju: crimson villa</t>
         </is>
       </c>
-      <c r="C7" s="34" t="inlineStr">
+      <c r="C7" s="39" t="inlineStr">
         <is>
           <t>19959-3
 TAMAN AKASIA</t>
@@ -12674,12 +13510,12 @@
           <t>M Legasi Phase 1</t>
         </is>
       </c>
-      <c r="B8" s="39" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>m legasi</t>
         </is>
       </c>
-      <c r="C8" s="39" t="inlineStr">
+      <c r="C8" s="34" t="inlineStr">
         <is>
           <t>30897-1
 M LEGASI</t>
@@ -12697,12 +13533,12 @@
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="B9" s="34" t="inlineStr">
+      <c r="B9" s="39" t="inlineStr">
         <is>
           <t>m legasi</t>
         </is>
       </c>
-      <c r="C9" s="34" t="inlineStr">
+      <c r="C9" s="39" t="inlineStr">
         <is>
           <t>30897-2
 M LEGASI</t>
@@ -12720,12 +13556,12 @@
           <t>M Legasi Phase 3</t>
         </is>
       </c>
-      <c r="B10" s="39" t="inlineStr">
+      <c r="B10" s="34" t="inlineStr">
         <is>
           <t>m legasi</t>
         </is>
       </c>
-      <c r="C10" s="39" t="inlineStr">
+      <c r="C10" s="34" t="inlineStr">
         <is>
           <t>30897-3
 M LEGASI</t>
@@ -12743,12 +13579,12 @@
           <t>Sapphire Residence @Diamond City</t>
         </is>
       </c>
-      <c r="B11" s="34" t="inlineStr">
+      <c r="B11" s="39" t="inlineStr">
         <is>
           <t>sapphire</t>
         </is>
       </c>
-      <c r="C11" s="34" t="inlineStr">
+      <c r="C11" s="39" t="inlineStr">
         <is>
           <t>13170-7
 SAPPHIRE RESIDENCE</t>
@@ -12766,12 +13602,12 @@
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="B12" s="39" t="inlineStr">
+      <c r="B12" s="34" t="inlineStr">
         <is>
           <t>birchpark</t>
         </is>
       </c>
-      <c r="C12" s="39" t="inlineStr">
+      <c r="C12" s="34" t="inlineStr">
         <is>
           <t>19150-17
 BIRCHPARK</t>
@@ -12789,12 +13625,12 @@
           <t>Chorus @Setia Ecohill 2</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="39" t="inlineStr">
         <is>
           <t>ecohill</t>
         </is>
       </c>
-      <c r="C13" s="34" t="inlineStr">
+      <c r="C13" s="39" t="inlineStr">
         <is>
           <t>14421-21
 SETIA ECOHILL 2</t>
@@ -12812,12 +13648,12 @@
           <t>Banyan @Setia Ecohill 2</t>
         </is>
       </c>
-      <c r="B14" s="39" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>ecohill</t>
         </is>
       </c>
-      <c r="C14" s="39" t="inlineStr">
+      <c r="C14" s="34" t="inlineStr">
         <is>
           <t>14421-22
 SETIA ECOHILL 2</t>
@@ -12835,12 +13671,12 @@
           <t>Amani Gallery Homes</t>
         </is>
       </c>
-      <c r="B15" s="34" t="inlineStr">
+      <c r="B15" s="39" t="inlineStr">
         <is>
           <t>amani</t>
         </is>
       </c>
-      <c r="C15" s="34" t="inlineStr">
+      <c r="C15" s="39" t="inlineStr">
         <is>
           <t>6868-20
 GALLERY HOMES - AMANI</t>
@@ -12858,17 +13694,17 @@
           <t>Majestic Flora</t>
         </is>
       </c>
-      <c r="B16" s="39" t="inlineStr">
+      <c r="B16" s="34" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C16" s="39" t="inlineStr">
+      <c r="C16" s="34" t="inlineStr">
         <is>
           <t>No TEDUH code recorded</t>
         </is>
       </c>
-      <c r="D16" s="39" t="inlineStr"/>
+      <c r="D16" s="34" t="inlineStr"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="65" t="inlineStr">
@@ -12876,17 +13712,17 @@
           <t>Astrea @Eco Radiance</t>
         </is>
       </c>
-      <c r="B17" s="34" t="inlineStr">
+      <c r="B17" s="39" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C17" s="34" t="inlineStr">
+      <c r="C17" s="39" t="inlineStr">
         <is>
           <t>No TEDUH code recorded</t>
         </is>
       </c>
-      <c r="D17" s="34" t="inlineStr"/>
+      <c r="D17" s="39" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Broga_Weekly_Tracking.xlsx
+++ b/Broga_Weekly_Tracking.xlsx
@@ -12,7 +12,7 @@
     <sheet name="TEDUH Search Reference" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Snapshot History'!$A$3:$A$293</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Snapshot History'!$A$3:$A$315</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Snapshot History'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Oct 2026'!$1:$3</definedName>
   </definedNames>
@@ -126,12 +126,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00F7F8F4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F7F8F4"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -473,16 +473,16 @@
     <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -850,7 +850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H293"/>
+  <dimension ref="A1:H315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -985,36 +985,36 @@
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="59" t="n">
+      <c r="A6" s="57" t="n">
         <v>45582</v>
       </c>
-      <c r="B6" s="39" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C6" s="39" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D6" s="40" t="inlineStr">
+      <c r="D6" s="35" t="inlineStr">
         <is>
           <t>Booked</t>
         </is>
       </c>
-      <c r="E6" s="40" t="inlineStr">
+      <c r="E6" s="35" t="inlineStr">
         <is>
           <t>— / 48</t>
         </is>
       </c>
-      <c r="F6" s="60" t="n"/>
-      <c r="G6" s="42" t="inlineStr">
+      <c r="F6" s="58" t="n"/>
+      <c r="G6" s="37" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="H6" s="39" t="inlineStr">
+      <c r="H6" s="34" t="inlineStr">
         <is>
           <t>8% Booked (4/48 units); Non-signed status retained for audit; excluded from signed trend</t>
         </is>
@@ -1057,72 +1057,72 @@
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="57" t="n">
+      <c r="A8" s="59" t="n">
         <v>45625</v>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="39" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C8" s="34" t="inlineStr">
+      <c r="C8" s="39" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D8" s="35" t="inlineStr">
+      <c r="D8" s="40" t="inlineStr">
         <is>
           <t>Booked</t>
         </is>
       </c>
-      <c r="E8" s="35" t="inlineStr">
+      <c r="E8" s="40" t="inlineStr">
         <is>
           <t>— / 48</t>
         </is>
       </c>
-      <c r="F8" s="58" t="n"/>
-      <c r="G8" s="37" t="inlineStr">
+      <c r="F8" s="60" t="n"/>
+      <c r="G8" s="42" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="H8" s="34" t="inlineStr">
+      <c r="H8" s="39" t="inlineStr">
         <is>
           <t>15% Booked (7/48 units); Non-signed status retained for audit; excluded from signed trend</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="57" t="n">
+      <c r="A9" s="59" t="n">
         <v>45733</v>
       </c>
-      <c r="B9" s="34" t="inlineStr">
+      <c r="B9" s="39" t="inlineStr">
         <is>
           <t>Amani Gallery Homes</t>
         </is>
       </c>
-      <c r="C9" s="34" t="inlineStr">
+      <c r="C9" s="39" t="inlineStr">
         <is>
           <t>20' x 70' / 20' x 72'</t>
         </is>
       </c>
-      <c r="D9" s="35" t="inlineStr">
+      <c r="D9" s="40" t="inlineStr">
         <is>
           <t>Booked</t>
         </is>
       </c>
-      <c r="E9" s="35" t="inlineStr">
+      <c r="E9" s="40" t="inlineStr">
         <is>
           <t>— / 81</t>
         </is>
       </c>
-      <c r="F9" s="58" t="n"/>
-      <c r="G9" s="37" t="inlineStr">
+      <c r="F9" s="60" t="n"/>
+      <c r="G9" s="42" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="H9" s="34" t="inlineStr">
+      <c r="H9" s="39" t="inlineStr">
         <is>
           <t>11% Booked (9/81 units); Non-signed status retained for audit; excluded from signed trend</t>
         </is>
@@ -1165,36 +1165,36 @@
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="59" t="n">
+      <c r="A11" s="57" t="n">
         <v>45733</v>
       </c>
-      <c r="B11" s="39" t="inlineStr">
+      <c r="B11" s="34" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C11" s="39" t="inlineStr">
+      <c r="C11" s="34" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D11" s="40" t="inlineStr">
+      <c r="D11" s="35" t="inlineStr">
         <is>
           <t>Booked</t>
         </is>
       </c>
-      <c r="E11" s="40" t="inlineStr">
+      <c r="E11" s="35" t="inlineStr">
         <is>
           <t>— / 48</t>
         </is>
       </c>
-      <c r="F11" s="60" t="n"/>
-      <c r="G11" s="42" t="inlineStr">
+      <c r="F11" s="58" t="n"/>
+      <c r="G11" s="37" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="H11" s="39" t="inlineStr">
+      <c r="H11" s="34" t="inlineStr">
         <is>
           <t>15% Booked (7/48 units); Non-signed status retained for audit; excluded from signed trend</t>
         </is>
@@ -1277,36 +1277,36 @@
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="57" t="n">
+      <c r="A14" s="59" t="n">
         <v>45889</v>
       </c>
-      <c r="B14" s="34" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C14" s="34" t="inlineStr">
+      <c r="C14" s="39" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D14" s="35" t="inlineStr">
+      <c r="D14" s="40" t="inlineStr">
         <is>
           <t>Booked</t>
         </is>
       </c>
-      <c r="E14" s="35" t="inlineStr">
+      <c r="E14" s="40" t="inlineStr">
         <is>
           <t>— / 48</t>
         </is>
       </c>
-      <c r="F14" s="58" t="n"/>
-      <c r="G14" s="37" t="inlineStr">
+      <c r="F14" s="60" t="n"/>
+      <c r="G14" s="42" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="H14" s="34" t="inlineStr">
+      <c r="H14" s="39" t="inlineStr">
         <is>
           <t>50% Booked (24/48 units); Non-signed status retained for audit; excluded from signed trend</t>
         </is>
@@ -1579,72 +1579,72 @@
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="59" t="n">
+      <c r="A22" s="57" t="n">
         <v>45911</v>
       </c>
-      <c r="B22" s="39" t="inlineStr">
+      <c r="B22" s="34" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C22" s="39" t="inlineStr">
+      <c r="C22" s="34" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D22" s="40" t="inlineStr">
+      <c r="D22" s="35" t="inlineStr">
         <is>
           <t>Booked</t>
         </is>
       </c>
-      <c r="E22" s="40" t="inlineStr">
+      <c r="E22" s="35" t="inlineStr">
         <is>
           <t>— / 48</t>
         </is>
       </c>
-      <c r="F22" s="60" t="n"/>
-      <c r="G22" s="42" t="inlineStr">
+      <c r="F22" s="58" t="n"/>
+      <c r="G22" s="37" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="H22" s="39" t="inlineStr">
+      <c r="H22" s="34" t="inlineStr">
         <is>
           <t>52% Booked (25/48 units); Non-signed status retained for audit; excluded from signed trend</t>
         </is>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="59" t="n">
+      <c r="A23" s="57" t="n">
         <v>45936</v>
       </c>
-      <c r="B23" s="39" t="inlineStr">
+      <c r="B23" s="34" t="inlineStr">
         <is>
           <t>Amani Gallery Homes</t>
         </is>
       </c>
-      <c r="C23" s="39" t="inlineStr">
+      <c r="C23" s="34" t="inlineStr">
         <is>
           <t>20' x 70' / 20' x 72'</t>
         </is>
       </c>
-      <c r="D23" s="40" t="inlineStr">
+      <c r="D23" s="35" t="inlineStr">
         <is>
           <t>Booked</t>
         </is>
       </c>
-      <c r="E23" s="40" t="inlineStr">
+      <c r="E23" s="35" t="inlineStr">
         <is>
           <t>— / 81</t>
         </is>
       </c>
-      <c r="F23" s="60" t="n"/>
-      <c r="G23" s="42" t="inlineStr">
+      <c r="F23" s="58" t="n"/>
+      <c r="G23" s="37" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="H23" s="39" t="inlineStr">
+      <c r="H23" s="34" t="inlineStr">
         <is>
           <t>35% Booked (28/81 units); Non-signed status retained for audit; excluded from signed trend</t>
         </is>
@@ -1677,7 +1677,7 @@
       <c r="F24" s="58" t="n">
         <v>0.3274336283185841</v>
       </c>
-      <c r="G24" s="42" t="inlineStr">
+      <c r="G24" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -1689,36 +1689,36 @@
       </c>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="57" t="n">
+      <c r="A25" s="59" t="n">
         <v>45936</v>
       </c>
-      <c r="B25" s="34" t="inlineStr">
+      <c r="B25" s="39" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C25" s="34" t="inlineStr">
+      <c r="C25" s="39" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D25" s="35" t="inlineStr">
+      <c r="D25" s="40" t="inlineStr">
         <is>
           <t>Booked</t>
         </is>
       </c>
-      <c r="E25" s="35" t="inlineStr">
+      <c r="E25" s="40" t="inlineStr">
         <is>
           <t>— / 48</t>
         </is>
       </c>
-      <c r="F25" s="58" t="n"/>
-      <c r="G25" s="37" t="inlineStr">
+      <c r="F25" s="60" t="n"/>
+      <c r="G25" s="42" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="H25" s="34" t="inlineStr">
+      <c r="H25" s="39" t="inlineStr">
         <is>
           <t>52% Booked (25/48 units); Non-signed status retained for audit; excluded from signed trend</t>
         </is>
@@ -1763,190 +1763,190 @@
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="59" t="n">
+      <c r="A27" s="57" t="n">
         <v>45936</v>
       </c>
-      <c r="B27" s="39" t="inlineStr">
+      <c r="B27" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C27" s="39" t="inlineStr">
+      <c r="C27" s="34" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D27" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E27" s="40" t="inlineStr">
+      <c r="D27" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E27" s="35" t="inlineStr">
         <is>
           <t>45 / 46</t>
         </is>
       </c>
-      <c r="F27" s="60" t="n">
+      <c r="F27" s="58" t="n">
         <v>0.9782608695652174</v>
       </c>
-      <c r="G27" s="42" t="inlineStr">
+      <c r="G27" s="37" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="H27" s="39" t="inlineStr">
+      <c r="H27" s="34" t="inlineStr">
         <is>
           <t>98% Signed (45/46 units); No earlier valid signed observation</t>
         </is>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="57" t="n">
+      <c r="A28" s="59" t="n">
         <v>45936</v>
       </c>
-      <c r="B28" s="34" t="inlineStr">
+      <c r="B28" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C28" s="34" t="inlineStr">
+      <c r="C28" s="39" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D28" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E28" s="35" t="inlineStr">
+      <c r="D28" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E28" s="40" t="inlineStr">
         <is>
           <t>47 / 56</t>
         </is>
       </c>
-      <c r="F28" s="58" t="n">
+      <c r="F28" s="60" t="n">
         <v>0.8392857142857143</v>
       </c>
-      <c r="G28" s="37" t="inlineStr">
+      <c r="G28" s="42" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="H28" s="34" t="inlineStr">
+      <c r="H28" s="39" t="inlineStr">
         <is>
           <t>84% Signed (47/56 units); No earlier valid signed observation</t>
         </is>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="59" t="n">
+      <c r="A29" s="57" t="n">
         <v>45936</v>
       </c>
-      <c r="B29" s="39" t="inlineStr">
+      <c r="B29" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C29" s="39" t="inlineStr">
+      <c r="C29" s="34" t="inlineStr">
         <is>
           <t>20' x 75'</t>
         </is>
       </c>
-      <c r="D29" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E29" s="40" t="inlineStr">
+      <c r="D29" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E29" s="35" t="inlineStr">
         <is>
           <t>13 / 25</t>
         </is>
       </c>
-      <c r="F29" s="60" t="n">
+      <c r="F29" s="58" t="n">
         <v>0.52</v>
       </c>
-      <c r="G29" s="42" t="inlineStr">
+      <c r="G29" s="37" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="H29" s="39" t="inlineStr">
+      <c r="H29" s="34" t="inlineStr">
         <is>
           <t>52% Signed (13/25 units); No earlier valid signed observation</t>
         </is>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="57" t="n">
+      <c r="A30" s="59" t="n">
         <v>45936</v>
       </c>
-      <c r="B30" s="34" t="inlineStr">
+      <c r="B30" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C30" s="34" t="inlineStr">
+      <c r="C30" s="39" t="inlineStr">
         <is>
           <t>20' x 80'</t>
         </is>
       </c>
-      <c r="D30" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E30" s="35" t="inlineStr">
+      <c r="D30" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E30" s="40" t="inlineStr">
         <is>
           <t>3 / 25</t>
         </is>
       </c>
-      <c r="F30" s="58" t="n">
+      <c r="F30" s="60" t="n">
         <v>0.12</v>
       </c>
-      <c r="G30" s="37" t="inlineStr">
+      <c r="G30" s="42" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="H30" s="34" t="inlineStr">
+      <c r="H30" s="39" t="inlineStr">
         <is>
           <t>12% Signed (3/25 units); No earlier valid signed observation</t>
         </is>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="59" t="n">
+      <c r="A31" s="57" t="n">
         <v>45936</v>
       </c>
-      <c r="B31" s="39" t="inlineStr">
+      <c r="B31" s="34" t="inlineStr">
         <is>
           <t>Chorus @Setia Ecohill 2</t>
         </is>
       </c>
-      <c r="C31" s="39" t="inlineStr">
+      <c r="C31" s="34" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D31" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E31" s="40" t="inlineStr">
+      <c r="D31" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E31" s="35" t="inlineStr">
         <is>
           <t>87 / 99</t>
         </is>
       </c>
-      <c r="F31" s="60" t="n">
+      <c r="F31" s="58" t="n">
         <v>0.8787878787878788</v>
       </c>
-      <c r="G31" s="42" t="inlineStr">
+      <c r="G31" s="37" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="H31" s="39" t="inlineStr">
+      <c r="H31" s="34" t="inlineStr">
         <is>
           <t>88% Signed (87/99 units); No earlier valid signed observation</t>
         </is>
@@ -2067,72 +2067,72 @@
       </c>
     </row>
     <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="59" t="n">
+      <c r="A35" s="57" t="n">
         <v>45936</v>
       </c>
-      <c r="B35" s="39" t="inlineStr">
+      <c r="B35" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C35" s="39" t="inlineStr">
+      <c r="C35" s="34" t="inlineStr">
         <is>
           <t>No group details</t>
         </is>
       </c>
-      <c r="D35" s="40" t="inlineStr">
+      <c r="D35" s="35" t="inlineStr">
         <is>
           <t>Yet to sign</t>
         </is>
       </c>
-      <c r="E35" s="40" t="inlineStr">
+      <c r="E35" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F35" s="60" t="n"/>
-      <c r="G35" s="42" t="inlineStr">
+      <c r="F35" s="58" t="n"/>
+      <c r="G35" s="37" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="H35" s="39" t="inlineStr">
+      <c r="H35" s="34" t="inlineStr">
         <is>
           <t>Yet to sign; Non-signed status retained for audit; excluded from signed trend</t>
         </is>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="57" t="n">
+      <c r="A36" s="59" t="n">
         <v>45936</v>
       </c>
-      <c r="B36" s="34" t="inlineStr">
+      <c r="B36" s="39" t="inlineStr">
         <is>
           <t>Sapphire Residence @Diamond City</t>
         </is>
       </c>
-      <c r="C36" s="34" t="inlineStr">
+      <c r="C36" s="39" t="inlineStr">
         <is>
           <t>No group details</t>
         </is>
       </c>
-      <c r="D36" s="35" t="inlineStr">
+      <c r="D36" s="40" t="inlineStr">
         <is>
           <t>Yet to sign</t>
         </is>
       </c>
-      <c r="E36" s="35" t="inlineStr">
+      <c r="E36" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F36" s="58" t="n"/>
-      <c r="G36" s="37" t="inlineStr">
+      <c r="F36" s="60" t="n"/>
+      <c r="G36" s="42" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="H36" s="34" t="inlineStr">
+      <c r="H36" s="39" t="inlineStr">
         <is>
           <t>Yet to sign; Non-signed status retained for audit; excluded from signed trend</t>
         </is>
@@ -2291,38 +2291,38 @@
       </c>
     </row>
     <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="59" t="n">
+      <c r="A41" s="57" t="n">
         <v>46080</v>
       </c>
-      <c r="B41" s="39" t="inlineStr">
+      <c r="B41" s="34" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C41" s="39" t="inlineStr">
+      <c r="C41" s="34" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D41" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E41" s="40" t="inlineStr">
+      <c r="D41" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E41" s="35" t="inlineStr">
         <is>
           <t>15 / 48</t>
         </is>
       </c>
-      <c r="F41" s="60" t="n">
+      <c r="F41" s="58" t="n">
         <v>0.3125</v>
       </c>
-      <c r="G41" s="42" t="inlineStr">
+      <c r="G41" s="37" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="H41" s="39" t="inlineStr">
+      <c r="H41" s="34" t="inlineStr">
         <is>
           <t>31% Signed (15/48 units); No earlier valid signed observation</t>
         </is>
@@ -2443,114 +2443,114 @@
       </c>
     </row>
     <row r="45" ht="24" customHeight="1">
-      <c r="A45" s="57" t="n">
+      <c r="A45" s="59" t="n">
         <v>46080</v>
       </c>
-      <c r="B45" s="34" t="inlineStr">
+      <c r="B45" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C45" s="34" t="inlineStr">
+      <c r="C45" s="39" t="inlineStr">
         <is>
           <t>20' x 60'</t>
         </is>
       </c>
-      <c r="D45" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E45" s="35" t="inlineStr">
+      <c r="D45" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E45" s="40" t="inlineStr">
         <is>
           <t>3 / 26</t>
         </is>
       </c>
-      <c r="F45" s="58" t="n">
+      <c r="F45" s="60" t="n">
         <v>0.1153846153846154</v>
       </c>
-      <c r="G45" s="37" t="inlineStr">
+      <c r="G45" s="42" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="H45" s="34" t="inlineStr">
+      <c r="H45" s="39" t="inlineStr">
         <is>
           <t>12% Signed (3/26 units); No earlier valid signed observation</t>
         </is>
       </c>
     </row>
     <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="59" t="n">
+      <c r="A46" s="57" t="n">
         <v>46080</v>
       </c>
-      <c r="B46" s="39" t="inlineStr">
+      <c r="B46" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C46" s="39" t="inlineStr">
+      <c r="C46" s="34" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D46" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E46" s="40" t="inlineStr">
+      <c r="D46" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E46" s="35" t="inlineStr">
         <is>
           <t>77 / 126</t>
         </is>
       </c>
-      <c r="F46" s="60" t="n">
+      <c r="F46" s="58" t="n">
         <v>0.6111111111111112</v>
       </c>
-      <c r="G46" s="42" t="inlineStr">
+      <c r="G46" s="37" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="H46" s="39" t="inlineStr">
+      <c r="H46" s="34" t="inlineStr">
         <is>
           <t>61% Signed (77/126 units); No earlier valid signed observation</t>
         </is>
       </c>
     </row>
     <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="57" t="n">
+      <c r="A47" s="59" t="n">
         <v>46080</v>
       </c>
-      <c r="B47" s="34" t="inlineStr">
+      <c r="B47" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C47" s="34" t="inlineStr">
+      <c r="C47" s="39" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D47" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E47" s="35" t="inlineStr">
+      <c r="D47" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E47" s="40" t="inlineStr">
         <is>
           <t>17 / 104</t>
         </is>
       </c>
-      <c r="F47" s="58" t="n">
+      <c r="F47" s="60" t="n">
         <v>0.1634615384615385</v>
       </c>
-      <c r="G47" s="37" t="inlineStr">
+      <c r="G47" s="42" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="H47" s="34" t="inlineStr">
+      <c r="H47" s="39" t="inlineStr">
         <is>
           <t>16% Signed (17/104 units); No earlier valid signed observation</t>
         </is>
@@ -2583,7 +2583,7 @@
       <c r="F48" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="G48" s="42" t="inlineStr">
+      <c r="G48" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -2633,38 +2633,38 @@
       </c>
     </row>
     <row r="50" ht="24" customHeight="1">
-      <c r="A50" s="57" t="n">
+      <c r="A50" s="59" t="n">
         <v>46181</v>
       </c>
-      <c r="B50" s="34" t="inlineStr">
+      <c r="B50" s="39" t="inlineStr">
         <is>
           <t>Amani Gallery Homes</t>
         </is>
       </c>
-      <c r="C50" s="34" t="inlineStr">
+      <c r="C50" s="39" t="inlineStr">
         <is>
           <t>20' x 70' / 20' x 72'</t>
         </is>
       </c>
-      <c r="D50" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E50" s="35" t="inlineStr">
+      <c r="D50" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E50" s="40" t="inlineStr">
         <is>
           <t>48 / 81</t>
         </is>
       </c>
-      <c r="F50" s="58" t="n">
+      <c r="F50" s="60" t="n">
         <v>0.5925925925925926</v>
       </c>
-      <c r="G50" s="37" t="inlineStr">
+      <c r="G50" s="42" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="H50" s="34" t="inlineStr">
+      <c r="H50" s="39" t="inlineStr">
         <is>
           <t>59% Signed (48/81 units); No earlier valid signed observation</t>
         </is>
@@ -2745,30 +2745,30 @@
       </c>
     </row>
     <row r="53" ht="24" customHeight="1">
-      <c r="A53" s="57" t="n">
+      <c r="A53" s="59" t="n">
         <v>46181</v>
       </c>
-      <c r="B53" s="34" t="inlineStr">
+      <c r="B53" s="39" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C53" s="34" t="inlineStr">
+      <c r="C53" s="39" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D53" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E53" s="35" t="inlineStr">
+      <c r="D53" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E53" s="40" t="inlineStr">
         <is>
           <t>19 / 48</t>
         </is>
       </c>
-      <c r="F53" s="58" t="n">
+      <c r="F53" s="60" t="n">
         <v>0.3958333333333333</v>
       </c>
       <c r="G53" s="43" t="inlineStr">
@@ -2776,7 +2776,7 @@
           <t>+4 signed · +8.3 pp</t>
         </is>
       </c>
-      <c r="H53" s="34" t="inlineStr">
+      <c r="H53" s="39" t="inlineStr">
         <is>
           <t>40% Signed (19/48 units); 101-day gap; not daily movement</t>
         </is>
@@ -2821,30 +2821,30 @@
       </c>
     </row>
     <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="59" t="n">
+      <c r="A55" s="57" t="n">
         <v>46181</v>
       </c>
-      <c r="B55" s="39" t="inlineStr">
+      <c r="B55" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C55" s="39" t="inlineStr">
+      <c r="C55" s="34" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D55" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E55" s="40" t="inlineStr">
+      <c r="D55" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E55" s="35" t="inlineStr">
         <is>
           <t>46 / 46</t>
         </is>
       </c>
-      <c r="F55" s="60" t="n">
+      <c r="F55" s="58" t="n">
         <v>1</v>
       </c>
       <c r="G55" s="43" t="inlineStr">
@@ -2852,37 +2852,37 @@
           <t>+1 signed · +2.2 pp</t>
         </is>
       </c>
-      <c r="H55" s="39" t="inlineStr">
+      <c r="H55" s="34" t="inlineStr">
         <is>
           <t>100% Signed (46/46 units); 245-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="56" ht="24" customHeight="1">
-      <c r="A56" s="57" t="n">
+      <c r="A56" s="59" t="n">
         <v>46181</v>
       </c>
-      <c r="B56" s="34" t="inlineStr">
+      <c r="B56" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C56" s="34" t="inlineStr">
+      <c r="C56" s="39" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D56" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E56" s="35" t="inlineStr">
+      <c r="D56" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E56" s="40" t="inlineStr">
         <is>
           <t>56 / 56</t>
         </is>
       </c>
-      <c r="F56" s="58" t="n">
+      <c r="F56" s="60" t="n">
         <v>1</v>
       </c>
       <c r="G56" s="43" t="inlineStr">
@@ -2890,37 +2890,37 @@
           <t>+9 signed · +16.1 pp</t>
         </is>
       </c>
-      <c r="H56" s="34" t="inlineStr">
+      <c r="H56" s="39" t="inlineStr">
         <is>
           <t>100% Signed (56/56 units); 245-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="57" ht="24" customHeight="1">
-      <c r="A57" s="59" t="n">
+      <c r="A57" s="57" t="n">
         <v>46181</v>
       </c>
-      <c r="B57" s="39" t="inlineStr">
+      <c r="B57" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C57" s="39" t="inlineStr">
+      <c r="C57" s="34" t="inlineStr">
         <is>
           <t>20' x 75'</t>
         </is>
       </c>
-      <c r="D57" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E57" s="40" t="inlineStr">
+      <c r="D57" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E57" s="35" t="inlineStr">
         <is>
           <t>24 / 25</t>
         </is>
       </c>
-      <c r="F57" s="60" t="n">
+      <c r="F57" s="58" t="n">
         <v>0.96</v>
       </c>
       <c r="G57" s="43" t="inlineStr">
@@ -2928,37 +2928,37 @@
           <t>+11 signed · +44.0 pp</t>
         </is>
       </c>
-      <c r="H57" s="39" t="inlineStr">
+      <c r="H57" s="34" t="inlineStr">
         <is>
           <t>96% Signed (24/25 units); 245-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="57" t="n">
+      <c r="A58" s="59" t="n">
         <v>46181</v>
       </c>
-      <c r="B58" s="34" t="inlineStr">
+      <c r="B58" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C58" s="34" t="inlineStr">
+      <c r="C58" s="39" t="inlineStr">
         <is>
           <t>20' x 80'</t>
         </is>
       </c>
-      <c r="D58" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E58" s="35" t="inlineStr">
+      <c r="D58" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E58" s="40" t="inlineStr">
         <is>
           <t>7 / 25</t>
         </is>
       </c>
-      <c r="F58" s="58" t="n">
+      <c r="F58" s="60" t="n">
         <v>0.28</v>
       </c>
       <c r="G58" s="43" t="inlineStr">
@@ -2966,37 +2966,37 @@
           <t>+4 signed · +16.0 pp</t>
         </is>
       </c>
-      <c r="H58" s="34" t="inlineStr">
+      <c r="H58" s="39" t="inlineStr">
         <is>
           <t>28% Signed (7/25 units); 245-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="59" ht="24" customHeight="1">
-      <c r="A59" s="57" t="n">
+      <c r="A59" s="59" t="n">
         <v>46181</v>
       </c>
-      <c r="B59" s="34" t="inlineStr">
+      <c r="B59" s="39" t="inlineStr">
         <is>
           <t>Chorus @Setia Ecohill 2</t>
         </is>
       </c>
-      <c r="C59" s="34" t="inlineStr">
+      <c r="C59" s="39" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D59" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E59" s="35" t="inlineStr">
+      <c r="D59" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E59" s="40" t="inlineStr">
         <is>
           <t>77 / 99</t>
         </is>
       </c>
-      <c r="F59" s="58" t="n">
+      <c r="F59" s="60" t="n">
         <v>0.7777777777777778</v>
       </c>
       <c r="G59" s="44" t="inlineStr">
@@ -3004,7 +3004,7 @@
           <t>-10 signed · -10.1 pp</t>
         </is>
       </c>
-      <c r="H59" s="34" t="inlineStr">
+      <c r="H59" s="39" t="inlineStr">
         <is>
           <t>78% Signed (77/99 units); 245-day gap; not daily movement; Signed count decreased; verify source/status correction</t>
         </is>
@@ -3075,7 +3075,7 @@
       <c r="F61" s="60" t="n">
         <v>0.9492753623188406</v>
       </c>
-      <c r="G61" s="42" t="inlineStr">
+      <c r="G61" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -3113,7 +3113,7 @@
       <c r="F62" s="58" t="n">
         <v>0.9629629629629629</v>
       </c>
-      <c r="G62" s="42" t="inlineStr">
+      <c r="G62" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -3125,30 +3125,30 @@
       </c>
     </row>
     <row r="63" ht="24" customHeight="1">
-      <c r="A63" s="59" t="n">
+      <c r="A63" s="57" t="n">
         <v>46181</v>
       </c>
-      <c r="B63" s="39" t="inlineStr">
+      <c r="B63" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C63" s="39" t="inlineStr">
+      <c r="C63" s="34" t="inlineStr">
         <is>
           <t>20' x 60'</t>
         </is>
       </c>
-      <c r="D63" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E63" s="40" t="inlineStr">
+      <c r="D63" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E63" s="35" t="inlineStr">
         <is>
           <t>17 / 26</t>
         </is>
       </c>
-      <c r="F63" s="60" t="n">
+      <c r="F63" s="58" t="n">
         <v>0.6538461538461539</v>
       </c>
       <c r="G63" s="43" t="inlineStr">
@@ -3156,37 +3156,37 @@
           <t>+14 signed · +53.8 pp</t>
         </is>
       </c>
-      <c r="H63" s="39" t="inlineStr">
+      <c r="H63" s="34" t="inlineStr">
         <is>
           <t>65% Signed (17/26 units); 101-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="64" ht="24" customHeight="1">
-      <c r="A64" s="57" t="n">
+      <c r="A64" s="59" t="n">
         <v>46181</v>
       </c>
-      <c r="B64" s="34" t="inlineStr">
+      <c r="B64" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C64" s="34" t="inlineStr">
+      <c r="C64" s="39" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D64" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E64" s="35" t="inlineStr">
+      <c r="D64" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E64" s="40" t="inlineStr">
         <is>
           <t>111 / 126</t>
         </is>
       </c>
-      <c r="F64" s="58" t="n">
+      <c r="F64" s="60" t="n">
         <v>0.8809523809523809</v>
       </c>
       <c r="G64" s="43" t="inlineStr">
@@ -3194,37 +3194,37 @@
           <t>+34 signed · +27.0 pp</t>
         </is>
       </c>
-      <c r="H64" s="34" t="inlineStr">
+      <c r="H64" s="39" t="inlineStr">
         <is>
           <t>88% Signed  (111/126 units); 101-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="65" ht="24" customHeight="1">
-      <c r="A65" s="59" t="n">
+      <c r="A65" s="57" t="n">
         <v>46181</v>
       </c>
-      <c r="B65" s="39" t="inlineStr">
+      <c r="B65" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C65" s="39" t="inlineStr">
+      <c r="C65" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D65" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E65" s="40" t="inlineStr">
+      <c r="D65" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E65" s="35" t="inlineStr">
         <is>
           <t>71 / 104</t>
         </is>
       </c>
-      <c r="F65" s="60" t="n">
+      <c r="F65" s="58" t="n">
         <v>0.6826923076923077</v>
       </c>
       <c r="G65" s="43" t="inlineStr">
@@ -3232,45 +3232,45 @@
           <t>+54 signed · +51.9 pp</t>
         </is>
       </c>
-      <c r="H65" s="39" t="inlineStr">
+      <c r="H65" s="34" t="inlineStr">
         <is>
           <t>68% Signed (71/104 units); 101-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="66" ht="24" customHeight="1">
-      <c r="A66" s="59" t="n">
+      <c r="A66" s="57" t="n">
         <v>46181</v>
       </c>
-      <c r="B66" s="39" t="inlineStr">
+      <c r="B66" s="34" t="inlineStr">
         <is>
           <t>Sapphire Residence @Diamond City</t>
         </is>
       </c>
-      <c r="C66" s="39" t="inlineStr">
+      <c r="C66" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D66" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E66" s="40" t="inlineStr">
+      <c r="D66" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E66" s="35" t="inlineStr">
         <is>
           <t>24 / 136</t>
         </is>
       </c>
-      <c r="F66" s="60" t="n">
+      <c r="F66" s="58" t="n">
         <v>0.1764705882352941</v>
       </c>
-      <c r="G66" s="42" t="inlineStr">
+      <c r="G66" s="37" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="H66" s="39" t="inlineStr">
+      <c r="H66" s="34" t="inlineStr">
         <is>
           <t>18% Signed (24/136 units); No earlier valid signed observation</t>
         </is>
@@ -3391,30 +3391,30 @@
       </c>
     </row>
     <row r="70" ht="24" customHeight="1">
-      <c r="A70" s="59" t="n">
+      <c r="A70" s="57" t="n">
         <v>46213</v>
       </c>
-      <c r="B70" s="39" t="inlineStr">
+      <c r="B70" s="34" t="inlineStr">
         <is>
           <t>Amani Gallery Homes</t>
         </is>
       </c>
-      <c r="C70" s="39" t="inlineStr">
+      <c r="C70" s="34" t="inlineStr">
         <is>
           <t>20' x 70' / 20' x 72'</t>
         </is>
       </c>
-      <c r="D70" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E70" s="40" t="inlineStr">
+      <c r="D70" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E70" s="35" t="inlineStr">
         <is>
           <t>53 / 81</t>
         </is>
       </c>
-      <c r="F70" s="60" t="n">
+      <c r="F70" s="58" t="n">
         <v>0.654320987654321</v>
       </c>
       <c r="G70" s="43" t="inlineStr">
@@ -3422,7 +3422,7 @@
           <t>+5 signed · +6.2 pp</t>
         </is>
       </c>
-      <c r="H70" s="39" t="inlineStr">
+      <c r="H70" s="34" t="inlineStr">
         <is>
           <t>65% Signed (53/81 units); 32-day gap; not daily movement</t>
         </is>
@@ -3503,38 +3503,38 @@
       </c>
     </row>
     <row r="73" ht="24" customHeight="1">
-      <c r="A73" s="59" t="n">
+      <c r="A73" s="57" t="n">
         <v>46213</v>
       </c>
-      <c r="B73" s="39" t="inlineStr">
+      <c r="B73" s="34" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C73" s="39" t="inlineStr">
+      <c r="C73" s="34" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D73" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E73" s="40" t="inlineStr">
+      <c r="D73" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E73" s="35" t="inlineStr">
         <is>
           <t>19 / 48</t>
         </is>
       </c>
-      <c r="F73" s="60" t="n">
+      <c r="F73" s="58" t="n">
         <v>0.3958333333333333</v>
       </c>
-      <c r="G73" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H73" s="39" t="inlineStr">
+      <c r="G73" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H73" s="34" t="inlineStr">
         <is>
           <t>40% Signed (19/48 units); 32-day gap; not daily movement</t>
         </is>
@@ -3567,7 +3567,7 @@
       <c r="F74" s="60" t="n">
         <v>0.6194690265486725</v>
       </c>
-      <c r="G74" s="42" t="inlineStr">
+      <c r="G74" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -3579,144 +3579,144 @@
       </c>
     </row>
     <row r="75" ht="24" customHeight="1">
-      <c r="A75" s="59" t="n">
+      <c r="A75" s="57" t="n">
         <v>46213</v>
       </c>
-      <c r="B75" s="39" t="inlineStr">
+      <c r="B75" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C75" s="39" t="inlineStr">
+      <c r="C75" s="34" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D75" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E75" s="40" t="inlineStr">
+      <c r="D75" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E75" s="35" t="inlineStr">
         <is>
           <t>46 / 46</t>
         </is>
       </c>
-      <c r="F75" s="60" t="n">
+      <c r="F75" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="G75" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H75" s="39" t="inlineStr">
+      <c r="G75" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H75" s="34" t="inlineStr">
         <is>
           <t>100% Signed (46/46 units); 32-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="76" ht="24" customHeight="1">
-      <c r="A76" s="57" t="n">
+      <c r="A76" s="59" t="n">
         <v>46213</v>
       </c>
-      <c r="B76" s="34" t="inlineStr">
+      <c r="B76" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C76" s="34" t="inlineStr">
+      <c r="C76" s="39" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D76" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E76" s="35" t="inlineStr">
+      <c r="D76" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E76" s="40" t="inlineStr">
         <is>
           <t>56 / 56</t>
         </is>
       </c>
-      <c r="F76" s="58" t="n">
+      <c r="F76" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="G76" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H76" s="34" t="inlineStr">
+      <c r="G76" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H76" s="39" t="inlineStr">
         <is>
           <t>100% Signed (56/56 units); 32-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="77" ht="24" customHeight="1">
-      <c r="A77" s="59" t="n">
+      <c r="A77" s="57" t="n">
         <v>46213</v>
       </c>
-      <c r="B77" s="39" t="inlineStr">
+      <c r="B77" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C77" s="39" t="inlineStr">
+      <c r="C77" s="34" t="inlineStr">
         <is>
           <t>20' x 75'</t>
         </is>
       </c>
-      <c r="D77" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E77" s="40" t="inlineStr">
+      <c r="D77" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E77" s="35" t="inlineStr">
         <is>
           <t>24 / 25</t>
         </is>
       </c>
-      <c r="F77" s="60" t="n">
+      <c r="F77" s="58" t="n">
         <v>0.96</v>
       </c>
-      <c r="G77" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H77" s="39" t="inlineStr">
+      <c r="G77" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H77" s="34" t="inlineStr">
         <is>
           <t>96% Signed (24/25 units); 32-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="78" ht="24" customHeight="1">
-      <c r="A78" s="57" t="n">
+      <c r="A78" s="59" t="n">
         <v>46213</v>
       </c>
-      <c r="B78" s="34" t="inlineStr">
+      <c r="B78" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C78" s="34" t="inlineStr">
+      <c r="C78" s="39" t="inlineStr">
         <is>
           <t>20' x 80'</t>
         </is>
       </c>
-      <c r="D78" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E78" s="35" t="inlineStr">
+      <c r="D78" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E78" s="40" t="inlineStr">
         <is>
           <t>8 / 25</t>
         </is>
       </c>
-      <c r="F78" s="58" t="n">
+      <c r="F78" s="60" t="n">
         <v>0.32</v>
       </c>
       <c r="G78" s="43" t="inlineStr">
@@ -3724,45 +3724,45 @@
           <t>+1 signed · +4.0 pp</t>
         </is>
       </c>
-      <c r="H78" s="34" t="inlineStr">
+      <c r="H78" s="39" t="inlineStr">
         <is>
           <t>32% Signed (8/25 units); 32-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="79" ht="24" customHeight="1">
-      <c r="A79" s="59" t="n">
+      <c r="A79" s="57" t="n">
         <v>46213</v>
       </c>
-      <c r="B79" s="39" t="inlineStr">
+      <c r="B79" s="34" t="inlineStr">
         <is>
           <t>Chorus @Setia Ecohill 2</t>
         </is>
       </c>
-      <c r="C79" s="39" t="inlineStr">
+      <c r="C79" s="34" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D79" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E79" s="40" t="inlineStr">
+      <c r="D79" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E79" s="35" t="inlineStr">
         <is>
           <t>77 / 99</t>
         </is>
       </c>
-      <c r="F79" s="60" t="n">
+      <c r="F79" s="58" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="G79" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H79" s="39" t="inlineStr">
+      <c r="G79" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H79" s="34" t="inlineStr">
         <is>
           <t>78% Signed (77/99 units); 32-day gap; not daily movement</t>
         </is>
@@ -3795,7 +3795,7 @@
       <c r="F80" s="60" t="n">
         <v>0.918918918918919</v>
       </c>
-      <c r="G80" s="42" t="inlineStr">
+      <c r="G80" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -3833,7 +3833,7 @@
       <c r="F81" s="58" t="n">
         <v>0.9492753623188406</v>
       </c>
-      <c r="G81" s="42" t="inlineStr">
+      <c r="G81" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -3871,7 +3871,7 @@
       <c r="F82" s="60" t="n">
         <v>0.9629629629629629</v>
       </c>
-      <c r="G82" s="42" t="inlineStr">
+      <c r="G82" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -3883,68 +3883,68 @@
       </c>
     </row>
     <row r="83" ht="24" customHeight="1">
-      <c r="A83" s="57" t="n">
+      <c r="A83" s="59" t="n">
         <v>46213</v>
       </c>
-      <c r="B83" s="34" t="inlineStr">
+      <c r="B83" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C83" s="34" t="inlineStr">
+      <c r="C83" s="39" t="inlineStr">
         <is>
           <t>20' x 60'</t>
         </is>
       </c>
-      <c r="D83" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E83" s="35" t="inlineStr">
+      <c r="D83" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E83" s="40" t="inlineStr">
         <is>
           <t>17 / 26</t>
         </is>
       </c>
-      <c r="F83" s="58" t="n">
+      <c r="F83" s="60" t="n">
         <v>0.6538461538461539</v>
       </c>
-      <c r="G83" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H83" s="34" t="inlineStr">
+      <c r="G83" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H83" s="39" t="inlineStr">
         <is>
           <t>65% Signed (17/26 units); 32-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="84" ht="24" customHeight="1">
-      <c r="A84" s="59" t="n">
+      <c r="A84" s="57" t="n">
         <v>46213</v>
       </c>
-      <c r="B84" s="39" t="inlineStr">
+      <c r="B84" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C84" s="39" t="inlineStr">
+      <c r="C84" s="34" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D84" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E84" s="40" t="inlineStr">
+      <c r="D84" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E84" s="35" t="inlineStr">
         <is>
           <t>116 / 126</t>
         </is>
       </c>
-      <c r="F84" s="60" t="n">
+      <c r="F84" s="58" t="n">
         <v>0.9206349206349206</v>
       </c>
       <c r="G84" s="43" t="inlineStr">
@@ -3952,37 +3952,37 @@
           <t>+5 signed · +4.0 pp</t>
         </is>
       </c>
-      <c r="H84" s="39" t="inlineStr">
+      <c r="H84" s="34" t="inlineStr">
         <is>
           <t>92% Signed  (116/126 units); 32-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="85" ht="24" customHeight="1">
-      <c r="A85" s="57" t="n">
+      <c r="A85" s="59" t="n">
         <v>46213</v>
       </c>
-      <c r="B85" s="34" t="inlineStr">
+      <c r="B85" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C85" s="34" t="inlineStr">
+      <c r="C85" s="39" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D85" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E85" s="35" t="inlineStr">
+      <c r="D85" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E85" s="40" t="inlineStr">
         <is>
           <t>89 / 104</t>
         </is>
       </c>
-      <c r="F85" s="58" t="n">
+      <c r="F85" s="60" t="n">
         <v>0.8557692307692307</v>
       </c>
       <c r="G85" s="43" t="inlineStr">
@@ -3990,7 +3990,7 @@
           <t>+18 signed · +17.3 pp</t>
         </is>
       </c>
-      <c r="H85" s="34" t="inlineStr">
+      <c r="H85" s="39" t="inlineStr">
         <is>
           <t>86% Signed (89/104 units); 32-day gap; not daily movement</t>
         </is>
@@ -4111,66 +4111,66 @@
       </c>
     </row>
     <row r="89" ht="24" customHeight="1">
-      <c r="A89" s="57" t="n">
+      <c r="A89" s="59" t="n">
         <v>46213</v>
       </c>
-      <c r="B89" s="34" t="inlineStr">
+      <c r="B89" s="39" t="inlineStr">
         <is>
           <t>Majestic Flora</t>
         </is>
       </c>
-      <c r="C89" s="34" t="inlineStr">
+      <c r="C89" s="39" t="inlineStr">
         <is>
           <t>No group details</t>
         </is>
       </c>
-      <c r="D89" s="35" t="inlineStr">
+      <c r="D89" s="40" t="inlineStr">
         <is>
           <t>Yet to sign</t>
         </is>
       </c>
-      <c r="E89" s="35" t="inlineStr">
+      <c r="E89" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F89" s="58" t="n"/>
-      <c r="G89" s="37" t="inlineStr">
+      <c r="F89" s="60" t="n"/>
+      <c r="G89" s="42" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="H89" s="34" t="inlineStr">
+      <c r="H89" s="39" t="inlineStr">
         <is>
           <t>Yet to Sign; Non-signed status retained for audit; excluded from signed trend</t>
         </is>
       </c>
     </row>
     <row r="90" ht="24" customHeight="1">
-      <c r="A90" s="57" t="n">
+      <c r="A90" s="59" t="n">
         <v>46213</v>
       </c>
-      <c r="B90" s="34" t="inlineStr">
+      <c r="B90" s="39" t="inlineStr">
         <is>
           <t>Sapphire Residence @Diamond City</t>
         </is>
       </c>
-      <c r="C90" s="34" t="inlineStr">
+      <c r="C90" s="39" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D90" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E90" s="35" t="inlineStr">
+      <c r="D90" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E90" s="40" t="inlineStr">
         <is>
           <t>30 / 136</t>
         </is>
       </c>
-      <c r="F90" s="58" t="n">
+      <c r="F90" s="60" t="n">
         <v>0.2205882352941176</v>
       </c>
       <c r="G90" s="43" t="inlineStr">
@@ -4178,7 +4178,7 @@
           <t>+6 signed · +4.4 pp</t>
         </is>
       </c>
-      <c r="H90" s="34" t="inlineStr">
+      <c r="H90" s="39" t="inlineStr">
         <is>
           <t>22% Signed (30/136 units); 32-day gap; not daily movement</t>
         </is>
@@ -4211,7 +4211,7 @@
       <c r="F91" s="60" t="n">
         <v>0.03703703703703703</v>
       </c>
-      <c r="G91" s="42" t="inlineStr">
+      <c r="G91" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -4299,30 +4299,30 @@
       </c>
     </row>
     <row r="94" ht="24" customHeight="1">
-      <c r="A94" s="57" t="n">
+      <c r="A94" s="59" t="n">
         <v>46308</v>
       </c>
-      <c r="B94" s="34" t="inlineStr">
+      <c r="B94" s="39" t="inlineStr">
         <is>
           <t>Amani Gallery Homes</t>
         </is>
       </c>
-      <c r="C94" s="34" t="inlineStr">
+      <c r="C94" s="39" t="inlineStr">
         <is>
           <t>20' x 70' / 20' x 72'</t>
         </is>
       </c>
-      <c r="D94" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E94" s="35" t="inlineStr">
+      <c r="D94" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E94" s="40" t="inlineStr">
         <is>
           <t>72 / 81</t>
         </is>
       </c>
-      <c r="F94" s="58" t="n">
+      <c r="F94" s="60" t="n">
         <v>0.8888888888888888</v>
       </c>
       <c r="G94" s="43" t="inlineStr">
@@ -4330,7 +4330,7 @@
           <t>+19 signed · +23.5 pp</t>
         </is>
       </c>
-      <c r="H94" s="34" t="inlineStr">
+      <c r="H94" s="39" t="inlineStr">
         <is>
           <t>88% Signed (72/81 units); 95-day gap; not daily movement</t>
         </is>
@@ -4399,7 +4399,7 @@
       <c r="F96" s="58" t="n">
         <v>0.6017699115044248</v>
       </c>
-      <c r="G96" s="42" t="inlineStr">
+      <c r="G96" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -4411,30 +4411,30 @@
       </c>
     </row>
     <row r="97" ht="24" customHeight="1">
-      <c r="A97" s="57" t="n">
+      <c r="A97" s="59" t="n">
         <v>46308</v>
       </c>
-      <c r="B97" s="34" t="inlineStr">
+      <c r="B97" s="39" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C97" s="34" t="inlineStr">
+      <c r="C97" s="39" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D97" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E97" s="35" t="inlineStr">
+      <c r="D97" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E97" s="40" t="inlineStr">
         <is>
           <t>21 / 48</t>
         </is>
       </c>
-      <c r="F97" s="58" t="n">
+      <c r="F97" s="60" t="n">
         <v>0.4375</v>
       </c>
       <c r="G97" s="43" t="inlineStr">
@@ -4442,7 +4442,7 @@
           <t>+2 signed · +4.2 pp</t>
         </is>
       </c>
-      <c r="H97" s="34" t="inlineStr">
+      <c r="H97" s="39" t="inlineStr">
         <is>
           <t>44% Signed (21/48 units); 95-day gap; not daily movement</t>
         </is>
@@ -4487,144 +4487,144 @@
       </c>
     </row>
     <row r="99" ht="24" customHeight="1">
-      <c r="A99" s="59" t="n">
+      <c r="A99" s="57" t="n">
         <v>46308</v>
       </c>
-      <c r="B99" s="39" t="inlineStr">
+      <c r="B99" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C99" s="39" t="inlineStr">
+      <c r="C99" s="34" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D99" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E99" s="40" t="inlineStr">
+      <c r="D99" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E99" s="35" t="inlineStr">
         <is>
           <t>46 / 46</t>
         </is>
       </c>
-      <c r="F99" s="60" t="n">
+      <c r="F99" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="G99" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H99" s="39" t="inlineStr">
+      <c r="G99" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H99" s="34" t="inlineStr">
         <is>
           <t>100% Signed (46/46 units); 95-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="100" ht="24" customHeight="1">
-      <c r="A100" s="57" t="n">
+      <c r="A100" s="59" t="n">
         <v>46308</v>
       </c>
-      <c r="B100" s="34" t="inlineStr">
+      <c r="B100" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C100" s="34" t="inlineStr">
+      <c r="C100" s="39" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D100" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E100" s="35" t="inlineStr">
+      <c r="D100" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E100" s="40" t="inlineStr">
         <is>
           <t>56 / 56</t>
         </is>
       </c>
-      <c r="F100" s="58" t="n">
+      <c r="F100" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="G100" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H100" s="34" t="inlineStr">
+      <c r="G100" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H100" s="39" t="inlineStr">
         <is>
           <t>100% Signed (56/56 units); 95-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="101" ht="24" customHeight="1">
-      <c r="A101" s="59" t="n">
+      <c r="A101" s="57" t="n">
         <v>46308</v>
       </c>
-      <c r="B101" s="39" t="inlineStr">
+      <c r="B101" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C101" s="39" t="inlineStr">
+      <c r="C101" s="34" t="inlineStr">
         <is>
           <t>20' x 75'</t>
         </is>
       </c>
-      <c r="D101" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E101" s="40" t="inlineStr">
+      <c r="D101" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E101" s="35" t="inlineStr">
         <is>
           <t>24 / 25</t>
         </is>
       </c>
-      <c r="F101" s="60" t="n">
+      <c r="F101" s="58" t="n">
         <v>0.96</v>
       </c>
-      <c r="G101" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H101" s="39" t="inlineStr">
+      <c r="G101" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H101" s="34" t="inlineStr">
         <is>
           <t>96% Signed (24/25 units); 95-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="102" ht="24" customHeight="1">
-      <c r="A102" s="57" t="n">
+      <c r="A102" s="59" t="n">
         <v>46308</v>
       </c>
-      <c r="B102" s="34" t="inlineStr">
+      <c r="B102" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C102" s="34" t="inlineStr">
+      <c r="C102" s="39" t="inlineStr">
         <is>
           <t>20' x 80'</t>
         </is>
       </c>
-      <c r="D102" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E102" s="35" t="inlineStr">
+      <c r="D102" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E102" s="40" t="inlineStr">
         <is>
           <t>10 / 25</t>
         </is>
       </c>
-      <c r="F102" s="58" t="n">
+      <c r="F102" s="60" t="n">
         <v>0.4</v>
       </c>
       <c r="G102" s="43" t="inlineStr">
@@ -4632,45 +4632,45 @@
           <t>+2 signed · +8.0 pp</t>
         </is>
       </c>
-      <c r="H102" s="34" t="inlineStr">
+      <c r="H102" s="39" t="inlineStr">
         <is>
           <t>40% Signed (10/25 units); 95-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="103" ht="24" customHeight="1">
-      <c r="A103" s="57" t="n">
+      <c r="A103" s="59" t="n">
         <v>46308</v>
       </c>
-      <c r="B103" s="34" t="inlineStr">
+      <c r="B103" s="39" t="inlineStr">
         <is>
           <t>Chorus @Setia Ecohill 2</t>
         </is>
       </c>
-      <c r="C103" s="34" t="inlineStr">
+      <c r="C103" s="39" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D103" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E103" s="35" t="inlineStr">
+      <c r="D103" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E103" s="40" t="inlineStr">
         <is>
           <t>77 / 99</t>
         </is>
       </c>
-      <c r="F103" s="58" t="n">
+      <c r="F103" s="60" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="G103" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H103" s="34" t="inlineStr">
+      <c r="G103" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H103" s="39" t="inlineStr">
         <is>
           <t>78% Signed (77/99 units); 95-day gap; not daily movement</t>
         </is>
@@ -4791,30 +4791,30 @@
       </c>
     </row>
     <row r="107" ht="24" customHeight="1">
-      <c r="A107" s="59" t="n">
+      <c r="A107" s="57" t="n">
         <v>46308</v>
       </c>
-      <c r="B107" s="39" t="inlineStr">
+      <c r="B107" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C107" s="39" t="inlineStr">
+      <c r="C107" s="34" t="inlineStr">
         <is>
           <t>20' x 60'</t>
         </is>
       </c>
-      <c r="D107" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E107" s="40" t="inlineStr">
+      <c r="D107" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E107" s="35" t="inlineStr">
         <is>
           <t>23 / 26</t>
         </is>
       </c>
-      <c r="F107" s="60" t="n">
+      <c r="F107" s="58" t="n">
         <v>0.8846153846153846</v>
       </c>
       <c r="G107" s="43" t="inlineStr">
@@ -4822,37 +4822,37 @@
           <t>+6 signed · +23.1 pp</t>
         </is>
       </c>
-      <c r="H107" s="39" t="inlineStr">
+      <c r="H107" s="34" t="inlineStr">
         <is>
           <t>88% Signed (23/26 units); 95-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="108" ht="24" customHeight="1">
-      <c r="A108" s="57" t="n">
+      <c r="A108" s="59" t="n">
         <v>46308</v>
       </c>
-      <c r="B108" s="34" t="inlineStr">
+      <c r="B108" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C108" s="34" t="inlineStr">
+      <c r="C108" s="39" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D108" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E108" s="35" t="inlineStr">
+      <c r="D108" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E108" s="40" t="inlineStr">
         <is>
           <t>124 / 126</t>
         </is>
       </c>
-      <c r="F108" s="58" t="n">
+      <c r="F108" s="60" t="n">
         <v>0.9841269841269841</v>
       </c>
       <c r="G108" s="43" t="inlineStr">
@@ -4860,37 +4860,37 @@
           <t>+8 signed · +6.3 pp</t>
         </is>
       </c>
-      <c r="H108" s="34" t="inlineStr">
+      <c r="H108" s="39" t="inlineStr">
         <is>
           <t>98% Signed  (124/126 units); 95-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="109" ht="24" customHeight="1">
-      <c r="A109" s="59" t="n">
+      <c r="A109" s="57" t="n">
         <v>46308</v>
       </c>
-      <c r="B109" s="39" t="inlineStr">
+      <c r="B109" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C109" s="39" t="inlineStr">
+      <c r="C109" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D109" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E109" s="40" t="inlineStr">
+      <c r="D109" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E109" s="35" t="inlineStr">
         <is>
           <t>98 / 104</t>
         </is>
       </c>
-      <c r="F109" s="60" t="n">
+      <c r="F109" s="58" t="n">
         <v>0.9423076923076923</v>
       </c>
       <c r="G109" s="43" t="inlineStr">
@@ -4898,7 +4898,7 @@
           <t>+9 signed · +8.7 pp</t>
         </is>
       </c>
-      <c r="H109" s="39" t="inlineStr">
+      <c r="H109" s="34" t="inlineStr">
         <is>
           <t>94% Signed (98/104 units); 95-day gap; not daily movement</t>
         </is>
@@ -5019,66 +5019,66 @@
       </c>
     </row>
     <row r="113" ht="24" customHeight="1">
-      <c r="A113" s="59" t="n">
+      <c r="A113" s="57" t="n">
         <v>46308</v>
       </c>
-      <c r="B113" s="39" t="inlineStr">
+      <c r="B113" s="34" t="inlineStr">
         <is>
           <t>Majestic Flora</t>
         </is>
       </c>
-      <c r="C113" s="39" t="inlineStr">
+      <c r="C113" s="34" t="inlineStr">
         <is>
           <t>No group details</t>
         </is>
       </c>
-      <c r="D113" s="40" t="inlineStr">
+      <c r="D113" s="35" t="inlineStr">
         <is>
           <t>Yet to sign</t>
         </is>
       </c>
-      <c r="E113" s="40" t="inlineStr">
+      <c r="E113" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F113" s="60" t="n"/>
-      <c r="G113" s="42" t="inlineStr">
+      <c r="F113" s="58" t="n"/>
+      <c r="G113" s="37" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="H113" s="39" t="inlineStr">
+      <c r="H113" s="34" t="inlineStr">
         <is>
           <t>Yet to Sign; Non-signed status retained for audit; excluded from signed trend</t>
         </is>
       </c>
     </row>
     <row r="114" ht="24" customHeight="1">
-      <c r="A114" s="59" t="n">
+      <c r="A114" s="57" t="n">
         <v>46308</v>
       </c>
-      <c r="B114" s="39" t="inlineStr">
+      <c r="B114" s="34" t="inlineStr">
         <is>
           <t>Sapphire Residence @Diamond City</t>
         </is>
       </c>
-      <c r="C114" s="39" t="inlineStr">
+      <c r="C114" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D114" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E114" s="40" t="inlineStr">
+      <c r="D114" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E114" s="35" t="inlineStr">
         <is>
           <t>45 / 136</t>
         </is>
       </c>
-      <c r="F114" s="60" t="n">
+      <c r="F114" s="58" t="n">
         <v>0.3308823529411765</v>
       </c>
       <c r="G114" s="43" t="inlineStr">
@@ -5086,7 +5086,7 @@
           <t>+15 signed · +11.0 pp</t>
         </is>
       </c>
-      <c r="H114" s="39" t="inlineStr">
+      <c r="H114" s="34" t="inlineStr">
         <is>
           <t>33% Signed (45/136 units); 95-day gap; not daily movement</t>
         </is>
@@ -5119,7 +5119,7 @@
       <c r="F115" s="60" t="n">
         <v>0.03703703703703703</v>
       </c>
-      <c r="G115" s="42" t="inlineStr">
+      <c r="G115" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -5195,7 +5195,7 @@
       <c r="F117" s="60" t="n">
         <v>0.2281879194630873</v>
       </c>
-      <c r="G117" s="42" t="inlineStr">
+      <c r="G117" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -5207,30 +5207,30 @@
       </c>
     </row>
     <row r="118" ht="24" customHeight="1">
-      <c r="A118" s="59" t="n">
+      <c r="A118" s="57" t="n">
         <v>46310</v>
       </c>
-      <c r="B118" s="39" t="inlineStr">
+      <c r="B118" s="34" t="inlineStr">
         <is>
           <t>Amani Gallery Homes</t>
         </is>
       </c>
-      <c r="C118" s="39" t="inlineStr">
+      <c r="C118" s="34" t="inlineStr">
         <is>
           <t>20' x 70' / 20' x 72'</t>
         </is>
       </c>
-      <c r="D118" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E118" s="40" t="inlineStr">
+      <c r="D118" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E118" s="35" t="inlineStr">
         <is>
           <t>74 / 81</t>
         </is>
       </c>
-      <c r="F118" s="60" t="n">
+      <c r="F118" s="58" t="n">
         <v>0.9135802469135802</v>
       </c>
       <c r="G118" s="43" t="inlineStr">
@@ -5238,7 +5238,7 @@
           <t>+2 signed · +2.5 pp</t>
         </is>
       </c>
-      <c r="H118" s="39" t="inlineStr">
+      <c r="H118" s="34" t="inlineStr">
         <is>
           <t>74/81 signed; 2-day gap; not daily movement</t>
         </is>
@@ -5271,7 +5271,7 @@
       <c r="F119" s="60" t="n">
         <v>0.6017699115044248</v>
       </c>
-      <c r="G119" s="42" t="inlineStr">
+      <c r="G119" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -5283,38 +5283,38 @@
       </c>
     </row>
     <row r="120" ht="24" customHeight="1">
-      <c r="A120" s="59" t="n">
+      <c r="A120" s="57" t="n">
         <v>46310</v>
       </c>
-      <c r="B120" s="39" t="inlineStr">
+      <c r="B120" s="34" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C120" s="39" t="inlineStr">
+      <c r="C120" s="34" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D120" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E120" s="40" t="inlineStr">
+      <c r="D120" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E120" s="35" t="inlineStr">
         <is>
           <t>21 / 48</t>
         </is>
       </c>
-      <c r="F120" s="60" t="n">
+      <c r="F120" s="58" t="n">
         <v>0.4375</v>
       </c>
-      <c r="G120" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H120" s="39" t="inlineStr">
+      <c r="G120" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H120" s="34" t="inlineStr">
         <is>
           <t>21/48 signed; 2-day gap; not daily movement</t>
         </is>
@@ -5347,7 +5347,7 @@
       <c r="F121" s="60" t="n">
         <v>0.6283185840707964</v>
       </c>
-      <c r="G121" s="42" t="inlineStr">
+      <c r="G121" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -5359,190 +5359,190 @@
       </c>
     </row>
     <row r="122" ht="24" customHeight="1">
-      <c r="A122" s="59" t="n">
+      <c r="A122" s="57" t="n">
         <v>46310</v>
       </c>
-      <c r="B122" s="39" t="inlineStr">
+      <c r="B122" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C122" s="39" t="inlineStr">
+      <c r="C122" s="34" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D122" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E122" s="40" t="inlineStr">
+      <c r="D122" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E122" s="35" t="inlineStr">
         <is>
           <t>46 / 46</t>
         </is>
       </c>
-      <c r="F122" s="60" t="n">
+      <c r="F122" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="G122" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H122" s="39" t="inlineStr">
+      <c r="G122" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H122" s="34" t="inlineStr">
         <is>
           <t>46/46 signed; 2-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="123" ht="24" customHeight="1">
-      <c r="A123" s="57" t="n">
+      <c r="A123" s="59" t="n">
         <v>46310</v>
       </c>
-      <c r="B123" s="34" t="inlineStr">
+      <c r="B123" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C123" s="34" t="inlineStr">
+      <c r="C123" s="39" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D123" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E123" s="35" t="inlineStr">
+      <c r="D123" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E123" s="40" t="inlineStr">
         <is>
           <t>56 / 56</t>
         </is>
       </c>
-      <c r="F123" s="58" t="n">
+      <c r="F123" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="G123" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H123" s="34" t="inlineStr">
+      <c r="G123" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H123" s="39" t="inlineStr">
         <is>
           <t>56/56 signed; 2-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="124" ht="24" customHeight="1">
-      <c r="A124" s="59" t="n">
+      <c r="A124" s="57" t="n">
         <v>46310</v>
       </c>
-      <c r="B124" s="39" t="inlineStr">
+      <c r="B124" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C124" s="39" t="inlineStr">
+      <c r="C124" s="34" t="inlineStr">
         <is>
           <t>20' x 75'</t>
         </is>
       </c>
-      <c r="D124" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E124" s="40" t="inlineStr">
+      <c r="D124" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E124" s="35" t="inlineStr">
         <is>
           <t>24 / 25</t>
         </is>
       </c>
-      <c r="F124" s="60" t="n">
+      <c r="F124" s="58" t="n">
         <v>0.96</v>
       </c>
-      <c r="G124" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H124" s="39" t="inlineStr">
+      <c r="G124" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H124" s="34" t="inlineStr">
         <is>
           <t>24/25 signed; 2-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="125" ht="24" customHeight="1">
-      <c r="A125" s="57" t="n">
+      <c r="A125" s="59" t="n">
         <v>46310</v>
       </c>
-      <c r="B125" s="34" t="inlineStr">
+      <c r="B125" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C125" s="34" t="inlineStr">
+      <c r="C125" s="39" t="inlineStr">
         <is>
           <t>20' x 80'</t>
         </is>
       </c>
-      <c r="D125" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E125" s="35" t="inlineStr">
+      <c r="D125" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E125" s="40" t="inlineStr">
         <is>
           <t>10 / 25</t>
         </is>
       </c>
-      <c r="F125" s="58" t="n">
+      <c r="F125" s="60" t="n">
         <v>0.4</v>
       </c>
-      <c r="G125" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H125" s="34" t="inlineStr">
+      <c r="G125" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H125" s="39" t="inlineStr">
         <is>
           <t>10/25 signed; 2-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="126" ht="24" customHeight="1">
-      <c r="A126" s="59" t="n">
+      <c r="A126" s="57" t="n">
         <v>46310</v>
       </c>
-      <c r="B126" s="39" t="inlineStr">
+      <c r="B126" s="34" t="inlineStr">
         <is>
           <t>Chorus @Setia Ecohill 2</t>
         </is>
       </c>
-      <c r="C126" s="39" t="inlineStr">
+      <c r="C126" s="34" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D126" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E126" s="40" t="inlineStr">
+      <c r="D126" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E126" s="35" t="inlineStr">
         <is>
           <t>77 / 99</t>
         </is>
       </c>
-      <c r="F126" s="60" t="n">
+      <c r="F126" s="58" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="G126" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H126" s="39" t="inlineStr">
+      <c r="G126" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H126" s="34" t="inlineStr">
         <is>
           <t>77/99 signed; 2-day gap; not daily movement</t>
         </is>
@@ -5575,7 +5575,7 @@
       <c r="F127" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="G127" s="42" t="inlineStr">
+      <c r="G127" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -5613,7 +5613,7 @@
       <c r="F128" s="58" t="n">
         <v>0.9710144927536232</v>
       </c>
-      <c r="G128" s="42" t="inlineStr">
+      <c r="G128" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -5651,7 +5651,7 @@
       <c r="F129" s="60" t="n">
         <v>0.9753086419753086</v>
       </c>
-      <c r="G129" s="42" t="inlineStr">
+      <c r="G129" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -5663,114 +5663,114 @@
       </c>
     </row>
     <row r="130" ht="24" customHeight="1">
-      <c r="A130" s="57" t="n">
+      <c r="A130" s="59" t="n">
         <v>46310</v>
       </c>
-      <c r="B130" s="34" t="inlineStr">
+      <c r="B130" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C130" s="34" t="inlineStr">
+      <c r="C130" s="39" t="inlineStr">
         <is>
           <t>20' x 60'</t>
         </is>
       </c>
-      <c r="D130" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E130" s="35" t="inlineStr">
+      <c r="D130" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E130" s="40" t="inlineStr">
         <is>
           <t>23 / 26</t>
         </is>
       </c>
-      <c r="F130" s="58" t="n">
+      <c r="F130" s="60" t="n">
         <v>0.8846153846153846</v>
       </c>
-      <c r="G130" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H130" s="34" t="inlineStr">
+      <c r="G130" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H130" s="39" t="inlineStr">
         <is>
           <t>23/26 signed; 2-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="131" ht="24" customHeight="1">
-      <c r="A131" s="59" t="n">
+      <c r="A131" s="57" t="n">
         <v>46310</v>
       </c>
-      <c r="B131" s="39" t="inlineStr">
+      <c r="B131" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C131" s="39" t="inlineStr">
+      <c r="C131" s="34" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D131" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E131" s="40" t="inlineStr">
+      <c r="D131" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E131" s="35" t="inlineStr">
         <is>
           <t>124 / 126</t>
         </is>
       </c>
-      <c r="F131" s="60" t="n">
+      <c r="F131" s="58" t="n">
         <v>0.9841269841269841</v>
       </c>
-      <c r="G131" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H131" s="39" t="inlineStr">
+      <c r="G131" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H131" s="34" t="inlineStr">
         <is>
           <t>124/126 signed; 2-day gap; not daily movement</t>
         </is>
       </c>
     </row>
     <row r="132" ht="24" customHeight="1">
-      <c r="A132" s="57" t="n">
+      <c r="A132" s="59" t="n">
         <v>46310</v>
       </c>
-      <c r="B132" s="34" t="inlineStr">
+      <c r="B132" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C132" s="34" t="inlineStr">
+      <c r="C132" s="39" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D132" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E132" s="35" t="inlineStr">
+      <c r="D132" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E132" s="40" t="inlineStr">
         <is>
           <t>98 / 104</t>
         </is>
       </c>
-      <c r="F132" s="58" t="n">
+      <c r="F132" s="60" t="n">
         <v>0.9423076923076923</v>
       </c>
-      <c r="G132" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H132" s="34" t="inlineStr">
+      <c r="G132" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H132" s="39" t="inlineStr">
         <is>
           <t>98/104 signed; 2-day gap; not daily movement</t>
         </is>
@@ -5803,7 +5803,7 @@
       <c r="F133" s="58" t="n">
         <v>0.6590909090909091</v>
       </c>
-      <c r="G133" s="42" t="inlineStr">
+      <c r="G133" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -5841,7 +5841,7 @@
       <c r="F134" s="60" t="n">
         <v>0.7411764705882353</v>
       </c>
-      <c r="G134" s="42" t="inlineStr">
+      <c r="G134" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -5891,38 +5891,38 @@
       </c>
     </row>
     <row r="136" ht="24" customHeight="1">
-      <c r="A136" s="57" t="n">
+      <c r="A136" s="59" t="n">
         <v>46310</v>
       </c>
-      <c r="B136" s="34" t="inlineStr">
+      <c r="B136" s="39" t="inlineStr">
         <is>
           <t>Sapphire Residence @Diamond City</t>
         </is>
       </c>
-      <c r="C136" s="34" t="inlineStr">
+      <c r="C136" s="39" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D136" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E136" s="35" t="inlineStr">
+      <c r="D136" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E136" s="40" t="inlineStr">
         <is>
           <t>45 / 136</t>
         </is>
       </c>
-      <c r="F136" s="58" t="n">
+      <c r="F136" s="60" t="n">
         <v>0.3308823529411765</v>
       </c>
-      <c r="G136" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H136" s="34" t="inlineStr">
+      <c r="G136" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H136" s="39" t="inlineStr">
         <is>
           <t>45/136 signed; 2-day gap; not daily movement</t>
         </is>
@@ -5955,7 +5955,7 @@
       <c r="F137" s="58" t="n">
         <v>0.03703703703703703</v>
       </c>
-      <c r="G137" s="42" t="inlineStr">
+      <c r="G137" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -6031,7 +6031,7 @@
       <c r="F139" s="58" t="n">
         <v>0.2281879194630873</v>
       </c>
-      <c r="G139" s="42" t="inlineStr">
+      <c r="G139" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -6043,38 +6043,38 @@
       </c>
     </row>
     <row r="140" ht="24" customHeight="1">
-      <c r="A140" s="57" t="n">
+      <c r="A140" s="59" t="n">
         <v>46311</v>
       </c>
-      <c r="B140" s="34" t="inlineStr">
+      <c r="B140" s="39" t="inlineStr">
         <is>
           <t>Amani Gallery Homes</t>
         </is>
       </c>
-      <c r="C140" s="34" t="inlineStr">
+      <c r="C140" s="39" t="inlineStr">
         <is>
           <t>20' x 70' / 20' x 72'</t>
         </is>
       </c>
-      <c r="D140" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E140" s="35" t="inlineStr">
+      <c r="D140" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E140" s="40" t="inlineStr">
         <is>
           <t>74 / 81</t>
         </is>
       </c>
-      <c r="F140" s="58" t="n">
+      <c r="F140" s="60" t="n">
         <v>0.9135802469135802</v>
       </c>
-      <c r="G140" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H140" s="34" t="inlineStr">
+      <c r="G140" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H140" s="39" t="inlineStr">
         <is>
           <t>74/81 signed; No scope change detected</t>
         </is>
@@ -6107,7 +6107,7 @@
       <c r="F141" s="58" t="n">
         <v>0.6017699115044248</v>
       </c>
-      <c r="G141" s="42" t="inlineStr">
+      <c r="G141" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -6119,38 +6119,38 @@
       </c>
     </row>
     <row r="142" ht="24" customHeight="1">
-      <c r="A142" s="57" t="n">
+      <c r="A142" s="59" t="n">
         <v>46311</v>
       </c>
-      <c r="B142" s="34" t="inlineStr">
+      <c r="B142" s="39" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C142" s="34" t="inlineStr">
+      <c r="C142" s="39" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D142" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E142" s="35" t="inlineStr">
+      <c r="D142" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E142" s="40" t="inlineStr">
         <is>
           <t>21 / 48</t>
         </is>
       </c>
-      <c r="F142" s="58" t="n">
+      <c r="F142" s="60" t="n">
         <v>0.4375</v>
       </c>
-      <c r="G142" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H142" s="34" t="inlineStr">
+      <c r="G142" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H142" s="39" t="inlineStr">
         <is>
           <t>21/48 signed; No scope change detected</t>
         </is>
@@ -6183,7 +6183,7 @@
       <c r="F143" s="58" t="n">
         <v>0.6283185840707964</v>
       </c>
-      <c r="G143" s="42" t="inlineStr">
+      <c r="G143" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -6195,190 +6195,190 @@
       </c>
     </row>
     <row r="144" ht="24" customHeight="1">
-      <c r="A144" s="59" t="n">
+      <c r="A144" s="57" t="n">
         <v>46311</v>
       </c>
-      <c r="B144" s="39" t="inlineStr">
+      <c r="B144" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C144" s="39" t="inlineStr">
+      <c r="C144" s="34" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D144" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E144" s="40" t="inlineStr">
+      <c r="D144" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E144" s="35" t="inlineStr">
         <is>
           <t>46 / 46</t>
         </is>
       </c>
-      <c r="F144" s="60" t="n">
+      <c r="F144" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="G144" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H144" s="39" t="inlineStr">
+      <c r="G144" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H144" s="34" t="inlineStr">
         <is>
           <t>46/46 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="145" ht="24" customHeight="1">
-      <c r="A145" s="57" t="n">
+      <c r="A145" s="59" t="n">
         <v>46311</v>
       </c>
-      <c r="B145" s="34" t="inlineStr">
+      <c r="B145" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C145" s="34" t="inlineStr">
+      <c r="C145" s="39" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D145" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E145" s="35" t="inlineStr">
+      <c r="D145" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E145" s="40" t="inlineStr">
         <is>
           <t>56 / 56</t>
         </is>
       </c>
-      <c r="F145" s="58" t="n">
+      <c r="F145" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="G145" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H145" s="34" t="inlineStr">
+      <c r="G145" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H145" s="39" t="inlineStr">
         <is>
           <t>56/56 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="146" ht="24" customHeight="1">
-      <c r="A146" s="59" t="n">
+      <c r="A146" s="57" t="n">
         <v>46311</v>
       </c>
-      <c r="B146" s="39" t="inlineStr">
+      <c r="B146" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C146" s="39" t="inlineStr">
+      <c r="C146" s="34" t="inlineStr">
         <is>
           <t>20' x 75'</t>
         </is>
       </c>
-      <c r="D146" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E146" s="40" t="inlineStr">
+      <c r="D146" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E146" s="35" t="inlineStr">
         <is>
           <t>24 / 25</t>
         </is>
       </c>
-      <c r="F146" s="60" t="n">
+      <c r="F146" s="58" t="n">
         <v>0.96</v>
       </c>
-      <c r="G146" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H146" s="39" t="inlineStr">
+      <c r="G146" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H146" s="34" t="inlineStr">
         <is>
           <t>24/25 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="147" ht="24" customHeight="1">
-      <c r="A147" s="57" t="n">
+      <c r="A147" s="59" t="n">
         <v>46311</v>
       </c>
-      <c r="B147" s="34" t="inlineStr">
+      <c r="B147" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C147" s="34" t="inlineStr">
+      <c r="C147" s="39" t="inlineStr">
         <is>
           <t>20' x 80'</t>
         </is>
       </c>
-      <c r="D147" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E147" s="35" t="inlineStr">
+      <c r="D147" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E147" s="40" t="inlineStr">
         <is>
           <t>10 / 25</t>
         </is>
       </c>
-      <c r="F147" s="58" t="n">
+      <c r="F147" s="60" t="n">
         <v>0.4</v>
       </c>
-      <c r="G147" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H147" s="34" t="inlineStr">
+      <c r="G147" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H147" s="39" t="inlineStr">
         <is>
           <t>10/25 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="148" ht="24" customHeight="1">
-      <c r="A148" s="57" t="n">
+      <c r="A148" s="59" t="n">
         <v>46311</v>
       </c>
-      <c r="B148" s="34" t="inlineStr">
+      <c r="B148" s="39" t="inlineStr">
         <is>
           <t>Chorus @Setia Ecohill 2</t>
         </is>
       </c>
-      <c r="C148" s="34" t="inlineStr">
+      <c r="C148" s="39" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D148" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E148" s="35" t="inlineStr">
+      <c r="D148" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E148" s="40" t="inlineStr">
         <is>
           <t>77 / 99</t>
         </is>
       </c>
-      <c r="F148" s="58" t="n">
+      <c r="F148" s="60" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="G148" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H148" s="34" t="inlineStr">
+      <c r="G148" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H148" s="39" t="inlineStr">
         <is>
           <t>77/99 signed; No scope change detected</t>
         </is>
@@ -6411,7 +6411,7 @@
       <c r="F149" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="G149" s="42" t="inlineStr">
+      <c r="G149" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -6449,7 +6449,7 @@
       <c r="F150" s="60" t="n">
         <v>0.9710144927536232</v>
       </c>
-      <c r="G150" s="42" t="inlineStr">
+      <c r="G150" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -6487,7 +6487,7 @@
       <c r="F151" s="58" t="n">
         <v>0.9753086419753086</v>
       </c>
-      <c r="G151" s="42" t="inlineStr">
+      <c r="G151" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -6499,114 +6499,114 @@
       </c>
     </row>
     <row r="152" ht="24" customHeight="1">
-      <c r="A152" s="59" t="n">
+      <c r="A152" s="57" t="n">
         <v>46311</v>
       </c>
-      <c r="B152" s="39" t="inlineStr">
+      <c r="B152" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C152" s="39" t="inlineStr">
+      <c r="C152" s="34" t="inlineStr">
         <is>
           <t>20' x 60'</t>
         </is>
       </c>
-      <c r="D152" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E152" s="40" t="inlineStr">
+      <c r="D152" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E152" s="35" t="inlineStr">
         <is>
           <t>23 / 26</t>
         </is>
       </c>
-      <c r="F152" s="60" t="n">
+      <c r="F152" s="58" t="n">
         <v>0.8846153846153846</v>
       </c>
-      <c r="G152" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H152" s="39" t="inlineStr">
+      <c r="G152" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H152" s="34" t="inlineStr">
         <is>
           <t>23/26 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="153" ht="24" customHeight="1">
-      <c r="A153" s="57" t="n">
+      <c r="A153" s="59" t="n">
         <v>46311</v>
       </c>
-      <c r="B153" s="34" t="inlineStr">
+      <c r="B153" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C153" s="34" t="inlineStr">
+      <c r="C153" s="39" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D153" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E153" s="35" t="inlineStr">
+      <c r="D153" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E153" s="40" t="inlineStr">
         <is>
           <t>124 / 126</t>
         </is>
       </c>
-      <c r="F153" s="58" t="n">
+      <c r="F153" s="60" t="n">
         <v>0.9841269841269841</v>
       </c>
-      <c r="G153" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H153" s="34" t="inlineStr">
+      <c r="G153" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H153" s="39" t="inlineStr">
         <is>
           <t>124/126 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="154" ht="24" customHeight="1">
-      <c r="A154" s="59" t="n">
+      <c r="A154" s="57" t="n">
         <v>46311</v>
       </c>
-      <c r="B154" s="39" t="inlineStr">
+      <c r="B154" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C154" s="39" t="inlineStr">
+      <c r="C154" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D154" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E154" s="40" t="inlineStr">
+      <c r="D154" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E154" s="35" t="inlineStr">
         <is>
           <t>98 / 104</t>
         </is>
       </c>
-      <c r="F154" s="60" t="n">
+      <c r="F154" s="58" t="n">
         <v>0.9423076923076923</v>
       </c>
-      <c r="G154" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H154" s="39" t="inlineStr">
+      <c r="G154" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H154" s="34" t="inlineStr">
         <is>
           <t>98/104 signed; No scope change detected</t>
         </is>
@@ -6639,7 +6639,7 @@
       <c r="F155" s="60" t="n">
         <v>0.6590909090909091</v>
       </c>
-      <c r="G155" s="42" t="inlineStr">
+      <c r="G155" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -6677,7 +6677,7 @@
       <c r="F156" s="58" t="n">
         <v>0.7411764705882353</v>
       </c>
-      <c r="G156" s="42" t="inlineStr">
+      <c r="G156" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -6715,7 +6715,7 @@
       <c r="F157" s="60" t="n">
         <v>0.2254901960784314</v>
       </c>
-      <c r="G157" s="42" t="inlineStr">
+      <c r="G157" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -6727,38 +6727,38 @@
       </c>
     </row>
     <row r="158" ht="24" customHeight="1">
-      <c r="A158" s="59" t="n">
+      <c r="A158" s="57" t="n">
         <v>46311</v>
       </c>
-      <c r="B158" s="39" t="inlineStr">
+      <c r="B158" s="34" t="inlineStr">
         <is>
           <t>Sapphire Residence @Diamond City</t>
         </is>
       </c>
-      <c r="C158" s="39" t="inlineStr">
+      <c r="C158" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D158" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E158" s="40" t="inlineStr">
+      <c r="D158" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E158" s="35" t="inlineStr">
         <is>
           <t>45 / 136</t>
         </is>
       </c>
-      <c r="F158" s="60" t="n">
+      <c r="F158" s="58" t="n">
         <v>0.3308823529411765</v>
       </c>
-      <c r="G158" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H158" s="39" t="inlineStr">
+      <c r="G158" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H158" s="34" t="inlineStr">
         <is>
           <t>45/136 signed; No scope change detected</t>
         </is>
@@ -6791,7 +6791,7 @@
       <c r="F159" s="58" t="n">
         <v>0.03703703703703703</v>
       </c>
-      <c r="G159" s="42" t="inlineStr">
+      <c r="G159" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -6829,7 +6829,7 @@
       <c r="F160" s="60" t="n">
         <v>0.5227272727272727</v>
       </c>
-      <c r="G160" s="42" t="inlineStr">
+      <c r="G160" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -6867,7 +6867,7 @@
       <c r="F161" s="60" t="n">
         <v>0.2281879194630873</v>
       </c>
-      <c r="G161" s="42" t="inlineStr">
+      <c r="G161" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -6879,38 +6879,38 @@
       </c>
     </row>
     <row r="162" ht="24" customHeight="1">
-      <c r="A162" s="59" t="n">
+      <c r="A162" s="57" t="n">
         <v>46312</v>
       </c>
-      <c r="B162" s="39" t="inlineStr">
+      <c r="B162" s="34" t="inlineStr">
         <is>
           <t>Amani Gallery Homes</t>
         </is>
       </c>
-      <c r="C162" s="39" t="inlineStr">
+      <c r="C162" s="34" t="inlineStr">
         <is>
           <t>20' x 70' / 20' x 72'</t>
         </is>
       </c>
-      <c r="D162" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E162" s="40" t="inlineStr">
+      <c r="D162" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E162" s="35" t="inlineStr">
         <is>
           <t>74 / 81</t>
         </is>
       </c>
-      <c r="F162" s="60" t="n">
+      <c r="F162" s="58" t="n">
         <v>0.9135802469135802</v>
       </c>
-      <c r="G162" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H162" s="39" t="inlineStr">
+      <c r="G162" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H162" s="34" t="inlineStr">
         <is>
           <t>74/81 signed; No scope change detected</t>
         </is>
@@ -6955,38 +6955,38 @@
       </c>
     </row>
     <row r="164" ht="24" customHeight="1">
-      <c r="A164" s="59" t="n">
+      <c r="A164" s="57" t="n">
         <v>46312</v>
       </c>
-      <c r="B164" s="39" t="inlineStr">
+      <c r="B164" s="34" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C164" s="39" t="inlineStr">
+      <c r="C164" s="34" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D164" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E164" s="40" t="inlineStr">
+      <c r="D164" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E164" s="35" t="inlineStr">
         <is>
           <t>21 / 48</t>
         </is>
       </c>
-      <c r="F164" s="60" t="n">
+      <c r="F164" s="58" t="n">
         <v>0.4375</v>
       </c>
-      <c r="G164" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H164" s="39" t="inlineStr">
+      <c r="G164" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H164" s="34" t="inlineStr">
         <is>
           <t>21/48 signed; No scope change detected</t>
         </is>
@@ -7019,7 +7019,7 @@
       <c r="F165" s="60" t="n">
         <v>0.6283185840707964</v>
       </c>
-      <c r="G165" s="42" t="inlineStr">
+      <c r="G165" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -7031,190 +7031,190 @@
       </c>
     </row>
     <row r="166" ht="24" customHeight="1">
-      <c r="A166" s="59" t="n">
+      <c r="A166" s="57" t="n">
         <v>46312</v>
       </c>
-      <c r="B166" s="39" t="inlineStr">
+      <c r="B166" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C166" s="39" t="inlineStr">
+      <c r="C166" s="34" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D166" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E166" s="40" t="inlineStr">
+      <c r="D166" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E166" s="35" t="inlineStr">
         <is>
           <t>46 / 46</t>
         </is>
       </c>
-      <c r="F166" s="60" t="n">
+      <c r="F166" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="G166" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H166" s="39" t="inlineStr">
+      <c r="G166" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H166" s="34" t="inlineStr">
         <is>
           <t>46/46 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="167" ht="24" customHeight="1">
-      <c r="A167" s="57" t="n">
+      <c r="A167" s="59" t="n">
         <v>46312</v>
       </c>
-      <c r="B167" s="34" t="inlineStr">
+      <c r="B167" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C167" s="34" t="inlineStr">
+      <c r="C167" s="39" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D167" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E167" s="35" t="inlineStr">
+      <c r="D167" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E167" s="40" t="inlineStr">
         <is>
           <t>56 / 56</t>
         </is>
       </c>
-      <c r="F167" s="58" t="n">
+      <c r="F167" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="G167" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H167" s="34" t="inlineStr">
+      <c r="G167" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H167" s="39" t="inlineStr">
         <is>
           <t>56/56 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="168" ht="24" customHeight="1">
-      <c r="A168" s="59" t="n">
+      <c r="A168" s="57" t="n">
         <v>46312</v>
       </c>
-      <c r="B168" s="39" t="inlineStr">
+      <c r="B168" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C168" s="39" t="inlineStr">
+      <c r="C168" s="34" t="inlineStr">
         <is>
           <t>20' x 75'</t>
         </is>
       </c>
-      <c r="D168" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E168" s="40" t="inlineStr">
+      <c r="D168" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E168" s="35" t="inlineStr">
         <is>
           <t>24 / 25</t>
         </is>
       </c>
-      <c r="F168" s="60" t="n">
+      <c r="F168" s="58" t="n">
         <v>0.96</v>
       </c>
-      <c r="G168" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H168" s="39" t="inlineStr">
+      <c r="G168" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H168" s="34" t="inlineStr">
         <is>
           <t>24/25 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="169" ht="24" customHeight="1">
-      <c r="A169" s="57" t="n">
+      <c r="A169" s="59" t="n">
         <v>46312</v>
       </c>
-      <c r="B169" s="34" t="inlineStr">
+      <c r="B169" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C169" s="34" t="inlineStr">
+      <c r="C169" s="39" t="inlineStr">
         <is>
           <t>20' x 80'</t>
         </is>
       </c>
-      <c r="D169" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E169" s="35" t="inlineStr">
+      <c r="D169" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E169" s="40" t="inlineStr">
         <is>
           <t>10 / 25</t>
         </is>
       </c>
-      <c r="F169" s="58" t="n">
+      <c r="F169" s="60" t="n">
         <v>0.4</v>
       </c>
-      <c r="G169" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H169" s="34" t="inlineStr">
+      <c r="G169" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H169" s="39" t="inlineStr">
         <is>
           <t>10/25 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="170" ht="24" customHeight="1">
-      <c r="A170" s="59" t="n">
+      <c r="A170" s="57" t="n">
         <v>46312</v>
       </c>
-      <c r="B170" s="39" t="inlineStr">
+      <c r="B170" s="34" t="inlineStr">
         <is>
           <t>Chorus @Setia Ecohill 2</t>
         </is>
       </c>
-      <c r="C170" s="39" t="inlineStr">
+      <c r="C170" s="34" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D170" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E170" s="40" t="inlineStr">
+      <c r="D170" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E170" s="35" t="inlineStr">
         <is>
           <t>77 / 99</t>
         </is>
       </c>
-      <c r="F170" s="60" t="n">
+      <c r="F170" s="58" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="G170" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H170" s="39" t="inlineStr">
+      <c r="G170" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H170" s="34" t="inlineStr">
         <is>
           <t>77/99 signed; No scope change detected</t>
         </is>
@@ -7247,7 +7247,7 @@
       <c r="F171" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="G171" s="42" t="inlineStr">
+      <c r="G171" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -7285,7 +7285,7 @@
       <c r="F172" s="58" t="n">
         <v>0.9710144927536232</v>
       </c>
-      <c r="G172" s="42" t="inlineStr">
+      <c r="G172" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -7323,7 +7323,7 @@
       <c r="F173" s="60" t="n">
         <v>0.9753086419753086</v>
       </c>
-      <c r="G173" s="42" t="inlineStr">
+      <c r="G173" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -7335,114 +7335,114 @@
       </c>
     </row>
     <row r="174" ht="24" customHeight="1">
-      <c r="A174" s="57" t="n">
+      <c r="A174" s="59" t="n">
         <v>46312</v>
       </c>
-      <c r="B174" s="34" t="inlineStr">
+      <c r="B174" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C174" s="34" t="inlineStr">
+      <c r="C174" s="39" t="inlineStr">
         <is>
           <t>20' x 60'</t>
         </is>
       </c>
-      <c r="D174" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E174" s="35" t="inlineStr">
+      <c r="D174" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E174" s="40" t="inlineStr">
         <is>
           <t>23 / 26</t>
         </is>
       </c>
-      <c r="F174" s="58" t="n">
+      <c r="F174" s="60" t="n">
         <v>0.8846153846153846</v>
       </c>
-      <c r="G174" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H174" s="34" t="inlineStr">
+      <c r="G174" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H174" s="39" t="inlineStr">
         <is>
           <t>23/26 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="175" ht="24" customHeight="1">
-      <c r="A175" s="59" t="n">
+      <c r="A175" s="57" t="n">
         <v>46312</v>
       </c>
-      <c r="B175" s="39" t="inlineStr">
+      <c r="B175" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C175" s="39" t="inlineStr">
+      <c r="C175" s="34" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D175" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E175" s="40" t="inlineStr">
+      <c r="D175" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E175" s="35" t="inlineStr">
         <is>
           <t>124 / 126</t>
         </is>
       </c>
-      <c r="F175" s="60" t="n">
+      <c r="F175" s="58" t="n">
         <v>0.9841269841269841</v>
       </c>
-      <c r="G175" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H175" s="39" t="inlineStr">
+      <c r="G175" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H175" s="34" t="inlineStr">
         <is>
           <t>124/126 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="176" ht="24" customHeight="1">
-      <c r="A176" s="57" t="n">
+      <c r="A176" s="59" t="n">
         <v>46312</v>
       </c>
-      <c r="B176" s="34" t="inlineStr">
+      <c r="B176" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C176" s="34" t="inlineStr">
+      <c r="C176" s="39" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D176" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E176" s="35" t="inlineStr">
+      <c r="D176" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E176" s="40" t="inlineStr">
         <is>
           <t>98 / 104</t>
         </is>
       </c>
-      <c r="F176" s="58" t="n">
+      <c r="F176" s="60" t="n">
         <v>0.9423076923076923</v>
       </c>
-      <c r="G176" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H176" s="34" t="inlineStr">
+      <c r="G176" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H176" s="39" t="inlineStr">
         <is>
           <t>98/104 signed; No scope change detected</t>
         </is>
@@ -7475,7 +7475,7 @@
       <c r="F177" s="58" t="n">
         <v>0.6590909090909091</v>
       </c>
-      <c r="G177" s="42" t="inlineStr">
+      <c r="G177" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -7563,38 +7563,38 @@
       </c>
     </row>
     <row r="180" ht="24" customHeight="1">
-      <c r="A180" s="57" t="n">
+      <c r="A180" s="59" t="n">
         <v>46312</v>
       </c>
-      <c r="B180" s="34" t="inlineStr">
+      <c r="B180" s="39" t="inlineStr">
         <is>
           <t>Sapphire Residence @Diamond City</t>
         </is>
       </c>
-      <c r="C180" s="34" t="inlineStr">
+      <c r="C180" s="39" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D180" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E180" s="35" t="inlineStr">
+      <c r="D180" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E180" s="40" t="inlineStr">
         <is>
           <t>45 / 136</t>
         </is>
       </c>
-      <c r="F180" s="58" t="n">
+      <c r="F180" s="60" t="n">
         <v>0.3308823529411765</v>
       </c>
-      <c r="G180" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H180" s="34" t="inlineStr">
+      <c r="G180" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H180" s="39" t="inlineStr">
         <is>
           <t>45/136 signed; No scope change detected</t>
         </is>
@@ -7627,7 +7627,7 @@
       <c r="F181" s="58" t="n">
         <v>0.03703703703703703</v>
       </c>
-      <c r="G181" s="42" t="inlineStr">
+      <c r="G181" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -7665,7 +7665,7 @@
       <c r="F182" s="60" t="n">
         <v>0.5227272727272727</v>
       </c>
-      <c r="G182" s="42" t="inlineStr">
+      <c r="G182" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -7703,7 +7703,7 @@
       <c r="F183" s="58" t="n">
         <v>0.2281879194630873</v>
       </c>
-      <c r="G183" s="42" t="inlineStr">
+      <c r="G183" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -7715,38 +7715,38 @@
       </c>
     </row>
     <row r="184" ht="24" customHeight="1">
-      <c r="A184" s="57" t="n">
+      <c r="A184" s="59" t="n">
         <v>46313</v>
       </c>
-      <c r="B184" s="34" t="inlineStr">
+      <c r="B184" s="39" t="inlineStr">
         <is>
           <t>Amani Gallery Homes</t>
         </is>
       </c>
-      <c r="C184" s="34" t="inlineStr">
+      <c r="C184" s="39" t="inlineStr">
         <is>
           <t>20' x 70' / 20' x 72'</t>
         </is>
       </c>
-      <c r="D184" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E184" s="35" t="inlineStr">
+      <c r="D184" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E184" s="40" t="inlineStr">
         <is>
           <t>74 / 81</t>
         </is>
       </c>
-      <c r="F184" s="58" t="n">
+      <c r="F184" s="60" t="n">
         <v>0.9135802469135802</v>
       </c>
-      <c r="G184" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H184" s="34" t="inlineStr">
+      <c r="G184" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H184" s="39" t="inlineStr">
         <is>
           <t>74/81 signed; No scope change detected</t>
         </is>
@@ -7779,7 +7779,7 @@
       <c r="F185" s="58" t="n">
         <v>0.6106194690265486</v>
       </c>
-      <c r="G185" s="42" t="inlineStr">
+      <c r="G185" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -7791,38 +7791,38 @@
       </c>
     </row>
     <row r="186" ht="24" customHeight="1">
-      <c r="A186" s="57" t="n">
+      <c r="A186" s="59" t="n">
         <v>46313</v>
       </c>
-      <c r="B186" s="34" t="inlineStr">
+      <c r="B186" s="39" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C186" s="34" t="inlineStr">
+      <c r="C186" s="39" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D186" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E186" s="35" t="inlineStr">
+      <c r="D186" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E186" s="40" t="inlineStr">
         <is>
           <t>21 / 48</t>
         </is>
       </c>
-      <c r="F186" s="58" t="n">
+      <c r="F186" s="60" t="n">
         <v>0.4375</v>
       </c>
-      <c r="G186" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H186" s="34" t="inlineStr">
+      <c r="G186" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H186" s="39" t="inlineStr">
         <is>
           <t>21/48 signed; No scope change detected</t>
         </is>
@@ -7855,7 +7855,7 @@
       <c r="F187" s="58" t="n">
         <v>0.6283185840707964</v>
       </c>
-      <c r="G187" s="42" t="inlineStr">
+      <c r="G187" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -7867,190 +7867,190 @@
       </c>
     </row>
     <row r="188" ht="24" customHeight="1">
-      <c r="A188" s="59" t="n">
+      <c r="A188" s="57" t="n">
         <v>46313</v>
       </c>
-      <c r="B188" s="39" t="inlineStr">
+      <c r="B188" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C188" s="39" t="inlineStr">
+      <c r="C188" s="34" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D188" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E188" s="40" t="inlineStr">
+      <c r="D188" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E188" s="35" t="inlineStr">
         <is>
           <t>46 / 46</t>
         </is>
       </c>
-      <c r="F188" s="60" t="n">
+      <c r="F188" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="G188" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H188" s="39" t="inlineStr">
+      <c r="G188" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H188" s="34" t="inlineStr">
         <is>
           <t>46/46 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="189" ht="24" customHeight="1">
-      <c r="A189" s="57" t="n">
+      <c r="A189" s="59" t="n">
         <v>46313</v>
       </c>
-      <c r="B189" s="34" t="inlineStr">
+      <c r="B189" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C189" s="34" t="inlineStr">
+      <c r="C189" s="39" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D189" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E189" s="35" t="inlineStr">
+      <c r="D189" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E189" s="40" t="inlineStr">
         <is>
           <t>56 / 56</t>
         </is>
       </c>
-      <c r="F189" s="58" t="n">
+      <c r="F189" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="G189" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H189" s="34" t="inlineStr">
+      <c r="G189" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H189" s="39" t="inlineStr">
         <is>
           <t>56/56 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="190" ht="24" customHeight="1">
-      <c r="A190" s="59" t="n">
+      <c r="A190" s="57" t="n">
         <v>46313</v>
       </c>
-      <c r="B190" s="39" t="inlineStr">
+      <c r="B190" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C190" s="39" t="inlineStr">
+      <c r="C190" s="34" t="inlineStr">
         <is>
           <t>20' x 75'</t>
         </is>
       </c>
-      <c r="D190" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E190" s="40" t="inlineStr">
+      <c r="D190" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E190" s="35" t="inlineStr">
         <is>
           <t>24 / 25</t>
         </is>
       </c>
-      <c r="F190" s="60" t="n">
+      <c r="F190" s="58" t="n">
         <v>0.96</v>
       </c>
-      <c r="G190" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H190" s="39" t="inlineStr">
+      <c r="G190" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H190" s="34" t="inlineStr">
         <is>
           <t>24/25 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="191" ht="24" customHeight="1">
-      <c r="A191" s="57" t="n">
+      <c r="A191" s="59" t="n">
         <v>46313</v>
       </c>
-      <c r="B191" s="34" t="inlineStr">
+      <c r="B191" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C191" s="34" t="inlineStr">
+      <c r="C191" s="39" t="inlineStr">
         <is>
           <t>20' x 80'</t>
         </is>
       </c>
-      <c r="D191" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E191" s="35" t="inlineStr">
+      <c r="D191" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E191" s="40" t="inlineStr">
         <is>
           <t>10 / 25</t>
         </is>
       </c>
-      <c r="F191" s="58" t="n">
+      <c r="F191" s="60" t="n">
         <v>0.4</v>
       </c>
-      <c r="G191" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H191" s="34" t="inlineStr">
+      <c r="G191" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H191" s="39" t="inlineStr">
         <is>
           <t>10/25 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="192" ht="24" customHeight="1">
-      <c r="A192" s="57" t="n">
+      <c r="A192" s="59" t="n">
         <v>46313</v>
       </c>
-      <c r="B192" s="34" t="inlineStr">
+      <c r="B192" s="39" t="inlineStr">
         <is>
           <t>Chorus @Setia Ecohill 2</t>
         </is>
       </c>
-      <c r="C192" s="34" t="inlineStr">
+      <c r="C192" s="39" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D192" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E192" s="35" t="inlineStr">
+      <c r="D192" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E192" s="40" t="inlineStr">
         <is>
           <t>77 / 99</t>
         </is>
       </c>
-      <c r="F192" s="58" t="n">
+      <c r="F192" s="60" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="G192" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H192" s="34" t="inlineStr">
+      <c r="G192" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H192" s="39" t="inlineStr">
         <is>
           <t>77/99 signed; No scope change detected</t>
         </is>
@@ -8083,7 +8083,7 @@
       <c r="F193" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="G193" s="42" t="inlineStr">
+      <c r="G193" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -8121,7 +8121,7 @@
       <c r="F194" s="60" t="n">
         <v>0.9710144927536232</v>
       </c>
-      <c r="G194" s="42" t="inlineStr">
+      <c r="G194" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -8159,7 +8159,7 @@
       <c r="F195" s="58" t="n">
         <v>0.9753086419753086</v>
       </c>
-      <c r="G195" s="42" t="inlineStr">
+      <c r="G195" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -8171,114 +8171,114 @@
       </c>
     </row>
     <row r="196" ht="24" customHeight="1">
-      <c r="A196" s="59" t="n">
+      <c r="A196" s="57" t="n">
         <v>46313</v>
       </c>
-      <c r="B196" s="39" t="inlineStr">
+      <c r="B196" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C196" s="39" t="inlineStr">
+      <c r="C196" s="34" t="inlineStr">
         <is>
           <t>20' x 60'</t>
         </is>
       </c>
-      <c r="D196" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E196" s="40" t="inlineStr">
+      <c r="D196" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E196" s="35" t="inlineStr">
         <is>
           <t>23 / 26</t>
         </is>
       </c>
-      <c r="F196" s="60" t="n">
+      <c r="F196" s="58" t="n">
         <v>0.8846153846153846</v>
       </c>
-      <c r="G196" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H196" s="39" t="inlineStr">
+      <c r="G196" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H196" s="34" t="inlineStr">
         <is>
           <t>23/26 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="197" ht="24" customHeight="1">
-      <c r="A197" s="57" t="n">
+      <c r="A197" s="59" t="n">
         <v>46313</v>
       </c>
-      <c r="B197" s="34" t="inlineStr">
+      <c r="B197" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C197" s="34" t="inlineStr">
+      <c r="C197" s="39" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D197" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E197" s="35" t="inlineStr">
+      <c r="D197" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E197" s="40" t="inlineStr">
         <is>
           <t>124 / 126</t>
         </is>
       </c>
-      <c r="F197" s="58" t="n">
+      <c r="F197" s="60" t="n">
         <v>0.9841269841269841</v>
       </c>
-      <c r="G197" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H197" s="34" t="inlineStr">
+      <c r="G197" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H197" s="39" t="inlineStr">
         <is>
           <t>124/126 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="198" ht="24" customHeight="1">
-      <c r="A198" s="59" t="n">
+      <c r="A198" s="57" t="n">
         <v>46313</v>
       </c>
-      <c r="B198" s="39" t="inlineStr">
+      <c r="B198" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C198" s="39" t="inlineStr">
+      <c r="C198" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D198" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E198" s="40" t="inlineStr">
+      <c r="D198" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E198" s="35" t="inlineStr">
         <is>
           <t>98 / 104</t>
         </is>
       </c>
-      <c r="F198" s="60" t="n">
+      <c r="F198" s="58" t="n">
         <v>0.9423076923076923</v>
       </c>
-      <c r="G198" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H198" s="39" t="inlineStr">
+      <c r="G198" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H198" s="34" t="inlineStr">
         <is>
           <t>98/104 signed; No scope change detected</t>
         </is>
@@ -8311,7 +8311,7 @@
       <c r="F199" s="60" t="n">
         <v>0.6590909090909091</v>
       </c>
-      <c r="G199" s="42" t="inlineStr">
+      <c r="G199" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -8349,7 +8349,7 @@
       <c r="F200" s="58" t="n">
         <v>0.7647058823529411</v>
       </c>
-      <c r="G200" s="42" t="inlineStr">
+      <c r="G200" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -8387,7 +8387,7 @@
       <c r="F201" s="60" t="n">
         <v>0.2352941176470588</v>
       </c>
-      <c r="G201" s="42" t="inlineStr">
+      <c r="G201" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -8399,38 +8399,38 @@
       </c>
     </row>
     <row r="202" ht="24" customHeight="1">
-      <c r="A202" s="59" t="n">
+      <c r="A202" s="57" t="n">
         <v>46313</v>
       </c>
-      <c r="B202" s="39" t="inlineStr">
+      <c r="B202" s="34" t="inlineStr">
         <is>
           <t>Sapphire Residence @Diamond City</t>
         </is>
       </c>
-      <c r="C202" s="39" t="inlineStr">
+      <c r="C202" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D202" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E202" s="40" t="inlineStr">
+      <c r="D202" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E202" s="35" t="inlineStr">
         <is>
           <t>45 / 136</t>
         </is>
       </c>
-      <c r="F202" s="60" t="n">
+      <c r="F202" s="58" t="n">
         <v>0.3308823529411765</v>
       </c>
-      <c r="G202" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H202" s="39" t="inlineStr">
+      <c r="G202" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H202" s="34" t="inlineStr">
         <is>
           <t>45/136 signed; No scope change detected</t>
         </is>
@@ -8463,7 +8463,7 @@
       <c r="F203" s="58" t="n">
         <v>0.03703703703703703</v>
       </c>
-      <c r="G203" s="42" t="inlineStr">
+      <c r="G203" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -8501,7 +8501,7 @@
       <c r="F204" s="60" t="n">
         <v>0.5227272727272727</v>
       </c>
-      <c r="G204" s="42" t="inlineStr">
+      <c r="G204" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -8539,7 +8539,7 @@
       <c r="F205" s="60" t="n">
         <v>0.2281879194630873</v>
       </c>
-      <c r="G205" s="42" t="inlineStr">
+      <c r="G205" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -8551,38 +8551,38 @@
       </c>
     </row>
     <row r="206" ht="24" customHeight="1">
-      <c r="A206" s="59" t="n">
+      <c r="A206" s="57" t="n">
         <v>46314</v>
       </c>
-      <c r="B206" s="39" t="inlineStr">
+      <c r="B206" s="34" t="inlineStr">
         <is>
           <t>Amani Gallery Homes</t>
         </is>
       </c>
-      <c r="C206" s="39" t="inlineStr">
+      <c r="C206" s="34" t="inlineStr">
         <is>
           <t>20' x 70' / 20' x 72'</t>
         </is>
       </c>
-      <c r="D206" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E206" s="40" t="inlineStr">
+      <c r="D206" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E206" s="35" t="inlineStr">
         <is>
           <t>74 / 81</t>
         </is>
       </c>
-      <c r="F206" s="60" t="n">
+      <c r="F206" s="58" t="n">
         <v>0.9135802469135802</v>
       </c>
-      <c r="G206" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H206" s="39" t="inlineStr">
+      <c r="G206" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H206" s="34" t="inlineStr">
         <is>
           <t>74/81 signed; No scope change detected</t>
         </is>
@@ -8615,7 +8615,7 @@
       <c r="F207" s="60" t="n">
         <v>0.6106194690265486</v>
       </c>
-      <c r="G207" s="42" t="inlineStr">
+      <c r="G207" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -8627,38 +8627,38 @@
       </c>
     </row>
     <row r="208" ht="24" customHeight="1">
-      <c r="A208" s="59" t="n">
+      <c r="A208" s="57" t="n">
         <v>46314</v>
       </c>
-      <c r="B208" s="39" t="inlineStr">
+      <c r="B208" s="34" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C208" s="39" t="inlineStr">
+      <c r="C208" s="34" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D208" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E208" s="40" t="inlineStr">
+      <c r="D208" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E208" s="35" t="inlineStr">
         <is>
           <t>21 / 48</t>
         </is>
       </c>
-      <c r="F208" s="60" t="n">
+      <c r="F208" s="58" t="n">
         <v>0.4375</v>
       </c>
-      <c r="G208" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H208" s="39" t="inlineStr">
+      <c r="G208" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H208" s="34" t="inlineStr">
         <is>
           <t>21/48 signed; No scope change detected</t>
         </is>
@@ -8691,7 +8691,7 @@
       <c r="F209" s="60" t="n">
         <v>0.6283185840707964</v>
       </c>
-      <c r="G209" s="42" t="inlineStr">
+      <c r="G209" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -8703,190 +8703,190 @@
       </c>
     </row>
     <row r="210" ht="24" customHeight="1">
-      <c r="A210" s="59" t="n">
+      <c r="A210" s="57" t="n">
         <v>46314</v>
       </c>
-      <c r="B210" s="39" t="inlineStr">
+      <c r="B210" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C210" s="39" t="inlineStr">
+      <c r="C210" s="34" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D210" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E210" s="40" t="inlineStr">
+      <c r="D210" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E210" s="35" t="inlineStr">
         <is>
           <t>46 / 46</t>
         </is>
       </c>
-      <c r="F210" s="60" t="n">
+      <c r="F210" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="G210" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H210" s="39" t="inlineStr">
+      <c r="G210" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H210" s="34" t="inlineStr">
         <is>
           <t>46/46 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="211" ht="24" customHeight="1">
-      <c r="A211" s="57" t="n">
+      <c r="A211" s="59" t="n">
         <v>46314</v>
       </c>
-      <c r="B211" s="34" t="inlineStr">
+      <c r="B211" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C211" s="34" t="inlineStr">
+      <c r="C211" s="39" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D211" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E211" s="35" t="inlineStr">
+      <c r="D211" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E211" s="40" t="inlineStr">
         <is>
           <t>56 / 56</t>
         </is>
       </c>
-      <c r="F211" s="58" t="n">
+      <c r="F211" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="G211" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H211" s="34" t="inlineStr">
+      <c r="G211" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H211" s="39" t="inlineStr">
         <is>
           <t>56/56 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="212" ht="24" customHeight="1">
-      <c r="A212" s="59" t="n">
+      <c r="A212" s="57" t="n">
         <v>46314</v>
       </c>
-      <c r="B212" s="39" t="inlineStr">
+      <c r="B212" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C212" s="39" t="inlineStr">
+      <c r="C212" s="34" t="inlineStr">
         <is>
           <t>20' x 75'</t>
         </is>
       </c>
-      <c r="D212" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E212" s="40" t="inlineStr">
+      <c r="D212" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E212" s="35" t="inlineStr">
         <is>
           <t>24 / 25</t>
         </is>
       </c>
-      <c r="F212" s="60" t="n">
+      <c r="F212" s="58" t="n">
         <v>0.96</v>
       </c>
-      <c r="G212" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H212" s="39" t="inlineStr">
+      <c r="G212" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H212" s="34" t="inlineStr">
         <is>
           <t>24/25 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="213" ht="24" customHeight="1">
-      <c r="A213" s="57" t="n">
+      <c r="A213" s="59" t="n">
         <v>46314</v>
       </c>
-      <c r="B213" s="34" t="inlineStr">
+      <c r="B213" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C213" s="34" t="inlineStr">
+      <c r="C213" s="39" t="inlineStr">
         <is>
           <t>20' x 80'</t>
         </is>
       </c>
-      <c r="D213" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E213" s="35" t="inlineStr">
+      <c r="D213" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E213" s="40" t="inlineStr">
         <is>
           <t>10 / 25</t>
         </is>
       </c>
-      <c r="F213" s="58" t="n">
+      <c r="F213" s="60" t="n">
         <v>0.4</v>
       </c>
-      <c r="G213" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H213" s="34" t="inlineStr">
+      <c r="G213" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H213" s="39" t="inlineStr">
         <is>
           <t>10/25 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="214" ht="24" customHeight="1">
-      <c r="A214" s="59" t="n">
+      <c r="A214" s="57" t="n">
         <v>46314</v>
       </c>
-      <c r="B214" s="39" t="inlineStr">
+      <c r="B214" s="34" t="inlineStr">
         <is>
           <t>Chorus @Setia Ecohill 2</t>
         </is>
       </c>
-      <c r="C214" s="39" t="inlineStr">
+      <c r="C214" s="34" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D214" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E214" s="40" t="inlineStr">
+      <c r="D214" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E214" s="35" t="inlineStr">
         <is>
           <t>77 / 99</t>
         </is>
       </c>
-      <c r="F214" s="60" t="n">
+      <c r="F214" s="58" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="G214" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H214" s="39" t="inlineStr">
+      <c r="G214" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H214" s="34" t="inlineStr">
         <is>
           <t>77/99 signed; No scope change detected</t>
         </is>
@@ -8919,7 +8919,7 @@
       <c r="F215" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="G215" s="42" t="inlineStr">
+      <c r="G215" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -8957,7 +8957,7 @@
       <c r="F216" s="58" t="n">
         <v>0.9710144927536232</v>
       </c>
-      <c r="G216" s="42" t="inlineStr">
+      <c r="G216" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -8995,7 +8995,7 @@
       <c r="F217" s="60" t="n">
         <v>0.9753086419753086</v>
       </c>
-      <c r="G217" s="42" t="inlineStr">
+      <c r="G217" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -9007,114 +9007,114 @@
       </c>
     </row>
     <row r="218" ht="24" customHeight="1">
-      <c r="A218" s="57" t="n">
+      <c r="A218" s="59" t="n">
         <v>46314</v>
       </c>
-      <c r="B218" s="34" t="inlineStr">
+      <c r="B218" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C218" s="34" t="inlineStr">
+      <c r="C218" s="39" t="inlineStr">
         <is>
           <t>20' x 60'</t>
         </is>
       </c>
-      <c r="D218" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E218" s="35" t="inlineStr">
+      <c r="D218" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E218" s="40" t="inlineStr">
         <is>
           <t>23 / 26</t>
         </is>
       </c>
-      <c r="F218" s="58" t="n">
+      <c r="F218" s="60" t="n">
         <v>0.8846153846153846</v>
       </c>
-      <c r="G218" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H218" s="34" t="inlineStr">
+      <c r="G218" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H218" s="39" t="inlineStr">
         <is>
           <t>23/26 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="219" ht="24" customHeight="1">
-      <c r="A219" s="59" t="n">
+      <c r="A219" s="57" t="n">
         <v>46314</v>
       </c>
-      <c r="B219" s="39" t="inlineStr">
+      <c r="B219" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C219" s="39" t="inlineStr">
+      <c r="C219" s="34" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D219" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E219" s="40" t="inlineStr">
+      <c r="D219" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E219" s="35" t="inlineStr">
         <is>
           <t>124 / 126</t>
         </is>
       </c>
-      <c r="F219" s="60" t="n">
+      <c r="F219" s="58" t="n">
         <v>0.9841269841269841</v>
       </c>
-      <c r="G219" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H219" s="39" t="inlineStr">
+      <c r="G219" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H219" s="34" t="inlineStr">
         <is>
           <t>124/126 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="220" ht="24" customHeight="1">
-      <c r="A220" s="57" t="n">
+      <c r="A220" s="59" t="n">
         <v>46314</v>
       </c>
-      <c r="B220" s="34" t="inlineStr">
+      <c r="B220" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C220" s="34" t="inlineStr">
+      <c r="C220" s="39" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D220" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E220" s="35" t="inlineStr">
+      <c r="D220" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E220" s="40" t="inlineStr">
         <is>
           <t>98 / 104</t>
         </is>
       </c>
-      <c r="F220" s="58" t="n">
+      <c r="F220" s="60" t="n">
         <v>0.9423076923076923</v>
       </c>
-      <c r="G220" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H220" s="34" t="inlineStr">
+      <c r="G220" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H220" s="39" t="inlineStr">
         <is>
           <t>98/104 signed; No scope change detected</t>
         </is>
@@ -9147,7 +9147,7 @@
       <c r="F221" s="58" t="n">
         <v>0.6590909090909091</v>
       </c>
-      <c r="G221" s="42" t="inlineStr">
+      <c r="G221" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -9185,7 +9185,7 @@
       <c r="F222" s="60" t="n">
         <v>0.7647058823529411</v>
       </c>
-      <c r="G222" s="42" t="inlineStr">
+      <c r="G222" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -9223,7 +9223,7 @@
       <c r="F223" s="58" t="n">
         <v>0.2352941176470588</v>
       </c>
-      <c r="G223" s="42" t="inlineStr">
+      <c r="G223" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -9235,38 +9235,38 @@
       </c>
     </row>
     <row r="224" ht="24" customHeight="1">
-      <c r="A224" s="57" t="n">
+      <c r="A224" s="59" t="n">
         <v>46314</v>
       </c>
-      <c r="B224" s="34" t="inlineStr">
+      <c r="B224" s="39" t="inlineStr">
         <is>
           <t>Sapphire Residence @Diamond City</t>
         </is>
       </c>
-      <c r="C224" s="34" t="inlineStr">
+      <c r="C224" s="39" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D224" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E224" s="35" t="inlineStr">
+      <c r="D224" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E224" s="40" t="inlineStr">
         <is>
           <t>45 / 136</t>
         </is>
       </c>
-      <c r="F224" s="58" t="n">
+      <c r="F224" s="60" t="n">
         <v>0.3308823529411765</v>
       </c>
-      <c r="G224" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H224" s="34" t="inlineStr">
+      <c r="G224" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H224" s="39" t="inlineStr">
         <is>
           <t>45/136 signed; No scope change detected</t>
         </is>
@@ -9299,7 +9299,7 @@
       <c r="F225" s="58" t="n">
         <v>0.03703703703703703</v>
       </c>
-      <c r="G225" s="42" t="inlineStr">
+      <c r="G225" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -9337,7 +9337,7 @@
       <c r="F226" s="60" t="n">
         <v>0.5227272727272727</v>
       </c>
-      <c r="G226" s="42" t="inlineStr">
+      <c r="G226" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -9375,7 +9375,7 @@
       <c r="F227" s="58" t="n">
         <v>0.2281879194630873</v>
       </c>
-      <c r="G227" s="42" t="inlineStr">
+      <c r="G227" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -9387,38 +9387,38 @@
       </c>
     </row>
     <row r="228" ht="24" customHeight="1">
-      <c r="A228" s="57" t="n">
+      <c r="A228" s="59" t="n">
         <v>46315</v>
       </c>
-      <c r="B228" s="34" t="inlineStr">
+      <c r="B228" s="39" t="inlineStr">
         <is>
           <t>Amani Gallery Homes</t>
         </is>
       </c>
-      <c r="C228" s="34" t="inlineStr">
+      <c r="C228" s="39" t="inlineStr">
         <is>
           <t>20' x 70' / 20' x 72'</t>
         </is>
       </c>
-      <c r="D228" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E228" s="35" t="inlineStr">
+      <c r="D228" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E228" s="40" t="inlineStr">
         <is>
           <t>74 / 81</t>
         </is>
       </c>
-      <c r="F228" s="58" t="n">
+      <c r="F228" s="60" t="n">
         <v>0.9135802469135802</v>
       </c>
-      <c r="G228" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H228" s="34" t="inlineStr">
+      <c r="G228" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H228" s="39" t="inlineStr">
         <is>
           <t>74/81 signed; No scope change detected</t>
         </is>
@@ -9451,7 +9451,7 @@
       <c r="F229" s="58" t="n">
         <v>0.6106194690265486</v>
       </c>
-      <c r="G229" s="42" t="inlineStr">
+      <c r="G229" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -9463,38 +9463,38 @@
       </c>
     </row>
     <row r="230" ht="24" customHeight="1">
-      <c r="A230" s="57" t="n">
+      <c r="A230" s="59" t="n">
         <v>46315</v>
       </c>
-      <c r="B230" s="34" t="inlineStr">
+      <c r="B230" s="39" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C230" s="34" t="inlineStr">
+      <c r="C230" s="39" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D230" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E230" s="35" t="inlineStr">
+      <c r="D230" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E230" s="40" t="inlineStr">
         <is>
           <t>21 / 48</t>
         </is>
       </c>
-      <c r="F230" s="58" t="n">
+      <c r="F230" s="60" t="n">
         <v>0.4375</v>
       </c>
-      <c r="G230" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H230" s="34" t="inlineStr">
+      <c r="G230" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H230" s="39" t="inlineStr">
         <is>
           <t>21/48 signed; No scope change detected</t>
         </is>
@@ -9527,7 +9527,7 @@
       <c r="F231" s="58" t="n">
         <v>0.6283185840707964</v>
       </c>
-      <c r="G231" s="42" t="inlineStr">
+      <c r="G231" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -9539,190 +9539,190 @@
       </c>
     </row>
     <row r="232" ht="24" customHeight="1">
-      <c r="A232" s="59" t="n">
+      <c r="A232" s="57" t="n">
         <v>46315</v>
       </c>
-      <c r="B232" s="39" t="inlineStr">
+      <c r="B232" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C232" s="39" t="inlineStr">
+      <c r="C232" s="34" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D232" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E232" s="40" t="inlineStr">
+      <c r="D232" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E232" s="35" t="inlineStr">
         <is>
           <t>46 / 46</t>
         </is>
       </c>
-      <c r="F232" s="60" t="n">
+      <c r="F232" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="G232" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H232" s="39" t="inlineStr">
+      <c r="G232" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H232" s="34" t="inlineStr">
         <is>
           <t>46/46 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="233" ht="24" customHeight="1">
-      <c r="A233" s="57" t="n">
+      <c r="A233" s="59" t="n">
         <v>46315</v>
       </c>
-      <c r="B233" s="34" t="inlineStr">
+      <c r="B233" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C233" s="34" t="inlineStr">
+      <c r="C233" s="39" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D233" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E233" s="35" t="inlineStr">
+      <c r="D233" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E233" s="40" t="inlineStr">
         <is>
           <t>56 / 56</t>
         </is>
       </c>
-      <c r="F233" s="58" t="n">
+      <c r="F233" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="G233" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H233" s="34" t="inlineStr">
+      <c r="G233" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H233" s="39" t="inlineStr">
         <is>
           <t>56/56 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="234" ht="24" customHeight="1">
-      <c r="A234" s="59" t="n">
+      <c r="A234" s="57" t="n">
         <v>46315</v>
       </c>
-      <c r="B234" s="39" t="inlineStr">
+      <c r="B234" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C234" s="39" t="inlineStr">
+      <c r="C234" s="34" t="inlineStr">
         <is>
           <t>20' x 75'</t>
         </is>
       </c>
-      <c r="D234" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E234" s="40" t="inlineStr">
+      <c r="D234" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E234" s="35" t="inlineStr">
         <is>
           <t>24 / 25</t>
         </is>
       </c>
-      <c r="F234" s="60" t="n">
+      <c r="F234" s="58" t="n">
         <v>0.96</v>
       </c>
-      <c r="G234" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H234" s="39" t="inlineStr">
+      <c r="G234" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H234" s="34" t="inlineStr">
         <is>
           <t>24/25 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="235" ht="24" customHeight="1">
-      <c r="A235" s="57" t="n">
+      <c r="A235" s="59" t="n">
         <v>46315</v>
       </c>
-      <c r="B235" s="34" t="inlineStr">
+      <c r="B235" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C235" s="34" t="inlineStr">
+      <c r="C235" s="39" t="inlineStr">
         <is>
           <t>20' x 80'</t>
         </is>
       </c>
-      <c r="D235" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E235" s="35" t="inlineStr">
+      <c r="D235" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E235" s="40" t="inlineStr">
         <is>
           <t>10 / 25</t>
         </is>
       </c>
-      <c r="F235" s="58" t="n">
+      <c r="F235" s="60" t="n">
         <v>0.4</v>
       </c>
-      <c r="G235" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H235" s="34" t="inlineStr">
+      <c r="G235" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H235" s="39" t="inlineStr">
         <is>
           <t>10/25 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="236" ht="24" customHeight="1">
-      <c r="A236" s="57" t="n">
+      <c r="A236" s="59" t="n">
         <v>46315</v>
       </c>
-      <c r="B236" s="34" t="inlineStr">
+      <c r="B236" s="39" t="inlineStr">
         <is>
           <t>Chorus @Setia Ecohill 2</t>
         </is>
       </c>
-      <c r="C236" s="34" t="inlineStr">
+      <c r="C236" s="39" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D236" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E236" s="35" t="inlineStr">
+      <c r="D236" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E236" s="40" t="inlineStr">
         <is>
           <t>77 / 99</t>
         </is>
       </c>
-      <c r="F236" s="58" t="n">
+      <c r="F236" s="60" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="G236" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H236" s="34" t="inlineStr">
+      <c r="G236" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H236" s="39" t="inlineStr">
         <is>
           <t>77/99 signed; No scope change detected</t>
         </is>
@@ -9755,7 +9755,7 @@
       <c r="F237" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="G237" s="42" t="inlineStr">
+      <c r="G237" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -9793,7 +9793,7 @@
       <c r="F238" s="60" t="n">
         <v>0.9710144927536232</v>
       </c>
-      <c r="G238" s="42" t="inlineStr">
+      <c r="G238" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -9831,7 +9831,7 @@
       <c r="F239" s="58" t="n">
         <v>0.9753086419753086</v>
       </c>
-      <c r="G239" s="42" t="inlineStr">
+      <c r="G239" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -9843,114 +9843,114 @@
       </c>
     </row>
     <row r="240" ht="24" customHeight="1">
-      <c r="A240" s="59" t="n">
+      <c r="A240" s="57" t="n">
         <v>46315</v>
       </c>
-      <c r="B240" s="39" t="inlineStr">
+      <c r="B240" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C240" s="39" t="inlineStr">
+      <c r="C240" s="34" t="inlineStr">
         <is>
           <t>20' x 60'</t>
         </is>
       </c>
-      <c r="D240" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E240" s="40" t="inlineStr">
+      <c r="D240" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E240" s="35" t="inlineStr">
         <is>
           <t>23 / 26</t>
         </is>
       </c>
-      <c r="F240" s="60" t="n">
+      <c r="F240" s="58" t="n">
         <v>0.8846153846153846</v>
       </c>
-      <c r="G240" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H240" s="39" t="inlineStr">
+      <c r="G240" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H240" s="34" t="inlineStr">
         <is>
           <t>23/26 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="241" ht="24" customHeight="1">
-      <c r="A241" s="57" t="n">
+      <c r="A241" s="59" t="n">
         <v>46315</v>
       </c>
-      <c r="B241" s="34" t="inlineStr">
+      <c r="B241" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C241" s="34" t="inlineStr">
+      <c r="C241" s="39" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D241" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E241" s="35" t="inlineStr">
+      <c r="D241" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E241" s="40" t="inlineStr">
         <is>
           <t>124 / 126</t>
         </is>
       </c>
-      <c r="F241" s="58" t="n">
+      <c r="F241" s="60" t="n">
         <v>0.9841269841269841</v>
       </c>
-      <c r="G241" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H241" s="34" t="inlineStr">
+      <c r="G241" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H241" s="39" t="inlineStr">
         <is>
           <t>124/126 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="242" ht="24" customHeight="1">
-      <c r="A242" s="59" t="n">
+      <c r="A242" s="57" t="n">
         <v>46315</v>
       </c>
-      <c r="B242" s="39" t="inlineStr">
+      <c r="B242" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C242" s="39" t="inlineStr">
+      <c r="C242" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D242" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E242" s="40" t="inlineStr">
+      <c r="D242" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E242" s="35" t="inlineStr">
         <is>
           <t>98 / 104</t>
         </is>
       </c>
-      <c r="F242" s="60" t="n">
+      <c r="F242" s="58" t="n">
         <v>0.9423076923076923</v>
       </c>
-      <c r="G242" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H242" s="39" t="inlineStr">
+      <c r="G242" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H242" s="34" t="inlineStr">
         <is>
           <t>98/104 signed; No scope change detected</t>
         </is>
@@ -9983,7 +9983,7 @@
       <c r="F243" s="60" t="n">
         <v>0.6590909090909091</v>
       </c>
-      <c r="G243" s="42" t="inlineStr">
+      <c r="G243" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -10021,7 +10021,7 @@
       <c r="F244" s="58" t="n">
         <v>0.7647058823529411</v>
       </c>
-      <c r="G244" s="42" t="inlineStr">
+      <c r="G244" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -10059,7 +10059,7 @@
       <c r="F245" s="60" t="n">
         <v>0.2352941176470588</v>
       </c>
-      <c r="G245" s="42" t="inlineStr">
+      <c r="G245" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -10071,38 +10071,38 @@
       </c>
     </row>
     <row r="246" ht="24" customHeight="1">
-      <c r="A246" s="59" t="n">
+      <c r="A246" s="57" t="n">
         <v>46315</v>
       </c>
-      <c r="B246" s="39" t="inlineStr">
+      <c r="B246" s="34" t="inlineStr">
         <is>
           <t>Sapphire Residence @Diamond City</t>
         </is>
       </c>
-      <c r="C246" s="39" t="inlineStr">
+      <c r="C246" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D246" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E246" s="40" t="inlineStr">
+      <c r="D246" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E246" s="35" t="inlineStr">
         <is>
           <t>45 / 136</t>
         </is>
       </c>
-      <c r="F246" s="60" t="n">
+      <c r="F246" s="58" t="n">
         <v>0.3308823529411765</v>
       </c>
-      <c r="G246" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H246" s="39" t="inlineStr">
+      <c r="G246" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H246" s="34" t="inlineStr">
         <is>
           <t>45/136 signed; No scope change detected</t>
         </is>
@@ -10135,7 +10135,7 @@
       <c r="F247" s="58" t="n">
         <v>0.03703703703703703</v>
       </c>
-      <c r="G247" s="42" t="inlineStr">
+      <c r="G247" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -10173,7 +10173,7 @@
       <c r="F248" s="60" t="n">
         <v>0.5227272727272727</v>
       </c>
-      <c r="G248" s="42" t="inlineStr">
+      <c r="G248" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -10211,7 +10211,7 @@
       <c r="F249" s="60" t="n">
         <v>0.2281879194630873</v>
       </c>
-      <c r="G249" s="42" t="inlineStr">
+      <c r="G249" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -10223,38 +10223,38 @@
       </c>
     </row>
     <row r="250" ht="24" customHeight="1">
-      <c r="A250" s="59" t="n">
+      <c r="A250" s="57" t="n">
         <v>46316</v>
       </c>
-      <c r="B250" s="39" t="inlineStr">
+      <c r="B250" s="34" t="inlineStr">
         <is>
           <t>Amani Gallery Homes</t>
         </is>
       </c>
-      <c r="C250" s="39" t="inlineStr">
+      <c r="C250" s="34" t="inlineStr">
         <is>
           <t>20' x 70' / 20' x 72'</t>
         </is>
       </c>
-      <c r="D250" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E250" s="40" t="inlineStr">
+      <c r="D250" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E250" s="35" t="inlineStr">
         <is>
           <t>74 / 81</t>
         </is>
       </c>
-      <c r="F250" s="60" t="n">
+      <c r="F250" s="58" t="n">
         <v>0.9135802469135802</v>
       </c>
-      <c r="G250" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H250" s="39" t="inlineStr">
+      <c r="G250" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H250" s="34" t="inlineStr">
         <is>
           <t>74/81 signed; No scope change detected</t>
         </is>
@@ -10287,7 +10287,7 @@
       <c r="F251" s="60" t="n">
         <v>0.6106194690265486</v>
       </c>
-      <c r="G251" s="42" t="inlineStr">
+      <c r="G251" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -10299,30 +10299,30 @@
       </c>
     </row>
     <row r="252" ht="24" customHeight="1">
-      <c r="A252" s="59" t="n">
+      <c r="A252" s="57" t="n">
         <v>46316</v>
       </c>
-      <c r="B252" s="39" t="inlineStr">
+      <c r="B252" s="34" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C252" s="39" t="inlineStr">
+      <c r="C252" s="34" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D252" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E252" s="40" t="inlineStr">
+      <c r="D252" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E252" s="35" t="inlineStr">
         <is>
           <t>22 / 48</t>
         </is>
       </c>
-      <c r="F252" s="60" t="n">
+      <c r="F252" s="58" t="n">
         <v>0.4583333333333333</v>
       </c>
       <c r="G252" s="43" t="inlineStr">
@@ -10330,7 +10330,7 @@
           <t>+1 signed · +2.1 pp</t>
         </is>
       </c>
-      <c r="H252" s="39" t="inlineStr">
+      <c r="H252" s="34" t="inlineStr">
         <is>
           <t>22/48 signed; No scope change detected</t>
         </is>
@@ -10363,7 +10363,7 @@
       <c r="F253" s="60" t="n">
         <v>0.6283185840707964</v>
       </c>
-      <c r="G253" s="42" t="inlineStr">
+      <c r="G253" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -10375,106 +10375,106 @@
       </c>
     </row>
     <row r="254" ht="24" customHeight="1">
-      <c r="A254" s="59" t="n">
+      <c r="A254" s="57" t="n">
         <v>46316</v>
       </c>
-      <c r="B254" s="39" t="inlineStr">
+      <c r="B254" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C254" s="39" t="inlineStr">
+      <c r="C254" s="34" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D254" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E254" s="40" t="inlineStr">
+      <c r="D254" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E254" s="35" t="inlineStr">
         <is>
           <t>46 / 46</t>
         </is>
       </c>
-      <c r="F254" s="60" t="n">
+      <c r="F254" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="G254" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H254" s="39" t="inlineStr">
+      <c r="G254" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H254" s="34" t="inlineStr">
         <is>
           <t>46/46 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="255" ht="24" customHeight="1">
-      <c r="A255" s="57" t="n">
+      <c r="A255" s="59" t="n">
         <v>46316</v>
       </c>
-      <c r="B255" s="34" t="inlineStr">
+      <c r="B255" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C255" s="34" t="inlineStr">
+      <c r="C255" s="39" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D255" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E255" s="35" t="inlineStr">
+      <c r="D255" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E255" s="40" t="inlineStr">
         <is>
           <t>56 / 56</t>
         </is>
       </c>
-      <c r="F255" s="58" t="n">
+      <c r="F255" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="G255" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H255" s="34" t="inlineStr">
+      <c r="G255" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H255" s="39" t="inlineStr">
         <is>
           <t>56/56 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="256" ht="24" customHeight="1">
-      <c r="A256" s="59" t="n">
+      <c r="A256" s="57" t="n">
         <v>46316</v>
       </c>
-      <c r="B256" s="39" t="inlineStr">
+      <c r="B256" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C256" s="39" t="inlineStr">
+      <c r="C256" s="34" t="inlineStr">
         <is>
           <t>20' x 75'</t>
         </is>
       </c>
-      <c r="D256" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E256" s="40" t="inlineStr">
+      <c r="D256" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E256" s="35" t="inlineStr">
         <is>
           <t>25 / 25</t>
         </is>
       </c>
-      <c r="F256" s="60" t="n">
+      <c r="F256" s="58" t="n">
         <v>1</v>
       </c>
       <c r="G256" s="43" t="inlineStr">
@@ -10482,83 +10482,83 @@
           <t>+1 signed · +4.0 pp</t>
         </is>
       </c>
-      <c r="H256" s="39" t="inlineStr">
+      <c r="H256" s="34" t="inlineStr">
         <is>
           <t>25/25 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="257" ht="24" customHeight="1">
-      <c r="A257" s="57" t="n">
+      <c r="A257" s="59" t="n">
         <v>46316</v>
       </c>
-      <c r="B257" s="34" t="inlineStr">
+      <c r="B257" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C257" s="34" t="inlineStr">
+      <c r="C257" s="39" t="inlineStr">
         <is>
           <t>20' x 80'</t>
         </is>
       </c>
-      <c r="D257" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E257" s="35" t="inlineStr">
+      <c r="D257" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E257" s="40" t="inlineStr">
         <is>
           <t>10 / 25</t>
         </is>
       </c>
-      <c r="F257" s="58" t="n">
+      <c r="F257" s="60" t="n">
         <v>0.4</v>
       </c>
-      <c r="G257" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H257" s="34" t="inlineStr">
+      <c r="G257" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H257" s="39" t="inlineStr">
         <is>
           <t>10/25 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="258" ht="24" customHeight="1">
-      <c r="A258" s="59" t="n">
+      <c r="A258" s="57" t="n">
         <v>46316</v>
       </c>
-      <c r="B258" s="39" t="inlineStr">
+      <c r="B258" s="34" t="inlineStr">
         <is>
           <t>Chorus @Setia Ecohill 2</t>
         </is>
       </c>
-      <c r="C258" s="39" t="inlineStr">
+      <c r="C258" s="34" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D258" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E258" s="40" t="inlineStr">
+      <c r="D258" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E258" s="35" t="inlineStr">
         <is>
           <t>77 / 99</t>
         </is>
       </c>
-      <c r="F258" s="60" t="n">
+      <c r="F258" s="58" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="G258" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H258" s="39" t="inlineStr">
+      <c r="G258" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H258" s="34" t="inlineStr">
         <is>
           <t>77/99 signed; No scope change detected</t>
         </is>
@@ -10591,7 +10591,7 @@
       <c r="F259" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="G259" s="42" t="inlineStr">
+      <c r="G259" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -10629,7 +10629,7 @@
       <c r="F260" s="58" t="n">
         <v>0.9710144927536232</v>
       </c>
-      <c r="G260" s="42" t="inlineStr">
+      <c r="G260" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -10667,7 +10667,7 @@
       <c r="F261" s="60" t="n">
         <v>0.9753086419753086</v>
       </c>
-      <c r="G261" s="42" t="inlineStr">
+      <c r="G261" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -10679,114 +10679,114 @@
       </c>
     </row>
     <row r="262" ht="24" customHeight="1">
-      <c r="A262" s="57" t="n">
+      <c r="A262" s="59" t="n">
         <v>46316</v>
       </c>
-      <c r="B262" s="34" t="inlineStr">
+      <c r="B262" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C262" s="34" t="inlineStr">
+      <c r="C262" s="39" t="inlineStr">
         <is>
           <t>20' x 60'</t>
         </is>
       </c>
-      <c r="D262" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E262" s="35" t="inlineStr">
+      <c r="D262" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E262" s="40" t="inlineStr">
         <is>
           <t>23 / 26</t>
         </is>
       </c>
-      <c r="F262" s="58" t="n">
+      <c r="F262" s="60" t="n">
         <v>0.8846153846153846</v>
       </c>
-      <c r="G262" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H262" s="34" t="inlineStr">
+      <c r="G262" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H262" s="39" t="inlineStr">
         <is>
           <t>23/26 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="263" ht="24" customHeight="1">
-      <c r="A263" s="59" t="n">
+      <c r="A263" s="57" t="n">
         <v>46316</v>
       </c>
-      <c r="B263" s="39" t="inlineStr">
+      <c r="B263" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C263" s="39" t="inlineStr">
+      <c r="C263" s="34" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D263" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E263" s="40" t="inlineStr">
+      <c r="D263" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E263" s="35" t="inlineStr">
         <is>
           <t>124 / 126</t>
         </is>
       </c>
-      <c r="F263" s="60" t="n">
+      <c r="F263" s="58" t="n">
         <v>0.9841269841269841</v>
       </c>
-      <c r="G263" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H263" s="39" t="inlineStr">
+      <c r="G263" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H263" s="34" t="inlineStr">
         <is>
           <t>124/126 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="264" ht="24" customHeight="1">
-      <c r="A264" s="57" t="n">
+      <c r="A264" s="59" t="n">
         <v>46316</v>
       </c>
-      <c r="B264" s="34" t="inlineStr">
+      <c r="B264" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C264" s="34" t="inlineStr">
+      <c r="C264" s="39" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D264" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E264" s="35" t="inlineStr">
+      <c r="D264" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E264" s="40" t="inlineStr">
         <is>
           <t>98 / 104</t>
         </is>
       </c>
-      <c r="F264" s="58" t="n">
+      <c r="F264" s="60" t="n">
         <v>0.9423076923076923</v>
       </c>
-      <c r="G264" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H264" s="34" t="inlineStr">
+      <c r="G264" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H264" s="39" t="inlineStr">
         <is>
           <t>98/104 signed; No scope change detected</t>
         </is>
@@ -10819,7 +10819,7 @@
       <c r="F265" s="58" t="n">
         <v>0.6590909090909091</v>
       </c>
-      <c r="G265" s="42" t="inlineStr">
+      <c r="G265" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -10857,7 +10857,7 @@
       <c r="F266" s="60" t="n">
         <v>0.7647058823529411</v>
       </c>
-      <c r="G266" s="42" t="inlineStr">
+      <c r="G266" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -10907,38 +10907,38 @@
       </c>
     </row>
     <row r="268" ht="24" customHeight="1">
-      <c r="A268" s="57" t="n">
+      <c r="A268" s="59" t="n">
         <v>46316</v>
       </c>
-      <c r="B268" s="34" t="inlineStr">
+      <c r="B268" s="39" t="inlineStr">
         <is>
           <t>Sapphire Residence @Diamond City</t>
         </is>
       </c>
-      <c r="C268" s="34" t="inlineStr">
+      <c r="C268" s="39" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D268" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E268" s="35" t="inlineStr">
+      <c r="D268" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E268" s="40" t="inlineStr">
         <is>
           <t>45 / 136</t>
         </is>
       </c>
-      <c r="F268" s="58" t="n">
+      <c r="F268" s="60" t="n">
         <v>0.3308823529411765</v>
       </c>
-      <c r="G268" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H268" s="34" t="inlineStr">
+      <c r="G268" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H268" s="39" t="inlineStr">
         <is>
           <t>45/136 signed; No scope change detected</t>
         </is>
@@ -10971,7 +10971,7 @@
       <c r="F269" s="58" t="n">
         <v>0.03703703703703703</v>
       </c>
-      <c r="G269" s="42" t="inlineStr">
+      <c r="G269" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -11047,7 +11047,7 @@
       <c r="F271" s="58" t="n">
         <v>0.2281879194630873</v>
       </c>
-      <c r="G271" s="42" t="inlineStr">
+      <c r="G271" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -11059,38 +11059,38 @@
       </c>
     </row>
     <row r="272" ht="24" customHeight="1">
-      <c r="A272" s="57" t="n">
+      <c r="A272" s="59" t="n">
         <v>46317</v>
       </c>
-      <c r="B272" s="34" t="inlineStr">
+      <c r="B272" s="39" t="inlineStr">
         <is>
           <t>Amani Gallery Homes</t>
         </is>
       </c>
-      <c r="C272" s="34" t="inlineStr">
+      <c r="C272" s="39" t="inlineStr">
         <is>
           <t>20' x 70' / 20' x 72'</t>
         </is>
       </c>
-      <c r="D272" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E272" s="35" t="inlineStr">
+      <c r="D272" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E272" s="40" t="inlineStr">
         <is>
           <t>74 / 81</t>
         </is>
       </c>
-      <c r="F272" s="58" t="n">
+      <c r="F272" s="60" t="n">
         <v>0.9135802469135802</v>
       </c>
-      <c r="G272" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H272" s="34" t="inlineStr">
+      <c r="G272" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H272" s="39" t="inlineStr">
         <is>
           <t>74/81 signed; No scope change detected</t>
         </is>
@@ -11123,7 +11123,7 @@
       <c r="F273" s="58" t="n">
         <v>0.6106194690265486</v>
       </c>
-      <c r="G273" s="42" t="inlineStr">
+      <c r="G273" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -11135,38 +11135,38 @@
       </c>
     </row>
     <row r="274" ht="24" customHeight="1">
-      <c r="A274" s="57" t="n">
+      <c r="A274" s="59" t="n">
         <v>46317</v>
       </c>
-      <c r="B274" s="34" t="inlineStr">
+      <c r="B274" s="39" t="inlineStr">
         <is>
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="C274" s="34" t="inlineStr">
+      <c r="C274" s="39" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D274" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E274" s="35" t="inlineStr">
+      <c r="D274" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E274" s="40" t="inlineStr">
         <is>
           <t>22 / 48</t>
         </is>
       </c>
-      <c r="F274" s="58" t="n">
+      <c r="F274" s="60" t="n">
         <v>0.4583333333333333</v>
       </c>
-      <c r="G274" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H274" s="34" t="inlineStr">
+      <c r="G274" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H274" s="39" t="inlineStr">
         <is>
           <t>22/48 signed; No scope change detected</t>
         </is>
@@ -11199,7 +11199,7 @@
       <c r="F275" s="58" t="n">
         <v>0.6283185840707964</v>
       </c>
-      <c r="G275" s="42" t="inlineStr">
+      <c r="G275" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -11211,190 +11211,190 @@
       </c>
     </row>
     <row r="276" ht="24" customHeight="1">
-      <c r="A276" s="59" t="n">
+      <c r="A276" s="57" t="n">
         <v>46317</v>
       </c>
-      <c r="B276" s="39" t="inlineStr">
+      <c r="B276" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C276" s="39" t="inlineStr">
+      <c r="C276" s="34" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D276" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E276" s="40" t="inlineStr">
+      <c r="D276" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E276" s="35" t="inlineStr">
         <is>
           <t>46 / 46</t>
         </is>
       </c>
-      <c r="F276" s="60" t="n">
+      <c r="F276" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="G276" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H276" s="39" t="inlineStr">
+      <c r="G276" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H276" s="34" t="inlineStr">
         <is>
           <t>46/46 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="277" ht="24" customHeight="1">
-      <c r="A277" s="57" t="n">
+      <c r="A277" s="59" t="n">
         <v>46317</v>
       </c>
-      <c r="B277" s="34" t="inlineStr">
+      <c r="B277" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C277" s="34" t="inlineStr">
+      <c r="C277" s="39" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D277" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E277" s="35" t="inlineStr">
+      <c r="D277" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E277" s="40" t="inlineStr">
         <is>
           <t>56 / 56</t>
         </is>
       </c>
-      <c r="F277" s="58" t="n">
+      <c r="F277" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="G277" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H277" s="34" t="inlineStr">
+      <c r="G277" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H277" s="39" t="inlineStr">
         <is>
           <t>56/56 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="278" ht="24" customHeight="1">
-      <c r="A278" s="59" t="n">
+      <c r="A278" s="57" t="n">
         <v>46317</v>
       </c>
-      <c r="B278" s="39" t="inlineStr">
+      <c r="B278" s="34" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C278" s="39" t="inlineStr">
+      <c r="C278" s="34" t="inlineStr">
         <is>
           <t>20' x 75'</t>
         </is>
       </c>
-      <c r="D278" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E278" s="40" t="inlineStr">
+      <c r="D278" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E278" s="35" t="inlineStr">
         <is>
           <t>25 / 25</t>
         </is>
       </c>
-      <c r="F278" s="60" t="n">
+      <c r="F278" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="G278" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H278" s="39" t="inlineStr">
+      <c r="G278" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H278" s="34" t="inlineStr">
         <is>
           <t>25/25 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="279" ht="24" customHeight="1">
-      <c r="A279" s="57" t="n">
+      <c r="A279" s="59" t="n">
         <v>46317</v>
       </c>
-      <c r="B279" s="34" t="inlineStr">
+      <c r="B279" s="39" t="inlineStr">
         <is>
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="C279" s="34" t="inlineStr">
+      <c r="C279" s="39" t="inlineStr">
         <is>
           <t>20' x 80'</t>
         </is>
       </c>
-      <c r="D279" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E279" s="35" t="inlineStr">
+      <c r="D279" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E279" s="40" t="inlineStr">
         <is>
           <t>10 / 25</t>
         </is>
       </c>
-      <c r="F279" s="58" t="n">
+      <c r="F279" s="60" t="n">
         <v>0.4</v>
       </c>
-      <c r="G279" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H279" s="34" t="inlineStr">
+      <c r="G279" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H279" s="39" t="inlineStr">
         <is>
           <t>10/25 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="280" ht="24" customHeight="1">
-      <c r="A280" s="57" t="n">
+      <c r="A280" s="59" t="n">
         <v>46317</v>
       </c>
-      <c r="B280" s="34" t="inlineStr">
+      <c r="B280" s="39" t="inlineStr">
         <is>
           <t>Chorus @Setia Ecohill 2</t>
         </is>
       </c>
-      <c r="C280" s="34" t="inlineStr">
+      <c r="C280" s="39" t="inlineStr">
         <is>
           <t>22' x 70'</t>
         </is>
       </c>
-      <c r="D280" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E280" s="35" t="inlineStr">
+      <c r="D280" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E280" s="40" t="inlineStr">
         <is>
           <t>77 / 99</t>
         </is>
       </c>
-      <c r="F280" s="58" t="n">
+      <c r="F280" s="60" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="G280" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H280" s="34" t="inlineStr">
+      <c r="G280" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H280" s="39" t="inlineStr">
         <is>
           <t>77/99 signed; No scope change detected</t>
         </is>
@@ -11427,7 +11427,7 @@
       <c r="F281" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="G281" s="42" t="inlineStr">
+      <c r="G281" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -11465,7 +11465,7 @@
       <c r="F282" s="60" t="n">
         <v>0.9710144927536232</v>
       </c>
-      <c r="G282" s="42" t="inlineStr">
+      <c r="G282" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -11503,7 +11503,7 @@
       <c r="F283" s="58" t="n">
         <v>0.9753086419753086</v>
       </c>
-      <c r="G283" s="42" t="inlineStr">
+      <c r="G283" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -11515,114 +11515,114 @@
       </c>
     </row>
     <row r="284" ht="24" customHeight="1">
-      <c r="A284" s="59" t="n">
+      <c r="A284" s="57" t="n">
         <v>46317</v>
       </c>
-      <c r="B284" s="39" t="inlineStr">
+      <c r="B284" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C284" s="39" t="inlineStr">
+      <c r="C284" s="34" t="inlineStr">
         <is>
           <t>20' x 60'</t>
         </is>
       </c>
-      <c r="D284" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E284" s="40" t="inlineStr">
+      <c r="D284" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E284" s="35" t="inlineStr">
         <is>
           <t>23 / 26</t>
         </is>
       </c>
-      <c r="F284" s="60" t="n">
+      <c r="F284" s="58" t="n">
         <v>0.8846153846153846</v>
       </c>
-      <c r="G284" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H284" s="39" t="inlineStr">
+      <c r="G284" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H284" s="34" t="inlineStr">
         <is>
           <t>23/26 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="285" ht="24" customHeight="1">
-      <c r="A285" s="57" t="n">
+      <c r="A285" s="59" t="n">
         <v>46317</v>
       </c>
-      <c r="B285" s="34" t="inlineStr">
+      <c r="B285" s="39" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C285" s="34" t="inlineStr">
+      <c r="C285" s="39" t="inlineStr">
         <is>
           <t>20' x 65'</t>
         </is>
       </c>
-      <c r="D285" s="35" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E285" s="35" t="inlineStr">
+      <c r="D285" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E285" s="40" t="inlineStr">
         <is>
           <t>124 / 126</t>
         </is>
       </c>
-      <c r="F285" s="58" t="n">
+      <c r="F285" s="60" t="n">
         <v>0.9841269841269841</v>
       </c>
-      <c r="G285" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H285" s="34" t="inlineStr">
+      <c r="G285" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H285" s="39" t="inlineStr">
         <is>
           <t>124/126 signed; No scope change detected</t>
         </is>
       </c>
     </row>
     <row r="286" ht="24" customHeight="1">
-      <c r="A286" s="59" t="n">
+      <c r="A286" s="57" t="n">
         <v>46317</v>
       </c>
-      <c r="B286" s="39" t="inlineStr">
+      <c r="B286" s="34" t="inlineStr">
         <is>
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="C286" s="39" t="inlineStr">
+      <c r="C286" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D286" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E286" s="40" t="inlineStr">
+      <c r="D286" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E286" s="35" t="inlineStr">
         <is>
           <t>98 / 104</t>
         </is>
       </c>
-      <c r="F286" s="60" t="n">
+      <c r="F286" s="58" t="n">
         <v>0.9423076923076923</v>
       </c>
-      <c r="G286" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H286" s="39" t="inlineStr">
+      <c r="G286" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H286" s="34" t="inlineStr">
         <is>
           <t>98/104 signed; No scope change detected</t>
         </is>
@@ -11655,7 +11655,7 @@
       <c r="F287" s="60" t="n">
         <v>0.6590909090909091</v>
       </c>
-      <c r="G287" s="42" t="inlineStr">
+      <c r="G287" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -11731,7 +11731,7 @@
       <c r="F289" s="60" t="n">
         <v>0.2450980392156863</v>
       </c>
-      <c r="G289" s="42" t="inlineStr">
+      <c r="G289" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -11743,38 +11743,38 @@
       </c>
     </row>
     <row r="290" ht="24" customHeight="1">
-      <c r="A290" s="59" t="n">
+      <c r="A290" s="57" t="n">
         <v>46317</v>
       </c>
-      <c r="B290" s="39" t="inlineStr">
+      <c r="B290" s="34" t="inlineStr">
         <is>
           <t>Sapphire Residence @Diamond City</t>
         </is>
       </c>
-      <c r="C290" s="39" t="inlineStr">
+      <c r="C290" s="34" t="inlineStr">
         <is>
           <t>20' x 70'</t>
         </is>
       </c>
-      <c r="D290" s="40" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="E290" s="40" t="inlineStr">
+      <c r="D290" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E290" s="35" t="inlineStr">
         <is>
           <t>45 / 136</t>
         </is>
       </c>
-      <c r="F290" s="60" t="n">
+      <c r="F290" s="58" t="n">
         <v>0.3308823529411765</v>
       </c>
-      <c r="G290" s="42" t="inlineStr">
-        <is>
-          <t>+0 signed · +0.0 pp</t>
-        </is>
-      </c>
-      <c r="H290" s="39" t="inlineStr">
+      <c r="G290" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H290" s="34" t="inlineStr">
         <is>
           <t>45/136 signed; No scope change detected</t>
         </is>
@@ -11807,7 +11807,7 @@
       <c r="F291" s="58" t="n">
         <v>0.03703703703703703</v>
       </c>
-      <c r="G291" s="42" t="inlineStr">
+      <c r="G291" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -11845,7 +11845,7 @@
       <c r="F292" s="60" t="n">
         <v>0.4653179190751445</v>
       </c>
-      <c r="G292" s="42" t="inlineStr">
+      <c r="G292" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -11883,7 +11883,7 @@
       <c r="F293" s="60" t="n">
         <v>0.2281879194630873</v>
       </c>
-      <c r="G293" s="42" t="inlineStr">
+      <c r="G293" s="37" t="inlineStr">
         <is>
           <t>+0 signed · +0.0 pp</t>
         </is>
@@ -11894,8 +11894,844 @@
         </is>
       </c>
     </row>
+    <row r="294" ht="24" customHeight="1">
+      <c r="A294" s="57" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B294" s="34" t="inlineStr">
+        <is>
+          <t>Amani Gallery Homes</t>
+        </is>
+      </c>
+      <c r="C294" s="34" t="inlineStr">
+        <is>
+          <t>20' x 70' / 20' x 72'</t>
+        </is>
+      </c>
+      <c r="D294" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E294" s="35" t="inlineStr">
+        <is>
+          <t>74 / 81</t>
+        </is>
+      </c>
+      <c r="F294" s="58" t="n">
+        <v>0.9135802469135802</v>
+      </c>
+      <c r="G294" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H294" s="34" t="inlineStr">
+        <is>
+          <t>74/81 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="24" customHeight="1">
+      <c r="A295" s="59" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B295" s="39" t="inlineStr">
+        <is>
+          <t>Balau Homes 2A</t>
+        </is>
+      </c>
+      <c r="C295" s="39" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D295" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E295" s="40" t="inlineStr">
+        <is>
+          <t>69 / 113</t>
+        </is>
+      </c>
+      <c r="F295" s="60" t="n">
+        <v>0.6106194690265486</v>
+      </c>
+      <c r="G295" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H295" s="39" t="inlineStr">
+        <is>
+          <t>69/113 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="24" customHeight="1">
+      <c r="A296" s="57" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B296" s="34" t="inlineStr">
+        <is>
+          <t>Balau Homes 2C</t>
+        </is>
+      </c>
+      <c r="C296" s="34" t="inlineStr">
+        <is>
+          <t>22' x 70'</t>
+        </is>
+      </c>
+      <c r="D296" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E296" s="35" t="inlineStr">
+        <is>
+          <t>22 / 48</t>
+        </is>
+      </c>
+      <c r="F296" s="58" t="n">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="G296" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H296" s="34" t="inlineStr">
+        <is>
+          <t>22/48 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="24" customHeight="1">
+      <c r="A297" s="59" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B297" s="39" t="inlineStr">
+        <is>
+          <t>Banyan @Setia Ecohill 2</t>
+        </is>
+      </c>
+      <c r="C297" s="39" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D297" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E297" s="40" t="inlineStr">
+        <is>
+          <t>71 / 113</t>
+        </is>
+      </c>
+      <c r="F297" s="60" t="n">
+        <v>0.6283185840707964</v>
+      </c>
+      <c r="G297" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H297" s="51" t="inlineStr">
+        <is>
+          <t>71/113 signed; Under revised scope since 08 Jun 2026 (99 → 113); review</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="24" customHeight="1">
+      <c r="A298" s="57" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B298" s="34" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C298" s="34" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D298" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E298" s="35" t="inlineStr">
+        <is>
+          <t>46 / 46</t>
+        </is>
+      </c>
+      <c r="F298" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G298" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H298" s="34" t="inlineStr">
+        <is>
+          <t>46/46 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="24" customHeight="1">
+      <c r="A299" s="59" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B299" s="39" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C299" s="39" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D299" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E299" s="40" t="inlineStr">
+        <is>
+          <t>56 / 56</t>
+        </is>
+      </c>
+      <c r="F299" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G299" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H299" s="39" t="inlineStr">
+        <is>
+          <t>56/56 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="24" customHeight="1">
+      <c r="A300" s="57" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B300" s="34" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C300" s="34" t="inlineStr">
+        <is>
+          <t>20' x 75'</t>
+        </is>
+      </c>
+      <c r="D300" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E300" s="35" t="inlineStr">
+        <is>
+          <t>25 / 25</t>
+        </is>
+      </c>
+      <c r="F300" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G300" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H300" s="34" t="inlineStr">
+        <is>
+          <t>25/25 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="24" customHeight="1">
+      <c r="A301" s="59" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B301" s="39" t="inlineStr">
+        <is>
+          <t>Birchpark @Eco Forest</t>
+        </is>
+      </c>
+      <c r="C301" s="39" t="inlineStr">
+        <is>
+          <t>20' x 80'</t>
+        </is>
+      </c>
+      <c r="D301" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E301" s="40" t="inlineStr">
+        <is>
+          <t>10 / 25</t>
+        </is>
+      </c>
+      <c r="F301" s="60" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G301" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H301" s="39" t="inlineStr">
+        <is>
+          <t>10/25 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="24" customHeight="1">
+      <c r="A302" s="57" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B302" s="34" t="inlineStr">
+        <is>
+          <t>Chorus @Setia Ecohill 2</t>
+        </is>
+      </c>
+      <c r="C302" s="34" t="inlineStr">
+        <is>
+          <t>22' x 70'</t>
+        </is>
+      </c>
+      <c r="D302" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E302" s="35" t="inlineStr">
+        <is>
+          <t>77 / 99</t>
+        </is>
+      </c>
+      <c r="F302" s="58" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="G302" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H302" s="34" t="inlineStr">
+        <is>
+          <t>77/99 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="24" customHeight="1">
+      <c r="A303" s="59" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B303" s="39" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C303" s="39" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D303" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E303" s="40" t="inlineStr">
+        <is>
+          <t>111 / 111</t>
+        </is>
+      </c>
+      <c r="F303" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G303" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H303" s="39" t="inlineStr">
+        <is>
+          <t>111/111 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="24" customHeight="1">
+      <c r="A304" s="57" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B304" s="34" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C304" s="34" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D304" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E304" s="35" t="inlineStr">
+        <is>
+          <t>134 / 138</t>
+        </is>
+      </c>
+      <c r="F304" s="58" t="n">
+        <v>0.9710144927536232</v>
+      </c>
+      <c r="G304" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H304" s="34" t="inlineStr">
+        <is>
+          <t>134/138 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="24" customHeight="1">
+      <c r="A305" s="59" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B305" s="39" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 1</t>
+        </is>
+      </c>
+      <c r="C305" s="39" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D305" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E305" s="40" t="inlineStr">
+        <is>
+          <t>79 / 81</t>
+        </is>
+      </c>
+      <c r="F305" s="60" t="n">
+        <v>0.9753086419753086</v>
+      </c>
+      <c r="G305" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H305" s="39" t="inlineStr">
+        <is>
+          <t>79/81 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="24" customHeight="1">
+      <c r="A306" s="59" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B306" s="39" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="C306" s="39" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D306" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E306" s="40" t="inlineStr">
+        <is>
+          <t>23 / 26</t>
+        </is>
+      </c>
+      <c r="F306" s="60" t="n">
+        <v>0.8846153846153846</v>
+      </c>
+      <c r="G306" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H306" s="39" t="inlineStr">
+        <is>
+          <t>23/26 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="24" customHeight="1">
+      <c r="A307" s="57" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B307" s="34" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="C307" s="34" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D307" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E307" s="35" t="inlineStr">
+        <is>
+          <t>124 / 126</t>
+        </is>
+      </c>
+      <c r="F307" s="58" t="n">
+        <v>0.9841269841269841</v>
+      </c>
+      <c r="G307" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H307" s="34" t="inlineStr">
+        <is>
+          <t>124/126 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="24" customHeight="1">
+      <c r="A308" s="59" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B308" s="39" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 2</t>
+        </is>
+      </c>
+      <c r="C308" s="39" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D308" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E308" s="40" t="inlineStr">
+        <is>
+          <t>98 / 104</t>
+        </is>
+      </c>
+      <c r="F308" s="60" t="n">
+        <v>0.9423076923076923</v>
+      </c>
+      <c r="G308" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H308" s="39" t="inlineStr">
+        <is>
+          <t>98/104 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="24" customHeight="1">
+      <c r="A309" s="57" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B309" s="34" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 3</t>
+        </is>
+      </c>
+      <c r="C309" s="34" t="inlineStr">
+        <is>
+          <t>20' x 60'</t>
+        </is>
+      </c>
+      <c r="D309" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E309" s="35" t="inlineStr">
+        <is>
+          <t>29 / 44</t>
+        </is>
+      </c>
+      <c r="F309" s="58" t="n">
+        <v>0.6590909090909091</v>
+      </c>
+      <c r="G309" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H309" s="34" t="inlineStr">
+        <is>
+          <t>29/44 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="24" customHeight="1">
+      <c r="A310" s="59" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B310" s="39" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 3</t>
+        </is>
+      </c>
+      <c r="C310" s="39" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D310" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E310" s="40" t="inlineStr">
+        <is>
+          <t>66 / 85</t>
+        </is>
+      </c>
+      <c r="F310" s="60" t="n">
+        <v>0.7764705882352941</v>
+      </c>
+      <c r="G310" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H310" s="39" t="inlineStr">
+        <is>
+          <t>66/85 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="24" customHeight="1">
+      <c r="A311" s="57" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B311" s="34" t="inlineStr">
+        <is>
+          <t>M Legasi Phase 3</t>
+        </is>
+      </c>
+      <c r="C311" s="34" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D311" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E311" s="35" t="inlineStr">
+        <is>
+          <t>25 / 102</t>
+        </is>
+      </c>
+      <c r="F311" s="58" t="n">
+        <v>0.2450980392156863</v>
+      </c>
+      <c r="G311" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H311" s="34" t="inlineStr">
+        <is>
+          <t>25/102 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="24" customHeight="1">
+      <c r="A312" s="59" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B312" s="39" t="inlineStr">
+        <is>
+          <t>Sapphire Residence @Diamond City</t>
+        </is>
+      </c>
+      <c r="C312" s="39" t="inlineStr">
+        <is>
+          <t>20' x 70'</t>
+        </is>
+      </c>
+      <c r="D312" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E312" s="40" t="inlineStr">
+        <is>
+          <t>45 / 136</t>
+        </is>
+      </c>
+      <c r="F312" s="60" t="n">
+        <v>0.3308823529411765</v>
+      </c>
+      <c r="G312" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H312" s="39" t="inlineStr">
+        <is>
+          <t>45/136 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="24" customHeight="1">
+      <c r="A313" s="57" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B313" s="34" t="inlineStr">
+        <is>
+          <t>Springvale Sempurna Heights</t>
+        </is>
+      </c>
+      <c r="C313" s="34" t="inlineStr">
+        <is>
+          <t>Group A · front-kitchen layout</t>
+        </is>
+      </c>
+      <c r="D313" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E313" s="35" t="inlineStr">
+        <is>
+          <t>1 / 27</t>
+        </is>
+      </c>
+      <c r="F313" s="58" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="G313" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H313" s="34" t="inlineStr">
+        <is>
+          <t>1/27 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="24" customHeight="1">
+      <c r="A314" s="59" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B314" s="39" t="inlineStr">
+        <is>
+          <t>Springvale Sempurna Heights</t>
+        </is>
+      </c>
+      <c r="C314" s="39" t="inlineStr">
+        <is>
+          <t>Group B · rear-kitchen layout</t>
+        </is>
+      </c>
+      <c r="D314" s="40" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E314" s="40" t="inlineStr">
+        <is>
+          <t>161 / 346</t>
+        </is>
+      </c>
+      <c r="F314" s="60" t="n">
+        <v>0.4653179190751445</v>
+      </c>
+      <c r="G314" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H314" s="51" t="inlineStr">
+        <is>
+          <t>161/346 signed; Under revised scope since 21 Oct 2026 (308 → 346); review</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="24" customHeight="1">
+      <c r="A315" s="57" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B315" s="34" t="inlineStr">
+        <is>
+          <t>Zinnia Residences</t>
+        </is>
+      </c>
+      <c r="C315" s="34" t="inlineStr">
+        <is>
+          <t>20' x 65'</t>
+        </is>
+      </c>
+      <c r="D315" s="35" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="E315" s="35" t="inlineStr">
+        <is>
+          <t>34 / 149</t>
+        </is>
+      </c>
+      <c r="F315" s="58" t="n">
+        <v>0.2281879194630873</v>
+      </c>
+      <c r="G315" s="37" t="inlineStr">
+        <is>
+          <t>+0 signed · +0.0 pp</t>
+        </is>
+      </c>
+      <c r="H315" s="34" t="inlineStr">
+        <is>
+          <t>34/149 signed; No scope change detected</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:A293"/>
+  <autoFilter ref="A3:A315"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
@@ -12998,112 +13834,112 @@
       </c>
       <c r="B15" s="28" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
+          <t>No change (18 Oct → 23 Oct; over 5 day(s))</t>
         </is>
       </c>
       <c r="C15" s="28" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
+          <t>No change (18 Oct → 23 Oct; over 5 day(s))</t>
         </is>
       </c>
       <c r="D15" s="28" t="inlineStr">
         <is>
-          <t>+1 signed (18 Oct → 22 Oct; over 4 day(s))</t>
+          <t>+1 signed (18 Oct → 23 Oct; over 5 day(s))</t>
         </is>
       </c>
       <c r="E15" s="28" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
+          <t>No change (18 Oct → 23 Oct; over 5 day(s))</t>
         </is>
       </c>
       <c r="F15" s="29" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
+          <t>No change (18 Oct → 23 Oct; over 5 day(s))</t>
         </is>
       </c>
       <c r="G15" s="30" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
+          <t>No change (18 Oct → 23 Oct; over 5 day(s))</t>
         </is>
       </c>
       <c r="H15" s="30" t="inlineStr">
         <is>
-          <t>+1 signed (18 Oct → 22 Oct; over 4 day(s))</t>
+          <t>+1 signed (18 Oct → 23 Oct; over 5 day(s))</t>
         </is>
       </c>
       <c r="I15" s="31" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
+          <t>No change (18 Oct → 23 Oct; over 5 day(s))</t>
         </is>
       </c>
       <c r="J15" s="28" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
+          <t>No change (18 Oct → 23 Oct; over 5 day(s))</t>
         </is>
       </c>
       <c r="K15" s="29" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
+          <t>No change (18 Oct → 23 Oct; over 5 day(s))</t>
         </is>
       </c>
       <c r="L15" s="30" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
+          <t>No change (18 Oct → 23 Oct; over 5 day(s))</t>
         </is>
       </c>
       <c r="M15" s="31" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
+          <t>No change (18 Oct → 23 Oct; over 5 day(s))</t>
         </is>
       </c>
       <c r="N15" s="29" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
+          <t>No change (18 Oct → 23 Oct; over 5 day(s))</t>
         </is>
       </c>
       <c r="O15" s="30" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
+          <t>No change (18 Oct → 23 Oct; over 5 day(s))</t>
         </is>
       </c>
       <c r="P15" s="31" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
+          <t>No change (18 Oct → 23 Oct; over 5 day(s))</t>
         </is>
       </c>
       <c r="Q15" s="29" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
+          <t>No change (18 Oct → 23 Oct; over 5 day(s))</t>
         </is>
       </c>
       <c r="R15" s="30" t="inlineStr">
         <is>
-          <t>+1 signed (18 Oct → 22 Oct; over 4 day(s))</t>
+          <t>+1 signed (18 Oct → 23 Oct; over 5 day(s))</t>
         </is>
       </c>
       <c r="S15" s="31" t="inlineStr">
         <is>
-          <t>+1 signed (18 Oct → 22 Oct; over 4 day(s))</t>
+          <t>+1 signed (18 Oct → 23 Oct; over 5 day(s))</t>
         </is>
       </c>
       <c r="T15" s="28" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
+          <t>No change (18 Oct → 23 Oct; over 5 day(s))</t>
         </is>
       </c>
       <c r="U15" s="29" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
+          <t>No change (18 Oct → 23 Oct; over 5 day(s))</t>
         </is>
       </c>
       <c r="V15" s="32" t="inlineStr">
         <is>
-          <t>⚠ Scope changed (308 → 346); 0 signed change; -5.7 pp (18 Oct → 22 Oct; over 4 day(s))</t>
+          <t>⚠ Scope changed (308 → 346); 0 signed change; -5.7 pp (18 Oct → 23 Oct; over 5 day(s))</t>
         </is>
       </c>
       <c r="W15" s="28" t="inlineStr">
         <is>
-          <t>No change (18 Oct → 22 Oct; over 4 day(s))</t>
+          <t>No change (18 Oct → 23 Oct; over 5 day(s))</t>
         </is>
       </c>
     </row>
@@ -13418,12 +14254,12 @@
           <t>Balau Homes 2A</t>
         </is>
       </c>
-      <c r="B4" s="34" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>Pemaju: Boustead</t>
         </is>
       </c>
-      <c r="C4" s="34" t="inlineStr">
+      <c r="C4" s="39" t="inlineStr">
         <is>
           <t>20094-4
 MUTIARA HILLS</t>
@@ -13441,12 +14277,12 @@
           <t>Balau Homes 2C</t>
         </is>
       </c>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
         <is>
           <t>Pemaju: Boustead</t>
         </is>
       </c>
-      <c r="C5" s="39" t="inlineStr">
+      <c r="C5" s="34" t="inlineStr">
         <is>
           <t>20094-5
 MUTIARA HILLS, SEMENYIH</t>
@@ -13464,12 +14300,12 @@
           <t>Springvale Sempurna Heights</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="39" t="inlineStr">
         <is>
           <t>springvale</t>
         </is>
       </c>
-      <c r="C6" s="34" t="inlineStr">
+      <c r="C6" s="39" t="inlineStr">
         <is>
           <t>19321-4
 SPRINGVALE SEMPURNA HEIGHT</t>
@@ -13487,12 +14323,12 @@
           <t>Zinnia Residences</t>
         </is>
       </c>
-      <c r="B7" s="39" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>Pemaju: crimson villa</t>
         </is>
       </c>
-      <c r="C7" s="39" t="inlineStr">
+      <c r="C7" s="34" t="inlineStr">
         <is>
           <t>19959-3
 TAMAN AKASIA</t>
@@ -13510,12 +14346,12 @@
           <t>M Legasi Phase 1</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="39" t="inlineStr">
         <is>
           <t>m legasi</t>
         </is>
       </c>
-      <c r="C8" s="34" t="inlineStr">
+      <c r="C8" s="39" t="inlineStr">
         <is>
           <t>30897-1
 M LEGASI</t>
@@ -13533,12 +14369,12 @@
           <t>M Legasi Phase 2</t>
         </is>
       </c>
-      <c r="B9" s="39" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>m legasi</t>
         </is>
       </c>
-      <c r="C9" s="39" t="inlineStr">
+      <c r="C9" s="34" t="inlineStr">
         <is>
           <t>30897-2
 M LEGASI</t>
@@ -13556,12 +14392,12 @@
           <t>M Legasi Phase 3</t>
         </is>
       </c>
-      <c r="B10" s="34" t="inlineStr">
+      <c r="B10" s="39" t="inlineStr">
         <is>
           <t>m legasi</t>
         </is>
       </c>
-      <c r="C10" s="34" t="inlineStr">
+      <c r="C10" s="39" t="inlineStr">
         <is>
           <t>30897-3
 M LEGASI</t>
@@ -13579,12 +14415,12 @@
           <t>Sapphire Residence @Diamond City</t>
         </is>
       </c>
-      <c r="B11" s="39" t="inlineStr">
+      <c r="B11" s="34" t="inlineStr">
         <is>
           <t>sapphire</t>
         </is>
       </c>
-      <c r="C11" s="39" t="inlineStr">
+      <c r="C11" s="34" t="inlineStr">
         <is>
           <t>13170-7
 SAPPHIRE RESIDENCE</t>
@@ -13602,12 +14438,12 @@
           <t>Birchpark @Eco Forest</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="39" t="inlineStr">
         <is>
           <t>birchpark</t>
         </is>
       </c>
-      <c r="C12" s="34" t="inlineStr">
+      <c r="C12" s="39" t="inlineStr">
         <is>
           <t>19150-17
 BIRCHPARK</t>
@@ -13625,12 +14461,12 @@
           <t>Chorus @Setia Ecohill 2</t>
         </is>
       </c>
-      <c r="B13" s="39" t="inlineStr">
+      <c r="B13" s="34" t="inlineStr">
         <is>
           <t>ecohill</t>
         </is>
       </c>
-      <c r="C13" s="39" t="inlineStr">
+      <c r="C13" s="34" t="inlineStr">
         <is>
           <t>14421-21
 SETIA ECOHILL 2</t>
@@ -13648,12 +14484,12 @@
           <t>Banyan @Setia Ecohill 2</t>
         </is>
       </c>
-      <c r="B14" s="34" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>ecohill</t>
         </is>
       </c>
-      <c r="C14" s="34" t="inlineStr">
+      <c r="C14" s="39" t="inlineStr">
         <is>
           <t>14421-22
 SETIA ECOHILL 2</t>
@@ -13671,12 +14507,12 @@
           <t>Amani Gallery Homes</t>
         </is>
       </c>
-      <c r="B15" s="39" t="inlineStr">
+      <c r="B15" s="34" t="inlineStr">
         <is>
           <t>amani</t>
         </is>
       </c>
-      <c r="C15" s="39" t="inlineStr">
+      <c r="C15" s="34" t="inlineStr">
         <is>
           <t>6868-20
 GALLERY HOMES - AMANI</t>
@@ -13694,17 +14530,17 @@
           <t>Majestic Flora</t>
         </is>
       </c>
-      <c r="B16" s="34" t="inlineStr">
+      <c r="B16" s="39" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C16" s="34" t="inlineStr">
+      <c r="C16" s="39" t="inlineStr">
         <is>
           <t>No TEDUH code recorded</t>
         </is>
       </c>
-      <c r="D16" s="34" t="inlineStr"/>
+      <c r="D16" s="39" t="inlineStr"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="65" t="inlineStr">
@@ -13712,17 +14548,17 @@
           <t>Astrea @Eco Radiance</t>
         </is>
       </c>
-      <c r="B17" s="39" t="inlineStr">
+      <c r="B17" s="34" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C17" s="39" t="inlineStr">
+      <c r="C17" s="34" t="inlineStr">
         <is>
           <t>No TEDUH code recorded</t>
         </is>
       </c>
-      <c r="D17" s="39" t="inlineStr"/>
+      <c r="D17" s="34" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
